--- a/外网端源码/其他楼交接班容量报表空模板.xlsx
+++ b/外网端源码/其他楼交接班容量报表空模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView windowHeight="22020"/>
   </bookViews>
   <sheets>
     <sheet name="本班组" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="387">
   <si>
     <t>班次</t>
   </si>
@@ -3193,28 +3193,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AF154"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="18.1818181818182" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.1851851851852" style="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.9363636363636" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.9351851851852" style="1" customWidth="1"/>
     <col min="7" max="8" width="9" style="1" customWidth="1"/>
-    <col min="9" max="9" width="16.4090909090909" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.4074074074074" style="1" customWidth="1"/>
     <col min="10" max="11" width="9" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.9363636363636" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.9351851851852" style="1" customWidth="1"/>
     <col min="13" max="13" width="9" style="1" customWidth="1"/>
-    <col min="14" max="14" width="8.75454545454545" style="1" customWidth="1"/>
-    <col min="15" max="15" width="38.1818181818182" style="1" customWidth="1"/>
+    <col min="14" max="14" width="8.75" style="1" customWidth="1"/>
+    <col min="15" max="15" width="38.1851851851852" style="1" customWidth="1"/>
     <col min="16" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="12.5909090909091" style="1" customWidth="1"/>
-    <col min="20" max="20" width="16.5090909090909" style="1" customWidth="1"/>
+    <col min="19" max="19" width="12.5925925925926" style="1" customWidth="1"/>
+    <col min="20" max="20" width="16.5092592592593" style="1" customWidth="1"/>
     <col min="21" max="21" width="9" style="1" customWidth="1"/>
-    <col min="22" max="22" width="14.1545454545455" style="1" customWidth="1"/>
+    <col min="22" max="22" width="14.1574074074074" style="1" customWidth="1"/>
     <col min="23" max="24" width="9" style="1" customWidth="1"/>
-    <col min="25" max="25" width="10.2545454545455" style="1" customWidth="1"/>
+    <col min="25" max="25" width="10.25" style="1" customWidth="1"/>
     <col min="26" max="27" width="9" style="1" customWidth="1"/>
-    <col min="28" max="28" width="17.4181818181818" style="1" customWidth="1"/>
+    <col min="28" max="28" width="17.4166666666667" style="1" customWidth="1"/>
     <col min="31" max="31" width="11" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4369,8 +4369,12 @@
       <c r="C27" s="30"/>
       <c r="D27" s="30"/>
       <c r="E27" s="30"/>
-      <c r="F27" s="69"/>
-      <c r="G27" s="90"/>
+      <c r="F27" s="69" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27" s="90" t="s">
+        <v>15</v>
+      </c>
       <c r="H27" s="30"/>
       <c r="I27" s="30"/>
       <c r="J27" s="30"/>
@@ -4382,8 +4386,12 @@
       <c r="P27" s="30"/>
       <c r="Q27" s="30"/>
       <c r="R27" s="30"/>
-      <c r="S27" s="69"/>
-      <c r="T27" s="69"/>
+      <c r="S27" s="69" t="s">
+        <v>15</v>
+      </c>
+      <c r="T27" s="69" t="s">
+        <v>15</v>
+      </c>
       <c r="U27" s="30"/>
       <c r="V27" s="30"/>
       <c r="W27" s="30"/>
@@ -4803,15 +4811,11 @@
       <c r="K35" s="100" t="s">
         <v>75</v>
       </c>
-      <c r="L35" s="102" t="s">
-        <v>15</v>
-      </c>
+      <c r="L35" s="102"/>
       <c r="M35" s="100" t="s">
         <v>76</v>
       </c>
-      <c r="N35" s="103" t="s">
-        <v>15</v>
-      </c>
+      <c r="N35" s="103"/>
       <c r="O35" s="53"/>
       <c r="P35" s="101" t="s">
         <v>74</v>
@@ -4834,15 +4838,11 @@
       <c r="X35" s="100" t="s">
         <v>75</v>
       </c>
-      <c r="Y35" s="102" t="s">
-        <v>15</v>
-      </c>
+      <c r="Y35" s="102"/>
       <c r="Z35" s="100" t="s">
         <v>76</v>
       </c>
-      <c r="AA35" s="102" t="s">
-        <v>15</v>
-      </c>
+      <c r="AA35" s="102"/>
       <c r="AB35" s="85" t="s">
         <v>108</v>
       </c>
@@ -4882,15 +4882,11 @@
       <c r="K36" s="100" t="s">
         <v>82</v>
       </c>
-      <c r="L36" s="102" t="s">
-        <v>15</v>
-      </c>
+      <c r="L36" s="102"/>
       <c r="M36" s="100" t="s">
         <v>83</v>
       </c>
-      <c r="N36" s="103" t="s">
-        <v>15</v>
-      </c>
+      <c r="N36" s="103"/>
       <c r="O36" s="53"/>
       <c r="P36" s="100" t="s">
         <v>78</v>
@@ -4919,15 +4915,11 @@
       <c r="X36" s="100" t="s">
         <v>82</v>
       </c>
-      <c r="Y36" s="102" t="s">
-        <v>15</v>
-      </c>
+      <c r="Y36" s="102"/>
       <c r="Z36" s="100" t="s">
         <v>83</v>
       </c>
-      <c r="AA36" s="102" t="s">
-        <v>15</v>
-      </c>
+      <c r="AA36" s="102"/>
       <c r="AB36" s="85" t="s">
         <v>104</v>
       </c>
@@ -5006,15 +4998,13 @@
       <c r="K38" s="100" t="s">
         <v>88</v>
       </c>
-      <c r="L38" s="102" t="s">
-        <v>15</v>
-      </c>
+      <c r="L38" s="102"/>
       <c r="M38" s="100" t="s">
         <v>89</v>
       </c>
-      <c r="N38" s="103" t="e">
+      <c r="N38" s="103">
         <f>N35-N36</f>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
       <c r="O38" s="53"/>
       <c r="P38" s="100" t="s">
@@ -5042,15 +5032,13 @@
       <c r="X38" s="100" t="s">
         <v>88</v>
       </c>
-      <c r="Y38" s="102" t="s">
-        <v>15</v>
-      </c>
+      <c r="Y38" s="102"/>
       <c r="Z38" s="100" t="s">
         <v>89</v>
       </c>
-      <c r="AA38" s="102" t="e">
+      <c r="AA38" s="102">
         <f>AA35-AA36</f>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
       <c r="AB38" s="85" t="s">
         <v>111</v>
@@ -5089,15 +5077,11 @@
       <c r="K39" s="100" t="s">
         <v>94</v>
       </c>
-      <c r="L39" s="102" t="s">
-        <v>15</v>
-      </c>
+      <c r="L39" s="102"/>
       <c r="M39" s="100" t="s">
         <v>95</v>
       </c>
-      <c r="N39" s="103" t="s">
-        <v>15</v>
-      </c>
+      <c r="N39" s="103"/>
       <c r="O39" s="53"/>
       <c r="P39" s="100" t="s">
         <v>91</v>
@@ -5124,15 +5108,11 @@
       <c r="X39" s="100" t="s">
         <v>94</v>
       </c>
-      <c r="Y39" s="102" t="s">
-        <v>15</v>
-      </c>
+      <c r="Y39" s="102"/>
       <c r="Z39" s="100" t="s">
         <v>95</v>
       </c>
-      <c r="AA39" s="102" t="s">
-        <v>15</v>
-      </c>
+      <c r="AA39" s="102"/>
       <c r="AB39" s="85" t="s">
         <v>113</v>
       </c>
@@ -5168,16 +5148,14 @@
       <c r="K40" s="100" t="s">
         <v>100</v>
       </c>
-      <c r="L40" s="102" t="e">
+      <c r="L40" s="102">
         <f>L39-L35</f>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
       <c r="M40" s="100" t="s">
         <v>101</v>
       </c>
-      <c r="N40" s="103" t="s">
-        <v>15</v>
-      </c>
+      <c r="N40" s="103"/>
       <c r="O40" s="53"/>
       <c r="P40" s="100" t="s">
         <v>97</v>
@@ -5202,16 +5180,14 @@
       <c r="X40" s="100" t="s">
         <v>100</v>
       </c>
-      <c r="Y40" s="102" t="e">
+      <c r="Y40" s="102">
         <f>Y39-Y35</f>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
       <c r="Z40" s="100" t="s">
         <v>101</v>
       </c>
-      <c r="AA40" s="102" t="s">
-        <v>15</v>
-      </c>
+      <c r="AA40" s="102"/>
       <c r="AB40" s="85" t="s">
         <v>115</v>
       </c>
@@ -5245,9 +5221,9 @@
       <c r="M41" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="N41" s="103" t="e">
+      <c r="N41" s="103">
         <f>N39-N40</f>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
       <c r="O41" s="53"/>
       <c r="P41" s="100" t="s">
@@ -5271,9 +5247,9 @@
       <c r="Z41" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="AA41" s="102" t="e">
+      <c r="AA41" s="102">
         <f>AA39-AA40</f>
-        <v>#VALUE!</v>
+        <v>0</v>
       </c>
       <c r="AB41" s="77"/>
       <c r="AC41" s="78"/>
@@ -6260,7 +6236,7 @@
       <c r="AD64" s="62"/>
       <c r="AE64" s="62"/>
     </row>
-    <row r="65" s="10" customFormat="1" ht="17.5" spans="1:32">
+    <row r="65" s="10" customFormat="1" ht="17.4" spans="1:32">
       <c r="A65" s="134"/>
       <c r="B65" s="135"/>
       <c r="C65" s="135"/>
@@ -11108,7 +11084,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{aa9873e0-b3ee-4b61-97ca-60ebe8490711}</x14:id>
+          <x14:id>{9cef6fb5-27f1-4826-aac0-8e3d1dc2f749}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11120,7 +11096,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fa04ff7d-e7b6-4f75-97c5-547db3ff1338}</x14:id>
+          <x14:id>{4748dc5e-ab71-497f-901b-e841925c3da6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11132,7 +11108,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a0f9c72e-9472-48c2-a3b7-d75ed7029e82}</x14:id>
+          <x14:id>{6224e9ef-6e7d-48e7-a133-6d9933ed6287}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11144,7 +11120,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{eaf28077-1c70-4a53-bbd7-f15b73e61db5}</x14:id>
+          <x14:id>{c11da46a-095e-4c19-8eea-0501128cd594}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11156,7 +11132,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{41712525-6ece-4b08-b8d3-9d3845852a53}</x14:id>
+          <x14:id>{8299d70b-3815-4dce-8787-aa74f6c2ca71}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11168,7 +11144,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0d2887e9-c6ae-429c-9c5c-9dbd0477bbac}</x14:id>
+          <x14:id>{963be238-8997-4f91-93cf-6686e907bf45}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11180,7 +11156,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f46084ea-dcb6-42bd-a0d6-64db48718725}</x14:id>
+          <x14:id>{34684714-ca78-4eff-b320-d38fb65bb9b6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11192,7 +11168,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{94f15dda-0d0a-4769-a449-4211f61782dc}</x14:id>
+          <x14:id>{0f3621a1-7c6d-4141-89a1-7f66f018293a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11206,7 +11182,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{43429ba3-2e5b-495d-9b71-3f834820802f}</x14:id>
+          <x14:id>{3bc95d45-3788-49dc-b2db-8179e40a70e0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11218,7 +11194,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{86537bc5-7ab9-409d-80ae-cbe4ffdbd11a}</x14:id>
+          <x14:id>{ba84b88b-506a-433d-a211-e4c365904d3d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11230,7 +11206,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d0cffe50-db3a-4e75-a937-5859344b2671}</x14:id>
+          <x14:id>{2f135eb2-2a00-4004-8e85-159ba7d7e12f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11242,7 +11218,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{42992f20-2b34-4e69-8927-84297e40cb77}</x14:id>
+          <x14:id>{612085f3-832c-4cd0-9422-dae4500dc354}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11254,7 +11230,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b5c2efb9-731c-47e2-8e75-2defb76932bb}</x14:id>
+          <x14:id>{a9afe528-9b7e-41f8-98f9-88158239f7f6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11266,7 +11242,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{734a5852-7e0d-4a73-9323-84faf665d4c1}</x14:id>
+          <x14:id>{53876d5a-d1af-420a-b420-aefa3619624b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11278,7 +11254,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a6eae9c2-528e-4110-b8cc-3e34c44ed3dd}</x14:id>
+          <x14:id>{c06f820b-e096-4ced-86e7-2f94210a2f79}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11290,7 +11266,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fc5b1b1f-c9a2-42da-b741-794cc7353231}</x14:id>
+          <x14:id>{48fe7be3-68ff-4b0c-918a-c5938af1cdad}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11304,7 +11280,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f449423e-64ed-4e39-8f50-125d20a5238b}</x14:id>
+          <x14:id>{5b106d49-67b3-43aa-93b2-3a28145e2de1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11316,7 +11292,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4751ce9e-4308-4980-9db3-cf29778b08aa}</x14:id>
+          <x14:id>{0614568c-1e55-4a23-9ee2-0de8a93734ac}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11328,7 +11304,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ae1bf825-491f-4627-b0b8-3911cc05c530}</x14:id>
+          <x14:id>{e72b1b8e-e3c3-48ee-b05b-ceee92ce05a7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11340,7 +11316,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d08897cd-e5a6-448c-8e36-068e0a304cec}</x14:id>
+          <x14:id>{d115ee5a-8963-4580-9341-11463f725d6c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11352,7 +11328,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d22b0a3a-d663-4bd0-b96c-2fde01c1819e}</x14:id>
+          <x14:id>{4a622ec7-f7aa-45a9-b0c1-acefc3c06c03}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11364,7 +11340,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2d570da1-cff8-4be1-8e3b-f00775dd52f1}</x14:id>
+          <x14:id>{306ca3aa-22a0-41ff-955d-7130dd57e8e1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11376,7 +11352,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2a0d7a0d-9b48-41dd-b9fe-cb47c71e7694}</x14:id>
+          <x14:id>{c2970437-2cc7-497d-ac43-7bebe7b82b2d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11388,7 +11364,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ab7611f9-cda9-4f81-9fdb-20d3244ceed6}</x14:id>
+          <x14:id>{4ed147d4-610a-4f1d-a769-2309cff55f22}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11402,7 +11378,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5bd36edc-4e10-443f-92bb-f4a3f3a6c6b8}</x14:id>
+          <x14:id>{60c59afc-2cd7-4d46-9f73-744a4ef17ff4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11414,7 +11390,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{19560f1c-6f5a-4b5d-9846-e73233382076}</x14:id>
+          <x14:id>{d0abca75-0cf2-40d6-910f-0cbb87227013}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11426,7 +11402,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{373cf832-e1ea-463a-874e-ca0321128e27}</x14:id>
+          <x14:id>{181e961e-8f5d-4ab7-ad56-54e719f96825}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11438,7 +11414,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f15d0d51-e8d1-4437-8d11-a82576c10b52}</x14:id>
+          <x14:id>{a7c294a2-1c03-4844-9f65-8b7f131f303e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11450,7 +11426,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9fc9a93b-9763-48d5-a058-9dffaf6af6da}</x14:id>
+          <x14:id>{2adef030-77e5-429c-b894-2882e568aed1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11462,7 +11438,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{94610865-7687-4172-98c0-0d604837e404}</x14:id>
+          <x14:id>{7dafd5bf-630f-4a33-8a8a-9d504337fc15}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11474,7 +11450,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{89e566b9-e737-46db-a25a-32faf312eb2d}</x14:id>
+          <x14:id>{0a8a44aa-c4a2-47f3-ab26-ee16b93f1e10}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11486,7 +11462,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cbd8b374-90b1-419d-b36f-78d9b0f07af3}</x14:id>
+          <x14:id>{2e6b45c9-e011-4a9f-a2e8-fb84ce54133b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11500,7 +11476,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{15d2dd97-a8fc-42fc-acd9-328a716cbb5c}</x14:id>
+          <x14:id>{4afe896b-e7ce-44a5-987f-492c59eadfec}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11512,7 +11488,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8604edfc-4b0d-4e02-9cd3-8e7f21a63ba7}</x14:id>
+          <x14:id>{66d1b68e-8087-4d8f-b17f-28f222060240}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11524,7 +11500,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fe7d76b5-851c-4d38-bf9e-0adc3087bc04}</x14:id>
+          <x14:id>{8a6e9796-5fa4-43ff-9c68-64db2fa6af08}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11536,7 +11512,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8227ced0-21d7-4e63-90ea-8c85c2172c7b}</x14:id>
+          <x14:id>{b407f0b2-6645-4a89-8eda-aeedc7b262fa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11548,7 +11524,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ec50bacd-7c22-41ff-be62-be0492650e28}</x14:id>
+          <x14:id>{29783639-204c-4c90-b2a4-2951d42a018d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11560,7 +11536,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7e15e1d2-ffbf-4cb5-9377-b01c38800de0}</x14:id>
+          <x14:id>{83ff2b7f-278c-4a26-aebd-8ed55708472d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11572,7 +11548,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{562e4acf-06a4-4331-b013-a9381983f7e9}</x14:id>
+          <x14:id>{98d37873-1a8a-47f6-9620-63c622a2d8e0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11584,7 +11560,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2679b03f-c717-496d-a47f-0fb1759ea747}</x14:id>
+          <x14:id>{2737ba3e-30a5-450e-a729-c6eeb1bb4deb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11598,7 +11574,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e051c854-f424-4f97-9cf3-74130ff478e7}</x14:id>
+          <x14:id>{39957837-dc92-4844-8862-d0d654fde516}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11610,7 +11586,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{54065d80-b0a0-4403-aad4-108e903cfdc2}</x14:id>
+          <x14:id>{d706b15d-9c8b-4632-aad8-bb1270a40394}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11622,7 +11598,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5b160a84-3c34-42fb-9640-4740da21719e}</x14:id>
+          <x14:id>{d91a71dd-6cc5-4e3a-98a8-559db153cfbd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11634,7 +11610,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5fe7beb5-de89-4c39-9413-1498f2504de9}</x14:id>
+          <x14:id>{05e22c6d-ff0c-4724-9ec0-2a98056f6889}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11646,7 +11622,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{67617d65-03a4-4695-9dbb-cd4698732438}</x14:id>
+          <x14:id>{55502b49-2158-4c14-80aa-dc2a415060a3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11658,7 +11634,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0b1fe81b-1579-475e-815d-14f279a89b42}</x14:id>
+          <x14:id>{f0534be1-8ca2-4565-b7cf-e676063c6c41}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11670,7 +11646,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4343cd32-0abe-4f91-b033-0ef48f5d0940}</x14:id>
+          <x14:id>{8cbd8797-5ae9-469c-b5d4-6db67c49a218}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11682,7 +11658,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2dbf4edc-b4f6-4128-8b18-62befc47b7e3}</x14:id>
+          <x14:id>{d1ee0243-0344-44dc-bbc7-356cd3c072be}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11696,7 +11672,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{10e25e35-da01-4b05-81ff-8af5b5c142b6}</x14:id>
+          <x14:id>{3c224dca-cdde-4199-9b57-cf9da0ee3c53}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11708,7 +11684,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{330d7808-ae3e-4709-b691-9ecf468a5cd8}</x14:id>
+          <x14:id>{52a4e15b-b0e8-4a3c-9e85-d218bde4952d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11720,7 +11696,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9987c89f-18a5-4525-9bb9-45ff1fd0b546}</x14:id>
+          <x14:id>{ec86acf4-6d80-4172-8a90-89723cc2ecd6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11734,7 +11710,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f45eb2a8-00d7-4eac-8b1b-60cfc1e42934}</x14:id>
+          <x14:id>{09d8f95d-5f92-4d93-8a52-a8966217a1da}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11746,7 +11722,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d0e9c784-2d31-46e3-bc70-7e459884b3a5}</x14:id>
+          <x14:id>{929f8a0f-662f-4cf9-b5b2-152cab2f4e5a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11758,7 +11734,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b082b7ee-05fd-401c-9117-c15e7e7bc1d0}</x14:id>
+          <x14:id>{0921a4e4-59b7-4835-adc7-a58dc310cad9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11772,7 +11748,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c46fbf50-fa2e-48d8-8d06-c6539c6c779c}</x14:id>
+          <x14:id>{af198761-db08-44e6-92c3-b2b92d820131}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11784,7 +11760,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{431e3765-6590-4641-9f0e-d68b8f2c6c5d}</x14:id>
+          <x14:id>{e4ad1068-1a14-4a0d-8cf8-b17cabad6b10}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11798,7 +11774,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1dcdcc10-7594-4f7d-812a-1f3c2ba38a84}</x14:id>
+          <x14:id>{625c0588-1710-41b0-b297-c98b2ec10a74}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11810,7 +11786,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3dcd5b39-fdbf-49b8-9353-676c7c3590bc}</x14:id>
+          <x14:id>{1758f066-671d-436c-b79e-e828e1eaef53}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11822,7 +11798,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7ddd7afa-ed6c-4d19-91ee-06002d8d1b7f}</x14:id>
+          <x14:id>{cd7330a4-0328-4cd3-a64f-48d644dff5ae}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11836,7 +11812,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5c07b905-349e-4a2d-b430-bb4d7ac85860}</x14:id>
+          <x14:id>{24e8eb18-0e9e-41b7-9a35-9b0a2a0bd3b5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11848,7 +11824,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c8c9d9aa-ee45-4d66-b2b2-58be51c524a9}</x14:id>
+          <x14:id>{1fb07516-5df2-48bc-925d-3f2fa5797fbc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11860,7 +11836,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7839ab6e-e2be-4312-b833-66fa3e4c9f07}</x14:id>
+          <x14:id>{b8624788-0e02-435c-a70a-96005bc51d22}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11874,7 +11850,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8930ba59-95c8-4f05-a69f-7820ffb64b68}</x14:id>
+          <x14:id>{b29e05f9-3b58-4710-9733-65a0c9a038bc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11886,7 +11862,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d44c1848-0434-4f9d-83ed-7650589ec994}</x14:id>
+          <x14:id>{4c826239-9a18-4821-8ce0-26addc416766}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11898,7 +11874,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0d16a92c-f53f-4955-b841-4b77a61cb245}</x14:id>
+          <x14:id>{089ce2d6-c751-450f-adbe-6bd2b40ecd11}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11912,7 +11888,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7a8cd518-76f9-49f5-b401-2ad8cefde44a}</x14:id>
+          <x14:id>{3b6326b3-874e-447c-9b74-dc405f97688d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11924,7 +11900,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b4209c88-a67e-4b4f-baa7-1fe8c88a0cb6}</x14:id>
+          <x14:id>{01996dae-c08a-452d-94d1-9095c864d6f1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11936,7 +11912,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{38c467a4-5e44-46d3-9559-9692b46dd54d}</x14:id>
+          <x14:id>{b0cd3a9f-a3cb-41be-b39e-a2fee70bd5f9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11950,7 +11926,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{339a5f35-080a-46b4-bccb-8bacd2c5240f}</x14:id>
+          <x14:id>{e61278ad-ac2f-4058-9265-18ca71240777}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11962,7 +11938,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{887ef401-7856-47a5-b305-ffef768b610a}</x14:id>
+          <x14:id>{edc6b379-3afc-4adb-98af-56203730cc40}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11974,7 +11950,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e9325cde-0ad4-43da-a2a1-136c2ec9199a}</x14:id>
+          <x14:id>{f43080a0-21db-42cd-bad1-92cc8d9da3cb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11988,7 +11964,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{07175fa1-5f89-4f51-af95-401a62e1a2d4}</x14:id>
+          <x14:id>{4ad2eddf-7e78-48fa-9b79-e57750129d45}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12000,7 +11976,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{aa2b516a-a20e-42b8-9c7f-2ed77ae61ebf}</x14:id>
+          <x14:id>{61774866-067d-4641-99a7-03f4a3c836fa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12012,7 +11988,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b8701955-4a16-479c-8f2b-d2a224e0c0d2}</x14:id>
+          <x14:id>{f66b1efe-71b5-478f-9617-67c089bd041b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12024,7 +12000,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a6c7ff95-17a3-4537-a599-2235dd00a17e}</x14:id>
+          <x14:id>{b3ca3735-2451-40ab-ad43-e67808a08a61}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12036,7 +12012,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e437c70f-aa76-441c-b4f0-bb738a1f6d16}</x14:id>
+          <x14:id>{10dde7d7-913b-441d-b712-928856656a7a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12048,7 +12024,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6468aa35-73cf-4e3c-9996-d0d30839b2f7}</x14:id>
+          <x14:id>{799ad7eb-c616-4d0c-b78c-2087ec1c901f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12060,7 +12036,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{432bc915-a0d9-4dcb-b56f-647b516ba97d}</x14:id>
+          <x14:id>{ec8393cb-f716-46db-93ae-ae5d79932c01}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12072,7 +12048,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c0736e08-d1c7-4b9f-b863-65c2c7377b59}</x14:id>
+          <x14:id>{6c02597c-56bf-43a3-befd-9cbe4c8ba60c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12086,7 +12062,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1f470d2a-f298-4423-bba1-4584d6e6041a}</x14:id>
+          <x14:id>{e94ba282-08c6-4f99-86b4-cff46cfe9b30}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12098,7 +12074,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9cd0397c-243b-4064-a845-d5ab2251b5c4}</x14:id>
+          <x14:id>{74ed936e-314e-4168-83b3-42184c20b15e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12112,7 +12088,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{81c785b6-d9ec-4e50-be20-ba1828fc7b08}</x14:id>
+          <x14:id>{cdf9b126-4d85-47ea-9032-ee6b83cdd204}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12126,7 +12102,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{79b6edcb-0864-4815-9590-d441def8ecc5}</x14:id>
+          <x14:id>{f51deae4-f6df-4fd4-8123-50a519e6883c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12140,7 +12116,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e2f097f9-60e2-41d7-ac88-952fb112f193}</x14:id>
+          <x14:id>{6d7bae07-c4ba-48e6-9112-5aac0bf34b22}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12154,7 +12130,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{848b3bdf-5226-43db-a571-6d78ab541026}</x14:id>
+          <x14:id>{b1c4895f-0f53-449e-9235-34aac4a42a5a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12168,7 +12144,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d1af849e-6cfa-447b-9666-60a64f0a3c6c}</x14:id>
+          <x14:id>{f32ca648-3d6d-4d5b-839d-274d93f45ea4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12180,7 +12156,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{88a765bc-ceaf-43f2-b1ac-254c53d9f821}</x14:id>
+          <x14:id>{3791ffab-4c9c-4e5d-8390-045514d80363}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12192,7 +12168,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b880d4d5-90b6-4164-a1f9-f61498a22dec}</x14:id>
+          <x14:id>{f0477eda-77f4-4297-a0fc-f51fefafe97f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12206,7 +12182,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{252c3fb7-85dd-4309-bf47-a7f7445ad33d}</x14:id>
+          <x14:id>{315b8d7c-0d53-4f07-95d7-f3eb1b825a8a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12218,7 +12194,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ed2ae304-a059-424f-ab1a-6738c2dfbbb5}</x14:id>
+          <x14:id>{59f17f4b-2050-4e12-baac-fc8fa7f45ea8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12230,7 +12206,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{06a91191-f7ee-41af-96c4-9098481de723}</x14:id>
+          <x14:id>{8c079828-6198-4193-9941-fc6fd9db51ac}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12244,7 +12220,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5240afe0-1a4e-4a62-858b-4dbc14260841}</x14:id>
+          <x14:id>{ef394594-a9af-4929-a0f1-f5c2abdf1626}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12256,7 +12232,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a8207689-0771-43bd-be70-2bac451b8a04}</x14:id>
+          <x14:id>{3b25587a-911c-4ecc-a210-8e2867ad2bef}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12268,7 +12244,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5afbf0a8-23db-4b75-a432-eb4c5cab17c7}</x14:id>
+          <x14:id>{14af986a-11fb-406a-9a8d-943d5bcf05ff}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12282,7 +12258,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d79459d6-884c-4a3c-b21c-ed4b9dd6430d}</x14:id>
+          <x14:id>{f72e9826-8cf6-4fb4-9fc7-47bcc31ff473}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12294,7 +12270,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{107698f6-313c-498b-9b8b-f8c72165b31a}</x14:id>
+          <x14:id>{6b53e93f-df6a-4324-8005-a8f22bea234d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12306,7 +12282,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d27e7a6f-c0c3-4597-93ba-dbd4e1ace09f}</x14:id>
+          <x14:id>{45672cff-bc6f-4ada-889a-783f7fc2b7db}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12320,7 +12296,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{911f05c4-d337-4296-bd10-b2f788f7ea15}</x14:id>
+          <x14:id>{6fff42f4-b967-4d21-997a-a8816a03661c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12332,7 +12308,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d1190f8f-cfbf-402f-a563-1b754a8cfb86}</x14:id>
+          <x14:id>{aca51d9e-f35a-4599-b9ac-7f12bb460be1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12346,7 +12322,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4016564b-8f81-4817-ad31-55622271c777}</x14:id>
+          <x14:id>{85c7428a-4028-4de5-b545-24770e243804}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12358,7 +12334,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{63bc00e1-4b5e-48dd-ada2-f422fffef014}</x14:id>
+          <x14:id>{b1d5c3ee-8fe5-417e-82f1-417264ecc2ea}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12370,7 +12346,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{25b4dfa6-6b69-48fb-bb36-8124ba70281d}</x14:id>
+          <x14:id>{5e91cb54-a545-471c-a311-ebac3b5f9596}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12384,7 +12360,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{999bc4c6-b06a-4795-9a2b-728ae4c09929}</x14:id>
+          <x14:id>{b3d38032-3b5d-493c-bb80-7ca9dc91dfd2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12396,7 +12372,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{91514c5a-78c8-4267-9557-de51ffedf53a}</x14:id>
+          <x14:id>{19636f01-0376-48d3-8afd-b4cfb5bc9b63}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12408,7 +12384,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d6549bd5-9cc0-4af3-8f63-7a52b5128f2a}</x14:id>
+          <x14:id>{edd90c9f-c9a0-4b8a-bc56-588a523e18e4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12422,7 +12398,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0d2a7e42-b164-4b3b-8686-4c60f3a77136}</x14:id>
+          <x14:id>{eefdf929-5606-4234-b533-44bd4d7e2221}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12434,7 +12410,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{31cced82-ae48-4a8c-a610-5d558d082985}</x14:id>
+          <x14:id>{53c4dfd0-9f25-4c07-9c95-f2a997b44be6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12468,7 +12444,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{aa9873e0-b3ee-4b61-97ca-60ebe8490711}">
+          <x14:cfRule type="dataBar" id="{9cef6fb5-27f1-4826-aac0-8e3d1dc2f749}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12479,7 +12455,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{fa04ff7d-e7b6-4f75-97c5-547db3ff1338}">
+          <x14:cfRule type="dataBar" id="{4748dc5e-ab71-497f-901b-e841925c3da6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12490,14 +12466,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a0f9c72e-9472-48c2-a3b7-d75ed7029e82}">
+          <x14:cfRule type="dataBar" id="{6224e9ef-6e7d-48e7-a133-6d9933ed6287}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{eaf28077-1c70-4a53-bbd7-f15b73e61db5}">
+          <x14:cfRule type="dataBar" id="{c11da46a-095e-4c19-8eea-0501128cd594}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12508,7 +12484,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{41712525-6ece-4b08-b8d3-9d3845852a53}">
+          <x14:cfRule type="dataBar" id="{8299d70b-3815-4dce-8787-aa74f6c2ca71}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12519,7 +12495,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0d2887e9-c6ae-429c-9c5c-9dbd0477bbac}">
+          <x14:cfRule type="dataBar" id="{963be238-8997-4f91-93cf-6686e907bf45}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12530,7 +12506,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f46084ea-dcb6-42bd-a0d6-64db48718725}">
+          <x14:cfRule type="dataBar" id="{34684714-ca78-4eff-b320-d38fb65bb9b6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12539,7 +12515,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{94f15dda-0d0a-4769-a449-4211f61782dc}">
+          <x14:cfRule type="dataBar" id="{0f3621a1-7c6d-4141-89a1-7f66f018293a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12551,7 +12527,7 @@
           <xm:sqref>AD56</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{43429ba3-2e5b-495d-9b71-3f834820802f}">
+          <x14:cfRule type="dataBar" id="{3bc95d45-3788-49dc-b2db-8179e40a70e0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12562,7 +12538,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{86537bc5-7ab9-409d-80ae-cbe4ffdbd11a}">
+          <x14:cfRule type="dataBar" id="{ba84b88b-506a-433d-a211-e4c365904d3d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12573,14 +12549,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d0cffe50-db3a-4e75-a937-5859344b2671}">
+          <x14:cfRule type="dataBar" id="{2f135eb2-2a00-4004-8e85-159ba7d7e12f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{42992f20-2b34-4e69-8927-84297e40cb77}">
+          <x14:cfRule type="dataBar" id="{612085f3-832c-4cd0-9422-dae4500dc354}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12591,7 +12567,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b5c2efb9-731c-47e2-8e75-2defb76932bb}">
+          <x14:cfRule type="dataBar" id="{a9afe528-9b7e-41f8-98f9-88158239f7f6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12602,7 +12578,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{734a5852-7e0d-4a73-9323-84faf665d4c1}">
+          <x14:cfRule type="dataBar" id="{53876d5a-d1af-420a-b420-aefa3619624b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12613,7 +12589,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a6eae9c2-528e-4110-b8cc-3e34c44ed3dd}">
+          <x14:cfRule type="dataBar" id="{c06f820b-e096-4ced-86e7-2f94210a2f79}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12622,7 +12598,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{fc5b1b1f-c9a2-42da-b741-794cc7353231}">
+          <x14:cfRule type="dataBar" id="{48fe7be3-68ff-4b0c-918a-c5938af1cdad}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12634,7 +12610,7 @@
           <xm:sqref>K60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f449423e-64ed-4e39-8f50-125d20a5238b}">
+          <x14:cfRule type="dataBar" id="{5b106d49-67b3-43aa-93b2-3a28145e2de1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12645,7 +12621,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4751ce9e-4308-4980-9db3-cf29778b08aa}">
+          <x14:cfRule type="dataBar" id="{0614568c-1e55-4a23-9ee2-0de8a93734ac}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12656,14 +12632,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ae1bf825-491f-4627-b0b8-3911cc05c530}">
+          <x14:cfRule type="dataBar" id="{e72b1b8e-e3c3-48ee-b05b-ceee92ce05a7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d08897cd-e5a6-448c-8e36-068e0a304cec}">
+          <x14:cfRule type="dataBar" id="{d115ee5a-8963-4580-9341-11463f725d6c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12674,7 +12650,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d22b0a3a-d663-4bd0-b96c-2fde01c1819e}">
+          <x14:cfRule type="dataBar" id="{4a622ec7-f7aa-45a9-b0c1-acefc3c06c03}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12685,7 +12661,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2d570da1-cff8-4be1-8e3b-f00775dd52f1}">
+          <x14:cfRule type="dataBar" id="{306ca3aa-22a0-41ff-955d-7130dd57e8e1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12696,7 +12672,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2a0d7a0d-9b48-41dd-b9fe-cb47c71e7694}">
+          <x14:cfRule type="dataBar" id="{c2970437-2cc7-497d-ac43-7bebe7b82b2d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12705,7 +12681,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ab7611f9-cda9-4f81-9fdb-20d3244ceed6}">
+          <x14:cfRule type="dataBar" id="{4ed147d4-610a-4f1d-a769-2309cff55f22}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12717,7 +12693,7 @@
           <xm:sqref>AD60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5bd36edc-4e10-443f-92bb-f4a3f3a6c6b8}">
+          <x14:cfRule type="dataBar" id="{60c59afc-2cd7-4d46-9f73-744a4ef17ff4}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12728,7 +12704,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{19560f1c-6f5a-4b5d-9846-e73233382076}">
+          <x14:cfRule type="dataBar" id="{d0abca75-0cf2-40d6-910f-0cbb87227013}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12739,14 +12715,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{373cf832-e1ea-463a-874e-ca0321128e27}">
+          <x14:cfRule type="dataBar" id="{181e961e-8f5d-4ab7-ad56-54e719f96825}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f15d0d51-e8d1-4437-8d11-a82576c10b52}">
+          <x14:cfRule type="dataBar" id="{a7c294a2-1c03-4844-9f65-8b7f131f303e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12757,7 +12733,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9fc9a93b-9763-48d5-a058-9dffaf6af6da}">
+          <x14:cfRule type="dataBar" id="{2adef030-77e5-429c-b894-2882e568aed1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12768,7 +12744,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{94610865-7687-4172-98c0-0d604837e404}">
+          <x14:cfRule type="dataBar" id="{7dafd5bf-630f-4a33-8a8a-9d504337fc15}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12779,7 +12755,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{89e566b9-e737-46db-a25a-32faf312eb2d}">
+          <x14:cfRule type="dataBar" id="{0a8a44aa-c4a2-47f3-ab26-ee16b93f1e10}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12788,7 +12764,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{cbd8b374-90b1-419d-b36f-78d9b0f07af3}">
+          <x14:cfRule type="dataBar" id="{2e6b45c9-e011-4a9f-a2e8-fb84ce54133b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12800,7 +12776,7 @@
           <xm:sqref>K61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{15d2dd97-a8fc-42fc-acd9-328a716cbb5c}">
+          <x14:cfRule type="dataBar" id="{4afe896b-e7ce-44a5-987f-492c59eadfec}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12811,7 +12787,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8604edfc-4b0d-4e02-9cd3-8e7f21a63ba7}">
+          <x14:cfRule type="dataBar" id="{66d1b68e-8087-4d8f-b17f-28f222060240}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12822,14 +12798,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{fe7d76b5-851c-4d38-bf9e-0adc3087bc04}">
+          <x14:cfRule type="dataBar" id="{8a6e9796-5fa4-43ff-9c68-64db2fa6af08}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8227ced0-21d7-4e63-90ea-8c85c2172c7b}">
+          <x14:cfRule type="dataBar" id="{b407f0b2-6645-4a89-8eda-aeedc7b262fa}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12840,7 +12816,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ec50bacd-7c22-41ff-be62-be0492650e28}">
+          <x14:cfRule type="dataBar" id="{29783639-204c-4c90-b2a4-2951d42a018d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12851,7 +12827,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7e15e1d2-ffbf-4cb5-9377-b01c38800de0}">
+          <x14:cfRule type="dataBar" id="{83ff2b7f-278c-4a26-aebd-8ed55708472d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12862,7 +12838,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{562e4acf-06a4-4331-b013-a9381983f7e9}">
+          <x14:cfRule type="dataBar" id="{98d37873-1a8a-47f6-9620-63c622a2d8e0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12871,7 +12847,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2679b03f-c717-496d-a47f-0fb1759ea747}">
+          <x14:cfRule type="dataBar" id="{2737ba3e-30a5-450e-a729-c6eeb1bb4deb}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12883,7 +12859,7 @@
           <xm:sqref>K62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e051c854-f424-4f97-9cf3-74130ff478e7}">
+          <x14:cfRule type="dataBar" id="{39957837-dc92-4844-8862-d0d654fde516}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12894,7 +12870,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{54065d80-b0a0-4403-aad4-108e903cfdc2}">
+          <x14:cfRule type="dataBar" id="{d706b15d-9c8b-4632-aad8-bb1270a40394}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12905,14 +12881,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5b160a84-3c34-42fb-9640-4740da21719e}">
+          <x14:cfRule type="dataBar" id="{d91a71dd-6cc5-4e3a-98a8-559db153cfbd}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5fe7beb5-de89-4c39-9413-1498f2504de9}">
+          <x14:cfRule type="dataBar" id="{05e22c6d-ff0c-4724-9ec0-2a98056f6889}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12923,7 +12899,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{67617d65-03a4-4695-9dbb-cd4698732438}">
+          <x14:cfRule type="dataBar" id="{55502b49-2158-4c14-80aa-dc2a415060a3}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12934,7 +12910,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0b1fe81b-1579-475e-815d-14f279a89b42}">
+          <x14:cfRule type="dataBar" id="{f0534be1-8ca2-4565-b7cf-e676063c6c41}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12945,7 +12921,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4343cd32-0abe-4f91-b033-0ef48f5d0940}">
+          <x14:cfRule type="dataBar" id="{8cbd8797-5ae9-469c-b5d4-6db67c49a218}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12954,7 +12930,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2dbf4edc-b4f6-4128-8b18-62befc47b7e3}">
+          <x14:cfRule type="dataBar" id="{d1ee0243-0344-44dc-bbc7-356cd3c072be}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12966,7 +12942,7 @@
           <xm:sqref>K63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{10e25e35-da01-4b05-81ff-8af5b5c142b6}">
+          <x14:cfRule type="dataBar" id="{3c224dca-cdde-4199-9b57-cf9da0ee3c53}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12975,7 +12951,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{330d7808-ae3e-4709-b691-9ecf468a5cd8}">
+          <x14:cfRule type="dataBar" id="{52a4e15b-b0e8-4a3c-9e85-d218bde4952d}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12984,7 +12960,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9987c89f-18a5-4525-9bb9-45ff1fd0b546}">
+          <x14:cfRule type="dataBar" id="{ec86acf4-6d80-4172-8a90-89723cc2ecd6}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -12997,7 +12973,7 @@
           <xm:sqref>AB67</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f45eb2a8-00d7-4eac-8b1b-60cfc1e42934}">
+          <x14:cfRule type="dataBar" id="{09d8f95d-5f92-4d93-8a52-a8966217a1da}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13006,7 +12982,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d0e9c784-2d31-46e3-bc70-7e459884b3a5}">
+          <x14:cfRule type="dataBar" id="{929f8a0f-662f-4cf9-b5b2-152cab2f4e5a}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13015,7 +12991,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b082b7ee-05fd-401c-9117-c15e7e7bc1d0}">
+          <x14:cfRule type="dataBar" id="{0921a4e4-59b7-4835-adc7-a58dc310cad9}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13028,7 +13004,7 @@
           <xm:sqref>AB101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c46fbf50-fa2e-48d8-8d06-c6539c6c779c}">
+          <x14:cfRule type="dataBar" id="{af198761-db08-44e6-92c3-b2b92d820131}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13037,7 +13013,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{431e3765-6590-4641-9f0e-d68b8f2c6c5d}">
+          <x14:cfRule type="dataBar" id="{e4ad1068-1a14-4a0d-8cf8-b17cabad6b10}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13049,7 +13025,7 @@
           <xm:sqref>AB115</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1dcdcc10-7594-4f7d-812a-1f3c2ba38a84}">
+          <x14:cfRule type="dataBar" id="{625c0588-1710-41b0-b297-c98b2ec10a74}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13058,7 +13034,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3dcd5b39-fdbf-49b8-9353-676c7c3590bc}">
+          <x14:cfRule type="dataBar" id="{1758f066-671d-436c-b79e-e828e1eaef53}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13067,7 +13043,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7ddd7afa-ed6c-4d19-91ee-06002d8d1b7f}">
+          <x14:cfRule type="dataBar" id="{cd7330a4-0328-4cd3-a64f-48d644dff5ae}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13080,7 +13056,7 @@
           <xm:sqref>AB125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5c07b905-349e-4a2d-b430-bb4d7ac85860}">
+          <x14:cfRule type="dataBar" id="{24e8eb18-0e9e-41b7-9a35-9b0a2a0bd3b5}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13089,7 +13065,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c8c9d9aa-ee45-4d66-b2b2-58be51c524a9}">
+          <x14:cfRule type="dataBar" id="{1fb07516-5df2-48bc-925d-3f2fa5797fbc}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13098,7 +13074,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7839ab6e-e2be-4312-b833-66fa3e4c9f07}">
+          <x14:cfRule type="dataBar" id="{b8624788-0e02-435c-a70a-96005bc51d22}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13111,7 +13087,7 @@
           <xm:sqref>K135</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8930ba59-95c8-4f05-a69f-7820ffb64b68}">
+          <x14:cfRule type="dataBar" id="{b29e05f9-3b58-4710-9733-65a0c9a038bc}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13120,7 +13096,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d44c1848-0434-4f9d-83ed-7650589ec994}">
+          <x14:cfRule type="dataBar" id="{4c826239-9a18-4821-8ce0-26addc416766}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13129,7 +13105,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0d16a92c-f53f-4955-b841-4b77a61cb245}">
+          <x14:cfRule type="dataBar" id="{089ce2d6-c751-450f-adbe-6bd2b40ecd11}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13142,7 +13118,7 @@
           <xm:sqref>K140</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7a8cd518-76f9-49f5-b401-2ad8cefde44a}">
+          <x14:cfRule type="dataBar" id="{3b6326b3-874e-447c-9b74-dc405f97688d}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13151,7 +13127,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b4209c88-a67e-4b4f-baa7-1fe8c88a0cb6}">
+          <x14:cfRule type="dataBar" id="{01996dae-c08a-452d-94d1-9095c864d6f1}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13160,7 +13136,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{38c467a4-5e44-46d3-9559-9692b46dd54d}">
+          <x14:cfRule type="dataBar" id="{b0cd3a9f-a3cb-41be-b39e-a2fee70bd5f9}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13173,7 +13149,7 @@
           <xm:sqref>K145</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{339a5f35-080a-46b4-bccb-8bacd2c5240f}">
+          <x14:cfRule type="dataBar" id="{e61278ad-ac2f-4058-9265-18ca71240777}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13182,7 +13158,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{887ef401-7856-47a5-b305-ffef768b610a}">
+          <x14:cfRule type="dataBar" id="{edc6b379-3afc-4adb-98af-56203730cc40}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13191,7 +13167,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e9325cde-0ad4-43da-a2a1-136c2ec9199a}">
+          <x14:cfRule type="dataBar" id="{f43080a0-21db-42cd-bad1-92cc8d9da3cb}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13204,7 +13180,7 @@
           <xm:sqref>K150</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{07175fa1-5f89-4f51-af95-401a62e1a2d4}">
+          <x14:cfRule type="dataBar" id="{4ad2eddf-7e78-48fa-9b79-e57750129d45}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -13215,7 +13191,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{aa2b516a-a20e-42b8-9c7f-2ed77ae61ebf}">
+          <x14:cfRule type="dataBar" id="{61774866-067d-4641-99a7-03f4a3c836fa}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13226,14 +13202,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b8701955-4a16-479c-8f2b-d2a224e0c0d2}">
+          <x14:cfRule type="dataBar" id="{f66b1efe-71b5-478f-9617-67c089bd041b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a6c7ff95-17a3-4537-a599-2235dd00a17e}">
+          <x14:cfRule type="dataBar" id="{b3ca3735-2451-40ab-ad43-e67808a08a61}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -13244,7 +13220,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e437c70f-aa76-441c-b4f0-bb738a1f6d16}">
+          <x14:cfRule type="dataBar" id="{10dde7d7-913b-441d-b712-928856656a7a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -13255,7 +13231,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6468aa35-73cf-4e3c-9996-d0d30839b2f7}">
+          <x14:cfRule type="dataBar" id="{799ad7eb-c616-4d0c-b78c-2087ec1c901f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13266,7 +13242,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{432bc915-a0d9-4dcb-b56f-647b516ba97d}">
+          <x14:cfRule type="dataBar" id="{ec8393cb-f716-46db-93ae-ae5d79932c01}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13275,7 +13251,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c0736e08-d1c7-4b9f-b863-65c2c7377b59}">
+          <x14:cfRule type="dataBar" id="{6c02597c-56bf-43a3-befd-9cbe4c8ba60c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13287,7 +13263,7 @@
           <xm:sqref>K57:K58</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1f470d2a-f298-4423-bba1-4584d6e6041a}">
+          <x14:cfRule type="dataBar" id="{e94ba282-08c6-4f99-86b4-cff46cfe9b30}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13296,7 +13272,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9cd0397c-243b-4064-a845-d5ab2251b5c4}">
+          <x14:cfRule type="dataBar" id="{74ed936e-314e-4168-83b3-42184c20b15e}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13309,7 +13285,7 @@
           <xm:sqref>Y67:Y86</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{81c785b6-d9ec-4e50-be20-ba1828fc7b08}">
+          <x14:cfRule type="dataBar" id="{cdf9b126-4d85-47ea-9032-ee6b83cdd204}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13322,7 +13298,7 @@
           <xm:sqref>Y77:Y86</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{79b6edcb-0864-4815-9590-d441def8ecc5}">
+          <x14:cfRule type="dataBar" id="{f51deae4-f6df-4fd4-8123-50a519e6883c}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13335,7 +13311,7 @@
           <xm:sqref>AB115:AB124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e2f097f9-60e2-41d7-ac88-952fb112f193}">
+          <x14:cfRule type="dataBar" id="{6d7bae07-c4ba-48e6-9112-5aac0bf34b22}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13347,7 +13323,7 @@
           <xm:sqref>AD56:AE57</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{848b3bdf-5226-43db-a571-6d78ab541026}">
+          <x14:cfRule type="dataBar" id="{b1c4895f-0f53-449e-9235-34aac4a42a5a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13359,7 +13335,7 @@
           <xm:sqref>AD60:AE63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d1af849e-6cfa-447b-9666-60a64f0a3c6c}">
+          <x14:cfRule type="dataBar" id="{f32ca648-3d6d-4d5b-839d-274d93f45ea4}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13368,7 +13344,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{88a765bc-ceaf-43f2-b1ac-254c53d9f821}">
+          <x14:cfRule type="dataBar" id="{3791ffab-4c9c-4e5d-8390-045514d80363}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13377,7 +13353,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b880d4d5-90b6-4164-a1f9-f61498a22dec}">
+          <x14:cfRule type="dataBar" id="{f0477eda-77f4-4297-a0fc-f51fefafe97f}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13390,7 +13366,7 @@
           <xm:sqref>F67 F72 F77 F82</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{252c3fb7-85dd-4309-bf47-a7f7445ad33d}">
+          <x14:cfRule type="dataBar" id="{315b8d7c-0d53-4f07-95d7-f3eb1b825a8a}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13399,7 +13375,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ed2ae304-a059-424f-ab1a-6738c2dfbbb5}">
+          <x14:cfRule type="dataBar" id="{59f17f4b-2050-4e12-baac-fc8fa7f45ea8}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13408,7 +13384,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{06a91191-f7ee-41af-96c4-9098481de723}">
+          <x14:cfRule type="dataBar" id="{8c079828-6198-4193-9941-fc6fd9db51ac}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13421,7 +13397,7 @@
           <xm:sqref>K67 K77 K87 K101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5240afe0-1a4e-4a62-858b-4dbc14260841}">
+          <x14:cfRule type="dataBar" id="{ef394594-a9af-4929-a0f1-f5c2abdf1626}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13430,7 +13406,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a8207689-0771-43bd-be70-2bac451b8a04}">
+          <x14:cfRule type="dataBar" id="{3b25587a-911c-4ecc-a210-8e2867ad2bef}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13439,7 +13415,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5afbf0a8-23db-4b75-a432-eb4c5cab17c7}">
+          <x14:cfRule type="dataBar" id="{14af986a-11fb-406a-9a8d-943d5bcf05ff}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13452,7 +13428,7 @@
           <xm:sqref>AB77 AB87</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d79459d6-884c-4a3c-b21c-ed4b9dd6430d}">
+          <x14:cfRule type="dataBar" id="{f72e9826-8cf6-4fb4-9fc7-47bcc31ff473}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13461,7 +13437,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{107698f6-313c-498b-9b8b-f8c72165b31a}">
+          <x14:cfRule type="dataBar" id="{6b53e93f-df6a-4324-8005-a8f22bea234d}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13470,7 +13446,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d27e7a6f-c0c3-4597-93ba-dbd4e1ace09f}">
+          <x14:cfRule type="dataBar" id="{45672cff-bc6f-4ada-889a-783f7fc2b7db}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13483,7 +13459,7 @@
           <xm:sqref>F87 F94 F101 F108</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{911f05c4-d337-4296-bd10-b2f788f7ea15}">
+          <x14:cfRule type="dataBar" id="{6fff42f4-b967-4d21-997a-a8816a03661c}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13492,7 +13468,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d1190f8f-cfbf-402f-a563-1b754a8cfb86}">
+          <x14:cfRule type="dataBar" id="{aca51d9e-f35a-4599-b9ac-7f12bb460be1}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13505,7 +13481,7 @@
           <xm:sqref>Y87 Y101</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4016564b-8f81-4817-ad31-55622271c777}">
+          <x14:cfRule type="dataBar" id="{85c7428a-4028-4de5-b545-24770e243804}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13514,7 +13490,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{63bc00e1-4b5e-48dd-ada2-f422fffef014}">
+          <x14:cfRule type="dataBar" id="{b1d5c3ee-8fe5-417e-82f1-417264ecc2ea}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13523,7 +13499,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{25b4dfa6-6b69-48fb-bb36-8124ba70281d}">
+          <x14:cfRule type="dataBar" id="{5e91cb54-a545-471c-a311-ebac3b5f9596}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13536,7 +13512,7 @@
           <xm:sqref>F115 F120 F125 F130 F135 F140 F145 F150</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{999bc4c6-b06a-4795-9a2b-728ae4c09929}">
+          <x14:cfRule type="dataBar" id="{b3d38032-3b5d-493c-bb80-7ca9dc91dfd2}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13545,7 +13521,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{91514c5a-78c8-4267-9557-de51ffedf53a}">
+          <x14:cfRule type="dataBar" id="{19636f01-0376-48d3-8afd-b4cfb5bc9b63}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13554,7 +13530,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d6549bd5-9cc0-4af3-8f63-7a52b5128f2a}">
+          <x14:cfRule type="dataBar" id="{edd90c9f-c9a0-4b8a-bc56-588a523e18e4}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13567,7 +13543,7 @@
           <xm:sqref>K115 K125</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0d2a7e42-b164-4b3b-8686-4c60f3a77136}">
+          <x14:cfRule type="dataBar" id="{eefdf929-5606-4234-b533-44bd4d7e2221}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13576,7 +13552,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{31cced82-ae48-4a8c-a610-5d558d082985}">
+          <x14:cfRule type="dataBar" id="{53c4dfd0-9f25-4c07-9c95-f2a997b44be6}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13598,12 +13574,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="26.8818181818182" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.38181818181818" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.21818181818182" style="1" customWidth="1"/>
-    <col min="18" max="18" width="9.38181818181818" style="1" customWidth="1"/>
+    <col min="1" max="1" width="26.8796296296296" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.37962962962963" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.22222222222222" style="1" customWidth="1"/>
+    <col min="18" max="18" width="9.37962962962963" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">

--- a/外网端源码/其他楼交接班容量报表空模板.xlsx
+++ b/外网端源码/其他楼交接班容量报表空模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="22020"/>
+    <workbookView windowWidth="24750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="本班组" sheetId="1" r:id="rId1"/>
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="欧0">本班组!$U$17</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">本班组!$A$2:$AG$154</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">本班组!$A$2:$AG$156</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="388">
   <si>
     <t>班次</t>
   </si>
@@ -482,6 +482,9 @@
   <si>
     <t>压差
 （Mpa）</t>
+  </si>
+  <si>
+    <t>二次泵</t>
   </si>
   <si>
     <t>二次泵
@@ -3197,29 +3200,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AF154"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:AF156"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="18.1851851851852" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.1818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.9351851851852" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.9363636363636" style="1" customWidth="1"/>
     <col min="7" max="8" width="9" style="1" customWidth="1"/>
-    <col min="9" max="9" width="16.4074074074074" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.4090909090909" style="1" customWidth="1"/>
     <col min="10" max="11" width="9" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.9351851851852" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.9363636363636" style="1" customWidth="1"/>
     <col min="13" max="13" width="9" style="1" customWidth="1"/>
-    <col min="14" max="14" width="8.75" style="1" customWidth="1"/>
-    <col min="15" max="15" width="38.1851851851852" style="1" customWidth="1"/>
+    <col min="14" max="14" width="8.75454545454545" style="1" customWidth="1"/>
+    <col min="15" max="15" width="38.1818181818182" style="1" customWidth="1"/>
     <col min="16" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="12.5925925925926" style="1" customWidth="1"/>
-    <col min="20" max="20" width="16.5092592592593" style="1" customWidth="1"/>
+    <col min="19" max="19" width="12.5909090909091" style="1" customWidth="1"/>
+    <col min="20" max="20" width="16.5090909090909" style="1" customWidth="1"/>
     <col min="21" max="21" width="9" style="1" customWidth="1"/>
-    <col min="22" max="22" width="14.1574074074074" style="1" customWidth="1"/>
+    <col min="22" max="22" width="14.1545454545455" style="1" customWidth="1"/>
     <col min="23" max="24" width="9" style="1" customWidth="1"/>
-    <col min="25" max="25" width="10.25" style="1" customWidth="1"/>
+    <col min="25" max="25" width="10.2545454545455" style="1" customWidth="1"/>
     <col min="26" max="27" width="9" style="1" customWidth="1"/>
-    <col min="28" max="28" width="17.4166666666667" style="1" customWidth="1"/>
+    <col min="28" max="28" width="17.4181818181818" style="1" customWidth="1"/>
     <col min="31" max="31" width="11" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5598,15 +5601,13 @@
       <c r="AD48" s="82"/>
       <c r="AE48" s="83"/>
     </row>
-    <row r="49" ht="42" customHeight="1" spans="1:31">
-      <c r="A49" s="65"/>
-      <c r="B49" s="66"/>
-      <c r="C49" s="104" t="s">
+    <row r="49" ht="25.05" customHeight="1" spans="1:31">
+      <c r="A49" s="46"/>
+      <c r="B49" s="47"/>
+      <c r="C49" s="92" t="s">
         <v>134</v>
       </c>
-      <c r="D49" s="92" t="s">
-        <v>118</v>
-      </c>
+      <c r="D49" s="14"/>
       <c r="E49" s="14"/>
       <c r="F49" s="14"/>
       <c r="G49" s="14"/>
@@ -5617,13 +5618,11 @@
       <c r="L49" s="14"/>
       <c r="M49" s="14"/>
       <c r="N49" s="15"/>
-      <c r="O49" s="30"/>
-      <c r="P49" s="104" t="s">
+      <c r="O49" s="55"/>
+      <c r="P49" s="92" t="s">
         <v>134</v>
       </c>
-      <c r="Q49" s="92" t="s">
-        <v>118</v>
-      </c>
+      <c r="Q49" s="14"/>
       <c r="R49" s="14"/>
       <c r="S49" s="14"/>
       <c r="T49" s="14"/>
@@ -5639,52 +5638,82 @@
       <c r="AD49" s="82"/>
       <c r="AE49" s="83"/>
     </row>
-    <row r="50" spans="1:31">
-      <c r="A50" s="26" t="s">
+    <row r="50" ht="42" customHeight="1" spans="1:31">
+      <c r="A50" s="46"/>
+      <c r="B50" s="47"/>
+      <c r="C50" s="104" t="s">
+        <v>130</v>
+      </c>
+      <c r="D50" s="106" t="s">
+        <v>15</v>
+      </c>
+      <c r="E50" s="104" t="s">
+        <v>131</v>
+      </c>
+      <c r="F50" s="15"/>
+      <c r="G50" s="106">
+        <v>0</v>
+      </c>
+      <c r="H50" s="15"/>
+      <c r="I50" s="104" t="s">
+        <v>132</v>
+      </c>
+      <c r="J50" s="15"/>
+      <c r="K50" s="106">
+        <v>0</v>
+      </c>
+      <c r="L50" s="15"/>
+      <c r="M50" s="104" t="s">
+        <v>133</v>
+      </c>
+      <c r="N50" s="106">
+        <f>K50-G50</f>
+        <v>0</v>
+      </c>
+      <c r="O50" s="55"/>
+      <c r="P50" s="104" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q50" s="106" t="s">
+        <v>15</v>
+      </c>
+      <c r="R50" s="104" t="s">
+        <v>131</v>
+      </c>
+      <c r="S50" s="15"/>
+      <c r="T50" s="106">
+        <v>0</v>
+      </c>
+      <c r="U50" s="15"/>
+      <c r="V50" s="104" t="s">
+        <v>132</v>
+      </c>
+      <c r="W50" s="15"/>
+      <c r="X50" s="106">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="15"/>
+      <c r="Z50" s="104" t="s">
+        <v>133</v>
+      </c>
+      <c r="AA50" s="104">
+        <f>X50-T50</f>
+        <v>0</v>
+      </c>
+      <c r="AB50" s="81"/>
+      <c r="AC50" s="82"/>
+      <c r="AD50" s="82"/>
+      <c r="AE50" s="83"/>
+    </row>
+    <row r="51" ht="42" customHeight="1" spans="1:31">
+      <c r="A51" s="65"/>
+      <c r="B51" s="66"/>
+      <c r="C51" s="104" t="s">
         <v>135</v>
       </c>
-      <c r="B50" s="15"/>
-      <c r="C50" s="110" t="s">
-        <v>15</v>
-      </c>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="14"/>
-      <c r="J50" s="14"/>
-      <c r="K50" s="14"/>
-      <c r="L50" s="14"/>
-      <c r="M50" s="14"/>
-      <c r="N50" s="14"/>
-      <c r="O50" s="14"/>
-      <c r="P50" s="14"/>
-      <c r="Q50" s="14"/>
-      <c r="R50" s="14"/>
-      <c r="S50" s="14"/>
-      <c r="T50" s="14"/>
-      <c r="U50" s="14"/>
-      <c r="V50" s="14"/>
-      <c r="W50" s="14"/>
-      <c r="X50" s="14"/>
-      <c r="Y50" s="14"/>
-      <c r="Z50" s="14"/>
-      <c r="AA50" s="14"/>
-      <c r="AB50" s="14"/>
-      <c r="AC50" s="14"/>
-      <c r="AD50" s="14"/>
-      <c r="AE50" s="15"/>
-    </row>
-    <row r="51" spans="1:31">
-      <c r="A51" s="26" t="s">
-        <v>136</v>
-      </c>
-      <c r="B51" s="15"/>
-      <c r="C51" s="110" t="s">
-        <v>15</v>
-      </c>
-      <c r="D51" s="14"/>
+      <c r="D51" s="92" t="s">
+        <v>118</v>
+      </c>
       <c r="E51" s="14"/>
       <c r="F51" s="14"/>
       <c r="G51" s="14"/>
@@ -5694,10 +5723,14 @@
       <c r="K51" s="14"/>
       <c r="L51" s="14"/>
       <c r="M51" s="14"/>
-      <c r="N51" s="14"/>
-      <c r="O51" s="14"/>
-      <c r="P51" s="14"/>
-      <c r="Q51" s="14"/>
+      <c r="N51" s="15"/>
+      <c r="O51" s="30"/>
+      <c r="P51" s="104" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q51" s="92" t="s">
+        <v>118</v>
+      </c>
       <c r="R51" s="14"/>
       <c r="S51" s="14"/>
       <c r="T51" s="14"/>
@@ -5707,15 +5740,15 @@
       <c r="X51" s="14"/>
       <c r="Y51" s="14"/>
       <c r="Z51" s="14"/>
-      <c r="AA51" s="14"/>
-      <c r="AB51" s="14"/>
-      <c r="AC51" s="14"/>
-      <c r="AD51" s="14"/>
-      <c r="AE51" s="15"/>
+      <c r="AA51" s="15"/>
+      <c r="AB51" s="81"/>
+      <c r="AC51" s="82"/>
+      <c r="AD51" s="82"/>
+      <c r="AE51" s="83"/>
     </row>
     <row r="52" spans="1:31">
       <c r="A52" s="26" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B52" s="15"/>
       <c r="C52" s="110" t="s">
@@ -5752,7 +5785,7 @@
     </row>
     <row r="53" spans="1:31">
       <c r="A53" s="26" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B53" s="15"/>
       <c r="C53" s="110" t="s">
@@ -5788,11 +5821,13 @@
       <c r="AE53" s="15"/>
     </row>
     <row r="54" spans="1:31">
-      <c r="A54" s="111" t="s">
-        <v>139</v>
-      </c>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
+      <c r="A54" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="B54" s="15"/>
+      <c r="C54" s="110" t="s">
+        <v>15</v>
+      </c>
       <c r="D54" s="14"/>
       <c r="E54" s="14"/>
       <c r="F54" s="14"/>
@@ -5822,24 +5857,26 @@
       <c r="AD54" s="14"/>
       <c r="AE54" s="15"/>
     </row>
-    <row r="55" ht="28" customHeight="1" spans="1:31">
-      <c r="A55" s="112" t="s">
-        <v>140</v>
-      </c>
-      <c r="B55" s="113"/>
-      <c r="C55" s="113"/>
-      <c r="D55" s="113"/>
-      <c r="E55" s="113"/>
-      <c r="F55" s="113"/>
-      <c r="G55" s="113"/>
-      <c r="H55" s="113"/>
-      <c r="I55" s="113"/>
-      <c r="J55" s="113"/>
-      <c r="K55" s="113"/>
-      <c r="L55" s="113"/>
-      <c r="M55" s="64"/>
-      <c r="N55" s="64"/>
-      <c r="O55" s="114"/>
+    <row r="55" spans="1:31">
+      <c r="A55" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="B55" s="15"/>
+      <c r="C55" s="110" t="s">
+        <v>15</v>
+      </c>
+      <c r="D55" s="14"/>
+      <c r="E55" s="14"/>
+      <c r="F55" s="14"/>
+      <c r="G55" s="14"/>
+      <c r="H55" s="14"/>
+      <c r="I55" s="14"/>
+      <c r="J55" s="14"/>
+      <c r="K55" s="14"/>
+      <c r="L55" s="14"/>
+      <c r="M55" s="14"/>
+      <c r="N55" s="14"/>
+      <c r="O55" s="14"/>
       <c r="P55" s="14"/>
       <c r="Q55" s="14"/>
       <c r="R55" s="14"/>
@@ -5850,207 +5887,187 @@
       <c r="W55" s="14"/>
       <c r="X55" s="14"/>
       <c r="Y55" s="14"/>
-      <c r="Z55" s="15"/>
-      <c r="AA55" s="64"/>
-      <c r="AB55" s="115" t="s">
-        <v>141</v>
-      </c>
-      <c r="AC55" s="115" t="s">
-        <v>142</v>
-      </c>
-      <c r="AD55" s="116" t="s">
-        <v>143</v>
-      </c>
+      <c r="Z55" s="14"/>
+      <c r="AA55" s="14"/>
+      <c r="AB55" s="14"/>
+      <c r="AC55" s="14"/>
+      <c r="AD55" s="14"/>
       <c r="AE55" s="15"/>
     </row>
     <row r="56" spans="1:31">
-      <c r="A56" s="117" t="s">
-        <v>144</v>
-      </c>
-      <c r="B56" s="72"/>
-      <c r="C56" s="118" t="s">
-        <v>145</v>
-      </c>
-      <c r="D56" s="72"/>
-      <c r="E56" s="118" t="s">
-        <v>146</v>
-      </c>
-      <c r="F56" s="72"/>
-      <c r="G56" s="119" t="s">
-        <v>147</v>
-      </c>
-      <c r="H56" s="72"/>
-      <c r="I56" s="118" t="s">
-        <v>148</v>
-      </c>
-      <c r="J56" s="72"/>
-      <c r="K56" s="118" t="s">
-        <v>149</v>
-      </c>
-      <c r="L56" s="72"/>
-      <c r="M56" s="120"/>
-      <c r="N56" s="120"/>
-      <c r="O56" s="121" t="s">
-        <v>150</v>
-      </c>
+      <c r="A56" s="111" t="s">
+        <v>140</v>
+      </c>
+      <c r="B56" s="14"/>
+      <c r="C56" s="14"/>
+      <c r="D56" s="14"/>
+      <c r="E56" s="14"/>
+      <c r="F56" s="14"/>
+      <c r="G56" s="14"/>
+      <c r="H56" s="14"/>
+      <c r="I56" s="14"/>
+      <c r="J56" s="14"/>
+      <c r="K56" s="14"/>
+      <c r="L56" s="14"/>
+      <c r="M56" s="14"/>
+      <c r="N56" s="14"/>
+      <c r="O56" s="14"/>
       <c r="P56" s="14"/>
-      <c r="Q56" s="15"/>
-      <c r="R56" s="104" t="s">
-        <v>77</v>
-      </c>
+      <c r="Q56" s="14"/>
+      <c r="R56" s="14"/>
       <c r="S56" s="14"/>
       <c r="T56" s="14"/>
-      <c r="U56" s="15"/>
-      <c r="V56" s="104" t="s">
-        <v>151</v>
-      </c>
+      <c r="U56" s="14"/>
+      <c r="V56" s="14"/>
       <c r="W56" s="14"/>
-      <c r="X56" s="15"/>
-      <c r="Y56" s="104" t="s">
-        <v>152</v>
-      </c>
-      <c r="Z56" s="15"/>
-      <c r="AA56" s="64"/>
-      <c r="AB56" s="122">
-        <v>1272</v>
-      </c>
-      <c r="AC56" s="122">
-        <v>2</v>
-      </c>
-      <c r="AD56" s="68">
-        <f>AC56/AB56</f>
-        <v>0.00157232704402516</v>
-      </c>
-      <c r="AE56" s="42"/>
-    </row>
-    <row r="57" spans="1:31">
-      <c r="A57" s="117" t="s">
-        <v>153</v>
-      </c>
-      <c r="B57" s="72"/>
-      <c r="C57" s="118"/>
-      <c r="D57" s="72"/>
-      <c r="E57" s="118"/>
-      <c r="F57" s="72"/>
-      <c r="G57" s="118"/>
-      <c r="H57" s="72"/>
-      <c r="I57" s="118"/>
-      <c r="J57" s="72"/>
-      <c r="K57" s="123"/>
-      <c r="L57" s="72"/>
+      <c r="X56" s="14"/>
+      <c r="Y56" s="14"/>
+      <c r="Z56" s="14"/>
+      <c r="AA56" s="14"/>
+      <c r="AB56" s="14"/>
+      <c r="AC56" s="14"/>
+      <c r="AD56" s="14"/>
+      <c r="AE56" s="15"/>
+    </row>
+    <row r="57" ht="28" customHeight="1" spans="1:31">
+      <c r="A57" s="112" t="s">
+        <v>141</v>
+      </c>
+      <c r="B57" s="113"/>
+      <c r="C57" s="113"/>
+      <c r="D57" s="113"/>
+      <c r="E57" s="113"/>
+      <c r="F57" s="113"/>
+      <c r="G57" s="113"/>
+      <c r="H57" s="113"/>
+      <c r="I57" s="113"/>
+      <c r="J57" s="113"/>
+      <c r="K57" s="113"/>
+      <c r="L57" s="113"/>
       <c r="M57" s="64"/>
       <c r="N57" s="64"/>
-      <c r="O57" s="28"/>
-      <c r="P57" s="56"/>
-      <c r="Q57" s="42"/>
-      <c r="R57" s="124"/>
-      <c r="S57" s="56"/>
-      <c r="T57" s="56"/>
-      <c r="U57" s="125"/>
-      <c r="V57" s="126"/>
-      <c r="W57" s="56"/>
-      <c r="X57" s="125"/>
-      <c r="Y57" s="127"/>
-      <c r="Z57" s="42"/>
+      <c r="O57" s="114"/>
+      <c r="P57" s="14"/>
+      <c r="Q57" s="14"/>
+      <c r="R57" s="14"/>
+      <c r="S57" s="14"/>
+      <c r="T57" s="14"/>
+      <c r="U57" s="14"/>
+      <c r="V57" s="14"/>
+      <c r="W57" s="14"/>
+      <c r="X57" s="14"/>
+      <c r="Y57" s="14"/>
+      <c r="Z57" s="15"/>
       <c r="AA57" s="64"/>
-      <c r="AB57" s="30"/>
-      <c r="AC57" s="30"/>
-      <c r="AD57" s="65"/>
-      <c r="AE57" s="66"/>
+      <c r="AB57" s="115" t="s">
+        <v>142</v>
+      </c>
+      <c r="AC57" s="115" t="s">
+        <v>143</v>
+      </c>
+      <c r="AD57" s="116" t="s">
+        <v>144</v>
+      </c>
+      <c r="AE57" s="15"/>
     </row>
     <row r="58" spans="1:31">
       <c r="A58" s="117" t="s">
+        <v>145</v>
+      </c>
+      <c r="B58" s="72"/>
+      <c r="C58" s="118" t="s">
+        <v>146</v>
+      </c>
+      <c r="D58" s="72"/>
+      <c r="E58" s="118" t="s">
+        <v>147</v>
+      </c>
+      <c r="F58" s="72"/>
+      <c r="G58" s="119" t="s">
+        <v>148</v>
+      </c>
+      <c r="H58" s="72"/>
+      <c r="I58" s="118" t="s">
+        <v>149</v>
+      </c>
+      <c r="J58" s="72"/>
+      <c r="K58" s="118" t="s">
+        <v>150</v>
+      </c>
+      <c r="L58" s="72"/>
+      <c r="M58" s="120"/>
+      <c r="N58" s="120"/>
+      <c r="O58" s="121" t="s">
+        <v>151</v>
+      </c>
+      <c r="P58" s="14"/>
+      <c r="Q58" s="15"/>
+      <c r="R58" s="104" t="s">
+        <v>77</v>
+      </c>
+      <c r="S58" s="14"/>
+      <c r="T58" s="14"/>
+      <c r="U58" s="15"/>
+      <c r="V58" s="104" t="s">
+        <v>152</v>
+      </c>
+      <c r="W58" s="14"/>
+      <c r="X58" s="15"/>
+      <c r="Y58" s="104" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z58" s="15"/>
+      <c r="AA58" s="64"/>
+      <c r="AB58" s="122">
+        <v>1272</v>
+      </c>
+      <c r="AC58" s="122">
+        <v>2</v>
+      </c>
+      <c r="AD58" s="68">
+        <f>AC58/AB58</f>
+        <v>0.00157232704402516</v>
+      </c>
+      <c r="AE58" s="42"/>
+    </row>
+    <row r="59" spans="1:31">
+      <c r="A59" s="117" t="s">
         <v>154</v>
       </c>
-      <c r="B58" s="72"/>
-      <c r="C58" s="118"/>
-      <c r="D58" s="72"/>
-      <c r="E58" s="118"/>
-      <c r="F58" s="72"/>
-      <c r="G58" s="118"/>
-      <c r="H58" s="72"/>
-      <c r="I58" s="118"/>
-      <c r="J58" s="72"/>
-      <c r="K58" s="123"/>
-      <c r="L58" s="72"/>
-      <c r="M58" s="64"/>
-      <c r="N58" s="64"/>
-      <c r="O58" s="65"/>
-      <c r="P58" s="12"/>
-      <c r="Q58" s="66"/>
-      <c r="R58" s="65"/>
-      <c r="S58" s="12"/>
-      <c r="T58" s="12"/>
-      <c r="U58" s="128"/>
-      <c r="V58" s="129"/>
-      <c r="W58" s="12"/>
-      <c r="X58" s="128"/>
-      <c r="Y58" s="129"/>
-      <c r="Z58" s="66"/>
-      <c r="AA58" s="64"/>
-      <c r="AB58" s="130"/>
-      <c r="AC58" s="14"/>
-      <c r="AD58" s="14"/>
-      <c r="AE58" s="15"/>
-    </row>
-    <row r="59" ht="28" customHeight="1" spans="1:31">
-      <c r="A59" s="131"/>
-      <c r="B59" s="131"/>
-      <c r="C59" s="117" t="s">
-        <v>145</v>
-      </c>
+      <c r="B59" s="72"/>
+      <c r="C59" s="118"/>
       <c r="D59" s="72"/>
-      <c r="E59" s="118" t="s">
-        <v>155</v>
-      </c>
+      <c r="E59" s="118"/>
       <c r="F59" s="72"/>
-      <c r="G59" s="119" t="s">
-        <v>147</v>
-      </c>
+      <c r="G59" s="118"/>
       <c r="H59" s="72"/>
-      <c r="I59" s="118" t="s">
-        <v>148</v>
-      </c>
+      <c r="I59" s="118"/>
       <c r="J59" s="72"/>
-      <c r="K59" s="118" t="s">
-        <v>149</v>
-      </c>
+      <c r="K59" s="123"/>
       <c r="L59" s="72"/>
-      <c r="M59" s="120"/>
-      <c r="N59" s="120"/>
-      <c r="O59" s="132" t="s">
-        <v>156</v>
-      </c>
-      <c r="P59" s="14"/>
-      <c r="Q59" s="14"/>
-      <c r="R59" s="15"/>
-      <c r="S59" s="104" t="s">
-        <v>157</v>
-      </c>
-      <c r="T59" s="14"/>
-      <c r="U59" s="15"/>
-      <c r="V59" s="104" t="s">
-        <v>158</v>
-      </c>
-      <c r="W59" s="14"/>
-      <c r="X59" s="14"/>
-      <c r="Y59" s="14"/>
-      <c r="Z59" s="15"/>
+      <c r="M59" s="64"/>
+      <c r="N59" s="64"/>
+      <c r="O59" s="28"/>
+      <c r="P59" s="56"/>
+      <c r="Q59" s="42"/>
+      <c r="R59" s="124"/>
+      <c r="S59" s="56"/>
+      <c r="T59" s="56"/>
+      <c r="U59" s="125"/>
+      <c r="V59" s="126"/>
+      <c r="W59" s="56"/>
+      <c r="X59" s="125"/>
+      <c r="Y59" s="127"/>
+      <c r="Z59" s="42"/>
       <c r="AA59" s="64"/>
-      <c r="AB59" s="116" t="s">
-        <v>159</v>
-      </c>
-      <c r="AC59" s="116" t="s">
-        <v>160</v>
-      </c>
-      <c r="AD59" s="116" t="s">
-        <v>161</v>
-      </c>
-      <c r="AE59" s="15"/>
+      <c r="AB59" s="30"/>
+      <c r="AC59" s="30"/>
+      <c r="AD59" s="65"/>
+      <c r="AE59" s="66"/>
     </row>
     <row r="60" spans="1:31">
       <c r="A60" s="117" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B60" s="72"/>
       <c r="C60" s="118"/>
@@ -6065,72 +6082,82 @@
       <c r="L60" s="72"/>
       <c r="M60" s="64"/>
       <c r="N60" s="64"/>
-      <c r="O60" s="132"/>
-      <c r="P60" s="56"/>
-      <c r="Q60" s="56"/>
-      <c r="R60" s="42"/>
-      <c r="S60" s="104">
-        <v>0</v>
-      </c>
-      <c r="T60" s="56"/>
-      <c r="U60" s="42"/>
-      <c r="V60" s="133"/>
-      <c r="W60" s="95"/>
-      <c r="X60" s="95"/>
-      <c r="Y60" s="95"/>
-      <c r="Z60" s="96"/>
+      <c r="O60" s="65"/>
+      <c r="P60" s="12"/>
+      <c r="Q60" s="66"/>
+      <c r="R60" s="65"/>
+      <c r="S60" s="12"/>
+      <c r="T60" s="12"/>
+      <c r="U60" s="128"/>
+      <c r="V60" s="129"/>
+      <c r="W60" s="12"/>
+      <c r="X60" s="128"/>
+      <c r="Y60" s="129"/>
+      <c r="Z60" s="66"/>
       <c r="AA60" s="64"/>
-      <c r="AB60" s="104">
-        <v>14100</v>
-      </c>
-      <c r="AC60" s="104">
-        <f>S60</f>
-        <v>0</v>
-      </c>
-      <c r="AD60" s="68">
-        <f>AC60/AB60</f>
-        <v>0</v>
-      </c>
-      <c r="AE60" s="42"/>
-    </row>
-    <row r="61" spans="1:31">
-      <c r="A61" s="117" t="s">
-        <v>163</v>
-      </c>
-      <c r="B61" s="72"/>
-      <c r="C61" s="118"/>
+      <c r="AB60" s="130"/>
+      <c r="AC60" s="14"/>
+      <c r="AD60" s="14"/>
+      <c r="AE60" s="15"/>
+    </row>
+    <row r="61" ht="28" customHeight="1" spans="1:31">
+      <c r="A61" s="131"/>
+      <c r="B61" s="131"/>
+      <c r="C61" s="117" t="s">
+        <v>146</v>
+      </c>
       <c r="D61" s="72"/>
-      <c r="E61" s="118"/>
+      <c r="E61" s="118" t="s">
+        <v>156</v>
+      </c>
       <c r="F61" s="72"/>
-      <c r="G61" s="118"/>
+      <c r="G61" s="119" t="s">
+        <v>148</v>
+      </c>
       <c r="H61" s="72"/>
-      <c r="I61" s="118"/>
+      <c r="I61" s="118" t="s">
+        <v>149</v>
+      </c>
       <c r="J61" s="72"/>
-      <c r="K61" s="123"/>
+      <c r="K61" s="118" t="s">
+        <v>150</v>
+      </c>
       <c r="L61" s="72"/>
-      <c r="M61" s="64"/>
-      <c r="N61" s="64"/>
-      <c r="O61" s="129"/>
-      <c r="P61" s="12"/>
-      <c r="Q61" s="12"/>
-      <c r="R61" s="66"/>
-      <c r="S61" s="65"/>
-      <c r="T61" s="12"/>
-      <c r="U61" s="66"/>
-      <c r="V61" s="97"/>
-      <c r="W61" s="98"/>
-      <c r="X61" s="98"/>
-      <c r="Y61" s="98"/>
-      <c r="Z61" s="99"/>
+      <c r="M61" s="120"/>
+      <c r="N61" s="120"/>
+      <c r="O61" s="132" t="s">
+        <v>157</v>
+      </c>
+      <c r="P61" s="14"/>
+      <c r="Q61" s="14"/>
+      <c r="R61" s="15"/>
+      <c r="S61" s="104" t="s">
+        <v>158</v>
+      </c>
+      <c r="T61" s="14"/>
+      <c r="U61" s="15"/>
+      <c r="V61" s="104" t="s">
+        <v>159</v>
+      </c>
+      <c r="W61" s="14"/>
+      <c r="X61" s="14"/>
+      <c r="Y61" s="14"/>
+      <c r="Z61" s="15"/>
       <c r="AA61" s="64"/>
-      <c r="AB61" s="30"/>
-      <c r="AC61" s="30"/>
-      <c r="AD61" s="65"/>
-      <c r="AE61" s="66"/>
+      <c r="AB61" s="116" t="s">
+        <v>160</v>
+      </c>
+      <c r="AC61" s="116" t="s">
+        <v>161</v>
+      </c>
+      <c r="AD61" s="116" t="s">
+        <v>162</v>
+      </c>
+      <c r="AE61" s="15"/>
     </row>
     <row r="62" spans="1:31">
       <c r="A62" s="117" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B62" s="72"/>
       <c r="C62" s="118"/>
@@ -6143,29 +6170,39 @@
       <c r="J62" s="72"/>
       <c r="K62" s="123"/>
       <c r="L62" s="72"/>
-      <c r="M62" s="134"/>
+      <c r="M62" s="64"/>
       <c r="N62" s="64"/>
-      <c r="O62" s="135"/>
-      <c r="P62" s="135"/>
-      <c r="Q62" s="135"/>
-      <c r="R62" s="135"/>
-      <c r="S62" s="135"/>
-      <c r="T62" s="135"/>
-      <c r="U62" s="135"/>
-      <c r="V62" s="135"/>
-      <c r="W62" s="135"/>
-      <c r="X62" s="135"/>
-      <c r="Y62" s="135"/>
-      <c r="Z62" s="135"/>
+      <c r="O62" s="132"/>
+      <c r="P62" s="56"/>
+      <c r="Q62" s="56"/>
+      <c r="R62" s="42"/>
+      <c r="S62" s="104">
+        <v>0</v>
+      </c>
+      <c r="T62" s="56"/>
+      <c r="U62" s="42"/>
+      <c r="V62" s="133"/>
+      <c r="W62" s="95"/>
+      <c r="X62" s="95"/>
+      <c r="Y62" s="95"/>
+      <c r="Z62" s="96"/>
       <c r="AA62" s="64"/>
-      <c r="AB62" s="135"/>
-      <c r="AC62" s="135"/>
-      <c r="AD62" s="136"/>
-      <c r="AE62" s="136"/>
+      <c r="AB62" s="104">
+        <v>14100</v>
+      </c>
+      <c r="AC62" s="104">
+        <f>S62</f>
+        <v>0</v>
+      </c>
+      <c r="AD62" s="68">
+        <f>AC62/AB62</f>
+        <v>0</v>
+      </c>
+      <c r="AE62" s="42"/>
     </row>
     <row r="63" spans="1:31">
       <c r="A63" s="117" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B63" s="72"/>
       <c r="C63" s="118"/>
@@ -6178,352 +6215,334 @@
       <c r="J63" s="72"/>
       <c r="K63" s="123"/>
       <c r="L63" s="72"/>
-      <c r="M63" s="134"/>
+      <c r="M63" s="64"/>
       <c r="N63" s="64"/>
-      <c r="O63" s="135"/>
-      <c r="P63" s="135"/>
-      <c r="Q63" s="135"/>
-      <c r="R63" s="135"/>
-      <c r="S63" s="135"/>
-      <c r="T63" s="135"/>
-      <c r="U63" s="135"/>
-      <c r="V63" s="135"/>
-      <c r="W63" s="135"/>
-      <c r="X63" s="135"/>
-      <c r="Y63" s="135"/>
-      <c r="Z63" s="135"/>
+      <c r="O63" s="129"/>
+      <c r="P63" s="12"/>
+      <c r="Q63" s="12"/>
+      <c r="R63" s="66"/>
+      <c r="S63" s="65"/>
+      <c r="T63" s="12"/>
+      <c r="U63" s="66"/>
+      <c r="V63" s="97"/>
+      <c r="W63" s="98"/>
+      <c r="X63" s="98"/>
+      <c r="Y63" s="98"/>
+      <c r="Z63" s="99"/>
       <c r="AA63" s="64"/>
-      <c r="AB63" s="135"/>
-      <c r="AC63" s="135"/>
-      <c r="AD63" s="136"/>
-      <c r="AE63" s="136"/>
+      <c r="AB63" s="30"/>
+      <c r="AC63" s="30"/>
+      <c r="AD63" s="65"/>
+      <c r="AE63" s="66"/>
     </row>
     <row r="64" spans="1:31">
-      <c r="A64" s="64"/>
-      <c r="B64" s="64"/>
-      <c r="C64" s="64"/>
-      <c r="D64" s="64"/>
-      <c r="E64" s="64"/>
-      <c r="F64" s="64"/>
-      <c r="G64" s="64"/>
-      <c r="H64" s="64"/>
-      <c r="I64" s="64"/>
-      <c r="J64" s="64"/>
-      <c r="K64" s="64"/>
-      <c r="L64" s="64"/>
-      <c r="M64" s="64"/>
+      <c r="A64" s="117" t="s">
+        <v>165</v>
+      </c>
+      <c r="B64" s="72"/>
+      <c r="C64" s="118"/>
+      <c r="D64" s="72"/>
+      <c r="E64" s="118"/>
+      <c r="F64" s="72"/>
+      <c r="G64" s="118"/>
+      <c r="H64" s="72"/>
+      <c r="I64" s="118"/>
+      <c r="J64" s="72"/>
+      <c r="K64" s="123"/>
+      <c r="L64" s="72"/>
+      <c r="M64" s="134"/>
       <c r="N64" s="64"/>
-      <c r="O64" s="64"/>
-      <c r="P64" s="64"/>
-      <c r="Q64" s="64"/>
-      <c r="R64" s="64"/>
-      <c r="S64" s="64"/>
-      <c r="T64" s="64"/>
-      <c r="U64" s="64"/>
-      <c r="V64" s="64"/>
-      <c r="W64" s="64"/>
-      <c r="X64" s="64"/>
-      <c r="Y64" s="64"/>
-      <c r="Z64" s="64"/>
+      <c r="O64" s="135"/>
+      <c r="P64" s="135"/>
+      <c r="Q64" s="135"/>
+      <c r="R64" s="135"/>
+      <c r="S64" s="135"/>
+      <c r="T64" s="135"/>
+      <c r="U64" s="135"/>
+      <c r="V64" s="135"/>
+      <c r="W64" s="135"/>
+      <c r="X64" s="135"/>
+      <c r="Y64" s="135"/>
+      <c r="Z64" s="135"/>
       <c r="AA64" s="64"/>
-      <c r="AB64" s="64"/>
-      <c r="AC64" s="64"/>
-      <c r="AD64" s="64"/>
-      <c r="AE64" s="64"/>
-    </row>
-    <row r="65" s="10" customFormat="1" ht="17.4" spans="1:32">
-      <c r="A65" s="137"/>
-      <c r="B65" s="138"/>
-      <c r="C65" s="138"/>
-      <c r="D65" s="138"/>
-      <c r="E65" s="138"/>
-      <c r="F65" s="139"/>
-      <c r="G65" s="139"/>
-      <c r="H65" s="138"/>
-      <c r="I65" s="138"/>
-      <c r="J65" s="138"/>
-      <c r="K65" s="138"/>
-      <c r="L65" s="138"/>
-      <c r="M65" s="138"/>
-      <c r="N65" s="138"/>
-      <c r="O65" s="138"/>
-      <c r="P65" s="138"/>
-      <c r="Q65" s="138"/>
-      <c r="R65" s="138"/>
-      <c r="S65" s="138"/>
-      <c r="T65" s="138"/>
-      <c r="U65" s="138"/>
-      <c r="V65" s="138"/>
-      <c r="W65" s="138"/>
-      <c r="X65" s="138"/>
-      <c r="Y65" s="138"/>
-      <c r="Z65" s="138"/>
-      <c r="AA65" s="138"/>
-      <c r="AB65" s="138"/>
-      <c r="AC65" s="138"/>
-      <c r="AD65" s="138"/>
-      <c r="AE65" s="140"/>
-    </row>
-    <row r="66" s="10" customFormat="1" ht="74" customHeight="1" spans="1:32">
-      <c r="A66" s="141" t="s">
+      <c r="AB64" s="135"/>
+      <c r="AC64" s="135"/>
+      <c r="AD64" s="136"/>
+      <c r="AE64" s="136"/>
+    </row>
+    <row r="65" spans="1:32">
+      <c r="A65" s="117" t="s">
         <v>166</v>
       </c>
-      <c r="B66" s="141" t="s">
+      <c r="B65" s="72"/>
+      <c r="C65" s="118"/>
+      <c r="D65" s="72"/>
+      <c r="E65" s="118"/>
+      <c r="F65" s="72"/>
+      <c r="G65" s="118"/>
+      <c r="H65" s="72"/>
+      <c r="I65" s="118"/>
+      <c r="J65" s="72"/>
+      <c r="K65" s="123"/>
+      <c r="L65" s="72"/>
+      <c r="M65" s="134"/>
+      <c r="N65" s="64"/>
+      <c r="O65" s="135"/>
+      <c r="P65" s="135"/>
+      <c r="Q65" s="135"/>
+      <c r="R65" s="135"/>
+      <c r="S65" s="135"/>
+      <c r="T65" s="135"/>
+      <c r="U65" s="135"/>
+      <c r="V65" s="135"/>
+      <c r="W65" s="135"/>
+      <c r="X65" s="135"/>
+      <c r="Y65" s="135"/>
+      <c r="Z65" s="135"/>
+      <c r="AA65" s="64"/>
+      <c r="AB65" s="135"/>
+      <c r="AC65" s="135"/>
+      <c r="AD65" s="136"/>
+      <c r="AE65" s="136"/>
+    </row>
+    <row r="66" spans="1:32">
+      <c r="A66" s="64"/>
+      <c r="B66" s="64"/>
+      <c r="C66" s="64"/>
+      <c r="D66" s="64"/>
+      <c r="E66" s="64"/>
+      <c r="F66" s="64"/>
+      <c r="G66" s="64"/>
+      <c r="H66" s="64"/>
+      <c r="I66" s="64"/>
+      <c r="J66" s="64"/>
+      <c r="K66" s="64"/>
+      <c r="L66" s="64"/>
+      <c r="M66" s="64"/>
+      <c r="N66" s="64"/>
+      <c r="O66" s="64"/>
+      <c r="P66" s="64"/>
+      <c r="Q66" s="64"/>
+      <c r="R66" s="64"/>
+      <c r="S66" s="64"/>
+      <c r="T66" s="64"/>
+      <c r="U66" s="64"/>
+      <c r="V66" s="64"/>
+      <c r="W66" s="64"/>
+      <c r="X66" s="64"/>
+      <c r="Y66" s="64"/>
+      <c r="Z66" s="64"/>
+      <c r="AA66" s="64"/>
+      <c r="AB66" s="64"/>
+      <c r="AC66" s="64"/>
+      <c r="AD66" s="64"/>
+      <c r="AE66" s="64"/>
+    </row>
+    <row r="67" s="10" customFormat="1" ht="17.5" spans="1:32">
+      <c r="A67" s="137"/>
+      <c r="B67" s="138"/>
+      <c r="C67" s="138"/>
+      <c r="D67" s="138"/>
+      <c r="E67" s="138"/>
+      <c r="F67" s="139"/>
+      <c r="G67" s="139"/>
+      <c r="H67" s="138"/>
+      <c r="I67" s="138"/>
+      <c r="J67" s="138"/>
+      <c r="K67" s="138"/>
+      <c r="L67" s="138"/>
+      <c r="M67" s="138"/>
+      <c r="N67" s="138"/>
+      <c r="O67" s="138"/>
+      <c r="P67" s="138"/>
+      <c r="Q67" s="138"/>
+      <c r="R67" s="138"/>
+      <c r="S67" s="138"/>
+      <c r="T67" s="138"/>
+      <c r="U67" s="138"/>
+      <c r="V67" s="138"/>
+      <c r="W67" s="138"/>
+      <c r="X67" s="138"/>
+      <c r="Y67" s="138"/>
+      <c r="Z67" s="138"/>
+      <c r="AA67" s="138"/>
+      <c r="AB67" s="138"/>
+      <c r="AC67" s="138"/>
+      <c r="AD67" s="138"/>
+      <c r="AE67" s="140"/>
+    </row>
+    <row r="68" s="10" customFormat="1" ht="74" customHeight="1" spans="1:32">
+      <c r="A68" s="141" t="s">
         <v>167</v>
       </c>
-      <c r="C66" s="141" t="s">
+      <c r="B68" s="141" t="s">
         <v>168</v>
       </c>
-      <c r="D66" s="142" t="s">
+      <c r="C68" s="141" t="s">
         <v>169</v>
       </c>
-      <c r="E66" s="141" t="s">
+      <c r="D68" s="142" t="s">
         <v>170</v>
       </c>
-      <c r="F66" s="141" t="s">
+      <c r="E68" s="141" t="s">
         <v>171</v>
       </c>
-      <c r="G66" s="42"/>
-      <c r="H66" s="141" t="s">
+      <c r="F68" s="141" t="s">
         <v>172</v>
       </c>
-      <c r="I66" s="141" t="s">
+      <c r="G68" s="42"/>
+      <c r="H68" s="141" t="s">
         <v>173</v>
       </c>
-      <c r="J66" s="141" t="s">
+      <c r="I68" s="141" t="s">
         <v>174</v>
       </c>
-      <c r="K66" s="141" t="s">
+      <c r="J68" s="141" t="s">
+        <v>175</v>
+      </c>
+      <c r="K68" s="141" t="s">
+        <v>172</v>
+      </c>
+      <c r="L68" s="141" t="s">
+        <v>176</v>
+      </c>
+      <c r="M68" s="141" t="s">
+        <v>177</v>
+      </c>
+      <c r="N68" s="141" t="s">
+        <v>178</v>
+      </c>
+      <c r="O68" s="141" t="s">
+        <v>179</v>
+      </c>
+      <c r="P68" s="141" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q68" s="141" t="s">
+        <v>178</v>
+      </c>
+      <c r="R68" s="141" t="s">
+        <v>181</v>
+      </c>
+      <c r="S68" s="141" t="s">
+        <v>182</v>
+      </c>
+      <c r="T68" s="42"/>
+      <c r="U68" s="141" t="s">
         <v>171</v>
       </c>
-      <c r="L66" s="141" t="s">
-        <v>175</v>
-      </c>
-      <c r="M66" s="141" t="s">
-        <v>176</v>
-      </c>
-      <c r="N66" s="141" t="s">
-        <v>177</v>
-      </c>
-      <c r="O66" s="141" t="s">
-        <v>178</v>
-      </c>
-      <c r="P66" s="141" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q66" s="141" t="s">
-        <v>177</v>
-      </c>
-      <c r="R66" s="141" t="s">
-        <v>180</v>
-      </c>
-      <c r="S66" s="141" t="s">
-        <v>181</v>
-      </c>
-      <c r="T66" s="42"/>
-      <c r="U66" s="141" t="s">
-        <v>170</v>
-      </c>
-      <c r="V66" s="141" t="s">
-        <v>171</v>
-      </c>
-      <c r="W66" s="141" t="s">
-        <v>182</v>
-      </c>
-      <c r="X66" s="141" t="s">
+      <c r="V68" s="141" t="s">
+        <v>172</v>
+      </c>
+      <c r="W68" s="141" t="s">
         <v>183</v>
       </c>
-      <c r="Y66" s="141" t="s">
+      <c r="X68" s="141" t="s">
         <v>184</v>
       </c>
-      <c r="Z66" s="141" t="s">
+      <c r="Y68" s="141" t="s">
         <v>185</v>
       </c>
-      <c r="AA66" s="141" t="s">
+      <c r="Z68" s="141" t="s">
         <v>186</v>
       </c>
-      <c r="AB66" s="141" t="s">
+      <c r="AA68" s="141" t="s">
         <v>187</v>
       </c>
-      <c r="AC66" s="141" t="s">
+      <c r="AB68" s="141" t="s">
         <v>188</v>
       </c>
-      <c r="AD66" s="141" t="s">
+      <c r="AC68" s="141" t="s">
         <v>189</v>
       </c>
-      <c r="AE66" s="143" t="s">
+      <c r="AD68" s="141" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="67" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
-      <c r="A67" s="144" t="s">
+      <c r="AE68" s="143" t="s">
         <v>191</v>
       </c>
-      <c r="B67" s="144" t="s">
+    </row>
+    <row r="69" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
+      <c r="A69" s="144" t="s">
         <v>192</v>
       </c>
-      <c r="C67" s="144" t="s">
+      <c r="B69" s="144" t="s">
         <v>193</v>
       </c>
-      <c r="D67" s="144"/>
-      <c r="E67" s="144"/>
-      <c r="F67" s="145">
-        <f>E67/2500</f>
-        <v>0</v>
-      </c>
-      <c r="G67" s="145"/>
-      <c r="H67" s="146" t="s">
+      <c r="C69" s="144" t="s">
         <v>194</v>
       </c>
-      <c r="I67" s="146" t="s">
-        <v>195</v>
-      </c>
-      <c r="J67" s="144"/>
-      <c r="K67" s="145">
-        <f>J67/300</f>
-        <v>0</v>
-      </c>
-      <c r="L67" s="144" t="s">
-        <v>193</v>
-      </c>
-      <c r="M67" s="144"/>
-      <c r="N67" s="144"/>
-      <c r="O67" s="147" t="s">
-        <v>196</v>
-      </c>
-      <c r="P67" s="144"/>
-      <c r="Q67" s="144"/>
-      <c r="R67" s="148"/>
-      <c r="S67" s="149" t="s">
-        <v>197</v>
-      </c>
-      <c r="T67" s="149"/>
-      <c r="U67" s="144">
-        <f t="shared" ref="U67:U130" si="0">R67*0.935</f>
-        <v>0</v>
-      </c>
-      <c r="V67" s="144">
-        <f t="shared" ref="V67:V130" si="1">U67/215</f>
-        <v>0</v>
-      </c>
-      <c r="W67" s="146">
-        <v>202</v>
-      </c>
-      <c r="X67" s="144">
-        <f>SUM(U67:U76)</f>
-        <v>0</v>
-      </c>
-      <c r="Y67" s="145">
-        <f>X67/2150</f>
-        <v>0</v>
-      </c>
-      <c r="Z67" s="144">
-        <v>170</v>
-      </c>
-      <c r="AA67" s="150">
-        <v>168</v>
-      </c>
-      <c r="AB67" s="145">
-        <f>67/Z67</f>
-        <v>0.394117647058824</v>
-      </c>
-      <c r="AC67" s="144">
-        <v>20</v>
-      </c>
-      <c r="AD67" s="144">
-        <v>0</v>
-      </c>
-      <c r="AE67" s="151" t="s">
-        <v>198</v>
-      </c>
-      <c r="AF67" s="152"/>
-    </row>
-    <row r="68" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
-      <c r="A68" s="144"/>
-      <c r="B68" s="144"/>
-      <c r="C68" s="144"/>
-      <c r="D68" s="144"/>
-      <c r="E68" s="144"/>
-      <c r="F68" s="145"/>
-      <c r="G68" s="145"/>
-      <c r="H68" s="146"/>
-      <c r="I68" s="146"/>
-      <c r="J68" s="144"/>
-      <c r="K68" s="145"/>
-      <c r="L68" s="144"/>
-      <c r="M68" s="144"/>
-      <c r="N68" s="144"/>
-      <c r="O68" s="147" t="s">
-        <v>199</v>
-      </c>
-      <c r="P68" s="144"/>
-      <c r="Q68" s="144"/>
-      <c r="R68" s="148"/>
-      <c r="S68" s="149" t="s">
-        <v>200</v>
-      </c>
-      <c r="T68" s="149"/>
-      <c r="U68" s="144">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V68" s="144">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W68" s="146"/>
-      <c r="X68" s="144"/>
-      <c r="Y68" s="145"/>
-      <c r="Z68" s="144"/>
-      <c r="AA68" s="150"/>
-      <c r="AB68" s="145"/>
-      <c r="AC68" s="144"/>
-      <c r="AD68" s="144"/>
-      <c r="AE68" s="153"/>
-      <c r="AF68" s="152"/>
-    </row>
-    <row r="69" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
-      <c r="A69" s="144"/>
-      <c r="B69" s="144"/>
-      <c r="C69" s="144"/>
       <c r="D69" s="144"/>
       <c r="E69" s="144"/>
-      <c r="F69" s="145"/>
+      <c r="F69" s="145">
+        <f>E69/2500</f>
+        <v>0</v>
+      </c>
       <c r="G69" s="145"/>
-      <c r="H69" s="146"/>
-      <c r="I69" s="146"/>
+      <c r="H69" s="146" t="s">
+        <v>195</v>
+      </c>
+      <c r="I69" s="146" t="s">
+        <v>196</v>
+      </c>
       <c r="J69" s="144"/>
-      <c r="K69" s="145"/>
-      <c r="L69" s="144"/>
+      <c r="K69" s="145">
+        <f>J69/300</f>
+        <v>0</v>
+      </c>
+      <c r="L69" s="144" t="s">
+        <v>194</v>
+      </c>
       <c r="M69" s="144"/>
       <c r="N69" s="144"/>
       <c r="O69" s="147" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="P69" s="144"/>
       <c r="Q69" s="144"/>
       <c r="R69" s="148"/>
       <c r="S69" s="149" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="T69" s="149"/>
       <c r="U69" s="144">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="U69:U132" si="0">R69*0.935</f>
         <v>0</v>
       </c>
       <c r="V69" s="144">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W69" s="146"/>
-      <c r="X69" s="144"/>
-      <c r="Y69" s="145"/>
-      <c r="Z69" s="144"/>
-      <c r="AA69" s="150"/>
-      <c r="AB69" s="145"/>
-      <c r="AC69" s="144"/>
-      <c r="AD69" s="144"/>
-      <c r="AE69" s="154"/>
+        <f t="shared" ref="V69:V132" si="1">U69/215</f>
+        <v>0</v>
+      </c>
+      <c r="W69" s="146">
+        <v>202</v>
+      </c>
+      <c r="X69" s="144">
+        <f>SUM(U69:U78)</f>
+        <v>0</v>
+      </c>
+      <c r="Y69" s="145">
+        <f>X69/2150</f>
+        <v>0</v>
+      </c>
+      <c r="Z69" s="144">
+        <v>170</v>
+      </c>
+      <c r="AA69" s="150">
+        <v>168</v>
+      </c>
+      <c r="AB69" s="145">
+        <f>67/Z69</f>
+        <v>0.394117647058824</v>
+      </c>
+      <c r="AC69" s="144">
+        <v>20</v>
+      </c>
+      <c r="AD69" s="144">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="151" t="s">
+        <v>199</v>
+      </c>
       <c r="AF69" s="152"/>
     </row>
     <row r="70" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -6542,13 +6561,13 @@
       <c r="M70" s="144"/>
       <c r="N70" s="144"/>
       <c r="O70" s="147" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="P70" s="144"/>
       <c r="Q70" s="144"/>
       <c r="R70" s="148"/>
       <c r="S70" s="149" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="T70" s="149"/>
       <c r="U70" s="144">
@@ -6567,7 +6586,7 @@
       <c r="AB70" s="145"/>
       <c r="AC70" s="144"/>
       <c r="AD70" s="144"/>
-      <c r="AE70" s="151"/>
+      <c r="AE70" s="153"/>
       <c r="AF70" s="152"/>
     </row>
     <row r="71" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -6586,13 +6605,13 @@
       <c r="M71" s="144"/>
       <c r="N71" s="144"/>
       <c r="O71" s="147" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="P71" s="144"/>
       <c r="Q71" s="144"/>
       <c r="R71" s="148"/>
       <c r="S71" s="149" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="T71" s="149"/>
       <c r="U71" s="144">
@@ -6616,22 +6635,13 @@
     </row>
     <row r="72" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A72" s="144"/>
-      <c r="B72" s="144" t="s">
-        <v>207</v>
-      </c>
-      <c r="C72" s="144" t="s">
-        <v>193</v>
-      </c>
+      <c r="B72" s="144"/>
+      <c r="C72" s="144"/>
       <c r="D72" s="144"/>
       <c r="E72" s="144"/>
-      <c r="F72" s="145">
-        <f>E72/2500</f>
-        <v>0</v>
-      </c>
+      <c r="F72" s="145"/>
       <c r="G72" s="145"/>
-      <c r="H72" s="146" t="s">
-        <v>194</v>
-      </c>
+      <c r="H72" s="146"/>
       <c r="I72" s="146"/>
       <c r="J72" s="144"/>
       <c r="K72" s="145"/>
@@ -6639,13 +6649,13 @@
       <c r="M72" s="144"/>
       <c r="N72" s="144"/>
       <c r="O72" s="147" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="P72" s="144"/>
       <c r="Q72" s="144"/>
       <c r="R72" s="148"/>
       <c r="S72" s="149" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="T72" s="149"/>
       <c r="U72" s="144">
@@ -6664,9 +6674,7 @@
       <c r="AB72" s="145"/>
       <c r="AC72" s="144"/>
       <c r="AD72" s="144"/>
-      <c r="AE72" s="151" t="s">
-        <v>210</v>
-      </c>
+      <c r="AE72" s="151"/>
       <c r="AF72" s="152"/>
     </row>
     <row r="73" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -6685,13 +6693,13 @@
       <c r="M73" s="144"/>
       <c r="N73" s="144"/>
       <c r="O73" s="147" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="P73" s="144"/>
       <c r="Q73" s="144"/>
       <c r="R73" s="148"/>
       <c r="S73" s="149" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="T73" s="149"/>
       <c r="U73" s="144">
@@ -6710,18 +6718,27 @@
       <c r="AB73" s="145"/>
       <c r="AC73" s="144"/>
       <c r="AD73" s="144"/>
-      <c r="AE73" s="153"/>
+      <c r="AE73" s="154"/>
       <c r="AF73" s="152"/>
     </row>
     <row r="74" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A74" s="144"/>
-      <c r="B74" s="144"/>
-      <c r="C74" s="144"/>
+      <c r="B74" s="144" t="s">
+        <v>208</v>
+      </c>
+      <c r="C74" s="144" t="s">
+        <v>194</v>
+      </c>
       <c r="D74" s="144"/>
       <c r="E74" s="144"/>
-      <c r="F74" s="145"/>
+      <c r="F74" s="145">
+        <f>E74/2500</f>
+        <v>0</v>
+      </c>
       <c r="G74" s="145"/>
-      <c r="H74" s="146"/>
+      <c r="H74" s="146" t="s">
+        <v>195</v>
+      </c>
       <c r="I74" s="146"/>
       <c r="J74" s="144"/>
       <c r="K74" s="145"/>
@@ -6729,13 +6746,13 @@
       <c r="M74" s="144"/>
       <c r="N74" s="144"/>
       <c r="O74" s="147" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="P74" s="144"/>
       <c r="Q74" s="144"/>
       <c r="R74" s="148"/>
       <c r="S74" s="149" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="T74" s="149"/>
       <c r="U74" s="144">
@@ -6754,7 +6771,9 @@
       <c r="AB74" s="145"/>
       <c r="AC74" s="144"/>
       <c r="AD74" s="144"/>
-      <c r="AE74" s="154"/>
+      <c r="AE74" s="151" t="s">
+        <v>211</v>
+      </c>
       <c r="AF74" s="152"/>
     </row>
     <row r="75" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -6773,13 +6792,13 @@
       <c r="M75" s="144"/>
       <c r="N75" s="144"/>
       <c r="O75" s="147" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P75" s="144"/>
       <c r="Q75" s="144"/>
       <c r="R75" s="148"/>
       <c r="S75" s="149" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="T75" s="149"/>
       <c r="U75" s="144">
@@ -6798,7 +6817,7 @@
       <c r="AB75" s="145"/>
       <c r="AC75" s="144"/>
       <c r="AD75" s="144"/>
-      <c r="AE75" s="151"/>
+      <c r="AE75" s="153"/>
       <c r="AF75" s="152"/>
     </row>
     <row r="76" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -6817,13 +6836,13 @@
       <c r="M76" s="144"/>
       <c r="N76" s="144"/>
       <c r="O76" s="147" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="P76" s="144"/>
       <c r="Q76" s="144"/>
       <c r="R76" s="148"/>
       <c r="S76" s="149" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="T76" s="149"/>
       <c r="U76" s="144">
@@ -6846,46 +6865,28 @@
       <c r="AF76" s="152"/>
     </row>
     <row r="77" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
-      <c r="A77" s="144" t="s">
-        <v>219</v>
-      </c>
-      <c r="B77" s="144" t="s">
-        <v>220</v>
-      </c>
-      <c r="C77" s="144" t="s">
-        <v>193</v>
-      </c>
+      <c r="A77" s="144"/>
+      <c r="B77" s="144"/>
+      <c r="C77" s="144"/>
       <c r="D77" s="144"/>
       <c r="E77" s="144"/>
-      <c r="F77" s="145">
-        <f>E77/2500</f>
-        <v>0</v>
-      </c>
+      <c r="F77" s="145"/>
       <c r="G77" s="145"/>
-      <c r="H77" s="146" t="s">
-        <v>194</v>
-      </c>
-      <c r="I77" s="155" t="s">
-        <v>221</v>
-      </c>
+      <c r="H77" s="146"/>
+      <c r="I77" s="146"/>
       <c r="J77" s="144"/>
-      <c r="K77" s="145">
-        <f>J77/300</f>
-        <v>0</v>
-      </c>
-      <c r="L77" s="144" t="s">
-        <v>193</v>
-      </c>
+      <c r="K77" s="145"/>
+      <c r="L77" s="144"/>
       <c r="M77" s="144"/>
       <c r="N77" s="144"/>
       <c r="O77" s="147" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="P77" s="144"/>
       <c r="Q77" s="144"/>
       <c r="R77" s="148"/>
       <c r="S77" s="149" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="T77" s="149"/>
       <c r="U77" s="144">
@@ -6896,36 +6897,15 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W77" s="146">
-        <v>201</v>
-      </c>
-      <c r="X77" s="144">
-        <f>SUM(U77:U86)</f>
-        <v>0</v>
-      </c>
-      <c r="Y77" s="145">
-        <f>X77/2150</f>
-        <v>0</v>
-      </c>
-      <c r="Z77" s="144">
-        <v>170</v>
-      </c>
-      <c r="AA77" s="150">
-        <v>170</v>
-      </c>
-      <c r="AB77" s="145">
-        <f>77/Z77</f>
-        <v>0.452941176470588</v>
-      </c>
-      <c r="AC77" s="144">
-        <v>20</v>
-      </c>
-      <c r="AD77" s="144">
-        <v>0</v>
-      </c>
-      <c r="AE77" s="151" t="s">
-        <v>198</v>
-      </c>
+      <c r="W77" s="146"/>
+      <c r="X77" s="144"/>
+      <c r="Y77" s="145"/>
+      <c r="Z77" s="144"/>
+      <c r="AA77" s="150"/>
+      <c r="AB77" s="145"/>
+      <c r="AC77" s="144"/>
+      <c r="AD77" s="144"/>
+      <c r="AE77" s="151"/>
       <c r="AF77" s="152"/>
     </row>
     <row r="78" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -6937,20 +6917,20 @@
       <c r="F78" s="145"/>
       <c r="G78" s="145"/>
       <c r="H78" s="146"/>
-      <c r="I78" s="155"/>
+      <c r="I78" s="146"/>
       <c r="J78" s="144"/>
       <c r="K78" s="145"/>
       <c r="L78" s="144"/>
       <c r="M78" s="144"/>
       <c r="N78" s="144"/>
       <c r="O78" s="147" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="P78" s="144"/>
       <c r="Q78" s="144"/>
       <c r="R78" s="148"/>
       <c r="S78" s="149" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="T78" s="149"/>
       <c r="U78" s="144">
@@ -6969,32 +6949,50 @@
       <c r="AB78" s="145"/>
       <c r="AC78" s="144"/>
       <c r="AD78" s="144"/>
-      <c r="AE78" s="153"/>
+      <c r="AE78" s="154"/>
       <c r="AF78" s="152"/>
     </row>
     <row r="79" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
-      <c r="A79" s="144"/>
-      <c r="B79" s="144"/>
-      <c r="C79" s="144"/>
+      <c r="A79" s="144" t="s">
+        <v>220</v>
+      </c>
+      <c r="B79" s="144" t="s">
+        <v>221</v>
+      </c>
+      <c r="C79" s="144" t="s">
+        <v>194</v>
+      </c>
       <c r="D79" s="144"/>
       <c r="E79" s="144"/>
-      <c r="F79" s="145"/>
+      <c r="F79" s="145">
+        <f>E79/2500</f>
+        <v>0</v>
+      </c>
       <c r="G79" s="145"/>
-      <c r="H79" s="146"/>
-      <c r="I79" s="155"/>
+      <c r="H79" s="146" t="s">
+        <v>195</v>
+      </c>
+      <c r="I79" s="155" t="s">
+        <v>222</v>
+      </c>
       <c r="J79" s="144"/>
-      <c r="K79" s="145"/>
-      <c r="L79" s="144"/>
+      <c r="K79" s="145">
+        <f>J79/300</f>
+        <v>0</v>
+      </c>
+      <c r="L79" s="144" t="s">
+        <v>194</v>
+      </c>
       <c r="M79" s="144"/>
       <c r="N79" s="144"/>
       <c r="O79" s="147" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="P79" s="144"/>
       <c r="Q79" s="144"/>
       <c r="R79" s="148"/>
       <c r="S79" s="149" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="T79" s="149"/>
       <c r="U79" s="144">
@@ -7005,15 +7003,36 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W79" s="146"/>
-      <c r="X79" s="144"/>
-      <c r="Y79" s="145"/>
-      <c r="Z79" s="144"/>
-      <c r="AA79" s="150"/>
-      <c r="AB79" s="145"/>
-      <c r="AC79" s="144"/>
-      <c r="AD79" s="144"/>
-      <c r="AE79" s="154"/>
+      <c r="W79" s="146">
+        <v>201</v>
+      </c>
+      <c r="X79" s="144">
+        <f>SUM(U79:U88)</f>
+        <v>0</v>
+      </c>
+      <c r="Y79" s="145">
+        <f>X79/2150</f>
+        <v>0</v>
+      </c>
+      <c r="Z79" s="144">
+        <v>170</v>
+      </c>
+      <c r="AA79" s="150">
+        <v>170</v>
+      </c>
+      <c r="AB79" s="145">
+        <f>77/Z79</f>
+        <v>0.452941176470588</v>
+      </c>
+      <c r="AC79" s="144">
+        <v>20</v>
+      </c>
+      <c r="AD79" s="144">
+        <v>0</v>
+      </c>
+      <c r="AE79" s="151" t="s">
+        <v>199</v>
+      </c>
       <c r="AF79" s="152"/>
     </row>
     <row r="80" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -7032,13 +7051,13 @@
       <c r="M80" s="144"/>
       <c r="N80" s="144"/>
       <c r="O80" s="147" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="P80" s="144"/>
       <c r="Q80" s="144"/>
       <c r="R80" s="148"/>
       <c r="S80" s="149" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="T80" s="149"/>
       <c r="U80" s="144">
@@ -7057,7 +7076,7 @@
       <c r="AB80" s="145"/>
       <c r="AC80" s="144"/>
       <c r="AD80" s="144"/>
-      <c r="AE80" s="151"/>
+      <c r="AE80" s="153"/>
       <c r="AF80" s="152"/>
     </row>
     <row r="81" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -7076,13 +7095,13 @@
       <c r="M81" s="144"/>
       <c r="N81" s="144"/>
       <c r="O81" s="147" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="P81" s="144"/>
       <c r="Q81" s="144"/>
       <c r="R81" s="148"/>
       <c r="S81" s="149" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="T81" s="149"/>
       <c r="U81" s="144">
@@ -7106,22 +7125,13 @@
     </row>
     <row r="82" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A82" s="144"/>
-      <c r="B82" s="144" t="s">
-        <v>232</v>
-      </c>
-      <c r="C82" s="144" t="s">
-        <v>193</v>
-      </c>
+      <c r="B82" s="144"/>
+      <c r="C82" s="144"/>
       <c r="D82" s="144"/>
       <c r="E82" s="144"/>
-      <c r="F82" s="145">
-        <f>E82/2500</f>
-        <v>0</v>
-      </c>
+      <c r="F82" s="145"/>
       <c r="G82" s="145"/>
-      <c r="H82" s="146" t="s">
-        <v>194</v>
-      </c>
+      <c r="H82" s="146"/>
       <c r="I82" s="155"/>
       <c r="J82" s="144"/>
       <c r="K82" s="145"/>
@@ -7129,13 +7139,13 @@
       <c r="M82" s="144"/>
       <c r="N82" s="144"/>
       <c r="O82" s="147" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="P82" s="144"/>
       <c r="Q82" s="144"/>
       <c r="R82" s="148"/>
       <c r="S82" s="149" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="T82" s="149"/>
       <c r="U82" s="144">
@@ -7154,9 +7164,7 @@
       <c r="AB82" s="145"/>
       <c r="AC82" s="144"/>
       <c r="AD82" s="144"/>
-      <c r="AE82" s="151" t="s">
-        <v>210</v>
-      </c>
+      <c r="AE82" s="151"/>
       <c r="AF82" s="152"/>
     </row>
     <row r="83" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -7175,13 +7183,13 @@
       <c r="M83" s="144"/>
       <c r="N83" s="144"/>
       <c r="O83" s="147" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="P83" s="144"/>
       <c r="Q83" s="144"/>
       <c r="R83" s="148"/>
       <c r="S83" s="149" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="T83" s="149"/>
       <c r="U83" s="144">
@@ -7200,18 +7208,27 @@
       <c r="AB83" s="145"/>
       <c r="AC83" s="144"/>
       <c r="AD83" s="144"/>
-      <c r="AE83" s="153"/>
+      <c r="AE83" s="154"/>
       <c r="AF83" s="152"/>
     </row>
     <row r="84" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A84" s="144"/>
-      <c r="B84" s="144"/>
-      <c r="C84" s="144"/>
+      <c r="B84" s="144" t="s">
+        <v>233</v>
+      </c>
+      <c r="C84" s="144" t="s">
+        <v>194</v>
+      </c>
       <c r="D84" s="144"/>
       <c r="E84" s="144"/>
-      <c r="F84" s="145"/>
+      <c r="F84" s="145">
+        <f>E84/2500</f>
+        <v>0</v>
+      </c>
       <c r="G84" s="145"/>
-      <c r="H84" s="146"/>
+      <c r="H84" s="146" t="s">
+        <v>195</v>
+      </c>
       <c r="I84" s="155"/>
       <c r="J84" s="144"/>
       <c r="K84" s="145"/>
@@ -7219,13 +7236,13 @@
       <c r="M84" s="144"/>
       <c r="N84" s="144"/>
       <c r="O84" s="147" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="P84" s="144"/>
       <c r="Q84" s="144"/>
       <c r="R84" s="148"/>
       <c r="S84" s="149" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="T84" s="149"/>
       <c r="U84" s="144">
@@ -7244,7 +7261,9 @@
       <c r="AB84" s="145"/>
       <c r="AC84" s="144"/>
       <c r="AD84" s="144"/>
-      <c r="AE84" s="154"/>
+      <c r="AE84" s="151" t="s">
+        <v>211</v>
+      </c>
       <c r="AF84" s="152"/>
     </row>
     <row r="85" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -7263,13 +7282,13 @@
       <c r="M85" s="144"/>
       <c r="N85" s="144"/>
       <c r="O85" s="147" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="P85" s="144"/>
       <c r="Q85" s="144"/>
       <c r="R85" s="148"/>
       <c r="S85" s="149" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="T85" s="149"/>
       <c r="U85" s="144">
@@ -7288,7 +7307,7 @@
       <c r="AB85" s="145"/>
       <c r="AC85" s="144"/>
       <c r="AD85" s="144"/>
-      <c r="AE85" s="151"/>
+      <c r="AE85" s="153"/>
       <c r="AF85" s="152"/>
     </row>
     <row r="86" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -7307,13 +7326,13 @@
       <c r="M86" s="144"/>
       <c r="N86" s="144"/>
       <c r="O86" s="147" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="P86" s="144"/>
       <c r="Q86" s="144"/>
       <c r="R86" s="148"/>
       <c r="S86" s="149" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="T86" s="149"/>
       <c r="U86" s="144">
@@ -7336,46 +7355,28 @@
       <c r="AF86" s="152"/>
     </row>
     <row r="87" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
-      <c r="A87" s="144" t="s">
-        <v>243</v>
-      </c>
-      <c r="B87" s="144" t="s">
-        <v>244</v>
-      </c>
-      <c r="C87" s="144" t="s">
-        <v>193</v>
-      </c>
+      <c r="A87" s="144"/>
+      <c r="B87" s="144"/>
+      <c r="C87" s="144"/>
       <c r="D87" s="144"/>
       <c r="E87" s="144"/>
-      <c r="F87" s="145">
-        <f>E87/2500</f>
-        <v>0</v>
-      </c>
+      <c r="F87" s="145"/>
       <c r="G87" s="145"/>
-      <c r="H87" s="146" t="s">
-        <v>194</v>
-      </c>
-      <c r="I87" s="146" t="s">
-        <v>245</v>
-      </c>
+      <c r="H87" s="146"/>
+      <c r="I87" s="155"/>
       <c r="J87" s="144"/>
-      <c r="K87" s="145">
-        <f>J87/300</f>
-        <v>0</v>
-      </c>
-      <c r="L87" s="144" t="s">
-        <v>193</v>
-      </c>
+      <c r="K87" s="145"/>
+      <c r="L87" s="144"/>
       <c r="M87" s="144"/>
       <c r="N87" s="144"/>
-      <c r="O87" s="156" t="s">
-        <v>246</v>
+      <c r="O87" s="147" t="s">
+        <v>240</v>
       </c>
       <c r="P87" s="144"/>
       <c r="Q87" s="144"/>
       <c r="R87" s="148"/>
       <c r="S87" s="149" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="T87" s="149"/>
       <c r="U87" s="144">
@@ -7386,36 +7387,15 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W87" s="146">
-        <v>302</v>
-      </c>
-      <c r="X87" s="144">
-        <f>SUM(U87:U100)</f>
-        <v>0</v>
-      </c>
-      <c r="Y87" s="145">
-        <f>X87/2150</f>
-        <v>0</v>
-      </c>
-      <c r="Z87" s="144">
-        <v>154</v>
-      </c>
-      <c r="AA87" s="150">
-        <v>140</v>
-      </c>
-      <c r="AB87" s="145">
-        <f>87/Z87</f>
-        <v>0.564935064935065</v>
-      </c>
-      <c r="AC87" s="144">
-        <v>12</v>
-      </c>
-      <c r="AD87" s="144">
-        <v>8</v>
-      </c>
-      <c r="AE87" s="151" t="s">
-        <v>198</v>
-      </c>
+      <c r="W87" s="146"/>
+      <c r="X87" s="144"/>
+      <c r="Y87" s="145"/>
+      <c r="Z87" s="144"/>
+      <c r="AA87" s="150"/>
+      <c r="AB87" s="145"/>
+      <c r="AC87" s="144"/>
+      <c r="AD87" s="144"/>
+      <c r="AE87" s="151"/>
       <c r="AF87" s="152"/>
     </row>
     <row r="88" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -7427,20 +7407,20 @@
       <c r="F88" s="145"/>
       <c r="G88" s="145"/>
       <c r="H88" s="146"/>
-      <c r="I88" s="146"/>
+      <c r="I88" s="155"/>
       <c r="J88" s="144"/>
       <c r="K88" s="145"/>
       <c r="L88" s="144"/>
       <c r="M88" s="144"/>
       <c r="N88" s="144"/>
-      <c r="O88" s="156" t="s">
-        <v>248</v>
+      <c r="O88" s="147" t="s">
+        <v>242</v>
       </c>
       <c r="P88" s="144"/>
       <c r="Q88" s="144"/>
       <c r="R88" s="148"/>
       <c r="S88" s="149" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="T88" s="149"/>
       <c r="U88" s="144">
@@ -7459,32 +7439,50 @@
       <c r="AB88" s="145"/>
       <c r="AC88" s="144"/>
       <c r="AD88" s="144"/>
-      <c r="AE88" s="153"/>
+      <c r="AE88" s="154"/>
       <c r="AF88" s="152"/>
     </row>
     <row r="89" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
-      <c r="A89" s="144"/>
-      <c r="B89" s="144"/>
-      <c r="C89" s="144"/>
+      <c r="A89" s="144" t="s">
+        <v>244</v>
+      </c>
+      <c r="B89" s="144" t="s">
+        <v>245</v>
+      </c>
+      <c r="C89" s="144" t="s">
+        <v>194</v>
+      </c>
       <c r="D89" s="144"/>
       <c r="E89" s="144"/>
-      <c r="F89" s="145"/>
+      <c r="F89" s="145">
+        <f>E89/2500</f>
+        <v>0</v>
+      </c>
       <c r="G89" s="145"/>
-      <c r="H89" s="146"/>
-      <c r="I89" s="146"/>
+      <c r="H89" s="146" t="s">
+        <v>195</v>
+      </c>
+      <c r="I89" s="146" t="s">
+        <v>246</v>
+      </c>
       <c r="J89" s="144"/>
-      <c r="K89" s="145"/>
-      <c r="L89" s="144"/>
+      <c r="K89" s="145">
+        <f>J89/300</f>
+        <v>0</v>
+      </c>
+      <c r="L89" s="144" t="s">
+        <v>194</v>
+      </c>
       <c r="M89" s="144"/>
       <c r="N89" s="144"/>
       <c r="O89" s="156" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="P89" s="144"/>
       <c r="Q89" s="144"/>
       <c r="R89" s="148"/>
       <c r="S89" s="149" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="T89" s="149"/>
       <c r="U89" s="144">
@@ -7495,15 +7493,36 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W89" s="146"/>
-      <c r="X89" s="144"/>
-      <c r="Y89" s="145"/>
-      <c r="Z89" s="144"/>
-      <c r="AA89" s="150"/>
-      <c r="AB89" s="145"/>
-      <c r="AC89" s="144"/>
-      <c r="AD89" s="144"/>
-      <c r="AE89" s="153"/>
+      <c r="W89" s="146">
+        <v>302</v>
+      </c>
+      <c r="X89" s="144">
+        <f>SUM(U89:U102)</f>
+        <v>0</v>
+      </c>
+      <c r="Y89" s="145">
+        <f>X89/2150</f>
+        <v>0</v>
+      </c>
+      <c r="Z89" s="144">
+        <v>154</v>
+      </c>
+      <c r="AA89" s="150">
+        <v>140</v>
+      </c>
+      <c r="AB89" s="145">
+        <f>87/Z89</f>
+        <v>0.564935064935065</v>
+      </c>
+      <c r="AC89" s="144">
+        <v>12</v>
+      </c>
+      <c r="AD89" s="144">
+        <v>8</v>
+      </c>
+      <c r="AE89" s="151" t="s">
+        <v>199</v>
+      </c>
       <c r="AF89" s="152"/>
     </row>
     <row r="90" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -7522,13 +7541,13 @@
       <c r="M90" s="144"/>
       <c r="N90" s="144"/>
       <c r="O90" s="156" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="P90" s="144"/>
       <c r="Q90" s="144"/>
       <c r="R90" s="148"/>
       <c r="S90" s="149" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="T90" s="149"/>
       <c r="U90" s="144">
@@ -7547,7 +7566,7 @@
       <c r="AB90" s="145"/>
       <c r="AC90" s="144"/>
       <c r="AD90" s="144"/>
-      <c r="AE90" s="154"/>
+      <c r="AE90" s="153"/>
       <c r="AF90" s="152"/>
     </row>
     <row r="91" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -7566,13 +7585,13 @@
       <c r="M91" s="144"/>
       <c r="N91" s="144"/>
       <c r="O91" s="156" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="P91" s="144"/>
       <c r="Q91" s="144"/>
       <c r="R91" s="148"/>
       <c r="S91" s="149" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="T91" s="149"/>
       <c r="U91" s="144">
@@ -7591,7 +7610,7 @@
       <c r="AB91" s="145"/>
       <c r="AC91" s="144"/>
       <c r="AD91" s="144"/>
-      <c r="AE91" s="151"/>
+      <c r="AE91" s="153"/>
       <c r="AF91" s="152"/>
     </row>
     <row r="92" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -7610,13 +7629,13 @@
       <c r="M92" s="144"/>
       <c r="N92" s="144"/>
       <c r="O92" s="156" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="P92" s="144"/>
       <c r="Q92" s="144"/>
       <c r="R92" s="148"/>
       <c r="S92" s="149" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="T92" s="149"/>
       <c r="U92" s="144">
@@ -7635,7 +7654,7 @@
       <c r="AB92" s="145"/>
       <c r="AC92" s="144"/>
       <c r="AD92" s="144"/>
-      <c r="AE92" s="153"/>
+      <c r="AE92" s="154"/>
       <c r="AF92" s="152"/>
     </row>
     <row r="93" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -7654,13 +7673,13 @@
       <c r="M93" s="144"/>
       <c r="N93" s="144"/>
       <c r="O93" s="156" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P93" s="144"/>
       <c r="Q93" s="144"/>
       <c r="R93" s="148"/>
       <c r="S93" s="149" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="T93" s="149"/>
       <c r="U93" s="144">
@@ -7679,27 +7698,18 @@
       <c r="AB93" s="145"/>
       <c r="AC93" s="144"/>
       <c r="AD93" s="144"/>
-      <c r="AE93" s="154"/>
+      <c r="AE93" s="151"/>
       <c r="AF93" s="152"/>
     </row>
     <row r="94" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A94" s="144"/>
-      <c r="B94" s="144" t="s">
-        <v>260</v>
-      </c>
-      <c r="C94" s="144" t="s">
-        <v>193</v>
-      </c>
+      <c r="B94" s="144"/>
+      <c r="C94" s="144"/>
       <c r="D94" s="144"/>
       <c r="E94" s="144"/>
-      <c r="F94" s="145">
-        <f>E94/2500</f>
-        <v>0</v>
-      </c>
+      <c r="F94" s="145"/>
       <c r="G94" s="145"/>
-      <c r="H94" s="146" t="s">
-        <v>194</v>
-      </c>
+      <c r="H94" s="146"/>
       <c r="I94" s="146"/>
       <c r="J94" s="144"/>
       <c r="K94" s="145"/>
@@ -7707,13 +7717,13 @@
       <c r="M94" s="144"/>
       <c r="N94" s="144"/>
       <c r="O94" s="156" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="P94" s="144"/>
       <c r="Q94" s="144"/>
       <c r="R94" s="148"/>
       <c r="S94" s="149" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="T94" s="149"/>
       <c r="U94" s="144">
@@ -7732,9 +7742,7 @@
       <c r="AB94" s="145"/>
       <c r="AC94" s="144"/>
       <c r="AD94" s="144"/>
-      <c r="AE94" s="151" t="s">
-        <v>210</v>
-      </c>
+      <c r="AE94" s="153"/>
       <c r="AF94" s="152"/>
     </row>
     <row r="95" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -7753,13 +7761,13 @@
       <c r="M95" s="144"/>
       <c r="N95" s="144"/>
       <c r="O95" s="156" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="P95" s="144"/>
       <c r="Q95" s="144"/>
       <c r="R95" s="148"/>
       <c r="S95" s="149" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="T95" s="149"/>
       <c r="U95" s="144">
@@ -7778,18 +7786,27 @@
       <c r="AB95" s="145"/>
       <c r="AC95" s="144"/>
       <c r="AD95" s="144"/>
-      <c r="AE95" s="153"/>
+      <c r="AE95" s="154"/>
       <c r="AF95" s="152"/>
     </row>
     <row r="96" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A96" s="144"/>
-      <c r="B96" s="144"/>
-      <c r="C96" s="144"/>
+      <c r="B96" s="144" t="s">
+        <v>261</v>
+      </c>
+      <c r="C96" s="144" t="s">
+        <v>194</v>
+      </c>
       <c r="D96" s="144"/>
       <c r="E96" s="144"/>
-      <c r="F96" s="145"/>
+      <c r="F96" s="145">
+        <f>E96/2500</f>
+        <v>0</v>
+      </c>
       <c r="G96" s="145"/>
-      <c r="H96" s="146"/>
+      <c r="H96" s="146" t="s">
+        <v>195</v>
+      </c>
       <c r="I96" s="146"/>
       <c r="J96" s="144"/>
       <c r="K96" s="145"/>
@@ -7797,13 +7814,13 @@
       <c r="M96" s="144"/>
       <c r="N96" s="144"/>
       <c r="O96" s="156" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="P96" s="144"/>
       <c r="Q96" s="144"/>
       <c r="R96" s="148"/>
       <c r="S96" s="149" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="T96" s="149"/>
       <c r="U96" s="144">
@@ -7822,7 +7839,9 @@
       <c r="AB96" s="145"/>
       <c r="AC96" s="144"/>
       <c r="AD96" s="144"/>
-      <c r="AE96" s="153"/>
+      <c r="AE96" s="151" t="s">
+        <v>211</v>
+      </c>
       <c r="AF96" s="152"/>
     </row>
     <row r="97" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -7841,13 +7860,13 @@
       <c r="M97" s="144"/>
       <c r="N97" s="144"/>
       <c r="O97" s="156" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="P97" s="144"/>
       <c r="Q97" s="144"/>
       <c r="R97" s="148"/>
       <c r="S97" s="149" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="T97" s="149"/>
       <c r="U97" s="144">
@@ -7866,7 +7885,7 @@
       <c r="AB97" s="145"/>
       <c r="AC97" s="144"/>
       <c r="AD97" s="144"/>
-      <c r="AE97" s="154"/>
+      <c r="AE97" s="153"/>
       <c r="AF97" s="152"/>
     </row>
     <row r="98" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -7885,13 +7904,13 @@
       <c r="M98" s="144"/>
       <c r="N98" s="144"/>
       <c r="O98" s="156" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="P98" s="144"/>
       <c r="Q98" s="144"/>
       <c r="R98" s="148"/>
       <c r="S98" s="149" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="T98" s="149"/>
       <c r="U98" s="144">
@@ -7910,7 +7929,7 @@
       <c r="AB98" s="145"/>
       <c r="AC98" s="144"/>
       <c r="AD98" s="144"/>
-      <c r="AE98" s="151"/>
+      <c r="AE98" s="153"/>
       <c r="AF98" s="152"/>
     </row>
     <row r="99" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -7929,13 +7948,13 @@
       <c r="M99" s="144"/>
       <c r="N99" s="144"/>
       <c r="O99" s="156" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="P99" s="144"/>
       <c r="Q99" s="144"/>
       <c r="R99" s="148"/>
       <c r="S99" s="149" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="T99" s="149"/>
       <c r="U99" s="144">
@@ -7954,7 +7973,7 @@
       <c r="AB99" s="145"/>
       <c r="AC99" s="144"/>
       <c r="AD99" s="144"/>
-      <c r="AE99" s="153"/>
+      <c r="AE99" s="154"/>
       <c r="AF99" s="152"/>
     </row>
     <row r="100" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -7973,13 +7992,13 @@
       <c r="M100" s="144"/>
       <c r="N100" s="144"/>
       <c r="O100" s="156" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="P100" s="144"/>
       <c r="Q100" s="144"/>
       <c r="R100" s="148"/>
       <c r="S100" s="149" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="T100" s="149"/>
       <c r="U100" s="144">
@@ -7998,50 +8017,32 @@
       <c r="AB100" s="145"/>
       <c r="AC100" s="144"/>
       <c r="AD100" s="144"/>
-      <c r="AE100" s="154"/>
+      <c r="AE100" s="151"/>
       <c r="AF100" s="152"/>
     </row>
     <row r="101" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
-      <c r="A101" s="144" t="s">
-        <v>275</v>
-      </c>
-      <c r="B101" s="144" t="s">
-        <v>276</v>
-      </c>
-      <c r="C101" s="144" t="s">
-        <v>193</v>
-      </c>
+      <c r="A101" s="144"/>
+      <c r="B101" s="144"/>
+      <c r="C101" s="144"/>
       <c r="D101" s="144"/>
       <c r="E101" s="144"/>
-      <c r="F101" s="145">
-        <f>E101/2500</f>
-        <v>0</v>
-      </c>
+      <c r="F101" s="145"/>
       <c r="G101" s="145"/>
-      <c r="H101" s="146" t="s">
-        <v>194</v>
-      </c>
-      <c r="I101" s="146" t="s">
-        <v>277</v>
-      </c>
+      <c r="H101" s="146"/>
+      <c r="I101" s="146"/>
       <c r="J101" s="144"/>
-      <c r="K101" s="145">
-        <f>J101/300</f>
-        <v>0</v>
-      </c>
-      <c r="L101" s="144" t="s">
-        <v>193</v>
-      </c>
+      <c r="K101" s="145"/>
+      <c r="L101" s="144"/>
       <c r="M101" s="144"/>
       <c r="N101" s="144"/>
       <c r="O101" s="156" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="P101" s="144"/>
       <c r="Q101" s="144"/>
       <c r="R101" s="148"/>
       <c r="S101" s="149" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="T101" s="149"/>
       <c r="U101" s="144">
@@ -8052,36 +8053,15 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W101" s="146">
-        <v>301</v>
-      </c>
-      <c r="X101" s="144">
-        <f>SUM(U101:U114)</f>
-        <v>0</v>
-      </c>
-      <c r="Y101" s="145">
-        <f>X101/2150</f>
-        <v>0</v>
-      </c>
-      <c r="Z101" s="144">
-        <v>154</v>
-      </c>
-      <c r="AA101" s="150">
-        <v>152</v>
-      </c>
-      <c r="AB101" s="145">
-        <f>101/Z101</f>
-        <v>0.655844155844156</v>
-      </c>
-      <c r="AC101" s="144">
-        <v>12</v>
-      </c>
-      <c r="AD101" s="144">
-        <v>8</v>
-      </c>
-      <c r="AE101" s="151" t="s">
-        <v>198</v>
-      </c>
+      <c r="W101" s="146"/>
+      <c r="X101" s="144"/>
+      <c r="Y101" s="145"/>
+      <c r="Z101" s="144"/>
+      <c r="AA101" s="150"/>
+      <c r="AB101" s="145"/>
+      <c r="AC101" s="144"/>
+      <c r="AD101" s="144"/>
+      <c r="AE101" s="153"/>
       <c r="AF101" s="152"/>
     </row>
     <row r="102" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -8099,14 +8079,14 @@
       <c r="L102" s="144"/>
       <c r="M102" s="144"/>
       <c r="N102" s="144"/>
-      <c r="O102" s="147" t="s">
-        <v>280</v>
+      <c r="O102" s="156" t="s">
+        <v>274</v>
       </c>
       <c r="P102" s="144"/>
       <c r="Q102" s="144"/>
       <c r="R102" s="148"/>
       <c r="S102" s="149" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="T102" s="149"/>
       <c r="U102" s="144">
@@ -8125,32 +8105,50 @@
       <c r="AB102" s="145"/>
       <c r="AC102" s="144"/>
       <c r="AD102" s="144"/>
-      <c r="AE102" s="153"/>
+      <c r="AE102" s="154"/>
       <c r="AF102" s="152"/>
     </row>
     <row r="103" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
-      <c r="A103" s="144"/>
-      <c r="B103" s="144"/>
-      <c r="C103" s="144"/>
+      <c r="A103" s="144" t="s">
+        <v>276</v>
+      </c>
+      <c r="B103" s="144" t="s">
+        <v>277</v>
+      </c>
+      <c r="C103" s="144" t="s">
+        <v>194</v>
+      </c>
       <c r="D103" s="144"/>
       <c r="E103" s="144"/>
-      <c r="F103" s="145"/>
+      <c r="F103" s="145">
+        <f>E103/2500</f>
+        <v>0</v>
+      </c>
       <c r="G103" s="145"/>
-      <c r="H103" s="146"/>
-      <c r="I103" s="146"/>
+      <c r="H103" s="146" t="s">
+        <v>195</v>
+      </c>
+      <c r="I103" s="146" t="s">
+        <v>278</v>
+      </c>
       <c r="J103" s="144"/>
-      <c r="K103" s="145"/>
-      <c r="L103" s="144"/>
+      <c r="K103" s="145">
+        <f>J103/300</f>
+        <v>0</v>
+      </c>
+      <c r="L103" s="144" t="s">
+        <v>194</v>
+      </c>
       <c r="M103" s="144"/>
       <c r="N103" s="144"/>
       <c r="O103" s="156" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="P103" s="144"/>
       <c r="Q103" s="144"/>
       <c r="R103" s="148"/>
       <c r="S103" s="149" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="T103" s="149"/>
       <c r="U103" s="144">
@@ -8161,15 +8159,36 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W103" s="146"/>
-      <c r="X103" s="144"/>
-      <c r="Y103" s="145"/>
-      <c r="Z103" s="144"/>
-      <c r="AA103" s="150"/>
-      <c r="AB103" s="145"/>
-      <c r="AC103" s="144"/>
-      <c r="AD103" s="144"/>
-      <c r="AE103" s="153"/>
+      <c r="W103" s="146">
+        <v>301</v>
+      </c>
+      <c r="X103" s="144">
+        <f>SUM(U103:U116)</f>
+        <v>0</v>
+      </c>
+      <c r="Y103" s="145">
+        <f>X103/2150</f>
+        <v>0</v>
+      </c>
+      <c r="Z103" s="144">
+        <v>154</v>
+      </c>
+      <c r="AA103" s="150">
+        <v>152</v>
+      </c>
+      <c r="AB103" s="145">
+        <f>101/Z103</f>
+        <v>0.655844155844156</v>
+      </c>
+      <c r="AC103" s="144">
+        <v>12</v>
+      </c>
+      <c r="AD103" s="144">
+        <v>8</v>
+      </c>
+      <c r="AE103" s="151" t="s">
+        <v>199</v>
+      </c>
       <c r="AF103" s="152"/>
     </row>
     <row r="104" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -8188,13 +8207,13 @@
       <c r="M104" s="144"/>
       <c r="N104" s="144"/>
       <c r="O104" s="147" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="P104" s="144"/>
       <c r="Q104" s="144"/>
       <c r="R104" s="148"/>
       <c r="S104" s="149" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="T104" s="149"/>
       <c r="U104" s="144">
@@ -8213,7 +8232,7 @@
       <c r="AB104" s="145"/>
       <c r="AC104" s="144"/>
       <c r="AD104" s="144"/>
-      <c r="AE104" s="154"/>
+      <c r="AE104" s="153"/>
       <c r="AF104" s="152"/>
     </row>
     <row r="105" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -8232,13 +8251,13 @@
       <c r="M105" s="144"/>
       <c r="N105" s="144"/>
       <c r="O105" s="156" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="P105" s="144"/>
       <c r="Q105" s="144"/>
       <c r="R105" s="148"/>
       <c r="S105" s="149" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="T105" s="149"/>
       <c r="U105" s="144">
@@ -8257,7 +8276,7 @@
       <c r="AB105" s="145"/>
       <c r="AC105" s="144"/>
       <c r="AD105" s="144"/>
-      <c r="AE105" s="151"/>
+      <c r="AE105" s="153"/>
       <c r="AF105" s="152"/>
     </row>
     <row r="106" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -8276,13 +8295,13 @@
       <c r="M106" s="144"/>
       <c r="N106" s="144"/>
       <c r="O106" s="147" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="P106" s="144"/>
       <c r="Q106" s="144"/>
       <c r="R106" s="148"/>
       <c r="S106" s="149" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="T106" s="149"/>
       <c r="U106" s="144">
@@ -8301,7 +8320,7 @@
       <c r="AB106" s="145"/>
       <c r="AC106" s="144"/>
       <c r="AD106" s="144"/>
-      <c r="AE106" s="153"/>
+      <c r="AE106" s="154"/>
       <c r="AF106" s="152"/>
     </row>
     <row r="107" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -8320,13 +8339,13 @@
       <c r="M107" s="144"/>
       <c r="N107" s="144"/>
       <c r="O107" s="156" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="P107" s="144"/>
       <c r="Q107" s="144"/>
       <c r="R107" s="148"/>
       <c r="S107" s="149" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="T107" s="149"/>
       <c r="U107" s="144">
@@ -8345,27 +8364,18 @@
       <c r="AB107" s="145"/>
       <c r="AC107" s="144"/>
       <c r="AD107" s="144"/>
-      <c r="AE107" s="154"/>
+      <c r="AE107" s="151"/>
       <c r="AF107" s="152"/>
     </row>
     <row r="108" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A108" s="144"/>
-      <c r="B108" s="144" t="s">
-        <v>292</v>
-      </c>
-      <c r="C108" s="144" t="s">
-        <v>193</v>
-      </c>
+      <c r="B108" s="144"/>
+      <c r="C108" s="144"/>
       <c r="D108" s="144"/>
       <c r="E108" s="144"/>
-      <c r="F108" s="145">
-        <f>E108/2500</f>
-        <v>0</v>
-      </c>
+      <c r="F108" s="145"/>
       <c r="G108" s="145"/>
-      <c r="H108" s="146" t="s">
-        <v>194</v>
-      </c>
+      <c r="H108" s="146"/>
       <c r="I108" s="146"/>
       <c r="J108" s="144"/>
       <c r="K108" s="145"/>
@@ -8373,13 +8383,13 @@
       <c r="M108" s="144"/>
       <c r="N108" s="144"/>
       <c r="O108" s="147" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="P108" s="144"/>
       <c r="Q108" s="144"/>
       <c r="R108" s="148"/>
       <c r="S108" s="149" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="T108" s="149"/>
       <c r="U108" s="144">
@@ -8398,9 +8408,7 @@
       <c r="AB108" s="145"/>
       <c r="AC108" s="144"/>
       <c r="AD108" s="144"/>
-      <c r="AE108" s="151" t="s">
-        <v>210</v>
-      </c>
+      <c r="AE108" s="153"/>
       <c r="AF108" s="152"/>
     </row>
     <row r="109" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -8418,14 +8426,14 @@
       <c r="L109" s="144"/>
       <c r="M109" s="144"/>
       <c r="N109" s="144"/>
-      <c r="O109" s="147" t="s">
-        <v>295</v>
+      <c r="O109" s="156" t="s">
+        <v>291</v>
       </c>
       <c r="P109" s="144"/>
       <c r="Q109" s="144"/>
       <c r="R109" s="148"/>
       <c r="S109" s="149" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="T109" s="149"/>
       <c r="U109" s="144">
@@ -8444,18 +8452,27 @@
       <c r="AB109" s="145"/>
       <c r="AC109" s="144"/>
       <c r="AD109" s="144"/>
-      <c r="AE109" s="153"/>
+      <c r="AE109" s="154"/>
       <c r="AF109" s="152"/>
     </row>
     <row r="110" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A110" s="144"/>
-      <c r="B110" s="144"/>
-      <c r="C110" s="144"/>
+      <c r="B110" s="144" t="s">
+        <v>293</v>
+      </c>
+      <c r="C110" s="144" t="s">
+        <v>194</v>
+      </c>
       <c r="D110" s="144"/>
       <c r="E110" s="144"/>
-      <c r="F110" s="145"/>
+      <c r="F110" s="145">
+        <f>E110/2500</f>
+        <v>0</v>
+      </c>
       <c r="G110" s="145"/>
-      <c r="H110" s="146"/>
+      <c r="H110" s="146" t="s">
+        <v>195</v>
+      </c>
       <c r="I110" s="146"/>
       <c r="J110" s="144"/>
       <c r="K110" s="145"/>
@@ -8463,13 +8480,13 @@
       <c r="M110" s="144"/>
       <c r="N110" s="144"/>
       <c r="O110" s="147" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="P110" s="144"/>
       <c r="Q110" s="144"/>
       <c r="R110" s="148"/>
       <c r="S110" s="149" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="T110" s="149"/>
       <c r="U110" s="144">
@@ -8488,7 +8505,9 @@
       <c r="AB110" s="145"/>
       <c r="AC110" s="144"/>
       <c r="AD110" s="144"/>
-      <c r="AE110" s="153"/>
+      <c r="AE110" s="151" t="s">
+        <v>211</v>
+      </c>
       <c r="AF110" s="152"/>
     </row>
     <row r="111" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -8507,13 +8526,13 @@
       <c r="M111" s="144"/>
       <c r="N111" s="144"/>
       <c r="O111" s="147" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="P111" s="144"/>
       <c r="Q111" s="144"/>
       <c r="R111" s="148"/>
       <c r="S111" s="149" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="T111" s="149"/>
       <c r="U111" s="144">
@@ -8532,7 +8551,7 @@
       <c r="AB111" s="145"/>
       <c r="AC111" s="144"/>
       <c r="AD111" s="144"/>
-      <c r="AE111" s="154"/>
+      <c r="AE111" s="153"/>
       <c r="AF111" s="152"/>
     </row>
     <row r="112" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -8551,13 +8570,13 @@
       <c r="M112" s="144"/>
       <c r="N112" s="144"/>
       <c r="O112" s="147" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="P112" s="144"/>
       <c r="Q112" s="144"/>
       <c r="R112" s="148"/>
       <c r="S112" s="149" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="T112" s="149"/>
       <c r="U112" s="144">
@@ -8576,7 +8595,7 @@
       <c r="AB112" s="145"/>
       <c r="AC112" s="144"/>
       <c r="AD112" s="144"/>
-      <c r="AE112" s="151"/>
+      <c r="AE112" s="153"/>
       <c r="AF112" s="152"/>
     </row>
     <row r="113" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -8595,13 +8614,13 @@
       <c r="M113" s="144"/>
       <c r="N113" s="144"/>
       <c r="O113" s="147" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="P113" s="144"/>
       <c r="Q113" s="144"/>
       <c r="R113" s="148"/>
       <c r="S113" s="149" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="T113" s="149"/>
       <c r="U113" s="144">
@@ -8620,7 +8639,7 @@
       <c r="AB113" s="145"/>
       <c r="AC113" s="144"/>
       <c r="AD113" s="144"/>
-      <c r="AE113" s="153"/>
+      <c r="AE113" s="154"/>
       <c r="AF113" s="152"/>
     </row>
     <row r="114" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -8639,13 +8658,13 @@
       <c r="M114" s="144"/>
       <c r="N114" s="144"/>
       <c r="O114" s="147" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="P114" s="144"/>
       <c r="Q114" s="144"/>
       <c r="R114" s="148"/>
       <c r="S114" s="149" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="T114" s="149"/>
       <c r="U114" s="144">
@@ -8664,50 +8683,32 @@
       <c r="AB114" s="145"/>
       <c r="AC114" s="144"/>
       <c r="AD114" s="144"/>
-      <c r="AE114" s="154"/>
+      <c r="AE114" s="151"/>
       <c r="AF114" s="152"/>
     </row>
     <row r="115" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
-      <c r="A115" s="144" t="s">
-        <v>307</v>
-      </c>
-      <c r="B115" s="144" t="s">
-        <v>308</v>
-      </c>
-      <c r="C115" s="144" t="s">
-        <v>193</v>
-      </c>
+      <c r="A115" s="144"/>
+      <c r="B115" s="144"/>
+      <c r="C115" s="144"/>
       <c r="D115" s="144"/>
       <c r="E115" s="144"/>
-      <c r="F115" s="145">
-        <f>E115/2500</f>
-        <v>0</v>
-      </c>
+      <c r="F115" s="145"/>
       <c r="G115" s="145"/>
-      <c r="H115" s="146" t="s">
-        <v>194</v>
-      </c>
-      <c r="I115" s="146" t="s">
-        <v>309</v>
-      </c>
+      <c r="H115" s="146"/>
+      <c r="I115" s="146"/>
       <c r="J115" s="144"/>
-      <c r="K115" s="145">
-        <f>J115/300</f>
-        <v>0</v>
-      </c>
-      <c r="L115" s="144" t="s">
-        <v>193</v>
-      </c>
+      <c r="K115" s="145"/>
+      <c r="L115" s="144"/>
       <c r="M115" s="144"/>
       <c r="N115" s="144"/>
       <c r="O115" s="147" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="P115" s="144"/>
       <c r="Q115" s="144"/>
       <c r="R115" s="148"/>
       <c r="S115" s="149" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="T115" s="149"/>
       <c r="U115" s="144">
@@ -8718,36 +8719,15 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W115" s="146">
-        <v>402</v>
-      </c>
-      <c r="X115" s="144">
-        <f>SUM(U115:U124)</f>
-        <v>0</v>
-      </c>
-      <c r="Y115" s="145">
-        <f>X115/2150</f>
-        <v>0</v>
-      </c>
-      <c r="Z115" s="144">
-        <v>170</v>
-      </c>
-      <c r="AA115" s="150">
-        <v>170</v>
-      </c>
-      <c r="AB115" s="145">
-        <f>115/Z115</f>
-        <v>0.676470588235294</v>
-      </c>
-      <c r="AC115" s="144">
-        <v>20</v>
-      </c>
-      <c r="AD115" s="144">
-        <v>0</v>
-      </c>
-      <c r="AE115" s="151" t="s">
-        <v>198</v>
-      </c>
+      <c r="W115" s="146"/>
+      <c r="X115" s="144"/>
+      <c r="Y115" s="145"/>
+      <c r="Z115" s="144"/>
+      <c r="AA115" s="150"/>
+      <c r="AB115" s="145"/>
+      <c r="AC115" s="144"/>
+      <c r="AD115" s="144"/>
+      <c r="AE115" s="153"/>
       <c r="AF115" s="152"/>
     </row>
     <row r="116" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -8766,13 +8746,13 @@
       <c r="M116" s="144"/>
       <c r="N116" s="144"/>
       <c r="O116" s="147" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="P116" s="144"/>
       <c r="Q116" s="144"/>
       <c r="R116" s="148"/>
       <c r="S116" s="149" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="T116" s="149"/>
       <c r="U116" s="144">
@@ -8791,32 +8771,50 @@
       <c r="AB116" s="145"/>
       <c r="AC116" s="144"/>
       <c r="AD116" s="144"/>
-      <c r="AE116" s="153"/>
+      <c r="AE116" s="154"/>
       <c r="AF116" s="152"/>
     </row>
     <row r="117" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
-      <c r="A117" s="144"/>
-      <c r="B117" s="144"/>
-      <c r="C117" s="144"/>
+      <c r="A117" s="144" t="s">
+        <v>308</v>
+      </c>
+      <c r="B117" s="144" t="s">
+        <v>309</v>
+      </c>
+      <c r="C117" s="144" t="s">
+        <v>194</v>
+      </c>
       <c r="D117" s="144"/>
       <c r="E117" s="144"/>
-      <c r="F117" s="145"/>
+      <c r="F117" s="145">
+        <f>E117/2500</f>
+        <v>0</v>
+      </c>
       <c r="G117" s="145"/>
-      <c r="H117" s="146"/>
-      <c r="I117" s="146"/>
+      <c r="H117" s="146" t="s">
+        <v>195</v>
+      </c>
+      <c r="I117" s="146" t="s">
+        <v>310</v>
+      </c>
       <c r="J117" s="144"/>
-      <c r="K117" s="145"/>
-      <c r="L117" s="144"/>
+      <c r="K117" s="145">
+        <f>J117/300</f>
+        <v>0</v>
+      </c>
+      <c r="L117" s="144" t="s">
+        <v>194</v>
+      </c>
       <c r="M117" s="144"/>
       <c r="N117" s="144"/>
       <c r="O117" s="147" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="P117" s="144"/>
       <c r="Q117" s="144"/>
       <c r="R117" s="148"/>
       <c r="S117" s="149" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="T117" s="149"/>
       <c r="U117" s="144">
@@ -8827,15 +8825,36 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W117" s="146"/>
-      <c r="X117" s="144"/>
-      <c r="Y117" s="145"/>
-      <c r="Z117" s="144"/>
-      <c r="AA117" s="150"/>
-      <c r="AB117" s="145"/>
-      <c r="AC117" s="144"/>
-      <c r="AD117" s="144"/>
-      <c r="AE117" s="154"/>
+      <c r="W117" s="146">
+        <v>402</v>
+      </c>
+      <c r="X117" s="144">
+        <f>SUM(U117:U126)</f>
+        <v>0</v>
+      </c>
+      <c r="Y117" s="145">
+        <f>X117/2150</f>
+        <v>0</v>
+      </c>
+      <c r="Z117" s="144">
+        <v>170</v>
+      </c>
+      <c r="AA117" s="150">
+        <v>170</v>
+      </c>
+      <c r="AB117" s="145">
+        <f>115/Z117</f>
+        <v>0.676470588235294</v>
+      </c>
+      <c r="AC117" s="144">
+        <v>20</v>
+      </c>
+      <c r="AD117" s="144">
+        <v>0</v>
+      </c>
+      <c r="AE117" s="151" t="s">
+        <v>199</v>
+      </c>
       <c r="AF117" s="152"/>
     </row>
     <row r="118" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -8854,13 +8873,13 @@
       <c r="M118" s="144"/>
       <c r="N118" s="144"/>
       <c r="O118" s="147" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="P118" s="144"/>
       <c r="Q118" s="144"/>
       <c r="R118" s="148"/>
       <c r="S118" s="149" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="T118" s="149"/>
       <c r="U118" s="144">
@@ -8879,7 +8898,7 @@
       <c r="AB118" s="145"/>
       <c r="AC118" s="144"/>
       <c r="AD118" s="144"/>
-      <c r="AE118" s="151"/>
+      <c r="AE118" s="153"/>
       <c r="AF118" s="152"/>
     </row>
     <row r="119" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -8898,13 +8917,13 @@
       <c r="M119" s="144"/>
       <c r="N119" s="144"/>
       <c r="O119" s="147" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="P119" s="144"/>
       <c r="Q119" s="144"/>
       <c r="R119" s="148"/>
       <c r="S119" s="149" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="T119" s="149"/>
       <c r="U119" s="144">
@@ -8928,22 +8947,13 @@
     </row>
     <row r="120" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A120" s="144"/>
-      <c r="B120" s="144" t="s">
-        <v>320</v>
-      </c>
-      <c r="C120" s="144" t="s">
-        <v>193</v>
-      </c>
+      <c r="B120" s="144"/>
+      <c r="C120" s="144"/>
       <c r="D120" s="144"/>
       <c r="E120" s="144"/>
-      <c r="F120" s="145">
-        <f>E120/2500</f>
-        <v>0</v>
-      </c>
+      <c r="F120" s="145"/>
       <c r="G120" s="145"/>
-      <c r="H120" s="146" t="s">
-        <v>194</v>
-      </c>
+      <c r="H120" s="146"/>
       <c r="I120" s="146"/>
       <c r="J120" s="144"/>
       <c r="K120" s="145"/>
@@ -8951,13 +8961,13 @@
       <c r="M120" s="144"/>
       <c r="N120" s="144"/>
       <c r="O120" s="147" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="P120" s="144"/>
       <c r="Q120" s="144"/>
       <c r="R120" s="148"/>
       <c r="S120" s="149" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="T120" s="149"/>
       <c r="U120" s="144">
@@ -8976,9 +8986,7 @@
       <c r="AB120" s="145"/>
       <c r="AC120" s="144"/>
       <c r="AD120" s="144"/>
-      <c r="AE120" s="151" t="s">
-        <v>210</v>
-      </c>
+      <c r="AE120" s="151"/>
       <c r="AF120" s="152"/>
     </row>
     <row r="121" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -8997,13 +9005,13 @@
       <c r="M121" s="144"/>
       <c r="N121" s="144"/>
       <c r="O121" s="147" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="P121" s="144"/>
       <c r="Q121" s="144"/>
       <c r="R121" s="148"/>
       <c r="S121" s="149" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="T121" s="149"/>
       <c r="U121" s="144">
@@ -9022,18 +9030,27 @@
       <c r="AB121" s="145"/>
       <c r="AC121" s="144"/>
       <c r="AD121" s="144"/>
-      <c r="AE121" s="153"/>
+      <c r="AE121" s="154"/>
       <c r="AF121" s="152"/>
     </row>
     <row r="122" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A122" s="144"/>
-      <c r="B122" s="144"/>
-      <c r="C122" s="144"/>
+      <c r="B122" s="144" t="s">
+        <v>321</v>
+      </c>
+      <c r="C122" s="144" t="s">
+        <v>194</v>
+      </c>
       <c r="D122" s="144"/>
       <c r="E122" s="144"/>
-      <c r="F122" s="145"/>
+      <c r="F122" s="145">
+        <f>E122/2500</f>
+        <v>0</v>
+      </c>
       <c r="G122" s="145"/>
-      <c r="H122" s="146"/>
+      <c r="H122" s="146" t="s">
+        <v>195</v>
+      </c>
       <c r="I122" s="146"/>
       <c r="J122" s="144"/>
       <c r="K122" s="145"/>
@@ -9041,13 +9058,13 @@
       <c r="M122" s="144"/>
       <c r="N122" s="144"/>
       <c r="O122" s="147" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="P122" s="144"/>
       <c r="Q122" s="144"/>
       <c r="R122" s="148"/>
       <c r="S122" s="149" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="T122" s="149"/>
       <c r="U122" s="144">
@@ -9066,7 +9083,9 @@
       <c r="AB122" s="145"/>
       <c r="AC122" s="144"/>
       <c r="AD122" s="144"/>
-      <c r="AE122" s="154"/>
+      <c r="AE122" s="151" t="s">
+        <v>211</v>
+      </c>
       <c r="AF122" s="152"/>
     </row>
     <row r="123" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -9085,13 +9104,13 @@
       <c r="M123" s="144"/>
       <c r="N123" s="144"/>
       <c r="O123" s="147" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="P123" s="144"/>
       <c r="Q123" s="144"/>
       <c r="R123" s="148"/>
       <c r="S123" s="149" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="T123" s="149"/>
       <c r="U123" s="144">
@@ -9110,7 +9129,7 @@
       <c r="AB123" s="145"/>
       <c r="AC123" s="144"/>
       <c r="AD123" s="144"/>
-      <c r="AE123" s="151"/>
+      <c r="AE123" s="153"/>
       <c r="AF123" s="152"/>
     </row>
     <row r="124" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -9129,13 +9148,13 @@
       <c r="M124" s="144"/>
       <c r="N124" s="144"/>
       <c r="O124" s="147" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="P124" s="144"/>
       <c r="Q124" s="144"/>
       <c r="R124" s="148"/>
       <c r="S124" s="149" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="T124" s="149"/>
       <c r="U124" s="144">
@@ -9158,46 +9177,28 @@
       <c r="AF124" s="152"/>
     </row>
     <row r="125" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
-      <c r="A125" s="144" t="s">
-        <v>331</v>
-      </c>
-      <c r="B125" s="144" t="s">
-        <v>332</v>
-      </c>
-      <c r="C125" s="144" t="s">
-        <v>193</v>
-      </c>
+      <c r="A125" s="144"/>
+      <c r="B125" s="144"/>
+      <c r="C125" s="144"/>
       <c r="D125" s="144"/>
       <c r="E125" s="144"/>
-      <c r="F125" s="145">
-        <f>E125/2500</f>
-        <v>0</v>
-      </c>
+      <c r="F125" s="145"/>
       <c r="G125" s="145"/>
-      <c r="H125" s="146" t="s">
-        <v>194</v>
-      </c>
-      <c r="I125" s="146" t="s">
-        <v>333</v>
-      </c>
+      <c r="H125" s="146"/>
+      <c r="I125" s="146"/>
       <c r="J125" s="144"/>
-      <c r="K125" s="145">
-        <f>J125/300</f>
-        <v>0</v>
-      </c>
-      <c r="L125" s="144" t="s">
-        <v>193</v>
-      </c>
+      <c r="K125" s="145"/>
+      <c r="L125" s="144"/>
       <c r="M125" s="144"/>
       <c r="N125" s="144"/>
       <c r="O125" s="147" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="P125" s="144"/>
       <c r="Q125" s="144"/>
       <c r="R125" s="148"/>
       <c r="S125" s="149" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="T125" s="149"/>
       <c r="U125" s="144">
@@ -9208,36 +9209,15 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W125" s="146">
-        <v>401</v>
-      </c>
-      <c r="X125" s="144">
-        <f>SUM(U125:U134)</f>
-        <v>0</v>
-      </c>
-      <c r="Y125" s="145">
-        <f>X125/2150</f>
-        <v>0</v>
-      </c>
-      <c r="Z125" s="144">
-        <v>170</v>
-      </c>
-      <c r="AA125" s="150">
-        <v>170</v>
-      </c>
-      <c r="AB125" s="145">
-        <f>125/Z125</f>
-        <v>0.735294117647059</v>
-      </c>
-      <c r="AC125" s="144">
-        <v>20</v>
-      </c>
-      <c r="AD125" s="144">
-        <v>0</v>
-      </c>
-      <c r="AE125" s="151" t="s">
-        <v>198</v>
-      </c>
+      <c r="W125" s="146"/>
+      <c r="X125" s="144"/>
+      <c r="Y125" s="145"/>
+      <c r="Z125" s="144"/>
+      <c r="AA125" s="150"/>
+      <c r="AB125" s="145"/>
+      <c r="AC125" s="144"/>
+      <c r="AD125" s="144"/>
+      <c r="AE125" s="151"/>
       <c r="AF125" s="152"/>
     </row>
     <row r="126" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -9256,13 +9236,13 @@
       <c r="M126" s="144"/>
       <c r="N126" s="144"/>
       <c r="O126" s="147" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="P126" s="144"/>
       <c r="Q126" s="144"/>
       <c r="R126" s="148"/>
       <c r="S126" s="149" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="T126" s="149"/>
       <c r="U126" s="144">
@@ -9281,32 +9261,50 @@
       <c r="AB126" s="145"/>
       <c r="AC126" s="144"/>
       <c r="AD126" s="144"/>
-      <c r="AE126" s="153"/>
+      <c r="AE126" s="154"/>
       <c r="AF126" s="152"/>
     </row>
     <row r="127" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
-      <c r="A127" s="144"/>
-      <c r="B127" s="144"/>
-      <c r="C127" s="144"/>
+      <c r="A127" s="144" t="s">
+        <v>332</v>
+      </c>
+      <c r="B127" s="144" t="s">
+        <v>333</v>
+      </c>
+      <c r="C127" s="144" t="s">
+        <v>194</v>
+      </c>
       <c r="D127" s="144"/>
       <c r="E127" s="144"/>
-      <c r="F127" s="145"/>
+      <c r="F127" s="145">
+        <f>E127/2500</f>
+        <v>0</v>
+      </c>
       <c r="G127" s="145"/>
-      <c r="H127" s="146"/>
-      <c r="I127" s="146"/>
+      <c r="H127" s="146" t="s">
+        <v>195</v>
+      </c>
+      <c r="I127" s="146" t="s">
+        <v>334</v>
+      </c>
       <c r="J127" s="144"/>
-      <c r="K127" s="145"/>
-      <c r="L127" s="144"/>
+      <c r="K127" s="145">
+        <f>J127/300</f>
+        <v>0</v>
+      </c>
+      <c r="L127" s="144" t="s">
+        <v>194</v>
+      </c>
       <c r="M127" s="144"/>
       <c r="N127" s="144"/>
       <c r="O127" s="147" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="P127" s="144"/>
       <c r="Q127" s="144"/>
       <c r="R127" s="148"/>
       <c r="S127" s="149" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="T127" s="149"/>
       <c r="U127" s="144">
@@ -9317,15 +9315,36 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W127" s="146"/>
-      <c r="X127" s="144"/>
-      <c r="Y127" s="145"/>
-      <c r="Z127" s="144"/>
-      <c r="AA127" s="150"/>
-      <c r="AB127" s="145"/>
-      <c r="AC127" s="144"/>
-      <c r="AD127" s="144"/>
-      <c r="AE127" s="154"/>
+      <c r="W127" s="146">
+        <v>401</v>
+      </c>
+      <c r="X127" s="144">
+        <f>SUM(U127:U136)</f>
+        <v>0</v>
+      </c>
+      <c r="Y127" s="145">
+        <f>X127/2150</f>
+        <v>0</v>
+      </c>
+      <c r="Z127" s="144">
+        <v>170</v>
+      </c>
+      <c r="AA127" s="150">
+        <v>170</v>
+      </c>
+      <c r="AB127" s="145">
+        <f>125/Z127</f>
+        <v>0.735294117647059</v>
+      </c>
+      <c r="AC127" s="144">
+        <v>20</v>
+      </c>
+      <c r="AD127" s="144">
+        <v>0</v>
+      </c>
+      <c r="AE127" s="151" t="s">
+        <v>199</v>
+      </c>
       <c r="AF127" s="152"/>
     </row>
     <row r="128" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -9344,13 +9363,13 @@
       <c r="M128" s="144"/>
       <c r="N128" s="144"/>
       <c r="O128" s="147" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="P128" s="144"/>
       <c r="Q128" s="144"/>
       <c r="R128" s="148"/>
       <c r="S128" s="149" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="T128" s="149"/>
       <c r="U128" s="144">
@@ -9369,7 +9388,7 @@
       <c r="AB128" s="145"/>
       <c r="AC128" s="144"/>
       <c r="AD128" s="144"/>
-      <c r="AE128" s="151"/>
+      <c r="AE128" s="153"/>
       <c r="AF128" s="152"/>
     </row>
     <row r="129" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -9388,13 +9407,13 @@
       <c r="M129" s="144"/>
       <c r="N129" s="144"/>
       <c r="O129" s="147" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="P129" s="144"/>
       <c r="Q129" s="144"/>
       <c r="R129" s="148"/>
       <c r="S129" s="149" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="T129" s="149"/>
       <c r="U129" s="144">
@@ -9418,22 +9437,13 @@
     </row>
     <row r="130" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A130" s="144"/>
-      <c r="B130" s="144" t="s">
-        <v>344</v>
-      </c>
-      <c r="C130" s="144" t="s">
-        <v>193</v>
-      </c>
+      <c r="B130" s="144"/>
+      <c r="C130" s="144"/>
       <c r="D130" s="144"/>
       <c r="E130" s="144"/>
-      <c r="F130" s="145">
-        <f>E130/2500</f>
-        <v>0</v>
-      </c>
+      <c r="F130" s="145"/>
       <c r="G130" s="145"/>
-      <c r="H130" s="146" t="s">
-        <v>194</v>
-      </c>
+      <c r="H130" s="146"/>
       <c r="I130" s="146"/>
       <c r="J130" s="144"/>
       <c r="K130" s="145"/>
@@ -9441,13 +9451,13 @@
       <c r="M130" s="144"/>
       <c r="N130" s="144"/>
       <c r="O130" s="147" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="P130" s="144"/>
       <c r="Q130" s="144"/>
       <c r="R130" s="148"/>
       <c r="S130" s="149" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="T130" s="149"/>
       <c r="U130" s="144">
@@ -9466,9 +9476,7 @@
       <c r="AB130" s="145"/>
       <c r="AC130" s="144"/>
       <c r="AD130" s="144"/>
-      <c r="AE130" s="151" t="s">
-        <v>210</v>
-      </c>
+      <c r="AE130" s="151"/>
       <c r="AF130" s="152"/>
     </row>
     <row r="131" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -9487,21 +9495,21 @@
       <c r="M131" s="144"/>
       <c r="N131" s="144"/>
       <c r="O131" s="147" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="P131" s="144"/>
       <c r="Q131" s="144"/>
       <c r="R131" s="148"/>
       <c r="S131" s="149" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="T131" s="149"/>
       <c r="U131" s="144">
-        <f t="shared" ref="U131:U134" si="2">R131*0.935</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="V131" s="144">
-        <f t="shared" ref="V131:V134" si="3">U131/215</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="W131" s="146"/>
@@ -9512,18 +9520,27 @@
       <c r="AB131" s="145"/>
       <c r="AC131" s="144"/>
       <c r="AD131" s="144"/>
-      <c r="AE131" s="153"/>
+      <c r="AE131" s="154"/>
       <c r="AF131" s="152"/>
     </row>
     <row r="132" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A132" s="144"/>
-      <c r="B132" s="144"/>
-      <c r="C132" s="144"/>
+      <c r="B132" s="144" t="s">
+        <v>345</v>
+      </c>
+      <c r="C132" s="144" t="s">
+        <v>194</v>
+      </c>
       <c r="D132" s="144"/>
       <c r="E132" s="144"/>
-      <c r="F132" s="145"/>
+      <c r="F132" s="145">
+        <f>E132/2500</f>
+        <v>0</v>
+      </c>
       <c r="G132" s="145"/>
-      <c r="H132" s="146"/>
+      <c r="H132" s="146" t="s">
+        <v>195</v>
+      </c>
       <c r="I132" s="146"/>
       <c r="J132" s="144"/>
       <c r="K132" s="145"/>
@@ -9531,21 +9548,21 @@
       <c r="M132" s="144"/>
       <c r="N132" s="144"/>
       <c r="O132" s="147" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="P132" s="144"/>
       <c r="Q132" s="144"/>
       <c r="R132" s="148"/>
       <c r="S132" s="149" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="T132" s="149"/>
       <c r="U132" s="144">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="V132" s="144">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="W132" s="146"/>
@@ -9556,7 +9573,9 @@
       <c r="AB132" s="145"/>
       <c r="AC132" s="144"/>
       <c r="AD132" s="144"/>
-      <c r="AE132" s="154"/>
+      <c r="AE132" s="151" t="s">
+        <v>211</v>
+      </c>
       <c r="AF132" s="152"/>
     </row>
     <row r="133" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -9575,21 +9594,21 @@
       <c r="M133" s="144"/>
       <c r="N133" s="144"/>
       <c r="O133" s="147" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="P133" s="144"/>
       <c r="Q133" s="144"/>
       <c r="R133" s="148"/>
       <c r="S133" s="149" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="T133" s="149"/>
       <c r="U133" s="144">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="U133:U136" si="2">R133*0.935</f>
         <v>0</v>
       </c>
       <c r="V133" s="144">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="V133:V136" si="3">U133/215</f>
         <v>0</v>
       </c>
       <c r="W133" s="146"/>
@@ -9600,7 +9619,7 @@
       <c r="AB133" s="145"/>
       <c r="AC133" s="144"/>
       <c r="AD133" s="144"/>
-      <c r="AE133" s="151"/>
+      <c r="AE133" s="153"/>
       <c r="AF133" s="152"/>
     </row>
     <row r="134" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -9619,13 +9638,13 @@
       <c r="M134" s="144"/>
       <c r="N134" s="144"/>
       <c r="O134" s="147" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="P134" s="144"/>
       <c r="Q134" s="144"/>
       <c r="R134" s="148"/>
       <c r="S134" s="149" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="T134" s="149"/>
       <c r="U134" s="144">
@@ -9647,59 +9666,51 @@
       <c r="AE134" s="154"/>
       <c r="AF134" s="152"/>
     </row>
-    <row r="135" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
-      <c r="A135" s="144" t="s">
-        <v>355</v>
-      </c>
-      <c r="B135" s="144" t="s">
-        <v>356</v>
-      </c>
-      <c r="C135" s="144" t="s">
-        <v>193</v>
-      </c>
+    <row r="135" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
+      <c r="A135" s="144"/>
+      <c r="B135" s="144"/>
+      <c r="C135" s="144"/>
       <c r="D135" s="144"/>
       <c r="E135" s="144"/>
-      <c r="F135" s="145">
-        <f>E135/2500</f>
-        <v>0</v>
-      </c>
+      <c r="F135" s="145"/>
       <c r="G135" s="145"/>
-      <c r="H135" s="146" t="s">
-        <v>194</v>
-      </c>
-      <c r="I135" s="146" t="s">
-        <v>357</v>
-      </c>
-      <c r="J135" s="157"/>
-      <c r="K135" s="145">
-        <f>J135/300</f>
-        <v>0</v>
-      </c>
-      <c r="L135" s="144" t="s">
-        <v>193</v>
-      </c>
+      <c r="H135" s="146"/>
+      <c r="I135" s="146"/>
+      <c r="J135" s="144"/>
+      <c r="K135" s="145"/>
+      <c r="L135" s="144"/>
       <c r="M135" s="144"/>
       <c r="N135" s="144"/>
-      <c r="O135" s="152"/>
-      <c r="P135" s="152"/>
-      <c r="Q135" s="152"/>
-      <c r="R135" s="152"/>
-      <c r="S135" s="152"/>
-      <c r="T135" s="152"/>
-      <c r="U135" s="152"/>
-      <c r="V135" s="152"/>
-      <c r="W135" s="152"/>
-      <c r="X135" s="152"/>
-      <c r="Y135" s="152"/>
-      <c r="Z135" s="152"/>
-      <c r="AA135" s="152"/>
-      <c r="AB135" s="152"/>
-      <c r="AC135" s="152"/>
-      <c r="AD135" s="152"/>
-      <c r="AE135" s="152"/>
+      <c r="O135" s="147" t="s">
+        <v>352</v>
+      </c>
+      <c r="P135" s="144"/>
+      <c r="Q135" s="144"/>
+      <c r="R135" s="148"/>
+      <c r="S135" s="149" t="s">
+        <v>353</v>
+      </c>
+      <c r="T135" s="149"/>
+      <c r="U135" s="144">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V135" s="144">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W135" s="146"/>
+      <c r="X135" s="144"/>
+      <c r="Y135" s="145"/>
+      <c r="Z135" s="144"/>
+      <c r="AA135" s="150"/>
+      <c r="AB135" s="145"/>
+      <c r="AC135" s="144"/>
+      <c r="AD135" s="144"/>
+      <c r="AE135" s="151"/>
       <c r="AF135" s="152"/>
     </row>
-    <row r="136" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
+    <row r="136" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A136" s="144"/>
       <c r="B136" s="144"/>
       <c r="C136" s="144"/>
@@ -9709,43 +9720,71 @@
       <c r="G136" s="145"/>
       <c r="H136" s="146"/>
       <c r="I136" s="146"/>
-      <c r="J136" s="157"/>
+      <c r="J136" s="144"/>
       <c r="K136" s="145"/>
       <c r="L136" s="144"/>
       <c r="M136" s="144"/>
       <c r="N136" s="144"/>
-      <c r="O136" s="152"/>
-      <c r="P136" s="152"/>
-      <c r="Q136" s="152"/>
-      <c r="R136" s="152"/>
-      <c r="S136" s="152"/>
-      <c r="T136" s="152"/>
-      <c r="U136" s="152"/>
-      <c r="V136" s="152"/>
-      <c r="W136" s="152"/>
-      <c r="X136" s="152"/>
-      <c r="Y136" s="152"/>
-      <c r="Z136" s="152"/>
-      <c r="AA136" s="152"/>
-      <c r="AB136" s="152"/>
-      <c r="AC136" s="152"/>
-      <c r="AD136" s="152"/>
-      <c r="AE136" s="152"/>
+      <c r="O136" s="147" t="s">
+        <v>354</v>
+      </c>
+      <c r="P136" s="144"/>
+      <c r="Q136" s="144"/>
+      <c r="R136" s="148"/>
+      <c r="S136" s="149" t="s">
+        <v>355</v>
+      </c>
+      <c r="T136" s="149"/>
+      <c r="U136" s="144">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V136" s="144">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="W136" s="146"/>
+      <c r="X136" s="144"/>
+      <c r="Y136" s="145"/>
+      <c r="Z136" s="144"/>
+      <c r="AA136" s="150"/>
+      <c r="AB136" s="145"/>
+      <c r="AC136" s="144"/>
+      <c r="AD136" s="144"/>
+      <c r="AE136" s="154"/>
       <c r="AF136" s="152"/>
     </row>
     <row r="137" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
-      <c r="A137" s="144"/>
-      <c r="B137" s="144"/>
-      <c r="C137" s="144"/>
+      <c r="A137" s="144" t="s">
+        <v>356</v>
+      </c>
+      <c r="B137" s="144" t="s">
+        <v>357</v>
+      </c>
+      <c r="C137" s="144" t="s">
+        <v>194</v>
+      </c>
       <c r="D137" s="144"/>
       <c r="E137" s="144"/>
-      <c r="F137" s="145"/>
+      <c r="F137" s="145">
+        <f>E137/2500</f>
+        <v>0</v>
+      </c>
       <c r="G137" s="145"/>
-      <c r="H137" s="146"/>
-      <c r="I137" s="146"/>
+      <c r="H137" s="146" t="s">
+        <v>195</v>
+      </c>
+      <c r="I137" s="146" t="s">
+        <v>358</v>
+      </c>
       <c r="J137" s="157"/>
-      <c r="K137" s="145"/>
-      <c r="L137" s="144"/>
+      <c r="K137" s="145">
+        <f>J137/300</f>
+        <v>0</v>
+      </c>
+      <c r="L137" s="144" t="s">
+        <v>194</v>
+      </c>
       <c r="M137" s="144"/>
       <c r="N137" s="144"/>
       <c r="O137" s="152"/>
@@ -9837,30 +9876,16 @@
     </row>
     <row r="140" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A140" s="144"/>
-      <c r="B140" s="144" t="s">
-        <v>358</v>
-      </c>
-      <c r="C140" s="144" t="s">
-        <v>193</v>
-      </c>
+      <c r="B140" s="144"/>
+      <c r="C140" s="144"/>
       <c r="D140" s="144"/>
       <c r="E140" s="144"/>
-      <c r="F140" s="145">
-        <f>E140/2500</f>
-        <v>0</v>
-      </c>
+      <c r="F140" s="145"/>
       <c r="G140" s="145"/>
-      <c r="H140" s="146" t="s">
-        <v>194</v>
-      </c>
-      <c r="I140" s="146" t="s">
-        <v>359</v>
-      </c>
-      <c r="J140" s="144"/>
-      <c r="K140" s="145">
-        <f>J140/400</f>
-        <v>0</v>
-      </c>
+      <c r="H140" s="146"/>
+      <c r="I140" s="146"/>
+      <c r="J140" s="157"/>
+      <c r="K140" s="145"/>
       <c r="L140" s="144"/>
       <c r="M140" s="144"/>
       <c r="N140" s="144"/>
@@ -9893,7 +9918,7 @@
       <c r="G141" s="145"/>
       <c r="H141" s="146"/>
       <c r="I141" s="146"/>
-      <c r="J141" s="144"/>
+      <c r="J141" s="157"/>
       <c r="K141" s="145"/>
       <c r="L141" s="144"/>
       <c r="M141" s="144"/>
@@ -9919,16 +9944,30 @@
     </row>
     <row r="142" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A142" s="144"/>
-      <c r="B142" s="144"/>
-      <c r="C142" s="144"/>
+      <c r="B142" s="144" t="s">
+        <v>359</v>
+      </c>
+      <c r="C142" s="144" t="s">
+        <v>194</v>
+      </c>
       <c r="D142" s="144"/>
       <c r="E142" s="144"/>
-      <c r="F142" s="145"/>
+      <c r="F142" s="145">
+        <f>E142/2500</f>
+        <v>0</v>
+      </c>
       <c r="G142" s="145"/>
-      <c r="H142" s="146"/>
-      <c r="I142" s="146"/>
+      <c r="H142" s="146" t="s">
+        <v>195</v>
+      </c>
+      <c r="I142" s="146" t="s">
+        <v>360</v>
+      </c>
       <c r="J142" s="144"/>
-      <c r="K142" s="145"/>
+      <c r="K142" s="145">
+        <f>J142/400</f>
+        <v>0</v>
+      </c>
       <c r="L142" s="144"/>
       <c r="M142" s="144"/>
       <c r="N142" s="144"/>
@@ -10020,36 +10059,18 @@
       <c r="AF144" s="152"/>
     </row>
     <row r="145" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
-      <c r="A145" s="144" t="s">
-        <v>360</v>
-      </c>
-      <c r="B145" s="144" t="s">
-        <v>361</v>
-      </c>
-      <c r="C145" s="144" t="s">
-        <v>193</v>
-      </c>
+      <c r="A145" s="144"/>
+      <c r="B145" s="144"/>
+      <c r="C145" s="144"/>
       <c r="D145" s="144"/>
       <c r="E145" s="144"/>
-      <c r="F145" s="145">
-        <f>E145/2500</f>
-        <v>0</v>
-      </c>
+      <c r="F145" s="145"/>
       <c r="G145" s="145"/>
-      <c r="H145" s="146" t="s">
-        <v>194</v>
-      </c>
-      <c r="I145" s="146" t="s">
-        <v>362</v>
-      </c>
+      <c r="H145" s="146"/>
+      <c r="I145" s="146"/>
       <c r="J145" s="144"/>
-      <c r="K145" s="145">
-        <f>J145/300</f>
-        <v>0</v>
-      </c>
-      <c r="L145" s="144" t="s">
-        <v>193</v>
-      </c>
+      <c r="K145" s="145"/>
+      <c r="L145" s="144"/>
       <c r="M145" s="144"/>
       <c r="N145" s="144"/>
       <c r="O145" s="152"/>
@@ -10106,18 +10127,36 @@
       <c r="AF146" s="152"/>
     </row>
     <row r="147" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
-      <c r="A147" s="144"/>
-      <c r="B147" s="144"/>
-      <c r="C147" s="144"/>
+      <c r="A147" s="144" t="s">
+        <v>361</v>
+      </c>
+      <c r="B147" s="144" t="s">
+        <v>362</v>
+      </c>
+      <c r="C147" s="144" t="s">
+        <v>194</v>
+      </c>
       <c r="D147" s="144"/>
       <c r="E147" s="144"/>
-      <c r="F147" s="145"/>
+      <c r="F147" s="145">
+        <f>E147/2500</f>
+        <v>0</v>
+      </c>
       <c r="G147" s="145"/>
-      <c r="H147" s="146"/>
-      <c r="I147" s="146"/>
+      <c r="H147" s="146" t="s">
+        <v>195</v>
+      </c>
+      <c r="I147" s="146" t="s">
+        <v>363</v>
+      </c>
       <c r="J147" s="144"/>
-      <c r="K147" s="145"/>
-      <c r="L147" s="144"/>
+      <c r="K147" s="145">
+        <f>J147/300</f>
+        <v>0</v>
+      </c>
+      <c r="L147" s="144" t="s">
+        <v>194</v>
+      </c>
       <c r="M147" s="144"/>
       <c r="N147" s="144"/>
       <c r="O147" s="152"/>
@@ -10209,30 +10248,16 @@
     </row>
     <row r="150" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A150" s="144"/>
-      <c r="B150" s="144" t="s">
-        <v>363</v>
-      </c>
-      <c r="C150" s="144" t="s">
-        <v>193</v>
-      </c>
+      <c r="B150" s="144"/>
+      <c r="C150" s="144"/>
       <c r="D150" s="144"/>
       <c r="E150" s="144"/>
-      <c r="F150" s="145">
-        <f>E150/2500</f>
-        <v>0</v>
-      </c>
+      <c r="F150" s="145"/>
       <c r="G150" s="145"/>
-      <c r="H150" s="146" t="s">
-        <v>194</v>
-      </c>
-      <c r="I150" s="146" t="s">
-        <v>364</v>
-      </c>
+      <c r="H150" s="146"/>
+      <c r="I150" s="146"/>
       <c r="J150" s="144"/>
-      <c r="K150" s="145">
-        <f>J150/400</f>
-        <v>0</v>
-      </c>
+      <c r="K150" s="145"/>
       <c r="L150" s="144"/>
       <c r="M150" s="144"/>
       <c r="N150" s="144"/>
@@ -10291,16 +10316,30 @@
     </row>
     <row r="152" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A152" s="144"/>
-      <c r="B152" s="144"/>
-      <c r="C152" s="144"/>
+      <c r="B152" s="144" t="s">
+        <v>364</v>
+      </c>
+      <c r="C152" s="144" t="s">
+        <v>194</v>
+      </c>
       <c r="D152" s="144"/>
       <c r="E152" s="144"/>
-      <c r="F152" s="145"/>
+      <c r="F152" s="145">
+        <f>E152/2500</f>
+        <v>0</v>
+      </c>
       <c r="G152" s="145"/>
-      <c r="H152" s="146"/>
-      <c r="I152" s="146"/>
+      <c r="H152" s="146" t="s">
+        <v>195</v>
+      </c>
+      <c r="I152" s="146" t="s">
+        <v>365</v>
+      </c>
       <c r="J152" s="144"/>
-      <c r="K152" s="145"/>
+      <c r="K152" s="145">
+        <f>J152/400</f>
+        <v>0</v>
+      </c>
       <c r="L152" s="144"/>
       <c r="M152" s="144"/>
       <c r="N152" s="144"/>
@@ -10391,32 +10430,100 @@
       <c r="AE154" s="152"/>
       <c r="AF154" s="152"/>
     </row>
+    <row r="155" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
+      <c r="A155" s="144"/>
+      <c r="B155" s="144"/>
+      <c r="C155" s="144"/>
+      <c r="D155" s="144"/>
+      <c r="E155" s="144"/>
+      <c r="F155" s="145"/>
+      <c r="G155" s="145"/>
+      <c r="H155" s="146"/>
+      <c r="I155" s="146"/>
+      <c r="J155" s="144"/>
+      <c r="K155" s="145"/>
+      <c r="L155" s="144"/>
+      <c r="M155" s="144"/>
+      <c r="N155" s="144"/>
+      <c r="O155" s="152"/>
+      <c r="P155" s="152"/>
+      <c r="Q155" s="152"/>
+      <c r="R155" s="152"/>
+      <c r="S155" s="152"/>
+      <c r="T155" s="152"/>
+      <c r="U155" s="152"/>
+      <c r="V155" s="152"/>
+      <c r="W155" s="152"/>
+      <c r="X155" s="152"/>
+      <c r="Y155" s="152"/>
+      <c r="Z155" s="152"/>
+      <c r="AA155" s="152"/>
+      <c r="AB155" s="152"/>
+      <c r="AC155" s="152"/>
+      <c r="AD155" s="152"/>
+      <c r="AE155" s="152"/>
+      <c r="AF155" s="152"/>
+    </row>
+    <row r="156" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
+      <c r="A156" s="144"/>
+      <c r="B156" s="144"/>
+      <c r="C156" s="144"/>
+      <c r="D156" s="144"/>
+      <c r="E156" s="144"/>
+      <c r="F156" s="145"/>
+      <c r="G156" s="145"/>
+      <c r="H156" s="146"/>
+      <c r="I156" s="146"/>
+      <c r="J156" s="144"/>
+      <c r="K156" s="145"/>
+      <c r="L156" s="144"/>
+      <c r="M156" s="144"/>
+      <c r="N156" s="144"/>
+      <c r="O156" s="152"/>
+      <c r="P156" s="152"/>
+      <c r="Q156" s="152"/>
+      <c r="R156" s="152"/>
+      <c r="S156" s="152"/>
+      <c r="T156" s="152"/>
+      <c r="U156" s="152"/>
+      <c r="V156" s="152"/>
+      <c r="W156" s="152"/>
+      <c r="X156" s="152"/>
+      <c r="Y156" s="152"/>
+      <c r="Z156" s="152"/>
+      <c r="AA156" s="152"/>
+      <c r="AB156" s="152"/>
+      <c r="AC156" s="152"/>
+      <c r="AD156" s="152"/>
+      <c r="AE156" s="152"/>
+      <c r="AF156" s="152"/>
+    </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="D67:D154" name="数据1_1_1_3_1_1_1_1"/>
-    <protectedRange sqref="AA67:AA134" name="数据2_1_1_2_1_1_1_1_1_1_1_1_3_2_2_3_4_2_1_4_1"/>
-    <protectedRange sqref="AC101:AD134" name="数据2_1_1_1_1_1_1_1_1_2_1_2_1_1_3_1_4_2_1_3_1_1"/>
-    <protectedRange sqref="M67:N154" name="数据1_2_1_1_1_1_1"/>
-    <protectedRange sqref="H67:H154" name="数据1_1_1_4_1_1_1_1_1_1"/>
-    <protectedRange sqref="J135:J154" name="数据1_2_1_2_1_1"/>
-    <protectedRange sqref="R75:R134" name="数据1_1_1_5_1_1_1_2"/>
-    <protectedRange sqref="AC67:AD100" name="数据2_1_1_1_1_1_1_1_1_1_5_1_1_1_1_1_1_1_4_2_1_3_1"/>
-    <protectedRange sqref="E67:E154" name="数据1_1_1_4_1_1_1"/>
-    <protectedRange sqref="Q67:Q134" name="数据1_1_1_1_1_1_1_2_1"/>
-    <protectedRange sqref="H67:H154" name="数据1_1_1_4_1_1_1_1_1_1_1"/>
-    <protectedRange sqref="AA67:AA134" name="数据2_1_1_2_1_1_1_1_1_1_1_1_3_2_2_3_4_2_1_4"/>
-    <protectedRange sqref="J135:J154" name="数据1_2_1_2_1_1_1"/>
-    <protectedRange sqref="R67:R74" name="数据1_1_1_6_1_1_2"/>
-    <protectedRange sqref="R75:R134" name="数据1_1_1_5_1_1_1_2_1"/>
-    <protectedRange sqref="AC101:AD134" name="数据2_1_1_1_1_1_1_1_1_2_1_2_1_1_3_1_4_2_1_3_1"/>
-    <protectedRange sqref="AC67:AD100" name="数据2_1_1_1_1_1_1_1_1_1_5_1_1_1_1_1_1_1_4_2_1_3_1_1"/>
-    <protectedRange sqref="D67:D154" name="数据1_1_1_3_1_1_1_1_1"/>
-    <protectedRange sqref="E67:E154" name="数据1_1_1_4_1_1_1_1"/>
-    <protectedRange sqref="M67:N154" name="数据1_2_1_1_1_1"/>
-    <protectedRange sqref="Q67:Q134" name="数据1_1_1_1_1_1_1_2_1_1"/>
-    <protectedRange sqref="U67:U134" name="数据1_1_1_6_1_1_3"/>
+    <protectedRange sqref="D69:D156" name="数据1_1_1_3_1_1_1_1"/>
+    <protectedRange sqref="AA69:AA136" name="数据2_1_1_2_1_1_1_1_1_1_1_1_3_2_2_3_4_2_1_4_1"/>
+    <protectedRange sqref="AC103:AD136" name="数据2_1_1_1_1_1_1_1_1_2_1_2_1_1_3_1_4_2_1_3_1_1"/>
+    <protectedRange sqref="M69:N156" name="数据1_2_1_1_1_1_1"/>
+    <protectedRange sqref="H69:H156" name="数据1_1_1_4_1_1_1_1_1_1"/>
+    <protectedRange sqref="J137:J156" name="数据1_2_1_2_1_1"/>
+    <protectedRange sqref="R77:R136" name="数据1_1_1_5_1_1_1_2"/>
+    <protectedRange sqref="AC69:AD102" name="数据2_1_1_1_1_1_1_1_1_1_5_1_1_1_1_1_1_1_4_2_1_3_1"/>
+    <protectedRange sqref="E69:E156" name="数据1_1_1_4_1_1_1"/>
+    <protectedRange sqref="Q69:Q136" name="数据1_1_1_1_1_1_1_2_1"/>
+    <protectedRange sqref="H69:H156" name="数据1_1_1_4_1_1_1_1_1_1_1"/>
+    <protectedRange sqref="AA69:AA136" name="数据2_1_1_2_1_1_1_1_1_1_1_1_3_2_2_3_4_2_1_4"/>
+    <protectedRange sqref="J137:J156" name="数据1_2_1_2_1_1_1"/>
+    <protectedRange sqref="R69:R76" name="数据1_1_1_6_1_1_2"/>
+    <protectedRange sqref="R77:R136" name="数据1_1_1_5_1_1_1_2_1"/>
+    <protectedRange sqref="AC103:AD136" name="数据2_1_1_1_1_1_1_1_1_2_1_2_1_1_3_1_4_2_1_3_1"/>
+    <protectedRange sqref="AC69:AD102" name="数据2_1_1_1_1_1_1_1_1_1_5_1_1_1_1_1_1_1_4_2_1_3_1_1"/>
+    <protectedRange sqref="D69:D156" name="数据1_1_1_3_1_1_1_1_1"/>
+    <protectedRange sqref="E69:E156" name="数据1_1_1_4_1_1_1_1"/>
+    <protectedRange sqref="M69:N156" name="数据1_2_1_1_1_1"/>
+    <protectedRange sqref="Q69:Q136" name="数据1_1_1_1_1_1_1_2_1_1"/>
+    <protectedRange sqref="U69:U136" name="数据1_1_1_6_1_1_3"/>
   </protectedRanges>
-  <mergeCells count="652">
+  <mergeCells count="662">
     <mergeCell ref="A1:AE1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:H2"/>
@@ -10628,64 +10735,62 @@
     <mergeCell ref="T48:U48"/>
     <mergeCell ref="V48:W48"/>
     <mergeCell ref="X48:Y48"/>
-    <mergeCell ref="D49:N49"/>
-    <mergeCell ref="Q49:AA49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="C50:AE50"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="C51:AE51"/>
+    <mergeCell ref="C49:N49"/>
+    <mergeCell ref="P49:AA49"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="K50:L50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="T50:U50"/>
+    <mergeCell ref="V50:W50"/>
+    <mergeCell ref="X50:Y50"/>
+    <mergeCell ref="D51:N51"/>
+    <mergeCell ref="Q51:AA51"/>
     <mergeCell ref="A52:B52"/>
     <mergeCell ref="C52:AE52"/>
     <mergeCell ref="A53:B53"/>
     <mergeCell ref="C53:AE53"/>
-    <mergeCell ref="A54:AE54"/>
-    <mergeCell ref="A55:L55"/>
-    <mergeCell ref="O55:Z55"/>
-    <mergeCell ref="AD55:AE55"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="G56:H56"/>
-    <mergeCell ref="I56:J56"/>
-    <mergeCell ref="K56:L56"/>
-    <mergeCell ref="O56:Q56"/>
-    <mergeCell ref="R56:U56"/>
-    <mergeCell ref="V56:X56"/>
-    <mergeCell ref="Y56:Z56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="G57:H57"/>
-    <mergeCell ref="I57:J57"/>
-    <mergeCell ref="K57:L57"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="C54:AE54"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="C55:AE55"/>
+    <mergeCell ref="A56:AE56"/>
+    <mergeCell ref="A57:L57"/>
+    <mergeCell ref="O57:Z57"/>
+    <mergeCell ref="AD57:AE57"/>
     <mergeCell ref="A58:B58"/>
     <mergeCell ref="C58:D58"/>
     <mergeCell ref="E58:F58"/>
     <mergeCell ref="G58:H58"/>
     <mergeCell ref="I58:J58"/>
     <mergeCell ref="K58:L58"/>
-    <mergeCell ref="AB58:AE58"/>
+    <mergeCell ref="O58:Q58"/>
+    <mergeCell ref="R58:U58"/>
+    <mergeCell ref="V58:X58"/>
+    <mergeCell ref="Y58:Z58"/>
+    <mergeCell ref="A59:B59"/>
     <mergeCell ref="C59:D59"/>
     <mergeCell ref="E59:F59"/>
     <mergeCell ref="G59:H59"/>
     <mergeCell ref="I59:J59"/>
     <mergeCell ref="K59:L59"/>
-    <mergeCell ref="O59:R59"/>
-    <mergeCell ref="S59:U59"/>
-    <mergeCell ref="V59:Z59"/>
-    <mergeCell ref="AD59:AE59"/>
     <mergeCell ref="A60:B60"/>
     <mergeCell ref="C60:D60"/>
     <mergeCell ref="E60:F60"/>
     <mergeCell ref="G60:H60"/>
     <mergeCell ref="I60:J60"/>
     <mergeCell ref="K60:L60"/>
-    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="AB60:AE60"/>
     <mergeCell ref="C61:D61"/>
     <mergeCell ref="E61:F61"/>
     <mergeCell ref="G61:H61"/>
     <mergeCell ref="I61:J61"/>
     <mergeCell ref="K61:L61"/>
+    <mergeCell ref="O61:R61"/>
+    <mergeCell ref="S61:U61"/>
+    <mergeCell ref="V61:Z61"/>
+    <mergeCell ref="AD61:AE61"/>
     <mergeCell ref="A62:B62"/>
     <mergeCell ref="C62:D62"/>
     <mergeCell ref="E62:F62"/>
@@ -10698,10 +10803,20 @@
     <mergeCell ref="G63:H63"/>
     <mergeCell ref="I63:J63"/>
     <mergeCell ref="K63:L63"/>
-    <mergeCell ref="A65:AE65"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="S66:T66"/>
-    <mergeCell ref="S67:T67"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="I64:J64"/>
+    <mergeCell ref="K64:L64"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="G65:H65"/>
+    <mergeCell ref="I65:J65"/>
+    <mergeCell ref="K65:L65"/>
+    <mergeCell ref="A67:AE67"/>
+    <mergeCell ref="F68:G68"/>
     <mergeCell ref="S68:T68"/>
     <mergeCell ref="S69:T69"/>
     <mergeCell ref="S70:T70"/>
@@ -10769,176 +10884,178 @@
     <mergeCell ref="S132:T132"/>
     <mergeCell ref="S133:T133"/>
     <mergeCell ref="S134:T134"/>
+    <mergeCell ref="S135:T135"/>
+    <mergeCell ref="S136:T136"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A67:A76"/>
-    <mergeCell ref="A77:A86"/>
-    <mergeCell ref="A87:A100"/>
-    <mergeCell ref="A101:A114"/>
-    <mergeCell ref="A115:A124"/>
-    <mergeCell ref="A125:A134"/>
-    <mergeCell ref="A135:A144"/>
-    <mergeCell ref="A145:A154"/>
-    <mergeCell ref="B67:B71"/>
-    <mergeCell ref="B72:B76"/>
-    <mergeCell ref="B77:B81"/>
-    <mergeCell ref="B82:B86"/>
-    <mergeCell ref="B87:B93"/>
-    <mergeCell ref="B94:B100"/>
-    <mergeCell ref="B101:B107"/>
-    <mergeCell ref="B108:B114"/>
-    <mergeCell ref="B115:B119"/>
-    <mergeCell ref="B120:B124"/>
-    <mergeCell ref="B125:B129"/>
-    <mergeCell ref="B130:B134"/>
-    <mergeCell ref="B135:B139"/>
-    <mergeCell ref="B140:B144"/>
-    <mergeCell ref="B145:B149"/>
-    <mergeCell ref="B150:B154"/>
+    <mergeCell ref="A69:A78"/>
+    <mergeCell ref="A79:A88"/>
+    <mergeCell ref="A89:A102"/>
+    <mergeCell ref="A103:A116"/>
+    <mergeCell ref="A117:A126"/>
+    <mergeCell ref="A127:A136"/>
+    <mergeCell ref="A137:A146"/>
+    <mergeCell ref="A147:A156"/>
+    <mergeCell ref="B69:B73"/>
+    <mergeCell ref="B74:B78"/>
+    <mergeCell ref="B79:B83"/>
+    <mergeCell ref="B84:B88"/>
+    <mergeCell ref="B89:B95"/>
+    <mergeCell ref="B96:B102"/>
+    <mergeCell ref="B103:B109"/>
+    <mergeCell ref="B110:B116"/>
+    <mergeCell ref="B117:B121"/>
+    <mergeCell ref="B122:B126"/>
+    <mergeCell ref="B127:B131"/>
+    <mergeCell ref="B132:B136"/>
+    <mergeCell ref="B137:B141"/>
+    <mergeCell ref="B142:B146"/>
+    <mergeCell ref="B147:B151"/>
+    <mergeCell ref="B152:B156"/>
     <mergeCell ref="C26:C27"/>
     <mergeCell ref="C36:C37"/>
-    <mergeCell ref="C67:C71"/>
-    <mergeCell ref="C72:C76"/>
-    <mergeCell ref="C77:C81"/>
-    <mergeCell ref="C82:C86"/>
-    <mergeCell ref="C87:C93"/>
-    <mergeCell ref="C94:C100"/>
-    <mergeCell ref="C101:C107"/>
-    <mergeCell ref="C108:C114"/>
-    <mergeCell ref="C115:C119"/>
-    <mergeCell ref="C120:C124"/>
-    <mergeCell ref="C125:C129"/>
-    <mergeCell ref="C130:C134"/>
-    <mergeCell ref="C135:C139"/>
-    <mergeCell ref="C140:C144"/>
-    <mergeCell ref="C145:C149"/>
-    <mergeCell ref="C150:C154"/>
+    <mergeCell ref="C69:C73"/>
+    <mergeCell ref="C74:C78"/>
+    <mergeCell ref="C79:C83"/>
+    <mergeCell ref="C84:C88"/>
+    <mergeCell ref="C89:C95"/>
+    <mergeCell ref="C96:C102"/>
+    <mergeCell ref="C103:C109"/>
+    <mergeCell ref="C110:C116"/>
+    <mergeCell ref="C117:C121"/>
+    <mergeCell ref="C122:C126"/>
+    <mergeCell ref="C127:C131"/>
+    <mergeCell ref="C132:C136"/>
+    <mergeCell ref="C137:C141"/>
+    <mergeCell ref="C142:C146"/>
+    <mergeCell ref="C147:C151"/>
+    <mergeCell ref="C152:C156"/>
     <mergeCell ref="D26:D27"/>
     <mergeCell ref="D36:D37"/>
-    <mergeCell ref="D67:D71"/>
-    <mergeCell ref="D72:D76"/>
-    <mergeCell ref="D77:D81"/>
-    <mergeCell ref="D82:D86"/>
-    <mergeCell ref="D87:D93"/>
-    <mergeCell ref="D94:D100"/>
-    <mergeCell ref="D101:D107"/>
-    <mergeCell ref="D108:D114"/>
-    <mergeCell ref="D115:D119"/>
-    <mergeCell ref="D120:D124"/>
-    <mergeCell ref="D125:D129"/>
-    <mergeCell ref="D130:D134"/>
-    <mergeCell ref="D135:D139"/>
-    <mergeCell ref="D140:D144"/>
-    <mergeCell ref="D145:D149"/>
-    <mergeCell ref="D150:D154"/>
+    <mergeCell ref="D69:D73"/>
+    <mergeCell ref="D74:D78"/>
+    <mergeCell ref="D79:D83"/>
+    <mergeCell ref="D84:D88"/>
+    <mergeCell ref="D89:D95"/>
+    <mergeCell ref="D96:D102"/>
+    <mergeCell ref="D103:D109"/>
+    <mergeCell ref="D110:D116"/>
+    <mergeCell ref="D117:D121"/>
+    <mergeCell ref="D122:D126"/>
+    <mergeCell ref="D127:D131"/>
+    <mergeCell ref="D132:D136"/>
+    <mergeCell ref="D137:D141"/>
+    <mergeCell ref="D142:D146"/>
+    <mergeCell ref="D147:D151"/>
+    <mergeCell ref="D152:D156"/>
     <mergeCell ref="E26:E27"/>
     <mergeCell ref="E36:E37"/>
-    <mergeCell ref="E67:E71"/>
-    <mergeCell ref="E72:E76"/>
-    <mergeCell ref="E77:E81"/>
-    <mergeCell ref="E82:E86"/>
-    <mergeCell ref="E87:E93"/>
-    <mergeCell ref="E94:E100"/>
-    <mergeCell ref="E101:E107"/>
-    <mergeCell ref="E108:E114"/>
-    <mergeCell ref="E115:E119"/>
-    <mergeCell ref="E120:E124"/>
-    <mergeCell ref="E125:E129"/>
-    <mergeCell ref="E130:E134"/>
-    <mergeCell ref="E135:E139"/>
-    <mergeCell ref="E140:E144"/>
-    <mergeCell ref="E145:E149"/>
-    <mergeCell ref="E150:E154"/>
+    <mergeCell ref="E69:E73"/>
+    <mergeCell ref="E74:E78"/>
+    <mergeCell ref="E79:E83"/>
+    <mergeCell ref="E84:E88"/>
+    <mergeCell ref="E89:E95"/>
+    <mergeCell ref="E96:E102"/>
+    <mergeCell ref="E103:E109"/>
+    <mergeCell ref="E110:E116"/>
+    <mergeCell ref="E117:E121"/>
+    <mergeCell ref="E122:E126"/>
+    <mergeCell ref="E127:E131"/>
+    <mergeCell ref="E132:E136"/>
+    <mergeCell ref="E137:E141"/>
+    <mergeCell ref="E142:E146"/>
+    <mergeCell ref="E147:E151"/>
+    <mergeCell ref="E152:E156"/>
     <mergeCell ref="H26:H27"/>
     <mergeCell ref="H36:H37"/>
-    <mergeCell ref="H67:H71"/>
-    <mergeCell ref="H72:H76"/>
-    <mergeCell ref="H77:H81"/>
-    <mergeCell ref="H82:H86"/>
-    <mergeCell ref="H87:H93"/>
-    <mergeCell ref="H94:H100"/>
-    <mergeCell ref="H101:H107"/>
-    <mergeCell ref="H108:H114"/>
-    <mergeCell ref="H115:H119"/>
-    <mergeCell ref="H120:H124"/>
-    <mergeCell ref="H125:H129"/>
-    <mergeCell ref="H130:H134"/>
-    <mergeCell ref="H135:H139"/>
-    <mergeCell ref="H140:H144"/>
-    <mergeCell ref="H145:H149"/>
-    <mergeCell ref="H150:H154"/>
+    <mergeCell ref="H69:H73"/>
+    <mergeCell ref="H74:H78"/>
+    <mergeCell ref="H79:H83"/>
+    <mergeCell ref="H84:H88"/>
+    <mergeCell ref="H89:H95"/>
+    <mergeCell ref="H96:H102"/>
+    <mergeCell ref="H103:H109"/>
+    <mergeCell ref="H110:H116"/>
+    <mergeCell ref="H117:H121"/>
+    <mergeCell ref="H122:H126"/>
+    <mergeCell ref="H127:H131"/>
+    <mergeCell ref="H132:H136"/>
+    <mergeCell ref="H137:H141"/>
+    <mergeCell ref="H142:H146"/>
+    <mergeCell ref="H147:H151"/>
+    <mergeCell ref="H152:H156"/>
     <mergeCell ref="I26:I27"/>
     <mergeCell ref="I36:I37"/>
-    <mergeCell ref="I67:I76"/>
-    <mergeCell ref="I77:I86"/>
-    <mergeCell ref="I87:I100"/>
-    <mergeCell ref="I101:I114"/>
-    <mergeCell ref="I115:I124"/>
-    <mergeCell ref="I125:I134"/>
-    <mergeCell ref="I135:I139"/>
-    <mergeCell ref="I140:I144"/>
-    <mergeCell ref="I145:I149"/>
-    <mergeCell ref="I150:I154"/>
+    <mergeCell ref="I69:I78"/>
+    <mergeCell ref="I79:I88"/>
+    <mergeCell ref="I89:I102"/>
+    <mergeCell ref="I103:I116"/>
+    <mergeCell ref="I117:I126"/>
+    <mergeCell ref="I127:I136"/>
+    <mergeCell ref="I137:I141"/>
+    <mergeCell ref="I142:I146"/>
+    <mergeCell ref="I147:I151"/>
+    <mergeCell ref="I152:I156"/>
     <mergeCell ref="J26:J27"/>
     <mergeCell ref="J36:J37"/>
-    <mergeCell ref="J67:J76"/>
-    <mergeCell ref="J77:J86"/>
-    <mergeCell ref="J87:J100"/>
-    <mergeCell ref="J101:J114"/>
-    <mergeCell ref="J115:J124"/>
-    <mergeCell ref="J125:J134"/>
-    <mergeCell ref="J135:J139"/>
-    <mergeCell ref="J140:J144"/>
-    <mergeCell ref="J145:J149"/>
-    <mergeCell ref="J150:J154"/>
+    <mergeCell ref="J69:J78"/>
+    <mergeCell ref="J79:J88"/>
+    <mergeCell ref="J89:J102"/>
+    <mergeCell ref="J103:J116"/>
+    <mergeCell ref="J117:J126"/>
+    <mergeCell ref="J127:J136"/>
+    <mergeCell ref="J137:J141"/>
+    <mergeCell ref="J142:J146"/>
+    <mergeCell ref="J147:J151"/>
+    <mergeCell ref="J152:J156"/>
     <mergeCell ref="K26:K27"/>
     <mergeCell ref="K36:K37"/>
-    <mergeCell ref="K67:K76"/>
-    <mergeCell ref="K77:K86"/>
-    <mergeCell ref="K87:K100"/>
-    <mergeCell ref="K101:K114"/>
-    <mergeCell ref="K115:K124"/>
-    <mergeCell ref="K125:K134"/>
-    <mergeCell ref="K135:K139"/>
-    <mergeCell ref="K140:K144"/>
-    <mergeCell ref="K145:K149"/>
-    <mergeCell ref="K150:K154"/>
+    <mergeCell ref="K69:K78"/>
+    <mergeCell ref="K79:K88"/>
+    <mergeCell ref="K89:K102"/>
+    <mergeCell ref="K103:K116"/>
+    <mergeCell ref="K117:K126"/>
+    <mergeCell ref="K127:K136"/>
+    <mergeCell ref="K137:K141"/>
+    <mergeCell ref="K142:K146"/>
+    <mergeCell ref="K147:K151"/>
+    <mergeCell ref="K152:K156"/>
     <mergeCell ref="L26:L27"/>
     <mergeCell ref="L36:L37"/>
-    <mergeCell ref="L67:L76"/>
-    <mergeCell ref="L77:L86"/>
-    <mergeCell ref="L87:L100"/>
-    <mergeCell ref="L101:L114"/>
-    <mergeCell ref="L115:L124"/>
-    <mergeCell ref="L125:L134"/>
-    <mergeCell ref="L135:L144"/>
-    <mergeCell ref="L145:L154"/>
+    <mergeCell ref="L69:L78"/>
+    <mergeCell ref="L79:L88"/>
+    <mergeCell ref="L89:L102"/>
+    <mergeCell ref="L103:L116"/>
+    <mergeCell ref="L117:L126"/>
+    <mergeCell ref="L127:L136"/>
+    <mergeCell ref="L137:L146"/>
+    <mergeCell ref="L147:L156"/>
     <mergeCell ref="M26:M27"/>
     <mergeCell ref="M36:M37"/>
-    <mergeCell ref="M67:M76"/>
-    <mergeCell ref="M77:M86"/>
-    <mergeCell ref="M87:M100"/>
-    <mergeCell ref="M101:M114"/>
-    <mergeCell ref="M115:M124"/>
-    <mergeCell ref="M125:M134"/>
-    <mergeCell ref="M135:M139"/>
-    <mergeCell ref="M140:M144"/>
-    <mergeCell ref="M145:M149"/>
-    <mergeCell ref="M150:M154"/>
+    <mergeCell ref="M69:M78"/>
+    <mergeCell ref="M79:M88"/>
+    <mergeCell ref="M89:M102"/>
+    <mergeCell ref="M103:M116"/>
+    <mergeCell ref="M117:M126"/>
+    <mergeCell ref="M127:M136"/>
+    <mergeCell ref="M137:M141"/>
+    <mergeCell ref="M142:M146"/>
+    <mergeCell ref="M147:M151"/>
+    <mergeCell ref="M152:M156"/>
     <mergeCell ref="N26:N27"/>
     <mergeCell ref="N36:N37"/>
-    <mergeCell ref="N67:N76"/>
-    <mergeCell ref="N77:N86"/>
-    <mergeCell ref="N87:N100"/>
-    <mergeCell ref="N101:N114"/>
-    <mergeCell ref="N115:N124"/>
-    <mergeCell ref="N125:N134"/>
-    <mergeCell ref="N135:N139"/>
-    <mergeCell ref="N140:N144"/>
-    <mergeCell ref="N145:N149"/>
-    <mergeCell ref="N150:N154"/>
+    <mergeCell ref="N69:N78"/>
+    <mergeCell ref="N79:N88"/>
+    <mergeCell ref="N89:N102"/>
+    <mergeCell ref="N103:N116"/>
+    <mergeCell ref="N117:N126"/>
+    <mergeCell ref="N127:N136"/>
+    <mergeCell ref="N137:N141"/>
+    <mergeCell ref="N142:N146"/>
+    <mergeCell ref="N147:N151"/>
+    <mergeCell ref="N152:N156"/>
     <mergeCell ref="O11:O15"/>
     <mergeCell ref="O21:O42"/>
-    <mergeCell ref="O44:O49"/>
+    <mergeCell ref="O44:O51"/>
     <mergeCell ref="P26:P27"/>
     <mergeCell ref="P36:P37"/>
     <mergeCell ref="Q26:Q27"/>
@@ -10951,135 +11068,195 @@
     <mergeCell ref="V36:V37"/>
     <mergeCell ref="W26:W27"/>
     <mergeCell ref="W36:W37"/>
-    <mergeCell ref="W67:W76"/>
-    <mergeCell ref="W77:W86"/>
-    <mergeCell ref="W87:W100"/>
-    <mergeCell ref="W101:W114"/>
-    <mergeCell ref="W115:W124"/>
-    <mergeCell ref="W125:W134"/>
+    <mergeCell ref="W69:W78"/>
+    <mergeCell ref="W79:W88"/>
+    <mergeCell ref="W89:W102"/>
+    <mergeCell ref="W103:W116"/>
+    <mergeCell ref="W117:W126"/>
+    <mergeCell ref="W127:W136"/>
     <mergeCell ref="X26:X27"/>
     <mergeCell ref="X36:X37"/>
-    <mergeCell ref="X67:X76"/>
-    <mergeCell ref="X77:X86"/>
-    <mergeCell ref="X87:X100"/>
-    <mergeCell ref="X101:X114"/>
-    <mergeCell ref="X115:X124"/>
-    <mergeCell ref="X125:X134"/>
+    <mergeCell ref="X69:X78"/>
+    <mergeCell ref="X79:X88"/>
+    <mergeCell ref="X89:X102"/>
+    <mergeCell ref="X103:X116"/>
+    <mergeCell ref="X117:X126"/>
+    <mergeCell ref="X127:X136"/>
     <mergeCell ref="Y26:Y27"/>
     <mergeCell ref="Y36:Y37"/>
-    <mergeCell ref="Y67:Y76"/>
-    <mergeCell ref="Y77:Y86"/>
-    <mergeCell ref="Y87:Y100"/>
-    <mergeCell ref="Y101:Y114"/>
-    <mergeCell ref="Y115:Y124"/>
-    <mergeCell ref="Y125:Y134"/>
+    <mergeCell ref="Y69:Y78"/>
+    <mergeCell ref="Y79:Y88"/>
+    <mergeCell ref="Y89:Y102"/>
+    <mergeCell ref="Y103:Y116"/>
+    <mergeCell ref="Y117:Y126"/>
+    <mergeCell ref="Y127:Y136"/>
     <mergeCell ref="Z26:Z27"/>
     <mergeCell ref="Z36:Z37"/>
-    <mergeCell ref="Z67:Z76"/>
-    <mergeCell ref="Z77:Z86"/>
-    <mergeCell ref="Z87:Z100"/>
-    <mergeCell ref="Z101:Z114"/>
-    <mergeCell ref="Z115:Z124"/>
-    <mergeCell ref="Z125:Z134"/>
+    <mergeCell ref="Z69:Z78"/>
+    <mergeCell ref="Z79:Z88"/>
+    <mergeCell ref="Z89:Z102"/>
+    <mergeCell ref="Z103:Z116"/>
+    <mergeCell ref="Z117:Z126"/>
+    <mergeCell ref="Z127:Z136"/>
     <mergeCell ref="AA26:AA27"/>
     <mergeCell ref="AA36:AA37"/>
-    <mergeCell ref="AA67:AA76"/>
-    <mergeCell ref="AA77:AA86"/>
-    <mergeCell ref="AA87:AA100"/>
-    <mergeCell ref="AA101:AA114"/>
-    <mergeCell ref="AA115:AA124"/>
-    <mergeCell ref="AA125:AA134"/>
+    <mergeCell ref="AA69:AA78"/>
+    <mergeCell ref="AA79:AA88"/>
+    <mergeCell ref="AA89:AA102"/>
+    <mergeCell ref="AA103:AA116"/>
+    <mergeCell ref="AA117:AA126"/>
+    <mergeCell ref="AA127:AA136"/>
     <mergeCell ref="AB22:AB23"/>
     <mergeCell ref="AB26:AB27"/>
-    <mergeCell ref="AB56:AB57"/>
-    <mergeCell ref="AB60:AB61"/>
-    <mergeCell ref="AB67:AB76"/>
-    <mergeCell ref="AB77:AB86"/>
-    <mergeCell ref="AB87:AB100"/>
-    <mergeCell ref="AB101:AB114"/>
-    <mergeCell ref="AB115:AB124"/>
-    <mergeCell ref="AB125:AB134"/>
-    <mergeCell ref="AC56:AC57"/>
-    <mergeCell ref="AC60:AC61"/>
-    <mergeCell ref="AC67:AC76"/>
-    <mergeCell ref="AC77:AC86"/>
-    <mergeCell ref="AC87:AC100"/>
-    <mergeCell ref="AC101:AC114"/>
-    <mergeCell ref="AC115:AC124"/>
-    <mergeCell ref="AC125:AC134"/>
-    <mergeCell ref="AD67:AD76"/>
-    <mergeCell ref="AD77:AD86"/>
-    <mergeCell ref="AD87:AD100"/>
-    <mergeCell ref="AD101:AD114"/>
-    <mergeCell ref="AD115:AD124"/>
-    <mergeCell ref="AD125:AD134"/>
-    <mergeCell ref="AE67:AE69"/>
-    <mergeCell ref="AE70:AE71"/>
-    <mergeCell ref="AE72:AE74"/>
-    <mergeCell ref="AE75:AE76"/>
-    <mergeCell ref="AE77:AE79"/>
-    <mergeCell ref="AE80:AE81"/>
-    <mergeCell ref="AE82:AE84"/>
-    <mergeCell ref="AE85:AE86"/>
-    <mergeCell ref="AE87:AE90"/>
-    <mergeCell ref="AE91:AE93"/>
-    <mergeCell ref="AE94:AE97"/>
-    <mergeCell ref="AE98:AE100"/>
-    <mergeCell ref="AE101:AE104"/>
-    <mergeCell ref="AE105:AE107"/>
-    <mergeCell ref="AE108:AE111"/>
-    <mergeCell ref="AE112:AE114"/>
-    <mergeCell ref="AE115:AE117"/>
-    <mergeCell ref="AE118:AE119"/>
-    <mergeCell ref="AE120:AE122"/>
-    <mergeCell ref="AE123:AE124"/>
-    <mergeCell ref="AE125:AE127"/>
-    <mergeCell ref="AE128:AE129"/>
-    <mergeCell ref="AE130:AE132"/>
-    <mergeCell ref="AE133:AE134"/>
-    <mergeCell ref="V60:Z61"/>
-    <mergeCell ref="Y57:Z58"/>
+    <mergeCell ref="AB58:AB59"/>
+    <mergeCell ref="AB62:AB63"/>
+    <mergeCell ref="AB69:AB78"/>
+    <mergeCell ref="AB79:AB88"/>
+    <mergeCell ref="AB89:AB102"/>
+    <mergeCell ref="AB103:AB116"/>
+    <mergeCell ref="AB117:AB126"/>
+    <mergeCell ref="AB127:AB136"/>
+    <mergeCell ref="AC58:AC59"/>
+    <mergeCell ref="AC62:AC63"/>
+    <mergeCell ref="AC69:AC78"/>
+    <mergeCell ref="AC79:AC88"/>
+    <mergeCell ref="AC89:AC102"/>
+    <mergeCell ref="AC103:AC116"/>
+    <mergeCell ref="AC117:AC126"/>
+    <mergeCell ref="AC127:AC136"/>
+    <mergeCell ref="AD69:AD78"/>
+    <mergeCell ref="AD79:AD88"/>
+    <mergeCell ref="AD89:AD102"/>
+    <mergeCell ref="AD103:AD116"/>
+    <mergeCell ref="AD117:AD126"/>
+    <mergeCell ref="AD127:AD136"/>
+    <mergeCell ref="AE69:AE71"/>
+    <mergeCell ref="AE72:AE73"/>
+    <mergeCell ref="AE74:AE76"/>
+    <mergeCell ref="AE77:AE78"/>
+    <mergeCell ref="AE79:AE81"/>
+    <mergeCell ref="AE82:AE83"/>
+    <mergeCell ref="AE84:AE86"/>
+    <mergeCell ref="AE87:AE88"/>
+    <mergeCell ref="AE89:AE92"/>
+    <mergeCell ref="AE93:AE95"/>
+    <mergeCell ref="AE96:AE99"/>
+    <mergeCell ref="AE100:AE102"/>
+    <mergeCell ref="AE103:AE106"/>
+    <mergeCell ref="AE107:AE109"/>
+    <mergeCell ref="AE110:AE113"/>
+    <mergeCell ref="AE114:AE116"/>
+    <mergeCell ref="AE117:AE119"/>
+    <mergeCell ref="AE120:AE121"/>
+    <mergeCell ref="AE122:AE124"/>
+    <mergeCell ref="AE125:AE126"/>
+    <mergeCell ref="AE127:AE129"/>
+    <mergeCell ref="AE130:AE131"/>
+    <mergeCell ref="AE132:AE134"/>
+    <mergeCell ref="AE135:AE136"/>
     <mergeCell ref="AC26:AE27"/>
-    <mergeCell ref="AD56:AE57"/>
-    <mergeCell ref="V57:X58"/>
-    <mergeCell ref="S60:U61"/>
     <mergeCell ref="A11:B18"/>
     <mergeCell ref="AB36:AC37"/>
     <mergeCell ref="AD36:AE37"/>
-    <mergeCell ref="O60:R61"/>
-    <mergeCell ref="O57:Q58"/>
     <mergeCell ref="AB30:AE32"/>
-    <mergeCell ref="A20:B49"/>
-    <mergeCell ref="AD60:AE61"/>
-    <mergeCell ref="R57:U58"/>
-    <mergeCell ref="F67:G71"/>
-    <mergeCell ref="F72:G76"/>
-    <mergeCell ref="F77:G81"/>
-    <mergeCell ref="F82:G86"/>
-    <mergeCell ref="F87:G93"/>
-    <mergeCell ref="F94:G100"/>
-    <mergeCell ref="F101:G107"/>
-    <mergeCell ref="F108:G114"/>
-    <mergeCell ref="F115:G119"/>
-    <mergeCell ref="F120:G124"/>
-    <mergeCell ref="F125:G129"/>
-    <mergeCell ref="F130:G134"/>
-    <mergeCell ref="F135:G139"/>
-    <mergeCell ref="F140:G144"/>
-    <mergeCell ref="F145:G149"/>
-    <mergeCell ref="F150:G154"/>
     <mergeCell ref="P12:R14"/>
+    <mergeCell ref="V62:Z63"/>
+    <mergeCell ref="Y59:Z60"/>
+    <mergeCell ref="AD58:AE59"/>
+    <mergeCell ref="V59:X60"/>
+    <mergeCell ref="S62:U63"/>
+    <mergeCell ref="O62:R63"/>
+    <mergeCell ref="O59:Q60"/>
+    <mergeCell ref="A20:B51"/>
+    <mergeCell ref="AD62:AE63"/>
+    <mergeCell ref="R59:U60"/>
+    <mergeCell ref="F69:G73"/>
+    <mergeCell ref="F74:G78"/>
+    <mergeCell ref="F79:G83"/>
+    <mergeCell ref="F84:G88"/>
+    <mergeCell ref="F89:G95"/>
+    <mergeCell ref="F96:G102"/>
+    <mergeCell ref="F103:G109"/>
+    <mergeCell ref="F110:G116"/>
+    <mergeCell ref="F117:G121"/>
+    <mergeCell ref="F122:G126"/>
+    <mergeCell ref="F127:G131"/>
+    <mergeCell ref="F132:G136"/>
+    <mergeCell ref="F137:G141"/>
+    <mergeCell ref="F142:G146"/>
+    <mergeCell ref="F147:G151"/>
+    <mergeCell ref="F152:G156"/>
   </mergeCells>
-  <conditionalFormatting sqref="AD56">
-    <cfRule type="dataBar" priority="3771">
+  <conditionalFormatting sqref="AD58">
+    <cfRule type="dataBar" priority="3763">
       <dataBar>
-        <cfvo type="percentile" val="1"/>
-        <cfvo type="percentile" val="100"/>
+        <cfvo type="min"/>
+        <cfvo type="num" val="1"/>
         <color rgb="FFFFC000"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1e8b3770-52de-4a9b-8834-7c638ac4741c}</x14:id>
+          <x14:id>{1da3db35-e0de-4637-8cac-3c85e7214f3c}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3765">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFFFB628"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{474b9d92-1ffe-4115-82c8-ec6b40fcd5a4}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3766">
+      <dataBar>
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="1"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{e0ce3279-baf1-47aa-91c5-0b8563f222a0}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3767">
+      <dataBar>
+        <cfvo type="percentile" val="0"/>
+        <cfvo type="percentile" val="100"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{1e5930d1-e00e-452d-8fa3-dae07de9dcf7}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3768">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{eeccbae5-276b-43f8-a71f-e2eb915fb9bc}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3769">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFC000"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{556339b3-d1ef-439b-99d2-f8eb96afb18e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11091,11 +11268,85 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3787be42-499c-486c-a521-c3e6d6293ebb}</x14:id>
+          <x14:id>{2db46e07-ff34-4840-bd4a-135b2336675c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="dataBar" priority="3769">
+    <cfRule type="dataBar" priority="3771">
+      <dataBar>
+        <cfvo type="percentile" val="1"/>
+        <cfvo type="percentile" val="100"/>
+        <color rgb="FFFFC000"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{6521ab67-9f01-402a-97c0-0d915b92a321}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K62">
+    <cfRule type="dataBar" priority="3730">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFFFC000"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{9faa95e9-88d2-4727-86b2-0fb536804f95}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3732">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFFFB628"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{2587a784-9c20-4dcb-b833-c69f805759f0}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3733">
+      <dataBar>
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="1"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{43d832dc-c892-4954-b2c1-6b501a9267f2}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3734">
+      <dataBar>
+        <cfvo type="percentile" val="0"/>
+        <cfvo type="percentile" val="100"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{af39b56f-c4b5-4572-9790-21a3c54b81c8}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3735">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{0bcb0cd1-0bdc-477e-8a9b-33867e2f0fba}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3736">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -11103,81 +11354,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{45157450-b856-44a7-9e1f-77adb7a00daf}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3768">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c13c4471-d64d-41b5-8ad4-1a756db2ee8e}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3767">
-      <dataBar>
-        <cfvo type="percentile" val="0"/>
-        <cfvo type="percentile" val="100"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{16aef48e-1ce1-486e-923f-f5f5bd01be3e}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3766">
-      <dataBar>
-        <cfvo type="percent" val="0"/>
-        <cfvo type="percent" val="1"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e2e030aa-49db-40d0-84aa-d8ea4206d4a8}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3765">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FFFFB628"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{da41cb00-9115-4e63-b397-891482f467b4}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3763">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FFFFC000"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6cdfcf5e-47e0-476b-8a57-9b8dfca04074}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K60">
-    <cfRule type="dataBar" priority="3738">
-      <dataBar>
-        <cfvo type="percentile" val="1"/>
-        <cfvo type="percentile" val="100"/>
-        <color rgb="FFFFC000"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0344c197-1e9e-4c7e-ac5c-16b950aa3cbe}</x14:id>
+          <x14:id>{8bdadc4f-6d93-4c45-a48d-c2869299329c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11189,11 +11366,85 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{413f3b43-7896-4c7a-a2b4-f207e15171fe}</x14:id>
+          <x14:id>{673e544d-8894-4fc3-a197-f35ea33dc948}</x14:id>
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="dataBar" priority="3736">
+    <cfRule type="dataBar" priority="3738">
+      <dataBar>
+        <cfvo type="percentile" val="1"/>
+        <cfvo type="percentile" val="100"/>
+        <color rgb="FFFFC000"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{4d377490-d59b-4332-af3f-da73565f9d87}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD62">
+    <cfRule type="dataBar" priority="3752">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFFFC000"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{9dcc16f2-2563-4136-b255-ead55e4f64df}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3754">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFFFB628"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{20836c02-3095-4d39-b1e0-cbdfdf20850f}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3755">
+      <dataBar>
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="1"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{3a9c2586-9524-48e6-b4e3-e4793ca77f19}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3756">
+      <dataBar>
+        <cfvo type="percentile" val="0"/>
+        <cfvo type="percentile" val="100"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{9194b549-efb1-4449-8d2a-c19c0fa1a603}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3757">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{ec5fd816-b684-416b-b8d0-bcd438e0e1cd}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3758">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -11201,81 +11452,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{be48e123-c720-4554-8b92-481c50a6d608}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3735">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{64b97f82-07ab-4555-9b25-33806174f4aa}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3734">
-      <dataBar>
-        <cfvo type="percentile" val="0"/>
-        <cfvo type="percentile" val="100"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e7c5c8ee-896f-40da-8d23-6fac859fefc8}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3733">
-      <dataBar>
-        <cfvo type="percent" val="0"/>
-        <cfvo type="percent" val="1"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f9954ab7-2b71-49f0-891b-13718f2d04ee}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3732">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FFFFB628"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{94828de4-fdbf-4993-8190-e5bee81ded8c}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3730">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FFFFC000"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ecb377ea-565f-422a-882e-10f0ccd68045}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD60">
-    <cfRule type="dataBar" priority="3760">
-      <dataBar>
-        <cfvo type="percentile" val="1"/>
-        <cfvo type="percentile" val="100"/>
-        <color rgb="FFFFC000"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ccde9b04-50f3-4d8f-9109-698352fa504f}</x14:id>
+          <x14:id>{ae1c7fdc-3583-43fe-a643-40fcee8d880d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11287,11 +11464,85 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{425cdd90-e149-4743-8cb9-d13997cc693e}</x14:id>
+          <x14:id>{b7d0c8ad-79d9-485d-96f2-c0fd547b5797}</x14:id>
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="dataBar" priority="3758">
+    <cfRule type="dataBar" priority="3760">
+      <dataBar>
+        <cfvo type="percentile" val="1"/>
+        <cfvo type="percentile" val="100"/>
+        <color rgb="FFFFC000"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{dbffe5e6-9a99-4713-b84b-224185c9bea5}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K63">
+    <cfRule type="dataBar" priority="3719">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFFFC000"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{c9836aef-56e4-4308-aa81-4975bc28c8aa}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3721">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFFFB628"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{4f03b995-96e3-4cad-86b1-a19d196d956f}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3722">
+      <dataBar>
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="1"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{e66765d7-fd81-4ca0-b791-0b4e4f821316}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3723">
+      <dataBar>
+        <cfvo type="percentile" val="0"/>
+        <cfvo type="percentile" val="100"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{e943295f-0c7a-4057-a716-fca669db8cbd}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3724">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{b65dda20-f4b3-4ddd-b307-2c4e8621ba90}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3725">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -11299,81 +11550,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e8132e68-d9b8-4820-a81d-8024bf847763}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3757">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6f4b5c5d-4b86-4dda-bed1-4f28af88df95}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3756">
-      <dataBar>
-        <cfvo type="percentile" val="0"/>
-        <cfvo type="percentile" val="100"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{014b3738-1455-4bba-8137-d527239f491d}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3755">
-      <dataBar>
-        <cfvo type="percent" val="0"/>
-        <cfvo type="percent" val="1"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c13531eb-6e16-4bcf-a325-e0ab6a7a70fe}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3754">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FFFFB628"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{97af7452-e13a-4934-8072-a4f4e3ab2091}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3752">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FFFFC000"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{80bae544-b473-4e51-840b-d25dd513fca6}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K61">
-    <cfRule type="dataBar" priority="3727">
-      <dataBar>
-        <cfvo type="percentile" val="1"/>
-        <cfvo type="percentile" val="100"/>
-        <color rgb="FFFFC000"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7e0bb419-a44b-420f-9bc7-c41df6576092}</x14:id>
+          <x14:id>{87673fc6-aff5-4cd5-8937-8ebfa3b25ac8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11385,11 +11562,85 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6daa88a2-5946-4a8f-9072-30a3da7134b1}</x14:id>
+          <x14:id>{7702302b-a4f7-4023-b972-1e591c44c741}</x14:id>
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="dataBar" priority="3725">
+    <cfRule type="dataBar" priority="3727">
+      <dataBar>
+        <cfvo type="percentile" val="1"/>
+        <cfvo type="percentile" val="100"/>
+        <color rgb="FFFFC000"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{db276c26-b88a-45f5-ae0f-f8699e86348f}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K64">
+    <cfRule type="dataBar" priority="3708">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFFFC000"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{332a349c-ba9c-44ae-b309-36f044f3b59c}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3710">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFFFB628"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{0ff3786b-d8c8-466d-b37f-be6e728b64cb}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3711">
+      <dataBar>
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="1"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{85162bb4-1156-41df-a6a1-5a9b7fd44c51}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3712">
+      <dataBar>
+        <cfvo type="percentile" val="0"/>
+        <cfvo type="percentile" val="100"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{e9dadf45-3852-4644-8175-f3d774c883b1}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3713">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{f92c8313-2d16-483a-b750-c5f8bde29a51}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3714">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -11397,81 +11648,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{38d3b4d4-556c-4345-96d0-66b5b5e008bc}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3724">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a10bb8c9-e06b-4c0f-b29d-52a7142dd532}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3723">
-      <dataBar>
-        <cfvo type="percentile" val="0"/>
-        <cfvo type="percentile" val="100"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{63fd2a73-a6bc-46dc-bfe4-708b47479130}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3722">
-      <dataBar>
-        <cfvo type="percent" val="0"/>
-        <cfvo type="percent" val="1"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{423c381b-3327-481b-a1c8-0be0dc3dd7c7}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3721">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FFFFB628"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{99d2f907-f453-4631-b097-8962dd9c8571}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3719">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FFFFC000"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3940b725-5f6b-49a7-852d-630ee9f11360}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K62">
-    <cfRule type="dataBar" priority="3716">
-      <dataBar>
-        <cfvo type="percentile" val="1"/>
-        <cfvo type="percentile" val="100"/>
-        <color rgb="FFFFC000"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ee61a247-903a-4dcb-ac81-9f79e4fe24de}</x14:id>
+          <x14:id>{1354f2bd-ed6f-48c6-9b32-1c63461643bf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11483,11 +11660,85 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c1331c78-0ea9-4a02-93c0-ee3c104e9dec}</x14:id>
+          <x14:id>{751d7f5b-ee3b-4eac-8d8d-f5629105a874}</x14:id>
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="dataBar" priority="3714">
+    <cfRule type="dataBar" priority="3716">
+      <dataBar>
+        <cfvo type="percentile" val="1"/>
+        <cfvo type="percentile" val="100"/>
+        <color rgb="FFFFC000"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{efea9994-7ebf-4f3b-afdf-4be1f3d3c3bb}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K65">
+    <cfRule type="dataBar" priority="3697">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFFFC000"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{9a7b94d4-0abe-4442-a079-80e6113e65aa}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3699">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFFFB628"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{d2723b4a-e9c7-4284-bf96-1b02f99c9f40}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3700">
+      <dataBar>
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="1"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{d0a9292a-cf53-466d-bb98-84a6b079abac}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3701">
+      <dataBar>
+        <cfvo type="percentile" val="0"/>
+        <cfvo type="percentile" val="100"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{656d8af9-a1a7-4187-b1ca-6f9fc987f9e3}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3702">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{d848efc1-5079-431c-b889-11c2b8128978}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3703">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -11495,81 +11746,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cb470beb-03ba-4230-9e68-451a4efa6b49}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3713">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{69988816-12c0-4880-bf4f-85ac3b2af1e6}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3712">
-      <dataBar>
-        <cfvo type="percentile" val="0"/>
-        <cfvo type="percentile" val="100"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7d39ffca-0bba-4b82-9efb-3c46bd95b7ac}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3711">
-      <dataBar>
-        <cfvo type="percent" val="0"/>
-        <cfvo type="percent" val="1"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d28d096b-29cc-4fb8-9449-8bb8a41f42ab}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3710">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FFFFB628"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{33cfe6f6-4502-4434-be7a-529dc6912d82}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3708">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FFFFC000"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{27da9c7c-0d5f-41ba-a954-46fe6dab835b}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K63">
-    <cfRule type="dataBar" priority="3705">
-      <dataBar>
-        <cfvo type="percentile" val="1"/>
-        <cfvo type="percentile" val="100"/>
-        <color rgb="FFFFC000"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e30a51a0-7679-443e-8749-19c769492fbb}</x14:id>
+          <x14:id>{d6c1169e-903a-4a43-b569-024053012600}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11581,71 +11758,25 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{67ea24d5-8b8e-4907-a60f-84169a5685ee}</x14:id>
+          <x14:id>{09202eaf-4698-468c-b0f4-4f7934a661c6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="dataBar" priority="3703">
+    <cfRule type="dataBar" priority="3705">
       <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+        <cfvo type="percentile" val="1"/>
+        <cfvo type="percentile" val="100"/>
         <color rgb="FFFFC000"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a4ed9d67-82d9-40ce-bdcd-b685c57ef1ee}</x14:id>
+          <x14:id>{cbb49d92-2bfe-4d5b-94d8-5e669449f4d4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="dataBar" priority="3702">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{37b6cf6a-7aae-450d-a8a0-08dfae7b91d2}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3701">
-      <dataBar>
-        <cfvo type="percentile" val="0"/>
-        <cfvo type="percentile" val="100"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5d876759-eca5-476a-b9b6-999ec0def28e}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3700">
-      <dataBar>
-        <cfvo type="percent" val="0"/>
-        <cfvo type="percent" val="1"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6a8b02f2-5886-408c-9109-4825bae2d3eb}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3699">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FFFFB628"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d907ce44-aacc-4a33-a618-24affbf50091}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3697">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB69">
+    <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="num" val="1"/>
@@ -11653,21 +11784,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{95eb10d7-62c6-4c77-832d-9769ce49cb31}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB67">
-    <cfRule type="dataBar" priority="6">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FF008AEF"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ddce36f7-baa5-4839-895f-bc92b0ec04d4}</x14:id>
+          <x14:id>{50ddb17c-8b0b-489d-b05a-8b6ed8eadc39}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11679,11 +11796,25 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{67c4e4e1-7f20-483c-9557-7db520e2d3d2}</x14:id>
+          <x14:id>{793ff324-a580-4faf-b775-ce2a0a32f947}</x14:id>
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="dataBar" priority="4">
+    <cfRule type="dataBar" priority="6">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FF008AEF"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{795875a8-2197-4ea1-a2db-68f8b88009a5}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB103">
+    <cfRule type="dataBar" priority="10">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="num" val="1"/>
@@ -11691,21 +11822,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{63fbdfaf-9e30-48ca-90ec-4a301a31e911}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB101">
-    <cfRule type="dataBar" priority="12">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FF008AEF"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7e65e85f-fa61-410c-a345-0a23c88a0035}</x14:id>
+          <x14:id>{6b838c8f-79f2-48a1-994c-879afe768f49}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11717,11 +11834,25 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bacaa9a8-e6d3-47e3-84a3-bdd70a1a56b4}</x14:id>
+          <x14:id>{e6e7d347-d4d0-4fe8-864c-ca973fface99}</x14:id>
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="dataBar" priority="10">
+    <cfRule type="dataBar" priority="12">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FF008AEF"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{945f2514-266e-4714-ae41-19452013187f}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB117">
+    <cfRule type="dataBar" priority="14">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="num" val="1"/>
@@ -11729,12 +11860,10 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e4c0f5c4-f169-494e-8af6-3e712d92e0de}</x14:id>
+          <x14:id>{49f721c3-43e3-42d6-88a4-6922da978388}</x14:id>
         </ext>
       </extLst>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB115">
     <cfRule type="dataBar" priority="15">
       <dataBar>
         <cfvo type="min"/>
@@ -11743,11 +11872,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fcda6376-3aaf-49c7-bac4-574a28c37293}</x14:id>
+          <x14:id>{775eeb1e-986d-4170-b7e9-1b7dbd146952}</x14:id>
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="dataBar" priority="14">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB127">
+    <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="num" val="1"/>
@@ -11755,21 +11886,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3eecc6f8-8560-47f8-ba06-cc20f7efd8e5}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB125">
-    <cfRule type="dataBar" priority="3">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FF008AEF"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ec5ef70d-ac43-425f-b229-a2b3e3c618ad}</x14:id>
+          <x14:id>{f3da6d2c-0058-49f7-891b-958eb706ca40}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11781,11 +11898,25 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ccd97f19-a002-415d-ac12-6ee67686bbe3}</x14:id>
+          <x14:id>{e669da9d-968a-4cb7-a0f8-de24d8b7204b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="dataBar" priority="1">
+    <cfRule type="dataBar" priority="3">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FF008AEF"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{73d7254b-8e4f-4eaa-910a-63b1cb687810}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K137">
+    <cfRule type="dataBar" priority="29">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="num" val="1"/>
@@ -11793,21 +11924,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e3b81819-ee72-4046-b137-7bc5715867b4}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K135">
-    <cfRule type="dataBar" priority="31">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FF008AEF"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5ef43eb2-0157-404d-90c5-947a8e7b0b5f}</x14:id>
+          <x14:id>{35190ae1-ddc7-4c8d-8458-af532f2cde6f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11819,11 +11936,25 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{61b7307b-a806-4a64-82df-6c65309f55e8}</x14:id>
+          <x14:id>{06b69c74-1b95-4997-b297-1f7cc576c3e6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="dataBar" priority="29">
+    <cfRule type="dataBar" priority="31">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FF008AEF"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{436a0d13-61f0-4be0-b5aa-22fc6eb8e6c1}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K142">
+    <cfRule type="dataBar" priority="32">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="num" val="1"/>
@@ -11831,21 +11962,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f74a1c6e-fdc4-4db4-92a8-803aef56e010}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K140">
-    <cfRule type="dataBar" priority="34">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FF008AEF"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{febed797-0e0f-47a1-a163-ab20968ceb01}</x14:id>
+          <x14:id>{706a3fcb-1d85-40b2-898e-fd06f3e2bcf0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11857,11 +11974,25 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a88de51a-989d-4738-86be-5e3332a68af1}</x14:id>
+          <x14:id>{231ca8ec-2eb4-4352-8e09-8a12a66c054f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="dataBar" priority="32">
+    <cfRule type="dataBar" priority="34">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FF008AEF"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{4e6d922e-0e9d-4bae-a172-645d781604e1}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K147">
+    <cfRule type="dataBar" priority="26">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="num" val="1"/>
@@ -11869,21 +12000,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{afefca44-d71b-4484-9f0b-684002a5e1db}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K145">
-    <cfRule type="dataBar" priority="28">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FF008AEF"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{219ced8e-8ca4-480a-8cdc-7482fa9b693f}</x14:id>
+          <x14:id>{c1437ea7-ec3a-48d8-873a-390dba8d7244}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11895,11 +12012,25 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6ecbd76b-ced0-4676-bcec-d7b9cf2955ce}</x14:id>
+          <x14:id>{c62a4a68-77e7-47b2-bf65-44fdcb3a6ba9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="dataBar" priority="26">
+    <cfRule type="dataBar" priority="28">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FF008AEF"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{308aaaf8-de3d-491d-8809-f9390adcd150}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K152">
+    <cfRule type="dataBar" priority="23">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="num" val="1"/>
@@ -11907,21 +12038,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4b6a12e6-0f5c-433f-aac3-b50c6e9d84f4}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K150">
-    <cfRule type="dataBar" priority="25">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FF008AEF"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{59675729-1197-43b9-be33-53035b524551}</x14:id>
+          <x14:id>{6e9531bb-ec62-46ba-9bfa-658ad9e5b0bb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11933,11 +12050,25 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c00acfc0-40a8-410c-864e-4926e5971cfa}</x14:id>
+          <x14:id>{4e0640a1-c697-4278-bd18-3640b683175e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="dataBar" priority="23">
+    <cfRule type="dataBar" priority="25">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FF008AEF"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{1dea3367-eacb-49a0-83c2-c9f651a841bf}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K59:K60">
+    <cfRule type="dataBar" priority="3741">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="num" val="1"/>
@@ -11945,21 +12076,67 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{46814940-472d-4e06-ae14-afe89bfeec27}</x14:id>
+          <x14:id>{b557506d-2332-4c67-912e-e6bdae802d34}</x14:id>
         </ext>
       </extLst>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K57:K58">
-    <cfRule type="dataBar" priority="3749">
+    <cfRule type="dataBar" priority="3743">
       <dataBar>
-        <cfvo type="percentile" val="1"/>
+        <cfvo type="min"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFFFB628"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{50feb3ad-3624-4d68-b2ee-b8b2446f41b8}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3744">
+      <dataBar>
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="1"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{a4bf74ed-cbfa-4b68-b0d5-d7975c80e69d}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3745">
+      <dataBar>
+        <cfvo type="percentile" val="0"/>
         <cfvo type="percentile" val="100"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{e73e25a9-b3d3-4109-adcd-318d50948973}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3746">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{be8ac6ba-d692-4685-948d-8b2b4c46042b}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="dataBar" priority="3747">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
         <color rgb="FFFFC000"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cd61534e-c359-42ec-9124-7ab6662beeab}</x14:id>
+          <x14:id>{2274d0da-65c8-4d66-930f-fc62421f30ed}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11971,71 +12148,25 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{53206ac7-b206-4703-ba3e-d5d9ca7a1e60}</x14:id>
+          <x14:id>{cd557e40-4a23-4200-852a-f07214b169e1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="dataBar" priority="3747">
+    <cfRule type="dataBar" priority="3749">
       <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
+        <cfvo type="percentile" val="1"/>
+        <cfvo type="percentile" val="100"/>
         <color rgb="FFFFC000"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0d19a157-b3ca-4e11-a9da-1cca2520040d}</x14:id>
+          <x14:id>{cbb84d30-4e47-4591-83dd-f60f47757922}</x14:id>
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="dataBar" priority="3746">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d3d0c212-5aee-448b-a070-242011708b42}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3745">
-      <dataBar>
-        <cfvo type="percentile" val="0"/>
-        <cfvo type="percentile" val="100"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c23fb9c6-9cba-4166-b9c3-3bd59f70aacd}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3744">
-      <dataBar>
-        <cfvo type="percent" val="0"/>
-        <cfvo type="percent" val="1"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{105fec82-8b11-42e8-9226-379598cbd966}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3743">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FFFFB628"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{efa4a397-cb44-49a6-bae4-eeebb70903f0}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="3741">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y69:Y88">
+    <cfRule type="dataBar" priority="21">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="num" val="1"/>
@@ -12043,12 +12174,10 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f3e7e016-af16-450b-8df3-004215913877}</x14:id>
+          <x14:id>{63a08510-99d1-455f-9ac2-933b5d813967}</x14:id>
         </ext>
       </extLst>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y67:Y86">
     <cfRule type="dataBar" priority="22">
       <dataBar>
         <cfvo type="min"/>
@@ -12057,24 +12186,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d44df94a-5076-49cb-9936-4cf621eddc2d}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="21">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FFFFC000"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{da92200c-761e-443f-a4c4-db192f1101f5}</x14:id>
+          <x14:id>{3e43d9ad-f536-4b93-be9d-40b883fd13d0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y77:Y86">
+  <conditionalFormatting sqref="Y79:Y88">
     <cfRule type="dataBar" priority="20">
       <dataBar>
         <cfvo type="min"/>
@@ -12083,12 +12200,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{33d980ea-ba16-4745-846b-05c28897ee53}</x14:id>
+          <x14:id>{5f9bcfac-43de-4c82-983b-df2034727220}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB115:AB124">
+  <conditionalFormatting sqref="AB117:AB126">
     <cfRule type="dataBar" priority="13">
       <dataBar>
         <cfvo type="min"/>
@@ -12097,12 +12214,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7439dea7-d912-43cd-9e6f-0566a6c2d96d}</x14:id>
+          <x14:id>{8ac50690-eb3e-436a-bb90-364a1ef77013}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD56:AE57">
+  <conditionalFormatting sqref="AD58:AE59">
     <cfRule type="dataBar" priority="3762">
       <dataBar>
         <cfvo type="min"/>
@@ -12111,12 +12228,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{eb2cbcf3-61a9-4816-a085-2e25b96b3b72}</x14:id>
+          <x14:id>{8d01d611-0c1a-4df7-99bf-9a4f7500aa65}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD60:AE63">
+  <conditionalFormatting sqref="AD62:AE65">
     <cfRule type="dataBar" priority="3751">
       <dataBar>
         <cfvo type="min"/>
@@ -12125,21 +12242,21 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b5527b5a-6839-496c-a30a-1fc5a054ce8b}</x14:id>
+          <x14:id>{06bc5bb0-3a29-4b18-bc3a-64698600c1fe}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F67 F72 F77 F82">
-    <cfRule type="dataBar" priority="49">
+  <conditionalFormatting sqref="F69 F74 F79 F84">
+    <cfRule type="dataBar" priority="47">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="num" val="1"/>
-        <color rgb="FF008AEF"/>
+        <color rgb="FFFFC000"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1f453ab6-9401-4b9a-8c0b-e183e45668c8}</x14:id>
+          <x14:id>{5902d624-66be-4b22-937f-1f9ac871a476}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12151,11 +12268,25 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9029ff62-fed7-4b8f-a2e3-5b3cd0d2d2b6}</x14:id>
+          <x14:id>{9141eac8-21c4-45ec-88df-70bc8ffe0dba}</x14:id>
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="dataBar" priority="47">
+    <cfRule type="dataBar" priority="49">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FF008AEF"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{9e9d23a1-8322-4080-aa88-9e8d6e6e8ddf}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K69 K79 K89 K103">
+    <cfRule type="dataBar" priority="38">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="num" val="1"/>
@@ -12163,21 +12294,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{55700e31-1604-4d75-a8e6-1418f9c04a3c}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K67 K77 K87 K101">
-    <cfRule type="dataBar" priority="40">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FF008AEF"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{14ede531-c5db-43d2-8058-12dfe39155bb}</x14:id>
+          <x14:id>{e9fcbe0b-2a6f-4291-bb5d-999e5c13b8c6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12189,11 +12306,25 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a3b3d226-9b0b-44c5-bceb-37746fbcf4de}</x14:id>
+          <x14:id>{02498975-8e3b-4555-8b2a-27d512282a33}</x14:id>
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="dataBar" priority="38">
+    <cfRule type="dataBar" priority="40">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FF008AEF"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{f22738fc-b7a1-4b66-ac0a-2df173d21147}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB79 AB89">
+    <cfRule type="dataBar" priority="7">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="num" val="1"/>
@@ -12201,21 +12332,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c3c89555-ed8f-41d9-a02c-4007520a3107}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB77 AB87">
-    <cfRule type="dataBar" priority="9">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FF008AEF"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{42704703-c3fb-404b-94ac-cabaf5a19789}</x14:id>
+          <x14:id>{9fc64bf2-4283-4e67-acbc-a6cd9b17cd1d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12227,11 +12344,25 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d87782a6-9d1a-43c7-bc36-b238a9431d48}</x14:id>
+          <x14:id>{91f69053-db54-4ce6-8ec5-ff34b0c6a9de}</x14:id>
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="dataBar" priority="7">
+    <cfRule type="dataBar" priority="9">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FF008AEF"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{2ccd3aa7-106f-4180-9e53-76f7f699ec68}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F89 F96 F103 F110">
+    <cfRule type="dataBar" priority="44">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="num" val="1"/>
@@ -12239,21 +12370,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{564ee706-1991-4484-ab96-d058d3943360}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F87 F94 F101 F108">
-    <cfRule type="dataBar" priority="46">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FF008AEF"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{555b2b3e-60db-4156-91e7-90fcd85e4435}</x14:id>
+          <x14:id>{25470856-6f23-4593-8ec4-f86affb01ee0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12265,11 +12382,25 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{99b6cbf4-2ff7-4b85-843c-43a322d3f964}</x14:id>
+          <x14:id>{0839ac72-afc6-4229-9e68-09b9356349d3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="dataBar" priority="44">
+    <cfRule type="dataBar" priority="46">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FF008AEF"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{e37b83ed-9c68-45e0-b4eb-444c9bc888b3}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y89 Y103">
+    <cfRule type="dataBar" priority="18">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="num" val="1"/>
@@ -12277,12 +12408,10 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f2315674-98bd-4099-81f1-93475eb6c314}</x14:id>
+          <x14:id>{00cfb6ef-13e0-4395-b33b-0513f6ae6320}</x14:id>
         </ext>
       </extLst>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y87 Y101">
     <cfRule type="dataBar" priority="19">
       <dataBar>
         <cfvo type="min"/>
@@ -12291,11 +12420,13 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{eda8be22-ff95-4c9e-a4fd-0050de9d5e69}</x14:id>
+          <x14:id>{86936f7d-2a48-4bd5-9abe-940fc10c68a4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="dataBar" priority="18">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F117 F122 F127 F132 F137 F142 F147 F152">
+    <cfRule type="dataBar" priority="41">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="num" val="1"/>
@@ -12303,21 +12434,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a9cf91ef-35f7-420d-b299-112229bec113}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F115 F120 F125 F130 F135 F140 F145 F150">
-    <cfRule type="dataBar" priority="43">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FF008AEF"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3a480aac-6b3d-430f-b546-5fef7b6091db}</x14:id>
+          <x14:id>{8378c0a3-1189-4703-9bb8-28d85b14e686}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12329,11 +12446,25 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3a2efc8a-9d07-42cc-9580-4e7bc2c67214}</x14:id>
+          <x14:id>{dcbe0761-6206-4cad-b35b-c7883721cdc1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="dataBar" priority="41">
+    <cfRule type="dataBar" priority="43">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FF008AEF"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{5ae50ee2-7ea8-4cd9-a668-736ace3fd960}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K117 K127">
+    <cfRule type="dataBar" priority="35">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="num" val="1"/>
@@ -12341,21 +12472,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5908bf54-8df8-4a8d-8d72-0d1d755f12a1}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K115 K125">
-    <cfRule type="dataBar" priority="37">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FF008AEF"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bd6a70f5-bbfa-478b-84ff-8ea1b5b4e2dc}</x14:id>
+          <x14:id>{8a42bb25-8a8a-4eb1-b363-b34dae49c8e9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12367,11 +12484,25 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8326a89f-9aa6-446c-834e-8c3f20e40933}</x14:id>
+          <x14:id>{c909e2ce-ba4f-4b08-8248-09e330ec0f70}</x14:id>
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="dataBar" priority="35">
+    <cfRule type="dataBar" priority="37">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FF008AEF"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{81ecb00b-3b42-40b9-acb8-8ba0f5c396b7}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y117 Y127">
+    <cfRule type="dataBar" priority="16">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="num" val="1"/>
@@ -12379,12 +12510,10 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c976b550-afd6-4b18-9e85-00b2a3539b69}</x14:id>
+          <x14:id>{dc34360e-ce4c-4a57-8132-20b34c230b4c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y115 Y125">
     <cfRule type="dataBar" priority="17">
       <dataBar>
         <cfvo type="min"/>
@@ -12393,19 +12522,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8e644aa3-eed9-4e9c-bc3b-1b263fc0fd90}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="dataBar" priority="16">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FFFFC000"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f21c43e7-f549-43c5-9b24-b7f83871fd01}</x14:id>
+          <x14:id>{74322a95-9f58-4b91-82df-432823bc7208}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12427,7 +12544,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G6:I6 P6:R6">
       <formula1>"A班,B班,C班,D班"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A20:B49 A11:B18">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A51:B51 A11:B18 A20:B48 A49:B50">
       <formula1>"A楼,B楼,C楼,D楼,E楼"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12439,7 +12556,76 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1e8b3770-52de-4a9b-8834-7c638ac4741c}">
+          <x14:cfRule type="dataBar" id="{1da3db35-e0de-4637-8cac-3c85e7214f3c}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{474b9d92-1ffe-4115-82c8-ec6b40fcd5a4}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{e0ce3279-baf1-47aa-91c5-0b8563f222a0}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{1e5930d1-e00e-452d-8fa3-dae07de9dcf7}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="percentile">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percentile">
+                <xm:f>100</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{eeccbae5-276b-43f8-a71f-e2eb915fb9bc}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{556339b3-d1ef-439b-99d2-f8eb96afb18e}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="max"/>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{2db46e07-ff34-4840-bd4a-135b2336675c}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>100</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{6521ab67-9f01-402a-97c0-0d915b92a321}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12450,7 +12636,68 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3787be42-499c-486c-a521-c3e6d6293ebb}">
+          <xm:sqref>AD58</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{9faa95e9-88d2-4727-86b2-0fb536804f95}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{2587a784-9c20-4dcb-b833-c69f805759f0}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{43d832dc-c892-4954-b2c1-6b501a9267f2}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{af39b56f-c4b5-4572-9790-21a3c54b81c8}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="percentile">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percentile">
+                <xm:f>100</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{0bcb0cd1-0bdc-477e-8a9b-33867e2f0fba}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{8bdadc4f-6d93-4c45-a48d-c2869299329c}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="max"/>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{673e544d-8894-4fc3-a197-f35ea33dc948}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12461,14 +12708,61 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{45157450-b856-44a7-9e1f-77adb7a00daf}">
+          <x14:cfRule type="dataBar" id="{4d377490-d59b-4332-af3f-da73565f9d87}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="max"/>
+              <x14:cfvo type="percentile">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percentile">
+                <xm:f>100</xm:f>
+              </x14:cfvo>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c13c4471-d64d-41b5-8ad4-1a756db2ee8e}">
+          <xm:sqref>K62</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{9dcc16f2-2563-4136-b255-ead55e4f64df}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{20836c02-3095-4d39-b1e0-cbdfdf20850f}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{3a9c2586-9524-48e6-b4e3-e4793ca77f19}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{9194b549-efb1-4449-8d2a-c19c0fa1a603}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="percentile">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percentile">
+                <xm:f>100</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{ec5fd816-b684-416b-b8d0-bcd438e0e1cd}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12479,7 +12773,68 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{16aef48e-1ce1-486e-923f-f5f5bd01be3e}">
+          <x14:cfRule type="dataBar" id="{ae1c7fdc-3583-43fe-a643-40fcee8d880d}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="max"/>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{b7d0c8ad-79d9-485d-96f2-c0fd547b5797}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>100</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{dbffe5e6-9a99-4713-b84b-224185c9bea5}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="percentile">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percentile">
+                <xm:f>100</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>AD62</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{c9836aef-56e4-4308-aa81-4975bc28c8aa}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{4f03b995-96e3-4cad-86b1-a19d196d956f}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{e66765d7-fd81-4ca0-b791-0b4e4f821316}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{e943295f-0c7a-4057-a716-fca669db8cbd}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12490,7 +12845,68 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e2e030aa-49db-40d0-84aa-d8ea4206d4a8}">
+          <x14:cfRule type="dataBar" id="{b65dda20-f4b3-4ddd-b307-2c4e8621ba90}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{87673fc6-aff5-4cd5-8937-8ebfa3b25ac8}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="max"/>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{7702302b-a4f7-4023-b972-1e591c44c741}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>100</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{db276c26-b88a-45f5-ae0f-f8699e86348f}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="percentile">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percentile">
+                <xm:f>100</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>K63</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{332a349c-ba9c-44ae-b309-36f044f3b59c}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{0ff3786b-d8c8-466d-b37f-be6e728b64cb}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{85162bb4-1156-41df-a6a1-5a9b7fd44c51}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12501,28 +12917,47 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{da41cb00-9115-4e63-b397-891482f467b4}">
+          <x14:cfRule type="dataBar" id="{e9dadf45-3852-4644-8175-f3d774c883b1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
+              <x14:cfvo type="percentile">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percentile">
+                <xm:f>100</xm:f>
               </x14:cfvo>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6cdfcf5e-47e0-476b-8a57-9b8dfca04074}">
+          <x14:cfRule type="dataBar" id="{f92c8313-2d16-483a-b750-c5f8bde29a51}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
               <x14:cfvo type="num">
-                <xm:f>1</xm:f>
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
               </x14:cfvo>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>AD56</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0344c197-1e9e-4c7e-ac5c-16b950aa3cbe}">
+          <x14:cfRule type="dataBar" id="{1354f2bd-ed6f-48c6-9b32-1c63461643bf}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="max"/>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{751d7f5b-ee3b-4eac-8d8d-f5629105a874}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>100</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{efea9994-7ebf-4f3b-afdf-4be1f3d3c3bb}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12533,7 +12968,68 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{413f3b43-7896-4c7a-a2b4-f207e15171fe}">
+          <xm:sqref>K64</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{9a7b94d4-0abe-4442-a079-80e6113e65aa}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{d2723b4a-e9c7-4284-bf96-1b02f99c9f40}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{d0a9292a-cf53-466d-bb98-84a6b079abac}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{656d8af9-a1a7-4187-b1ca-6f9fc987f9e3}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="percentile">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percentile">
+                <xm:f>100</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{d848efc1-5079-431c-b889-11c2b8128978}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{d6c1169e-903a-4a43-b569-024053012600}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="max"/>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{09202eaf-4698-468c-b0f4-4f7934a661c6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12544,14 +13040,299 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{be48e123-c720-4554-8b92-481c50a6d608}">
+          <x14:cfRule type="dataBar" id="{cbb49d92-2bfe-4d5b-94d8-5e669449f4d4}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="max"/>
+              <x14:cfvo type="percentile">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percentile">
+                <xm:f>100</xm:f>
+              </x14:cfvo>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{64b97f82-07ab-4555-9b25-33806174f4aa}">
+          <xm:sqref>K65</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{50ddb17c-8b0b-489d-b05a-8b6ed8eadc39}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{793ff324-a580-4faf-b775-ce2a0a32f947}">
+            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{795875a8-2197-4ea1-a2db-68f8b88009a5}">
+            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>AB69</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{6b838c8f-79f2-48a1-994c-879afe768f49}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{e6e7d347-d4d0-4fe8-864c-ca973fface99}">
+            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{945f2514-266e-4714-ae41-19452013187f}">
+            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>AB103</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{49f721c3-43e3-42d6-88a4-6922da978388}">
+            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{775eeb1e-986d-4170-b7e9-1b7dbd146952}">
+            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>AB117</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{f3da6d2c-0058-49f7-891b-958eb706ca40}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{e669da9d-968a-4cb7-a0f8-de24d8b7204b}">
+            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{73d7254b-8e4f-4eaa-910a-63b1cb687810}">
+            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>AB127</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{35190ae1-ddc7-4c8d-8458-af532f2cde6f}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{06b69c74-1b95-4997-b297-1f7cc576c3e6}">
+            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{436a0d13-61f0-4be0-b5aa-22fc6eb8e6c1}">
+            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>K137</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{706a3fcb-1d85-40b2-898e-fd06f3e2bcf0}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{231ca8ec-2eb4-4352-8e09-8a12a66c054f}">
+            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{4e6d922e-0e9d-4bae-a172-645d781604e1}">
+            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>K142</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{c1437ea7-ec3a-48d8-873a-390dba8d7244}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{c62a4a68-77e7-47b2-bf65-44fdcb3a6ba9}">
+            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{308aaaf8-de3d-491d-8809-f9390adcd150}">
+            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>K147</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{6e9531bb-ec62-46ba-9bfa-658ad9e5b0bb}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{4e0640a1-c697-4278-bd18-3640b683175e}">
+            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{1dea3367-eacb-49a0-83c2-c9f651a841bf}">
+            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>K152</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{b557506d-2332-4c67-912e-e6bdae802d34}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{50feb3ad-3624-4d68-b2ee-b8b2446f41b8}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{a4bf74ed-cbfa-4b68-b0d5-d7975c80e69d}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{e73e25a9-b3d3-4109-adcd-318d50948973}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="percentile">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percentile">
+                <xm:f>100</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{be8ac6ba-d692-4685-948d-8b2b4c46042b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12562,50 +13343,25 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e7c5c8ee-896f-40da-8d23-6fac859fefc8}">
+          <x14:cfRule type="dataBar" id="{2274d0da-65c8-4d66-930f-fc62421f30ed}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="percentile">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="max"/>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{cd557e40-4a23-4200-852a-f07214b169e1}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
               </x14:cfvo>
-              <x14:cfvo type="percentile">
+              <x14:cfvo type="percent">
                 <xm:f>100</xm:f>
               </x14:cfvo>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f9954ab7-2b71-49f0-891b-13718f2d04ee}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="percent">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{94828de4-fdbf-4993-8190-e5bee81ded8c}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ecb377ea-565f-422a-882e-10f0ccd68045}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>K60</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ccde9b04-50f3-4d8f-9109-698352fa504f}">
+          <x14:cfRule type="dataBar" id="{cbb84d30-4e47-4591-83dd-f60f47757922}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12616,346 +13372,10 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{425cdd90-e149-4743-8cb9-d13997cc693e}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="percent">
-                <xm:f>100</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e8132e68-d9b8-4820-a81d-8024bf847763}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="max"/>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6f4b5c5d-4b86-4dda-bed1-4f28af88df95}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{014b3738-1455-4bba-8137-d527239f491d}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="percentile">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="percentile">
-                <xm:f>100</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c13531eb-6e16-4bcf-a325-e0ab6a7a70fe}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="percent">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{97af7452-e13a-4934-8072-a4f4e3ab2091}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{80bae544-b473-4e51-840b-d25dd513fca6}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>AD60</xm:sqref>
+          <xm:sqref>K59:K60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7e0bb419-a44b-420f-9bc7-c41df6576092}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="percentile">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="percentile">
-                <xm:f>100</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6daa88a2-5946-4a8f-9072-30a3da7134b1}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="percent">
-                <xm:f>100</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{38d3b4d4-556c-4345-96d0-66b5b5e008bc}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="max"/>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a10bb8c9-e06b-4c0f-b29d-52a7142dd532}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{63fd2a73-a6bc-46dc-bfe4-708b47479130}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="percentile">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="percentile">
-                <xm:f>100</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{423c381b-3327-481b-a1c8-0be0dc3dd7c7}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="percent">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{99d2f907-f453-4631-b097-8962dd9c8571}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3940b725-5f6b-49a7-852d-630ee9f11360}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>K61</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ee61a247-903a-4dcb-ac81-9f79e4fe24de}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="percentile">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="percentile">
-                <xm:f>100</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c1331c78-0ea9-4a02-93c0-ee3c104e9dec}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="percent">
-                <xm:f>100</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{cb470beb-03ba-4230-9e68-451a4efa6b49}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="max"/>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{69988816-12c0-4880-bf4f-85ac3b2af1e6}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7d39ffca-0bba-4b82-9efb-3c46bd95b7ac}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="percentile">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="percentile">
-                <xm:f>100</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d28d096b-29cc-4fb8-9449-8bb8a41f42ab}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="percent">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{33cfe6f6-4502-4434-be7a-529dc6912d82}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{27da9c7c-0d5f-41ba-a954-46fe6dab835b}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>K62</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e30a51a0-7679-443e-8749-19c769492fbb}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="percentile">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="percentile">
-                <xm:f>100</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{67ea24d5-8b8e-4907-a60f-84169a5685ee}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="percent">
-                <xm:f>100</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a4ed9d67-82d9-40ce-bdcd-b685c57ef1ee}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="max"/>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{37b6cf6a-7aae-450d-a8a0-08dfae7b91d2}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5d876759-eca5-476a-b9b6-999ec0def28e}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="percentile">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="percentile">
-                <xm:f>100</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6a8b02f2-5886-408c-9109-4825bae2d3eb}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="percent">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d907ce44-aacc-4a33-a618-24affbf50091}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{95eb10d7-62c6-4c77-832d-9769ce49cb31}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>K63</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ddce36f7-baa5-4839-895f-bc92b0ec04d4}">
-            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{67c4e4e1-7f20-483c-9557-7db520e2d3d2}">
-            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{63fbdfaf-9e30-48ca-90ec-4a301a31e911}">
+          <x14:cfRule type="dataBar" id="{63a08510-99d1-455f-9ac2-933b5d813967}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -12965,10 +13385,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>AB67</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7e65e85f-fa61-410c-a345-0a23c88a0035}">
+          <x14:cfRule type="dataBar" id="{3e43d9ad-f536-4b93-be9d-40b883fd13d0}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12977,16 +13394,10 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{bacaa9a8-e6d3-47e3-84a3-bdd70a1a56b4}">
-            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e4c0f5c4-f169-494e-8af6-3e712d92e0de}">
+          <xm:sqref>Y69:Y88</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{5f9bcfac-43de-4c82-983b-df2034727220}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -12996,49 +13407,10 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>AB101</xm:sqref>
+          <xm:sqref>Y79:Y88</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fcda6376-3aaf-49c7-bac4-574a28c37293}">
-            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3eecc6f8-8560-47f8-ba06-cc20f7efd8e5}">
-            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>AB115</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ec5ef70d-ac43-425f-b229-a2b3e3c618ad}">
-            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ccd97f19-a002-415d-ac12-6ee67686bbe3}">
-            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e3b81819-ee72-4046-b137-7bc5715867b4}">
+          <x14:cfRule type="dataBar" id="{8ac50690-eb3e-436a-bb90-364a1ef77013}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13048,11 +13420,11 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>AB125</xm:sqref>
+          <xm:sqref>AB117:AB126</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5ef43eb2-0157-404d-90c5-947a8e7b0b5f}">
-            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
+          <x14:cfRule type="dataBar" id="{8d01d611-0c1a-4df7-99bf-9a4f7500aa65}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
                 <xm:f>1</xm:f>
@@ -13060,8 +13432,11 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{61b7307b-a806-4a64-82df-6c65309f55e8}">
-            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
+          <xm:sqref>AD58:AE59</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{06bc5bb0-3a29-4b18-bc3a-64698600c1fe}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
                 <xm:f>1</xm:f>
@@ -13069,7 +13444,10 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f74a1c6e-fdc4-4db4-92a8-803aef56e010}">
+          <xm:sqref>AD62:AE65</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{5902d624-66be-4b22-937f-1f9ac871a476}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13079,10 +13457,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>K135</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{febed797-0e0f-47a1-a163-ab20968ceb01}">
+          <x14:cfRule type="dataBar" id="{9141eac8-21c4-45ec-88df-70bc8ffe0dba}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13091,7 +13466,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a88de51a-989d-4738-86be-5e3332a68af1}">
+          <x14:cfRule type="dataBar" id="{9e9d23a1-8322-4080-aa88-9e8d6e6e8ddf}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13100,7 +13475,10 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{afefca44-d71b-4484-9f0b-684002a5e1db}">
+          <xm:sqref>F69 F74 F79 F84</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{e9fcbe0b-2a6f-4291-bb5d-999e5c13b8c6}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13110,10 +13488,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>K140</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{219ced8e-8ca4-480a-8cdc-7482fa9b693f}">
+          <x14:cfRule type="dataBar" id="{02498975-8e3b-4555-8b2a-27d512282a33}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13122,7 +13497,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6ecbd76b-ced0-4676-bcec-d7b9cf2955ce}">
+          <x14:cfRule type="dataBar" id="{f22738fc-b7a1-4b66-ac0a-2df173d21147}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13131,7 +13506,10 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4b6a12e6-0f5c-433f-aac3-b50c6e9d84f4}">
+          <xm:sqref>K69 K79 K89 K103</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{9fc64bf2-4283-4e67-acbc-a6cd9b17cd1d}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13141,10 +13519,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>K145</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{59675729-1197-43b9-be33-53035b524551}">
+          <x14:cfRule type="dataBar" id="{91f69053-db54-4ce6-8ec5-ff34b0c6a9de}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13153,7 +13528,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c00acfc0-40a8-410c-864e-4926e5971cfa}">
+          <x14:cfRule type="dataBar" id="{2ccd3aa7-106f-4180-9e53-76f7f699ec68}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13162,7 +13537,10 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{46814940-472d-4e06-ae14-afe89bfeec27}">
+          <xm:sqref>AB79 AB89</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{25470856-6f23-4593-8ec4-f86affb01ee0}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13172,93 +13550,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>K150</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cd61534e-c359-42ec-9124-7ab6662beeab}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="percentile">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="percentile">
-                <xm:f>100</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{53206ac7-b206-4703-ba3e-d5d9ca7a1e60}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="percent">
-                <xm:f>100</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0d19a157-b3ca-4e11-a9da-1cca2520040d}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="max"/>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d3d0c212-5aee-448b-a070-242011708b42}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c23fb9c6-9cba-4166-b9c3-3bd59f70aacd}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="percentile">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="percentile">
-                <xm:f>100</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{105fec82-8b11-42e8-9226-379598cbd966}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="percent">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{efa4a397-cb44-49a6-bae4-eeebb70903f0}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f3e7e016-af16-450b-8df3-004215913877}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>K57:K58</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d44df94a-5076-49cb-9936-4cf621eddc2d}">
+          <x14:cfRule type="dataBar" id="{0839ac72-afc6-4229-9e68-09b9356349d3}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13267,7 +13559,19 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{da92200c-761e-443f-a4c4-db192f1101f5}">
+          <x14:cfRule type="dataBar" id="{e37b83ed-9c68-45e0-b4eb-444c9bc888b3}">
+            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F89 F96 F103 F110</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{00cfb6ef-13e0-4395-b33b-0513f6ae6320}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13277,10 +13581,19 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>Y67:Y86</xm:sqref>
+          <x14:cfRule type="dataBar" id="{86936f7d-2a48-4bd5-9abe-940fc10c68a4}">
+            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>Y89 Y103</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{33d980ea-ba16-4745-846b-05c28897ee53}">
+          <x14:cfRule type="dataBar" id="{8378c0a3-1189-4703-9bb8-28d85b14e686}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13290,10 +13603,28 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>Y77:Y86</xm:sqref>
+          <x14:cfRule type="dataBar" id="{dcbe0761-6206-4cad-b35b-c7883721cdc1}">
+            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{5ae50ee2-7ea8-4cd9-a668-736ace3fd960}">
+            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F117 F122 F127 F132 F137 F142 F147 F152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7439dea7-d912-43cd-9e6f-0566a6c2d96d}">
+          <x14:cfRule type="dataBar" id="{8a42bb25-8a8a-4eb1-b363-b34dae49c8e9}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13303,34 +13634,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>AB115:AB124</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{eb2cbcf3-61a9-4816-a085-2e25b96b3b72}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>AD56:AE57</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b5527b5a-6839-496c-a30a-1fc5a054ce8b}">
-            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>AD60:AE63</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1f453ab6-9401-4b9a-8c0b-e183e45668c8}">
+          <x14:cfRule type="dataBar" id="{c909e2ce-ba4f-4b08-8248-09e330ec0f70}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13339,7 +13643,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9029ff62-fed7-4b8f-a2e3-5b3cd0d2d2b6}">
+          <x14:cfRule type="dataBar" id="{81ecb00b-3b42-40b9-acb8-8ba0f5c396b7}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13348,7 +13652,10 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{55700e31-1604-4d75-a8e6-1418f9c04a3c}">
+          <xm:sqref>K117 K127</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{dc34360e-ce4c-4a57-8132-20b34c230b4c}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13358,10 +13665,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>F67 F72 F77 F82</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{14ede531-c5db-43d2-8058-12dfe39155bb}">
+          <x14:cfRule type="dataBar" id="{74322a95-9f58-4b91-82df-432823bc7208}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13370,194 +13674,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a3b3d226-9b0b-44c5-bceb-37746fbcf4de}">
-            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c3c89555-ed8f-41d9-a02c-4007520a3107}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>K67 K77 K87 K101</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{42704703-c3fb-404b-94ac-cabaf5a19789}">
-            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d87782a6-9d1a-43c7-bc36-b238a9431d48}">
-            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{564ee706-1991-4484-ab96-d058d3943360}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>AB77 AB87</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{555b2b3e-60db-4156-91e7-90fcd85e4435}">
-            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{99b6cbf4-2ff7-4b85-843c-43a322d3f964}">
-            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f2315674-98bd-4099-81f1-93475eb6c314}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>F87 F94 F101 F108</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{eda8be22-ff95-4c9e-a4fd-0050de9d5e69}">
-            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a9cf91ef-35f7-420d-b299-112229bec113}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>Y87 Y101</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3a480aac-6b3d-430f-b546-5fef7b6091db}">
-            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3a2efc8a-9d07-42cc-9580-4e7bc2c67214}">
-            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5908bf54-8df8-4a8d-8d72-0d1d755f12a1}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>F115 F120 F125 F130 F135 F140 F145 F150</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bd6a70f5-bbfa-478b-84ff-8ea1b5b4e2dc}">
-            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8326a89f-9aa6-446c-834e-8c3f20e40933}">
-            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c976b550-afd6-4b18-9e85-00b2a3539b69}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>K115 K125</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8e644aa3-eed9-4e9c-bc3b-1b263fc0fd90}">
-            <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
-              <x14:cfvo type="min"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:axisColor indexed="65"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f21c43e7-f549-43c5-9b24-b7f83871fd01}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>Y115 Y125</xm:sqref>
+          <xm:sqref>Y117 Y127</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -13569,73 +13686,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="26.8796296296296" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.37962962962963" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.22222222222222" style="1" customWidth="1"/>
-    <col min="18" max="18" width="9.37962962962963" style="1" customWidth="1"/>
+    <col min="1" max="1" width="26.8818181818182" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.38181818181818" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.21818181818182" style="1" customWidth="1"/>
+    <col min="18" max="18" width="9.38181818181818" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B2" s="4">
         <v>36.11</v>
@@ -13689,7 +13806,7 @@
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B3" s="6">
         <v>12689.5</v>
@@ -13746,7 +13863,7 @@
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:18">
       <c r="A4" s="9" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B4" s="7">
         <f t="shared" ref="B4:O4" si="0">B3*0.86/1000</f>
@@ -13817,7 +13934,7 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>

--- a/外网端源码/其他楼交接班容量报表空模板.xlsx
+++ b/外网端源码/其他楼交接班容量报表空模板.xlsx
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="389">
   <si>
     <t>班次</t>
   </si>
@@ -758,6 +758,9 @@
   </si>
   <si>
     <t>-201-RPP-DC-1</t>
+  </si>
+  <si>
+    <t>0</t>
   </si>
   <si>
     <t xml:space="preserve"> -218-HVDC-121</t>
@@ -2433,7 +2436,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="158">
+  <cellXfs count="160">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2827,7 +2830,13 @@
     <xf numFmtId="49" fontId="21" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="22" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4324,7 +4333,10 @@
       <c r="M26" s="84" t="s">
         <v>83</v>
       </c>
-      <c r="N26" s="93"/>
+      <c r="N26" s="93">
+        <f>I29</f>
+        <v>0</v>
+      </c>
       <c r="O26" s="55"/>
       <c r="P26" s="84" t="s">
         <v>78</v>
@@ -4353,7 +4365,10 @@
       <c r="Z26" s="84" t="s">
         <v>83</v>
       </c>
-      <c r="AA26" s="93"/>
+      <c r="AA26" s="93">
+        <f>V29</f>
+        <v>0</v>
+      </c>
       <c r="AB26" s="89" t="s">
         <v>84</v>
       </c>
@@ -4414,7 +4429,9 @@
       <c r="E28" s="84" t="s">
         <v>86</v>
       </c>
-      <c r="F28" s="74"/>
+      <c r="F28" s="74">
+        <v>18</v>
+      </c>
       <c r="G28" s="15"/>
       <c r="H28" s="84" t="s">
         <v>87</v>
@@ -4442,7 +4459,9 @@
       <c r="R28" s="84" t="s">
         <v>86</v>
       </c>
-      <c r="S28" s="74"/>
+      <c r="S28" s="74">
+        <v>18</v>
+      </c>
       <c r="T28" s="15"/>
       <c r="U28" s="84" t="s">
         <v>87</v>
@@ -4884,7 +4903,10 @@
       <c r="M36" s="104" t="s">
         <v>83</v>
       </c>
-      <c r="N36" s="107"/>
+      <c r="N36" s="107">
+        <f>I39</f>
+        <v>0</v>
+      </c>
       <c r="O36" s="55"/>
       <c r="P36" s="104" t="s">
         <v>78</v>
@@ -4917,7 +4939,10 @@
       <c r="Z36" s="104" t="s">
         <v>83</v>
       </c>
-      <c r="AA36" s="106"/>
+      <c r="AA36" s="106">
+        <f>V39</f>
+        <v>0</v>
+      </c>
       <c r="AB36" s="89" t="s">
         <v>104</v>
       </c>
@@ -4980,8 +5005,8 @@
       <c r="E38" s="104" t="s">
         <v>86</v>
       </c>
-      <c r="F38" s="106" t="s">
-        <v>15</v>
+      <c r="F38" s="106">
+        <v>18</v>
       </c>
       <c r="G38" s="15"/>
       <c r="H38" s="104" t="s">
@@ -5014,8 +5039,8 @@
       <c r="R38" s="104" t="s">
         <v>86</v>
       </c>
-      <c r="S38" s="106" t="s">
-        <v>15</v>
+      <c r="S38" s="106">
+        <v>18</v>
       </c>
       <c r="T38" s="15"/>
       <c r="U38" s="104" t="s">
@@ -5066,9 +5091,7 @@
       <c r="H39" s="104" t="s">
         <v>93</v>
       </c>
-      <c r="I39" s="106" t="s">
-        <v>15</v>
-      </c>
+      <c r="I39" s="106"/>
       <c r="J39" s="106" t="s">
         <v>15</v>
       </c>
@@ -5097,9 +5120,7 @@
       <c r="U39" s="104" t="s">
         <v>93</v>
       </c>
-      <c r="V39" s="106" t="s">
-        <v>15</v>
-      </c>
+      <c r="V39" s="106"/>
       <c r="W39" s="106" t="s">
         <v>15</v>
       </c>
@@ -6509,7 +6530,7 @@
         <f t="shared" ref="U69:U132" si="0">R69*0.935</f>
         <v>0</v>
       </c>
-      <c r="V69" s="144">
+      <c r="V69" s="150">
         <f t="shared" ref="V69:V132" si="1">U69/215</f>
         <v>0</v>
       </c>
@@ -6527,23 +6548,24 @@
       <c r="Z69" s="144">
         <v>170</v>
       </c>
-      <c r="AA69" s="150">
+      <c r="AA69" s="151">
         <v>168</v>
       </c>
       <c r="AB69" s="145">
         <f>67/Z69</f>
         <v>0.394117647058824</v>
       </c>
-      <c r="AC69" s="144">
+      <c r="AC69" s="152">
+        <v>0</v>
+      </c>
+      <c r="AD69" s="152">
+        <f>20-AC69</f>
         <v>20</v>
       </c>
-      <c r="AD69" s="144">
-        <v>0</v>
-      </c>
-      <c r="AE69" s="151" t="s">
+      <c r="AE69" s="153" t="s">
         <v>199</v>
       </c>
-      <c r="AF69" s="152"/>
+      <c r="AF69" s="154"/>
     </row>
     <row r="70" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A70" s="144"/>
@@ -6574,7 +6596,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V70" s="144">
+      <c r="V70" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6582,12 +6604,12 @@
       <c r="X70" s="144"/>
       <c r="Y70" s="145"/>
       <c r="Z70" s="144"/>
-      <c r="AA70" s="150"/>
+      <c r="AA70" s="151"/>
       <c r="AB70" s="145"/>
-      <c r="AC70" s="144"/>
-      <c r="AD70" s="144"/>
-      <c r="AE70" s="153"/>
-      <c r="AF70" s="152"/>
+      <c r="AC70" s="152"/>
+      <c r="AD70" s="152"/>
+      <c r="AE70" s="155"/>
+      <c r="AF70" s="154"/>
     </row>
     <row r="71" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A71" s="144"/>
@@ -6618,7 +6640,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V71" s="144">
+      <c r="V71" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6626,12 +6648,12 @@
       <c r="X71" s="144"/>
       <c r="Y71" s="145"/>
       <c r="Z71" s="144"/>
-      <c r="AA71" s="150"/>
+      <c r="AA71" s="151"/>
       <c r="AB71" s="145"/>
-      <c r="AC71" s="144"/>
-      <c r="AD71" s="144"/>
-      <c r="AE71" s="154"/>
-      <c r="AF71" s="152"/>
+      <c r="AC71" s="152"/>
+      <c r="AD71" s="152"/>
+      <c r="AE71" s="156"/>
+      <c r="AF71" s="154"/>
     </row>
     <row r="72" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A72" s="144"/>
@@ -6662,7 +6684,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V72" s="144">
+      <c r="V72" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6670,12 +6692,12 @@
       <c r="X72" s="144"/>
       <c r="Y72" s="145"/>
       <c r="Z72" s="144"/>
-      <c r="AA72" s="150"/>
+      <c r="AA72" s="151"/>
       <c r="AB72" s="145"/>
-      <c r="AC72" s="144"/>
-      <c r="AD72" s="144"/>
-      <c r="AE72" s="151"/>
-      <c r="AF72" s="152"/>
+      <c r="AC72" s="152"/>
+      <c r="AD72" s="152"/>
+      <c r="AE72" s="153"/>
+      <c r="AF72" s="154"/>
     </row>
     <row r="73" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A73" s="144"/>
@@ -6706,7 +6728,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V73" s="144">
+      <c r="V73" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6714,12 +6736,12 @@
       <c r="X73" s="144"/>
       <c r="Y73" s="145"/>
       <c r="Z73" s="144"/>
-      <c r="AA73" s="150"/>
+      <c r="AA73" s="151"/>
       <c r="AB73" s="145"/>
-      <c r="AC73" s="144"/>
-      <c r="AD73" s="144"/>
-      <c r="AE73" s="154"/>
-      <c r="AF73" s="152"/>
+      <c r="AC73" s="152"/>
+      <c r="AD73" s="152"/>
+      <c r="AE73" s="156"/>
+      <c r="AF73" s="154"/>
     </row>
     <row r="74" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A74" s="144"/>
@@ -6759,7 +6781,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V74" s="144">
+      <c r="V74" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6767,14 +6789,14 @@
       <c r="X74" s="144"/>
       <c r="Y74" s="145"/>
       <c r="Z74" s="144"/>
-      <c r="AA74" s="150"/>
+      <c r="AA74" s="151"/>
       <c r="AB74" s="145"/>
-      <c r="AC74" s="144"/>
-      <c r="AD74" s="144"/>
-      <c r="AE74" s="151" t="s">
+      <c r="AC74" s="152"/>
+      <c r="AD74" s="152"/>
+      <c r="AE74" s="153" t="s">
         <v>211</v>
       </c>
-      <c r="AF74" s="152"/>
+      <c r="AF74" s="154"/>
     </row>
     <row r="75" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A75" s="144"/>
@@ -6805,7 +6827,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V75" s="144">
+      <c r="V75" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6813,12 +6835,12 @@
       <c r="X75" s="144"/>
       <c r="Y75" s="145"/>
       <c r="Z75" s="144"/>
-      <c r="AA75" s="150"/>
+      <c r="AA75" s="151"/>
       <c r="AB75" s="145"/>
-      <c r="AC75" s="144"/>
-      <c r="AD75" s="144"/>
-      <c r="AE75" s="153"/>
-      <c r="AF75" s="152"/>
+      <c r="AC75" s="152"/>
+      <c r="AD75" s="152"/>
+      <c r="AE75" s="155"/>
+      <c r="AF75" s="154"/>
     </row>
     <row r="76" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A76" s="144"/>
@@ -6849,7 +6871,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V76" s="144">
+      <c r="V76" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6857,12 +6879,12 @@
       <c r="X76" s="144"/>
       <c r="Y76" s="145"/>
       <c r="Z76" s="144"/>
-      <c r="AA76" s="150"/>
+      <c r="AA76" s="151"/>
       <c r="AB76" s="145"/>
-      <c r="AC76" s="144"/>
-      <c r="AD76" s="144"/>
-      <c r="AE76" s="154"/>
-      <c r="AF76" s="152"/>
+      <c r="AC76" s="152"/>
+      <c r="AD76" s="152"/>
+      <c r="AE76" s="156"/>
+      <c r="AF76" s="154"/>
     </row>
     <row r="77" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A77" s="144"/>
@@ -6893,7 +6915,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V77" s="144">
+      <c r="V77" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6901,12 +6923,12 @@
       <c r="X77" s="144"/>
       <c r="Y77" s="145"/>
       <c r="Z77" s="144"/>
-      <c r="AA77" s="150"/>
+      <c r="AA77" s="151"/>
       <c r="AB77" s="145"/>
-      <c r="AC77" s="144"/>
-      <c r="AD77" s="144"/>
-      <c r="AE77" s="151"/>
-      <c r="AF77" s="152"/>
+      <c r="AC77" s="152"/>
+      <c r="AD77" s="152"/>
+      <c r="AE77" s="153"/>
+      <c r="AF77" s="154"/>
     </row>
     <row r="78" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A78" s="144"/>
@@ -6937,7 +6959,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V78" s="144">
+      <c r="V78" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6945,12 +6967,12 @@
       <c r="X78" s="144"/>
       <c r="Y78" s="145"/>
       <c r="Z78" s="144"/>
-      <c r="AA78" s="150"/>
+      <c r="AA78" s="151"/>
       <c r="AB78" s="145"/>
-      <c r="AC78" s="144"/>
-      <c r="AD78" s="144"/>
-      <c r="AE78" s="154"/>
-      <c r="AF78" s="152"/>
+      <c r="AC78" s="152"/>
+      <c r="AD78" s="152"/>
+      <c r="AE78" s="156"/>
+      <c r="AF78" s="154"/>
     </row>
     <row r="79" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A79" s="144" t="s">
@@ -6972,7 +6994,7 @@
       <c r="H79" s="146" t="s">
         <v>195</v>
       </c>
-      <c r="I79" s="155" t="s">
+      <c r="I79" s="157" t="s">
         <v>222</v>
       </c>
       <c r="J79" s="144"/>
@@ -6999,7 +7021,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V79" s="144">
+      <c r="V79" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7017,23 +7039,24 @@
       <c r="Z79" s="144">
         <v>170</v>
       </c>
-      <c r="AA79" s="150">
+      <c r="AA79" s="151">
         <v>170</v>
       </c>
       <c r="AB79" s="145">
         <f>77/Z79</f>
         <v>0.452941176470588</v>
       </c>
-      <c r="AC79" s="144">
+      <c r="AC79" s="144" t="s">
+        <v>225</v>
+      </c>
+      <c r="AD79" s="152">
+        <f>20-AC79</f>
         <v>20</v>
       </c>
-      <c r="AD79" s="144">
-        <v>0</v>
-      </c>
-      <c r="AE79" s="151" t="s">
+      <c r="AE79" s="153" t="s">
         <v>199</v>
       </c>
-      <c r="AF79" s="152"/>
+      <c r="AF79" s="154"/>
     </row>
     <row r="80" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A80" s="144"/>
@@ -7044,27 +7067,27 @@
       <c r="F80" s="145"/>
       <c r="G80" s="145"/>
       <c r="H80" s="146"/>
-      <c r="I80" s="155"/>
+      <c r="I80" s="157"/>
       <c r="J80" s="144"/>
       <c r="K80" s="145"/>
       <c r="L80" s="144"/>
       <c r="M80" s="144"/>
       <c r="N80" s="144"/>
       <c r="O80" s="147" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P80" s="144"/>
       <c r="Q80" s="144"/>
       <c r="R80" s="148"/>
       <c r="S80" s="149" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="T80" s="149"/>
       <c r="U80" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V80" s="144">
+      <c r="V80" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7072,12 +7095,12 @@
       <c r="X80" s="144"/>
       <c r="Y80" s="145"/>
       <c r="Z80" s="144"/>
-      <c r="AA80" s="150"/>
+      <c r="AA80" s="151"/>
       <c r="AB80" s="145"/>
       <c r="AC80" s="144"/>
-      <c r="AD80" s="144"/>
-      <c r="AE80" s="153"/>
-      <c r="AF80" s="152"/>
+      <c r="AD80" s="152"/>
+      <c r="AE80" s="155"/>
+      <c r="AF80" s="154"/>
     </row>
     <row r="81" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A81" s="144"/>
@@ -7088,27 +7111,27 @@
       <c r="F81" s="145"/>
       <c r="G81" s="145"/>
       <c r="H81" s="146"/>
-      <c r="I81" s="155"/>
+      <c r="I81" s="157"/>
       <c r="J81" s="144"/>
       <c r="K81" s="145"/>
       <c r="L81" s="144"/>
       <c r="M81" s="144"/>
       <c r="N81" s="144"/>
       <c r="O81" s="147" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P81" s="144"/>
       <c r="Q81" s="144"/>
       <c r="R81" s="148"/>
       <c r="S81" s="149" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="T81" s="149"/>
       <c r="U81" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V81" s="144">
+      <c r="V81" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7116,12 +7139,12 @@
       <c r="X81" s="144"/>
       <c r="Y81" s="145"/>
       <c r="Z81" s="144"/>
-      <c r="AA81" s="150"/>
+      <c r="AA81" s="151"/>
       <c r="AB81" s="145"/>
       <c r="AC81" s="144"/>
-      <c r="AD81" s="144"/>
-      <c r="AE81" s="154"/>
-      <c r="AF81" s="152"/>
+      <c r="AD81" s="152"/>
+      <c r="AE81" s="156"/>
+      <c r="AF81" s="154"/>
     </row>
     <row r="82" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A82" s="144"/>
@@ -7132,27 +7155,27 @@
       <c r="F82" s="145"/>
       <c r="G82" s="145"/>
       <c r="H82" s="146"/>
-      <c r="I82" s="155"/>
+      <c r="I82" s="157"/>
       <c r="J82" s="144"/>
       <c r="K82" s="145"/>
       <c r="L82" s="144"/>
       <c r="M82" s="144"/>
       <c r="N82" s="144"/>
       <c r="O82" s="147" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P82" s="144"/>
       <c r="Q82" s="144"/>
       <c r="R82" s="148"/>
       <c r="S82" s="149" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="T82" s="149"/>
       <c r="U82" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V82" s="144">
+      <c r="V82" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7160,12 +7183,12 @@
       <c r="X82" s="144"/>
       <c r="Y82" s="145"/>
       <c r="Z82" s="144"/>
-      <c r="AA82" s="150"/>
+      <c r="AA82" s="151"/>
       <c r="AB82" s="145"/>
       <c r="AC82" s="144"/>
-      <c r="AD82" s="144"/>
-      <c r="AE82" s="151"/>
-      <c r="AF82" s="152"/>
+      <c r="AD82" s="152"/>
+      <c r="AE82" s="153"/>
+      <c r="AF82" s="154"/>
     </row>
     <row r="83" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A83" s="144"/>
@@ -7176,27 +7199,27 @@
       <c r="F83" s="145"/>
       <c r="G83" s="145"/>
       <c r="H83" s="146"/>
-      <c r="I83" s="155"/>
+      <c r="I83" s="157"/>
       <c r="J83" s="144"/>
       <c r="K83" s="145"/>
       <c r="L83" s="144"/>
       <c r="M83" s="144"/>
       <c r="N83" s="144"/>
       <c r="O83" s="147" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P83" s="144"/>
       <c r="Q83" s="144"/>
       <c r="R83" s="148"/>
       <c r="S83" s="149" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="T83" s="149"/>
       <c r="U83" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V83" s="144">
+      <c r="V83" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7204,17 +7227,17 @@
       <c r="X83" s="144"/>
       <c r="Y83" s="145"/>
       <c r="Z83" s="144"/>
-      <c r="AA83" s="150"/>
+      <c r="AA83" s="151"/>
       <c r="AB83" s="145"/>
       <c r="AC83" s="144"/>
-      <c r="AD83" s="144"/>
-      <c r="AE83" s="154"/>
-      <c r="AF83" s="152"/>
+      <c r="AD83" s="152"/>
+      <c r="AE83" s="156"/>
+      <c r="AF83" s="154"/>
     </row>
     <row r="84" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A84" s="144"/>
       <c r="B84" s="144" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C84" s="144" t="s">
         <v>194</v>
@@ -7229,27 +7252,27 @@
       <c r="H84" s="146" t="s">
         <v>195</v>
       </c>
-      <c r="I84" s="155"/>
+      <c r="I84" s="157"/>
       <c r="J84" s="144"/>
       <c r="K84" s="145"/>
       <c r="L84" s="144"/>
       <c r="M84" s="144"/>
       <c r="N84" s="144"/>
       <c r="O84" s="147" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P84" s="144"/>
       <c r="Q84" s="144"/>
       <c r="R84" s="148"/>
       <c r="S84" s="149" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="T84" s="149"/>
       <c r="U84" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V84" s="144">
+      <c r="V84" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7257,14 +7280,14 @@
       <c r="X84" s="144"/>
       <c r="Y84" s="145"/>
       <c r="Z84" s="144"/>
-      <c r="AA84" s="150"/>
+      <c r="AA84" s="151"/>
       <c r="AB84" s="145"/>
       <c r="AC84" s="144"/>
-      <c r="AD84" s="144"/>
-      <c r="AE84" s="151" t="s">
+      <c r="AD84" s="152"/>
+      <c r="AE84" s="153" t="s">
         <v>211</v>
       </c>
-      <c r="AF84" s="152"/>
+      <c r="AF84" s="154"/>
     </row>
     <row r="85" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A85" s="144"/>
@@ -7275,27 +7298,27 @@
       <c r="F85" s="145"/>
       <c r="G85" s="145"/>
       <c r="H85" s="146"/>
-      <c r="I85" s="155"/>
+      <c r="I85" s="157"/>
       <c r="J85" s="144"/>
       <c r="K85" s="145"/>
       <c r="L85" s="144"/>
       <c r="M85" s="144"/>
       <c r="N85" s="144"/>
       <c r="O85" s="147" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P85" s="144"/>
       <c r="Q85" s="144"/>
       <c r="R85" s="148"/>
       <c r="S85" s="149" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="T85" s="149"/>
       <c r="U85" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V85" s="144">
+      <c r="V85" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7303,12 +7326,12 @@
       <c r="X85" s="144"/>
       <c r="Y85" s="145"/>
       <c r="Z85" s="144"/>
-      <c r="AA85" s="150"/>
+      <c r="AA85" s="151"/>
       <c r="AB85" s="145"/>
       <c r="AC85" s="144"/>
-      <c r="AD85" s="144"/>
-      <c r="AE85" s="153"/>
-      <c r="AF85" s="152"/>
+      <c r="AD85" s="152"/>
+      <c r="AE85" s="155"/>
+      <c r="AF85" s="154"/>
     </row>
     <row r="86" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A86" s="144"/>
@@ -7319,27 +7342,27 @@
       <c r="F86" s="145"/>
       <c r="G86" s="145"/>
       <c r="H86" s="146"/>
-      <c r="I86" s="155"/>
+      <c r="I86" s="157"/>
       <c r="J86" s="144"/>
       <c r="K86" s="145"/>
       <c r="L86" s="144"/>
       <c r="M86" s="144"/>
       <c r="N86" s="144"/>
       <c r="O86" s="147" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P86" s="144"/>
       <c r="Q86" s="144"/>
       <c r="R86" s="148"/>
       <c r="S86" s="149" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="T86" s="149"/>
       <c r="U86" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V86" s="144">
+      <c r="V86" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7347,12 +7370,12 @@
       <c r="X86" s="144"/>
       <c r="Y86" s="145"/>
       <c r="Z86" s="144"/>
-      <c r="AA86" s="150"/>
+      <c r="AA86" s="151"/>
       <c r="AB86" s="145"/>
       <c r="AC86" s="144"/>
-      <c r="AD86" s="144"/>
-      <c r="AE86" s="154"/>
-      <c r="AF86" s="152"/>
+      <c r="AD86" s="152"/>
+      <c r="AE86" s="156"/>
+      <c r="AF86" s="154"/>
     </row>
     <row r="87" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A87" s="144"/>
@@ -7363,27 +7386,27 @@
       <c r="F87" s="145"/>
       <c r="G87" s="145"/>
       <c r="H87" s="146"/>
-      <c r="I87" s="155"/>
+      <c r="I87" s="157"/>
       <c r="J87" s="144"/>
       <c r="K87" s="145"/>
       <c r="L87" s="144"/>
       <c r="M87" s="144"/>
       <c r="N87" s="144"/>
       <c r="O87" s="147" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P87" s="144"/>
       <c r="Q87" s="144"/>
       <c r="R87" s="148"/>
       <c r="S87" s="149" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="T87" s="149"/>
       <c r="U87" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V87" s="144">
+      <c r="V87" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7391,12 +7414,12 @@
       <c r="X87" s="144"/>
       <c r="Y87" s="145"/>
       <c r="Z87" s="144"/>
-      <c r="AA87" s="150"/>
+      <c r="AA87" s="151"/>
       <c r="AB87" s="145"/>
       <c r="AC87" s="144"/>
-      <c r="AD87" s="144"/>
-      <c r="AE87" s="151"/>
-      <c r="AF87" s="152"/>
+      <c r="AD87" s="152"/>
+      <c r="AE87" s="153"/>
+      <c r="AF87" s="154"/>
     </row>
     <row r="88" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A88" s="144"/>
@@ -7407,27 +7430,27 @@
       <c r="F88" s="145"/>
       <c r="G88" s="145"/>
       <c r="H88" s="146"/>
-      <c r="I88" s="155"/>
+      <c r="I88" s="157"/>
       <c r="J88" s="144"/>
       <c r="K88" s="145"/>
       <c r="L88" s="144"/>
       <c r="M88" s="144"/>
       <c r="N88" s="144"/>
       <c r="O88" s="147" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P88" s="144"/>
       <c r="Q88" s="144"/>
       <c r="R88" s="148"/>
       <c r="S88" s="149" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="T88" s="149"/>
       <c r="U88" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V88" s="144">
+      <c r="V88" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7435,19 +7458,19 @@
       <c r="X88" s="144"/>
       <c r="Y88" s="145"/>
       <c r="Z88" s="144"/>
-      <c r="AA88" s="150"/>
+      <c r="AA88" s="151"/>
       <c r="AB88" s="145"/>
       <c r="AC88" s="144"/>
-      <c r="AD88" s="144"/>
-      <c r="AE88" s="154"/>
-      <c r="AF88" s="152"/>
+      <c r="AD88" s="152"/>
+      <c r="AE88" s="156"/>
+      <c r="AF88" s="154"/>
     </row>
     <row r="89" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A89" s="144" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B89" s="144" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C89" s="144" t="s">
         <v>194</v>
@@ -7463,7 +7486,7 @@
         <v>195</v>
       </c>
       <c r="I89" s="146" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J89" s="144"/>
       <c r="K89" s="145">
@@ -7475,21 +7498,21 @@
       </c>
       <c r="M89" s="144"/>
       <c r="N89" s="144"/>
-      <c r="O89" s="156" t="s">
-        <v>247</v>
+      <c r="O89" s="158" t="s">
+        <v>248</v>
       </c>
       <c r="P89" s="144"/>
       <c r="Q89" s="144"/>
       <c r="R89" s="148"/>
       <c r="S89" s="149" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="T89" s="149"/>
       <c r="U89" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V89" s="144">
+      <c r="V89" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7507,23 +7530,24 @@
       <c r="Z89" s="144">
         <v>154</v>
       </c>
-      <c r="AA89" s="150">
+      <c r="AA89" s="151">
         <v>140</v>
       </c>
       <c r="AB89" s="145">
         <f>87/Z89</f>
         <v>0.564935064935065</v>
       </c>
-      <c r="AC89" s="144">
-        <v>12</v>
-      </c>
-      <c r="AD89" s="144">
-        <v>8</v>
-      </c>
-      <c r="AE89" s="151" t="s">
+      <c r="AC89" s="144" t="s">
+        <v>225</v>
+      </c>
+      <c r="AD89" s="152">
+        <f>20-AC89</f>
+        <v>20</v>
+      </c>
+      <c r="AE89" s="153" t="s">
         <v>199</v>
       </c>
-      <c r="AF89" s="152"/>
+      <c r="AF89" s="154"/>
     </row>
     <row r="90" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A90" s="144"/>
@@ -7540,21 +7564,21 @@
       <c r="L90" s="144"/>
       <c r="M90" s="144"/>
       <c r="N90" s="144"/>
-      <c r="O90" s="156" t="s">
-        <v>249</v>
+      <c r="O90" s="158" t="s">
+        <v>250</v>
       </c>
       <c r="P90" s="144"/>
       <c r="Q90" s="144"/>
       <c r="R90" s="148"/>
       <c r="S90" s="149" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="T90" s="149"/>
       <c r="U90" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V90" s="144">
+      <c r="V90" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7562,12 +7586,12 @@
       <c r="X90" s="144"/>
       <c r="Y90" s="145"/>
       <c r="Z90" s="144"/>
-      <c r="AA90" s="150"/>
+      <c r="AA90" s="151"/>
       <c r="AB90" s="145"/>
       <c r="AC90" s="144"/>
-      <c r="AD90" s="144"/>
-      <c r="AE90" s="153"/>
-      <c r="AF90" s="152"/>
+      <c r="AD90" s="152"/>
+      <c r="AE90" s="155"/>
+      <c r="AF90" s="154"/>
     </row>
     <row r="91" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A91" s="144"/>
@@ -7584,21 +7608,21 @@
       <c r="L91" s="144"/>
       <c r="M91" s="144"/>
       <c r="N91" s="144"/>
-      <c r="O91" s="156" t="s">
-        <v>251</v>
+      <c r="O91" s="158" t="s">
+        <v>252</v>
       </c>
       <c r="P91" s="144"/>
       <c r="Q91" s="144"/>
       <c r="R91" s="148"/>
       <c r="S91" s="149" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="T91" s="149"/>
       <c r="U91" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V91" s="144">
+      <c r="V91" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7606,12 +7630,12 @@
       <c r="X91" s="144"/>
       <c r="Y91" s="145"/>
       <c r="Z91" s="144"/>
-      <c r="AA91" s="150"/>
+      <c r="AA91" s="151"/>
       <c r="AB91" s="145"/>
       <c r="AC91" s="144"/>
-      <c r="AD91" s="144"/>
-      <c r="AE91" s="153"/>
-      <c r="AF91" s="152"/>
+      <c r="AD91" s="152"/>
+      <c r="AE91" s="155"/>
+      <c r="AF91" s="154"/>
     </row>
     <row r="92" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A92" s="144"/>
@@ -7628,21 +7652,21 @@
       <c r="L92" s="144"/>
       <c r="M92" s="144"/>
       <c r="N92" s="144"/>
-      <c r="O92" s="156" t="s">
-        <v>253</v>
+      <c r="O92" s="158" t="s">
+        <v>254</v>
       </c>
       <c r="P92" s="144"/>
       <c r="Q92" s="144"/>
       <c r="R92" s="148"/>
       <c r="S92" s="149" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="T92" s="149"/>
       <c r="U92" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V92" s="144">
+      <c r="V92" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7650,12 +7674,12 @@
       <c r="X92" s="144"/>
       <c r="Y92" s="145"/>
       <c r="Z92" s="144"/>
-      <c r="AA92" s="150"/>
+      <c r="AA92" s="151"/>
       <c r="AB92" s="145"/>
       <c r="AC92" s="144"/>
-      <c r="AD92" s="144"/>
-      <c r="AE92" s="154"/>
-      <c r="AF92" s="152"/>
+      <c r="AD92" s="152"/>
+      <c r="AE92" s="156"/>
+      <c r="AF92" s="154"/>
     </row>
     <row r="93" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A93" s="144"/>
@@ -7672,21 +7696,21 @@
       <c r="L93" s="144"/>
       <c r="M93" s="144"/>
       <c r="N93" s="144"/>
-      <c r="O93" s="156" t="s">
-        <v>255</v>
+      <c r="O93" s="158" t="s">
+        <v>256</v>
       </c>
       <c r="P93" s="144"/>
       <c r="Q93" s="144"/>
       <c r="R93" s="148"/>
       <c r="S93" s="149" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="T93" s="149"/>
       <c r="U93" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V93" s="144">
+      <c r="V93" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7694,12 +7718,12 @@
       <c r="X93" s="144"/>
       <c r="Y93" s="145"/>
       <c r="Z93" s="144"/>
-      <c r="AA93" s="150"/>
+      <c r="AA93" s="151"/>
       <c r="AB93" s="145"/>
       <c r="AC93" s="144"/>
-      <c r="AD93" s="144"/>
-      <c r="AE93" s="151"/>
-      <c r="AF93" s="152"/>
+      <c r="AD93" s="152"/>
+      <c r="AE93" s="153"/>
+      <c r="AF93" s="154"/>
     </row>
     <row r="94" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A94" s="144"/>
@@ -7716,21 +7740,21 @@
       <c r="L94" s="144"/>
       <c r="M94" s="144"/>
       <c r="N94" s="144"/>
-      <c r="O94" s="156" t="s">
-        <v>257</v>
+      <c r="O94" s="158" t="s">
+        <v>258</v>
       </c>
       <c r="P94" s="144"/>
       <c r="Q94" s="144"/>
       <c r="R94" s="148"/>
       <c r="S94" s="149" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="T94" s="149"/>
       <c r="U94" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V94" s="144">
+      <c r="V94" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7738,12 +7762,12 @@
       <c r="X94" s="144"/>
       <c r="Y94" s="145"/>
       <c r="Z94" s="144"/>
-      <c r="AA94" s="150"/>
+      <c r="AA94" s="151"/>
       <c r="AB94" s="145"/>
       <c r="AC94" s="144"/>
-      <c r="AD94" s="144"/>
-      <c r="AE94" s="153"/>
-      <c r="AF94" s="152"/>
+      <c r="AD94" s="152"/>
+      <c r="AE94" s="155"/>
+      <c r="AF94" s="154"/>
     </row>
     <row r="95" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A95" s="144"/>
@@ -7760,21 +7784,21 @@
       <c r="L95" s="144"/>
       <c r="M95" s="144"/>
       <c r="N95" s="144"/>
-      <c r="O95" s="156" t="s">
-        <v>259</v>
+      <c r="O95" s="158" t="s">
+        <v>260</v>
       </c>
       <c r="P95" s="144"/>
       <c r="Q95" s="144"/>
       <c r="R95" s="148"/>
       <c r="S95" s="149" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="T95" s="149"/>
       <c r="U95" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V95" s="144">
+      <c r="V95" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7782,17 +7806,17 @@
       <c r="X95" s="144"/>
       <c r="Y95" s="145"/>
       <c r="Z95" s="144"/>
-      <c r="AA95" s="150"/>
+      <c r="AA95" s="151"/>
       <c r="AB95" s="145"/>
       <c r="AC95" s="144"/>
-      <c r="AD95" s="144"/>
-      <c r="AE95" s="154"/>
-      <c r="AF95" s="152"/>
+      <c r="AD95" s="152"/>
+      <c r="AE95" s="156"/>
+      <c r="AF95" s="154"/>
     </row>
     <row r="96" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A96" s="144"/>
       <c r="B96" s="144" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C96" s="144" t="s">
         <v>194</v>
@@ -7813,21 +7837,21 @@
       <c r="L96" s="144"/>
       <c r="M96" s="144"/>
       <c r="N96" s="144"/>
-      <c r="O96" s="156" t="s">
-        <v>262</v>
+      <c r="O96" s="158" t="s">
+        <v>263</v>
       </c>
       <c r="P96" s="144"/>
       <c r="Q96" s="144"/>
       <c r="R96" s="148"/>
       <c r="S96" s="149" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="T96" s="149"/>
       <c r="U96" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V96" s="144">
+      <c r="V96" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7835,14 +7859,14 @@
       <c r="X96" s="144"/>
       <c r="Y96" s="145"/>
       <c r="Z96" s="144"/>
-      <c r="AA96" s="150"/>
+      <c r="AA96" s="151"/>
       <c r="AB96" s="145"/>
       <c r="AC96" s="144"/>
-      <c r="AD96" s="144"/>
-      <c r="AE96" s="151" t="s">
+      <c r="AD96" s="152"/>
+      <c r="AE96" s="153" t="s">
         <v>211</v>
       </c>
-      <c r="AF96" s="152"/>
+      <c r="AF96" s="154"/>
     </row>
     <row r="97" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A97" s="144"/>
@@ -7859,21 +7883,21 @@
       <c r="L97" s="144"/>
       <c r="M97" s="144"/>
       <c r="N97" s="144"/>
-      <c r="O97" s="156" t="s">
-        <v>264</v>
+      <c r="O97" s="158" t="s">
+        <v>265</v>
       </c>
       <c r="P97" s="144"/>
       <c r="Q97" s="144"/>
       <c r="R97" s="148"/>
       <c r="S97" s="149" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="T97" s="149"/>
       <c r="U97" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V97" s="144">
+      <c r="V97" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7881,12 +7905,12 @@
       <c r="X97" s="144"/>
       <c r="Y97" s="145"/>
       <c r="Z97" s="144"/>
-      <c r="AA97" s="150"/>
+      <c r="AA97" s="151"/>
       <c r="AB97" s="145"/>
       <c r="AC97" s="144"/>
-      <c r="AD97" s="144"/>
-      <c r="AE97" s="153"/>
-      <c r="AF97" s="152"/>
+      <c r="AD97" s="152"/>
+      <c r="AE97" s="155"/>
+      <c r="AF97" s="154"/>
     </row>
     <row r="98" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A98" s="144"/>
@@ -7903,21 +7927,21 @@
       <c r="L98" s="144"/>
       <c r="M98" s="144"/>
       <c r="N98" s="144"/>
-      <c r="O98" s="156" t="s">
-        <v>266</v>
+      <c r="O98" s="158" t="s">
+        <v>267</v>
       </c>
       <c r="P98" s="144"/>
       <c r="Q98" s="144"/>
       <c r="R98" s="148"/>
       <c r="S98" s="149" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="T98" s="149"/>
       <c r="U98" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V98" s="144">
+      <c r="V98" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7925,12 +7949,12 @@
       <c r="X98" s="144"/>
       <c r="Y98" s="145"/>
       <c r="Z98" s="144"/>
-      <c r="AA98" s="150"/>
+      <c r="AA98" s="151"/>
       <c r="AB98" s="145"/>
       <c r="AC98" s="144"/>
-      <c r="AD98" s="144"/>
-      <c r="AE98" s="153"/>
-      <c r="AF98" s="152"/>
+      <c r="AD98" s="152"/>
+      <c r="AE98" s="155"/>
+      <c r="AF98" s="154"/>
     </row>
     <row r="99" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A99" s="144"/>
@@ -7947,21 +7971,21 @@
       <c r="L99" s="144"/>
       <c r="M99" s="144"/>
       <c r="N99" s="144"/>
-      <c r="O99" s="156" t="s">
-        <v>268</v>
+      <c r="O99" s="158" t="s">
+        <v>269</v>
       </c>
       <c r="P99" s="144"/>
       <c r="Q99" s="144"/>
       <c r="R99" s="148"/>
       <c r="S99" s="149" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="T99" s="149"/>
       <c r="U99" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V99" s="144">
+      <c r="V99" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7969,12 +7993,12 @@
       <c r="X99" s="144"/>
       <c r="Y99" s="145"/>
       <c r="Z99" s="144"/>
-      <c r="AA99" s="150"/>
+      <c r="AA99" s="151"/>
       <c r="AB99" s="145"/>
       <c r="AC99" s="144"/>
-      <c r="AD99" s="144"/>
-      <c r="AE99" s="154"/>
-      <c r="AF99" s="152"/>
+      <c r="AD99" s="152"/>
+      <c r="AE99" s="156"/>
+      <c r="AF99" s="154"/>
     </row>
     <row r="100" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A100" s="144"/>
@@ -7991,21 +8015,21 @@
       <c r="L100" s="144"/>
       <c r="M100" s="144"/>
       <c r="N100" s="144"/>
-      <c r="O100" s="156" t="s">
-        <v>270</v>
+      <c r="O100" s="158" t="s">
+        <v>271</v>
       </c>
       <c r="P100" s="144"/>
       <c r="Q100" s="144"/>
       <c r="R100" s="148"/>
       <c r="S100" s="149" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="T100" s="149"/>
       <c r="U100" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V100" s="144">
+      <c r="V100" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -8013,12 +8037,12 @@
       <c r="X100" s="144"/>
       <c r="Y100" s="145"/>
       <c r="Z100" s="144"/>
-      <c r="AA100" s="150"/>
+      <c r="AA100" s="151"/>
       <c r="AB100" s="145"/>
       <c r="AC100" s="144"/>
-      <c r="AD100" s="144"/>
-      <c r="AE100" s="151"/>
-      <c r="AF100" s="152"/>
+      <c r="AD100" s="152"/>
+      <c r="AE100" s="153"/>
+      <c r="AF100" s="154"/>
     </row>
     <row r="101" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A101" s="144"/>
@@ -8035,21 +8059,21 @@
       <c r="L101" s="144"/>
       <c r="M101" s="144"/>
       <c r="N101" s="144"/>
-      <c r="O101" s="156" t="s">
-        <v>272</v>
+      <c r="O101" s="158" t="s">
+        <v>273</v>
       </c>
       <c r="P101" s="144"/>
       <c r="Q101" s="144"/>
       <c r="R101" s="148"/>
       <c r="S101" s="149" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="T101" s="149"/>
       <c r="U101" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V101" s="144">
+      <c r="V101" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -8057,12 +8081,12 @@
       <c r="X101" s="144"/>
       <c r="Y101" s="145"/>
       <c r="Z101" s="144"/>
-      <c r="AA101" s="150"/>
+      <c r="AA101" s="151"/>
       <c r="AB101" s="145"/>
       <c r="AC101" s="144"/>
-      <c r="AD101" s="144"/>
-      <c r="AE101" s="153"/>
-      <c r="AF101" s="152"/>
+      <c r="AD101" s="152"/>
+      <c r="AE101" s="155"/>
+      <c r="AF101" s="154"/>
     </row>
     <row r="102" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A102" s="144"/>
@@ -8079,21 +8103,21 @@
       <c r="L102" s="144"/>
       <c r="M102" s="144"/>
       <c r="N102" s="144"/>
-      <c r="O102" s="156" t="s">
-        <v>274</v>
+      <c r="O102" s="158" t="s">
+        <v>275</v>
       </c>
       <c r="P102" s="144"/>
       <c r="Q102" s="144"/>
       <c r="R102" s="148"/>
       <c r="S102" s="149" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="T102" s="149"/>
       <c r="U102" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V102" s="144">
+      <c r="V102" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -8101,19 +8125,19 @@
       <c r="X102" s="144"/>
       <c r="Y102" s="145"/>
       <c r="Z102" s="144"/>
-      <c r="AA102" s="150"/>
+      <c r="AA102" s="151"/>
       <c r="AB102" s="145"/>
       <c r="AC102" s="144"/>
-      <c r="AD102" s="144"/>
-      <c r="AE102" s="154"/>
-      <c r="AF102" s="152"/>
+      <c r="AD102" s="152"/>
+      <c r="AE102" s="156"/>
+      <c r="AF102" s="154"/>
     </row>
     <row r="103" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A103" s="144" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B103" s="144" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C103" s="144" t="s">
         <v>194</v>
@@ -8129,7 +8153,7 @@
         <v>195</v>
       </c>
       <c r="I103" s="146" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J103" s="144"/>
       <c r="K103" s="145">
@@ -8141,21 +8165,21 @@
       </c>
       <c r="M103" s="144"/>
       <c r="N103" s="144"/>
-      <c r="O103" s="156" t="s">
-        <v>279</v>
+      <c r="O103" s="158" t="s">
+        <v>280</v>
       </c>
       <c r="P103" s="144"/>
       <c r="Q103" s="144"/>
       <c r="R103" s="148"/>
       <c r="S103" s="149" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="T103" s="149"/>
       <c r="U103" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V103" s="144">
+      <c r="V103" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -8173,23 +8197,24 @@
       <c r="Z103" s="144">
         <v>154</v>
       </c>
-      <c r="AA103" s="150">
+      <c r="AA103" s="151">
         <v>152</v>
       </c>
       <c r="AB103" s="145">
         <f>101/Z103</f>
         <v>0.655844155844156</v>
       </c>
-      <c r="AC103" s="144">
-        <v>12</v>
-      </c>
-      <c r="AD103" s="144">
-        <v>8</v>
-      </c>
-      <c r="AE103" s="151" t="s">
+      <c r="AC103" s="144" t="s">
+        <v>225</v>
+      </c>
+      <c r="AD103" s="152">
+        <f>20-AC103</f>
+        <v>20</v>
+      </c>
+      <c r="AE103" s="153" t="s">
         <v>199</v>
       </c>
-      <c r="AF103" s="152"/>
+      <c r="AF103" s="154"/>
     </row>
     <row r="104" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A104" s="144"/>
@@ -8207,20 +8232,20 @@
       <c r="M104" s="144"/>
       <c r="N104" s="144"/>
       <c r="O104" s="147" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P104" s="144"/>
       <c r="Q104" s="144"/>
       <c r="R104" s="148"/>
       <c r="S104" s="149" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="T104" s="149"/>
       <c r="U104" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V104" s="144">
+      <c r="V104" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -8228,12 +8253,12 @@
       <c r="X104" s="144"/>
       <c r="Y104" s="145"/>
       <c r="Z104" s="144"/>
-      <c r="AA104" s="150"/>
+      <c r="AA104" s="151"/>
       <c r="AB104" s="145"/>
       <c r="AC104" s="144"/>
-      <c r="AD104" s="144"/>
-      <c r="AE104" s="153"/>
-      <c r="AF104" s="152"/>
+      <c r="AD104" s="152"/>
+      <c r="AE104" s="155"/>
+      <c r="AF104" s="154"/>
     </row>
     <row r="105" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A105" s="144"/>
@@ -8250,21 +8275,21 @@
       <c r="L105" s="144"/>
       <c r="M105" s="144"/>
       <c r="N105" s="144"/>
-      <c r="O105" s="156" t="s">
-        <v>283</v>
+      <c r="O105" s="158" t="s">
+        <v>284</v>
       </c>
       <c r="P105" s="144"/>
       <c r="Q105" s="144"/>
       <c r="R105" s="148"/>
       <c r="S105" s="149" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="T105" s="149"/>
       <c r="U105" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V105" s="144">
+      <c r="V105" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -8272,12 +8297,12 @@
       <c r="X105" s="144"/>
       <c r="Y105" s="145"/>
       <c r="Z105" s="144"/>
-      <c r="AA105" s="150"/>
+      <c r="AA105" s="151"/>
       <c r="AB105" s="145"/>
       <c r="AC105" s="144"/>
-      <c r="AD105" s="144"/>
-      <c r="AE105" s="153"/>
-      <c r="AF105" s="152"/>
+      <c r="AD105" s="152"/>
+      <c r="AE105" s="155"/>
+      <c r="AF105" s="154"/>
     </row>
     <row r="106" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A106" s="144"/>
@@ -8295,20 +8320,20 @@
       <c r="M106" s="144"/>
       <c r="N106" s="144"/>
       <c r="O106" s="147" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P106" s="144"/>
       <c r="Q106" s="144"/>
       <c r="R106" s="148"/>
       <c r="S106" s="149" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="T106" s="149"/>
       <c r="U106" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V106" s="144">
+      <c r="V106" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -8316,12 +8341,12 @@
       <c r="X106" s="144"/>
       <c r="Y106" s="145"/>
       <c r="Z106" s="144"/>
-      <c r="AA106" s="150"/>
+      <c r="AA106" s="151"/>
       <c r="AB106" s="145"/>
       <c r="AC106" s="144"/>
-      <c r="AD106" s="144"/>
-      <c r="AE106" s="154"/>
-      <c r="AF106" s="152"/>
+      <c r="AD106" s="152"/>
+      <c r="AE106" s="156"/>
+      <c r="AF106" s="154"/>
     </row>
     <row r="107" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A107" s="144"/>
@@ -8338,21 +8363,21 @@
       <c r="L107" s="144"/>
       <c r="M107" s="144"/>
       <c r="N107" s="144"/>
-      <c r="O107" s="156" t="s">
-        <v>287</v>
+      <c r="O107" s="158" t="s">
+        <v>288</v>
       </c>
       <c r="P107" s="144"/>
       <c r="Q107" s="144"/>
       <c r="R107" s="148"/>
       <c r="S107" s="149" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="T107" s="149"/>
       <c r="U107" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V107" s="144">
+      <c r="V107" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -8360,12 +8385,12 @@
       <c r="X107" s="144"/>
       <c r="Y107" s="145"/>
       <c r="Z107" s="144"/>
-      <c r="AA107" s="150"/>
+      <c r="AA107" s="151"/>
       <c r="AB107" s="145"/>
       <c r="AC107" s="144"/>
-      <c r="AD107" s="144"/>
-      <c r="AE107" s="151"/>
-      <c r="AF107" s="152"/>
+      <c r="AD107" s="152"/>
+      <c r="AE107" s="153"/>
+      <c r="AF107" s="154"/>
     </row>
     <row r="108" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A108" s="144"/>
@@ -8383,20 +8408,20 @@
       <c r="M108" s="144"/>
       <c r="N108" s="144"/>
       <c r="O108" s="147" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P108" s="144"/>
       <c r="Q108" s="144"/>
       <c r="R108" s="148"/>
       <c r="S108" s="149" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="T108" s="149"/>
       <c r="U108" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V108" s="144">
+      <c r="V108" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -8404,12 +8429,12 @@
       <c r="X108" s="144"/>
       <c r="Y108" s="145"/>
       <c r="Z108" s="144"/>
-      <c r="AA108" s="150"/>
+      <c r="AA108" s="151"/>
       <c r="AB108" s="145"/>
       <c r="AC108" s="144"/>
-      <c r="AD108" s="144"/>
-      <c r="AE108" s="153"/>
-      <c r="AF108" s="152"/>
+      <c r="AD108" s="152"/>
+      <c r="AE108" s="155"/>
+      <c r="AF108" s="154"/>
     </row>
     <row r="109" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A109" s="144"/>
@@ -8426,21 +8451,21 @@
       <c r="L109" s="144"/>
       <c r="M109" s="144"/>
       <c r="N109" s="144"/>
-      <c r="O109" s="156" t="s">
-        <v>291</v>
+      <c r="O109" s="158" t="s">
+        <v>292</v>
       </c>
       <c r="P109" s="144"/>
       <c r="Q109" s="144"/>
       <c r="R109" s="148"/>
       <c r="S109" s="149" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="T109" s="149"/>
       <c r="U109" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V109" s="144">
+      <c r="V109" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -8448,17 +8473,17 @@
       <c r="X109" s="144"/>
       <c r="Y109" s="145"/>
       <c r="Z109" s="144"/>
-      <c r="AA109" s="150"/>
+      <c r="AA109" s="151"/>
       <c r="AB109" s="145"/>
       <c r="AC109" s="144"/>
-      <c r="AD109" s="144"/>
-      <c r="AE109" s="154"/>
-      <c r="AF109" s="152"/>
+      <c r="AD109" s="152"/>
+      <c r="AE109" s="156"/>
+      <c r="AF109" s="154"/>
     </row>
     <row r="110" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A110" s="144"/>
       <c r="B110" s="144" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C110" s="144" t="s">
         <v>194</v>
@@ -8480,20 +8505,20 @@
       <c r="M110" s="144"/>
       <c r="N110" s="144"/>
       <c r="O110" s="147" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P110" s="144"/>
       <c r="Q110" s="144"/>
       <c r="R110" s="148"/>
       <c r="S110" s="149" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="T110" s="149"/>
       <c r="U110" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V110" s="144">
+      <c r="V110" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -8501,14 +8526,14 @@
       <c r="X110" s="144"/>
       <c r="Y110" s="145"/>
       <c r="Z110" s="144"/>
-      <c r="AA110" s="150"/>
+      <c r="AA110" s="151"/>
       <c r="AB110" s="145"/>
       <c r="AC110" s="144"/>
-      <c r="AD110" s="144"/>
-      <c r="AE110" s="151" t="s">
+      <c r="AD110" s="152"/>
+      <c r="AE110" s="153" t="s">
         <v>211</v>
       </c>
-      <c r="AF110" s="152"/>
+      <c r="AF110" s="154"/>
     </row>
     <row r="111" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A111" s="144"/>
@@ -8526,20 +8551,20 @@
       <c r="M111" s="144"/>
       <c r="N111" s="144"/>
       <c r="O111" s="147" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P111" s="144"/>
       <c r="Q111" s="144"/>
       <c r="R111" s="148"/>
       <c r="S111" s="149" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="T111" s="149"/>
       <c r="U111" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V111" s="144">
+      <c r="V111" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -8547,12 +8572,12 @@
       <c r="X111" s="144"/>
       <c r="Y111" s="145"/>
       <c r="Z111" s="144"/>
-      <c r="AA111" s="150"/>
+      <c r="AA111" s="151"/>
       <c r="AB111" s="145"/>
       <c r="AC111" s="144"/>
-      <c r="AD111" s="144"/>
-      <c r="AE111" s="153"/>
-      <c r="AF111" s="152"/>
+      <c r="AD111" s="152"/>
+      <c r="AE111" s="155"/>
+      <c r="AF111" s="154"/>
     </row>
     <row r="112" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A112" s="144"/>
@@ -8570,20 +8595,20 @@
       <c r="M112" s="144"/>
       <c r="N112" s="144"/>
       <c r="O112" s="147" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P112" s="144"/>
       <c r="Q112" s="144"/>
       <c r="R112" s="148"/>
       <c r="S112" s="149" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="T112" s="149"/>
       <c r="U112" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V112" s="144">
+      <c r="V112" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -8591,12 +8616,12 @@
       <c r="X112" s="144"/>
       <c r="Y112" s="145"/>
       <c r="Z112" s="144"/>
-      <c r="AA112" s="150"/>
+      <c r="AA112" s="151"/>
       <c r="AB112" s="145"/>
       <c r="AC112" s="144"/>
-      <c r="AD112" s="144"/>
-      <c r="AE112" s="153"/>
-      <c r="AF112" s="152"/>
+      <c r="AD112" s="152"/>
+      <c r="AE112" s="155"/>
+      <c r="AF112" s="154"/>
     </row>
     <row r="113" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A113" s="144"/>
@@ -8614,20 +8639,20 @@
       <c r="M113" s="144"/>
       <c r="N113" s="144"/>
       <c r="O113" s="147" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P113" s="144"/>
       <c r="Q113" s="144"/>
       <c r="R113" s="148"/>
       <c r="S113" s="149" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="T113" s="149"/>
       <c r="U113" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V113" s="144">
+      <c r="V113" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -8635,12 +8660,12 @@
       <c r="X113" s="144"/>
       <c r="Y113" s="145"/>
       <c r="Z113" s="144"/>
-      <c r="AA113" s="150"/>
+      <c r="AA113" s="151"/>
       <c r="AB113" s="145"/>
       <c r="AC113" s="144"/>
-      <c r="AD113" s="144"/>
-      <c r="AE113" s="154"/>
-      <c r="AF113" s="152"/>
+      <c r="AD113" s="152"/>
+      <c r="AE113" s="156"/>
+      <c r="AF113" s="154"/>
     </row>
     <row r="114" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A114" s="144"/>
@@ -8658,20 +8683,20 @@
       <c r="M114" s="144"/>
       <c r="N114" s="144"/>
       <c r="O114" s="147" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P114" s="144"/>
       <c r="Q114" s="144"/>
       <c r="R114" s="148"/>
       <c r="S114" s="149" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="T114" s="149"/>
       <c r="U114" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V114" s="144">
+      <c r="V114" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -8679,12 +8704,12 @@
       <c r="X114" s="144"/>
       <c r="Y114" s="145"/>
       <c r="Z114" s="144"/>
-      <c r="AA114" s="150"/>
+      <c r="AA114" s="151"/>
       <c r="AB114" s="145"/>
       <c r="AC114" s="144"/>
-      <c r="AD114" s="144"/>
-      <c r="AE114" s="151"/>
-      <c r="AF114" s="152"/>
+      <c r="AD114" s="152"/>
+      <c r="AE114" s="153"/>
+      <c r="AF114" s="154"/>
     </row>
     <row r="115" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A115" s="144"/>
@@ -8702,20 +8727,20 @@
       <c r="M115" s="144"/>
       <c r="N115" s="144"/>
       <c r="O115" s="147" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P115" s="144"/>
       <c r="Q115" s="144"/>
       <c r="R115" s="148"/>
       <c r="S115" s="149" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="T115" s="149"/>
       <c r="U115" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V115" s="144">
+      <c r="V115" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -8723,12 +8748,12 @@
       <c r="X115" s="144"/>
       <c r="Y115" s="145"/>
       <c r="Z115" s="144"/>
-      <c r="AA115" s="150"/>
+      <c r="AA115" s="151"/>
       <c r="AB115" s="145"/>
       <c r="AC115" s="144"/>
-      <c r="AD115" s="144"/>
-      <c r="AE115" s="153"/>
-      <c r="AF115" s="152"/>
+      <c r="AD115" s="152"/>
+      <c r="AE115" s="155"/>
+      <c r="AF115" s="154"/>
     </row>
     <row r="116" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A116" s="144"/>
@@ -8746,20 +8771,20 @@
       <c r="M116" s="144"/>
       <c r="N116" s="144"/>
       <c r="O116" s="147" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P116" s="144"/>
       <c r="Q116" s="144"/>
       <c r="R116" s="148"/>
       <c r="S116" s="149" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="T116" s="149"/>
       <c r="U116" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V116" s="144">
+      <c r="V116" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -8767,19 +8792,19 @@
       <c r="X116" s="144"/>
       <c r="Y116" s="145"/>
       <c r="Z116" s="144"/>
-      <c r="AA116" s="150"/>
+      <c r="AA116" s="151"/>
       <c r="AB116" s="145"/>
       <c r="AC116" s="144"/>
-      <c r="AD116" s="144"/>
-      <c r="AE116" s="154"/>
-      <c r="AF116" s="152"/>
+      <c r="AD116" s="152"/>
+      <c r="AE116" s="156"/>
+      <c r="AF116" s="154"/>
     </row>
     <row r="117" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A117" s="144" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B117" s="144" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C117" s="144" t="s">
         <v>194</v>
@@ -8795,7 +8820,7 @@
         <v>195</v>
       </c>
       <c r="I117" s="146" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J117" s="144"/>
       <c r="K117" s="145">
@@ -8808,20 +8833,20 @@
       <c r="M117" s="144"/>
       <c r="N117" s="144"/>
       <c r="O117" s="147" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P117" s="144"/>
       <c r="Q117" s="144"/>
       <c r="R117" s="148"/>
       <c r="S117" s="149" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="T117" s="149"/>
       <c r="U117" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V117" s="144">
+      <c r="V117" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -8839,23 +8864,24 @@
       <c r="Z117" s="144">
         <v>170</v>
       </c>
-      <c r="AA117" s="150">
+      <c r="AA117" s="151">
         <v>170</v>
       </c>
       <c r="AB117" s="145">
         <f>115/Z117</f>
         <v>0.676470588235294</v>
       </c>
-      <c r="AC117" s="144">
+      <c r="AC117" s="144" t="s">
+        <v>225</v>
+      </c>
+      <c r="AD117" s="152">
+        <f>20-AC117</f>
         <v>20</v>
       </c>
-      <c r="AD117" s="144">
-        <v>0</v>
-      </c>
-      <c r="AE117" s="151" t="s">
+      <c r="AE117" s="153" t="s">
         <v>199</v>
       </c>
-      <c r="AF117" s="152"/>
+      <c r="AF117" s="154"/>
     </row>
     <row r="118" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A118" s="144"/>
@@ -8873,20 +8899,20 @@
       <c r="M118" s="144"/>
       <c r="N118" s="144"/>
       <c r="O118" s="147" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P118" s="144"/>
       <c r="Q118" s="144"/>
       <c r="R118" s="148"/>
       <c r="S118" s="149" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="T118" s="149"/>
       <c r="U118" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V118" s="144">
+      <c r="V118" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -8894,12 +8920,12 @@
       <c r="X118" s="144"/>
       <c r="Y118" s="145"/>
       <c r="Z118" s="144"/>
-      <c r="AA118" s="150"/>
+      <c r="AA118" s="151"/>
       <c r="AB118" s="145"/>
       <c r="AC118" s="144"/>
-      <c r="AD118" s="144"/>
-      <c r="AE118" s="153"/>
-      <c r="AF118" s="152"/>
+      <c r="AD118" s="152"/>
+      <c r="AE118" s="155"/>
+      <c r="AF118" s="154"/>
     </row>
     <row r="119" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A119" s="144"/>
@@ -8917,20 +8943,20 @@
       <c r="M119" s="144"/>
       <c r="N119" s="144"/>
       <c r="O119" s="147" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="P119" s="144"/>
       <c r="Q119" s="144"/>
       <c r="R119" s="148"/>
       <c r="S119" s="149" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="T119" s="149"/>
       <c r="U119" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V119" s="144">
+      <c r="V119" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -8938,12 +8964,12 @@
       <c r="X119" s="144"/>
       <c r="Y119" s="145"/>
       <c r="Z119" s="144"/>
-      <c r="AA119" s="150"/>
+      <c r="AA119" s="151"/>
       <c r="AB119" s="145"/>
       <c r="AC119" s="144"/>
-      <c r="AD119" s="144"/>
-      <c r="AE119" s="154"/>
-      <c r="AF119" s="152"/>
+      <c r="AD119" s="152"/>
+      <c r="AE119" s="156"/>
+      <c r="AF119" s="154"/>
     </row>
     <row r="120" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A120" s="144"/>
@@ -8961,20 +8987,20 @@
       <c r="M120" s="144"/>
       <c r="N120" s="144"/>
       <c r="O120" s="147" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P120" s="144"/>
       <c r="Q120" s="144"/>
       <c r="R120" s="148"/>
       <c r="S120" s="149" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="T120" s="149"/>
       <c r="U120" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V120" s="144">
+      <c r="V120" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -8982,12 +9008,12 @@
       <c r="X120" s="144"/>
       <c r="Y120" s="145"/>
       <c r="Z120" s="144"/>
-      <c r="AA120" s="150"/>
+      <c r="AA120" s="151"/>
       <c r="AB120" s="145"/>
       <c r="AC120" s="144"/>
-      <c r="AD120" s="144"/>
-      <c r="AE120" s="151"/>
-      <c r="AF120" s="152"/>
+      <c r="AD120" s="152"/>
+      <c r="AE120" s="153"/>
+      <c r="AF120" s="154"/>
     </row>
     <row r="121" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A121" s="144"/>
@@ -9005,20 +9031,20 @@
       <c r="M121" s="144"/>
       <c r="N121" s="144"/>
       <c r="O121" s="147" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P121" s="144"/>
       <c r="Q121" s="144"/>
       <c r="R121" s="148"/>
       <c r="S121" s="149" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="T121" s="149"/>
       <c r="U121" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V121" s="144">
+      <c r="V121" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -9026,17 +9052,17 @@
       <c r="X121" s="144"/>
       <c r="Y121" s="145"/>
       <c r="Z121" s="144"/>
-      <c r="AA121" s="150"/>
+      <c r="AA121" s="151"/>
       <c r="AB121" s="145"/>
       <c r="AC121" s="144"/>
-      <c r="AD121" s="144"/>
-      <c r="AE121" s="154"/>
-      <c r="AF121" s="152"/>
+      <c r="AD121" s="152"/>
+      <c r="AE121" s="156"/>
+      <c r="AF121" s="154"/>
     </row>
     <row r="122" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A122" s="144"/>
       <c r="B122" s="144" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C122" s="144" t="s">
         <v>194</v>
@@ -9058,20 +9084,20 @@
       <c r="M122" s="144"/>
       <c r="N122" s="144"/>
       <c r="O122" s="147" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P122" s="144"/>
       <c r="Q122" s="144"/>
       <c r="R122" s="148"/>
       <c r="S122" s="149" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="T122" s="149"/>
       <c r="U122" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V122" s="144">
+      <c r="V122" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -9079,14 +9105,14 @@
       <c r="X122" s="144"/>
       <c r="Y122" s="145"/>
       <c r="Z122" s="144"/>
-      <c r="AA122" s="150"/>
+      <c r="AA122" s="151"/>
       <c r="AB122" s="145"/>
       <c r="AC122" s="144"/>
-      <c r="AD122" s="144"/>
-      <c r="AE122" s="151" t="s">
+      <c r="AD122" s="152"/>
+      <c r="AE122" s="153" t="s">
         <v>211</v>
       </c>
-      <c r="AF122" s="152"/>
+      <c r="AF122" s="154"/>
     </row>
     <row r="123" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A123" s="144"/>
@@ -9104,20 +9130,20 @@
       <c r="M123" s="144"/>
       <c r="N123" s="144"/>
       <c r="O123" s="147" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P123" s="144"/>
       <c r="Q123" s="144"/>
       <c r="R123" s="148"/>
       <c r="S123" s="149" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="T123" s="149"/>
       <c r="U123" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V123" s="144">
+      <c r="V123" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -9125,12 +9151,12 @@
       <c r="X123" s="144"/>
       <c r="Y123" s="145"/>
       <c r="Z123" s="144"/>
-      <c r="AA123" s="150"/>
+      <c r="AA123" s="151"/>
       <c r="AB123" s="145"/>
       <c r="AC123" s="144"/>
-      <c r="AD123" s="144"/>
-      <c r="AE123" s="153"/>
-      <c r="AF123" s="152"/>
+      <c r="AD123" s="152"/>
+      <c r="AE123" s="155"/>
+      <c r="AF123" s="154"/>
     </row>
     <row r="124" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A124" s="144"/>
@@ -9148,20 +9174,20 @@
       <c r="M124" s="144"/>
       <c r="N124" s="144"/>
       <c r="O124" s="147" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P124" s="144"/>
       <c r="Q124" s="144"/>
       <c r="R124" s="148"/>
       <c r="S124" s="149" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="T124" s="149"/>
       <c r="U124" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V124" s="144">
+      <c r="V124" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -9169,12 +9195,12 @@
       <c r="X124" s="144"/>
       <c r="Y124" s="145"/>
       <c r="Z124" s="144"/>
-      <c r="AA124" s="150"/>
+      <c r="AA124" s="151"/>
       <c r="AB124" s="145"/>
       <c r="AC124" s="144"/>
-      <c r="AD124" s="144"/>
-      <c r="AE124" s="154"/>
-      <c r="AF124" s="152"/>
+      <c r="AD124" s="152"/>
+      <c r="AE124" s="156"/>
+      <c r="AF124" s="154"/>
     </row>
     <row r="125" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A125" s="144"/>
@@ -9192,20 +9218,20 @@
       <c r="M125" s="144"/>
       <c r="N125" s="144"/>
       <c r="O125" s="147" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P125" s="144"/>
       <c r="Q125" s="144"/>
       <c r="R125" s="148"/>
       <c r="S125" s="149" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="T125" s="149"/>
       <c r="U125" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V125" s="144">
+      <c r="V125" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -9213,12 +9239,12 @@
       <c r="X125" s="144"/>
       <c r="Y125" s="145"/>
       <c r="Z125" s="144"/>
-      <c r="AA125" s="150"/>
+      <c r="AA125" s="151"/>
       <c r="AB125" s="145"/>
       <c r="AC125" s="144"/>
-      <c r="AD125" s="144"/>
-      <c r="AE125" s="151"/>
-      <c r="AF125" s="152"/>
+      <c r="AD125" s="152"/>
+      <c r="AE125" s="153"/>
+      <c r="AF125" s="154"/>
     </row>
     <row r="126" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A126" s="144"/>
@@ -9236,20 +9262,20 @@
       <c r="M126" s="144"/>
       <c r="N126" s="144"/>
       <c r="O126" s="147" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P126" s="144"/>
       <c r="Q126" s="144"/>
       <c r="R126" s="148"/>
       <c r="S126" s="149" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="T126" s="149"/>
       <c r="U126" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V126" s="144">
+      <c r="V126" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -9257,19 +9283,19 @@
       <c r="X126" s="144"/>
       <c r="Y126" s="145"/>
       <c r="Z126" s="144"/>
-      <c r="AA126" s="150"/>
+      <c r="AA126" s="151"/>
       <c r="AB126" s="145"/>
       <c r="AC126" s="144"/>
-      <c r="AD126" s="144"/>
-      <c r="AE126" s="154"/>
-      <c r="AF126" s="152"/>
+      <c r="AD126" s="152"/>
+      <c r="AE126" s="156"/>
+      <c r="AF126" s="154"/>
     </row>
     <row r="127" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A127" s="144" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B127" s="144" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C127" s="144" t="s">
         <v>194</v>
@@ -9285,7 +9311,7 @@
         <v>195</v>
       </c>
       <c r="I127" s="146" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J127" s="144"/>
       <c r="K127" s="145">
@@ -9298,20 +9324,20 @@
       <c r="M127" s="144"/>
       <c r="N127" s="144"/>
       <c r="O127" s="147" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P127" s="144"/>
       <c r="Q127" s="144"/>
       <c r="R127" s="148"/>
       <c r="S127" s="149" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="T127" s="149"/>
       <c r="U127" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V127" s="144">
+      <c r="V127" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -9329,23 +9355,24 @@
       <c r="Z127" s="144">
         <v>170</v>
       </c>
-      <c r="AA127" s="150">
+      <c r="AA127" s="151">
         <v>170</v>
       </c>
       <c r="AB127" s="145">
         <f>125/Z127</f>
         <v>0.735294117647059</v>
       </c>
-      <c r="AC127" s="144">
+      <c r="AC127" s="144" t="s">
+        <v>225</v>
+      </c>
+      <c r="AD127" s="152">
+        <f>20-AC127</f>
         <v>20</v>
       </c>
-      <c r="AD127" s="144">
-        <v>0</v>
-      </c>
-      <c r="AE127" s="151" t="s">
+      <c r="AE127" s="153" t="s">
         <v>199</v>
       </c>
-      <c r="AF127" s="152"/>
+      <c r="AF127" s="154"/>
     </row>
     <row r="128" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A128" s="144"/>
@@ -9363,20 +9390,20 @@
       <c r="M128" s="144"/>
       <c r="N128" s="144"/>
       <c r="O128" s="147" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P128" s="144"/>
       <c r="Q128" s="144"/>
       <c r="R128" s="148"/>
       <c r="S128" s="149" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="T128" s="149"/>
       <c r="U128" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V128" s="144">
+      <c r="V128" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -9384,12 +9411,12 @@
       <c r="X128" s="144"/>
       <c r="Y128" s="145"/>
       <c r="Z128" s="144"/>
-      <c r="AA128" s="150"/>
+      <c r="AA128" s="151"/>
       <c r="AB128" s="145"/>
       <c r="AC128" s="144"/>
-      <c r="AD128" s="144"/>
-      <c r="AE128" s="153"/>
-      <c r="AF128" s="152"/>
+      <c r="AD128" s="152"/>
+      <c r="AE128" s="155"/>
+      <c r="AF128" s="154"/>
     </row>
     <row r="129" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A129" s="144"/>
@@ -9407,20 +9434,20 @@
       <c r="M129" s="144"/>
       <c r="N129" s="144"/>
       <c r="O129" s="147" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P129" s="144"/>
       <c r="Q129" s="144"/>
       <c r="R129" s="148"/>
       <c r="S129" s="149" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="T129" s="149"/>
       <c r="U129" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V129" s="144">
+      <c r="V129" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -9428,12 +9455,12 @@
       <c r="X129" s="144"/>
       <c r="Y129" s="145"/>
       <c r="Z129" s="144"/>
-      <c r="AA129" s="150"/>
+      <c r="AA129" s="151"/>
       <c r="AB129" s="145"/>
       <c r="AC129" s="144"/>
-      <c r="AD129" s="144"/>
-      <c r="AE129" s="154"/>
-      <c r="AF129" s="152"/>
+      <c r="AD129" s="152"/>
+      <c r="AE129" s="156"/>
+      <c r="AF129" s="154"/>
     </row>
     <row r="130" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A130" s="144"/>
@@ -9451,20 +9478,20 @@
       <c r="M130" s="144"/>
       <c r="N130" s="144"/>
       <c r="O130" s="147" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P130" s="144"/>
       <c r="Q130" s="144"/>
       <c r="R130" s="148"/>
       <c r="S130" s="149" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="T130" s="149"/>
       <c r="U130" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V130" s="144">
+      <c r="V130" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -9472,12 +9499,12 @@
       <c r="X130" s="144"/>
       <c r="Y130" s="145"/>
       <c r="Z130" s="144"/>
-      <c r="AA130" s="150"/>
+      <c r="AA130" s="151"/>
       <c r="AB130" s="145"/>
       <c r="AC130" s="144"/>
-      <c r="AD130" s="144"/>
-      <c r="AE130" s="151"/>
-      <c r="AF130" s="152"/>
+      <c r="AD130" s="152"/>
+      <c r="AE130" s="153"/>
+      <c r="AF130" s="154"/>
     </row>
     <row r="131" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A131" s="144"/>
@@ -9495,20 +9522,20 @@
       <c r="M131" s="144"/>
       <c r="N131" s="144"/>
       <c r="O131" s="147" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P131" s="144"/>
       <c r="Q131" s="144"/>
       <c r="R131" s="148"/>
       <c r="S131" s="149" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="T131" s="149"/>
       <c r="U131" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V131" s="144">
+      <c r="V131" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -9516,17 +9543,17 @@
       <c r="X131" s="144"/>
       <c r="Y131" s="145"/>
       <c r="Z131" s="144"/>
-      <c r="AA131" s="150"/>
+      <c r="AA131" s="151"/>
       <c r="AB131" s="145"/>
       <c r="AC131" s="144"/>
-      <c r="AD131" s="144"/>
-      <c r="AE131" s="154"/>
-      <c r="AF131" s="152"/>
+      <c r="AD131" s="152"/>
+      <c r="AE131" s="156"/>
+      <c r="AF131" s="154"/>
     </row>
     <row r="132" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A132" s="144"/>
       <c r="B132" s="144" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C132" s="144" t="s">
         <v>194</v>
@@ -9548,20 +9575,20 @@
       <c r="M132" s="144"/>
       <c r="N132" s="144"/>
       <c r="O132" s="147" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P132" s="144"/>
       <c r="Q132" s="144"/>
       <c r="R132" s="148"/>
       <c r="S132" s="149" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="T132" s="149"/>
       <c r="U132" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V132" s="144">
+      <c r="V132" s="150">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -9569,14 +9596,14 @@
       <c r="X132" s="144"/>
       <c r="Y132" s="145"/>
       <c r="Z132" s="144"/>
-      <c r="AA132" s="150"/>
+      <c r="AA132" s="151"/>
       <c r="AB132" s="145"/>
       <c r="AC132" s="144"/>
-      <c r="AD132" s="144"/>
-      <c r="AE132" s="151" t="s">
+      <c r="AD132" s="152"/>
+      <c r="AE132" s="153" t="s">
         <v>211</v>
       </c>
-      <c r="AF132" s="152"/>
+      <c r="AF132" s="154"/>
     </row>
     <row r="133" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A133" s="144"/>
@@ -9594,20 +9621,20 @@
       <c r="M133" s="144"/>
       <c r="N133" s="144"/>
       <c r="O133" s="147" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P133" s="144"/>
       <c r="Q133" s="144"/>
       <c r="R133" s="148"/>
       <c r="S133" s="149" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="T133" s="149"/>
       <c r="U133" s="144">
         <f t="shared" ref="U133:U136" si="2">R133*0.935</f>
         <v>0</v>
       </c>
-      <c r="V133" s="144">
+      <c r="V133" s="150">
         <f t="shared" ref="V133:V136" si="3">U133/215</f>
         <v>0</v>
       </c>
@@ -9615,12 +9642,12 @@
       <c r="X133" s="144"/>
       <c r="Y133" s="145"/>
       <c r="Z133" s="144"/>
-      <c r="AA133" s="150"/>
+      <c r="AA133" s="151"/>
       <c r="AB133" s="145"/>
       <c r="AC133" s="144"/>
-      <c r="AD133" s="144"/>
-      <c r="AE133" s="153"/>
-      <c r="AF133" s="152"/>
+      <c r="AD133" s="152"/>
+      <c r="AE133" s="155"/>
+      <c r="AF133" s="154"/>
     </row>
     <row r="134" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A134" s="144"/>
@@ -9638,20 +9665,20 @@
       <c r="M134" s="144"/>
       <c r="N134" s="144"/>
       <c r="O134" s="147" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P134" s="144"/>
       <c r="Q134" s="144"/>
       <c r="R134" s="148"/>
       <c r="S134" s="149" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="T134" s="149"/>
       <c r="U134" s="144">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="V134" s="144">
+      <c r="V134" s="150">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -9659,12 +9686,12 @@
       <c r="X134" s="144"/>
       <c r="Y134" s="145"/>
       <c r="Z134" s="144"/>
-      <c r="AA134" s="150"/>
+      <c r="AA134" s="151"/>
       <c r="AB134" s="145"/>
       <c r="AC134" s="144"/>
-      <c r="AD134" s="144"/>
-      <c r="AE134" s="154"/>
-      <c r="AF134" s="152"/>
+      <c r="AD134" s="152"/>
+      <c r="AE134" s="156"/>
+      <c r="AF134" s="154"/>
     </row>
     <row r="135" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A135" s="144"/>
@@ -9682,20 +9709,20 @@
       <c r="M135" s="144"/>
       <c r="N135" s="144"/>
       <c r="O135" s="147" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P135" s="144"/>
       <c r="Q135" s="144"/>
       <c r="R135" s="148"/>
       <c r="S135" s="149" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="T135" s="149"/>
       <c r="U135" s="144">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="V135" s="144">
+      <c r="V135" s="150">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -9703,12 +9730,12 @@
       <c r="X135" s="144"/>
       <c r="Y135" s="145"/>
       <c r="Z135" s="144"/>
-      <c r="AA135" s="150"/>
+      <c r="AA135" s="151"/>
       <c r="AB135" s="145"/>
       <c r="AC135" s="144"/>
-      <c r="AD135" s="144"/>
-      <c r="AE135" s="151"/>
-      <c r="AF135" s="152"/>
+      <c r="AD135" s="152"/>
+      <c r="AE135" s="153"/>
+      <c r="AF135" s="154"/>
     </row>
     <row r="136" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
       <c r="A136" s="144"/>
@@ -9726,20 +9753,20 @@
       <c r="M136" s="144"/>
       <c r="N136" s="144"/>
       <c r="O136" s="147" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P136" s="144"/>
       <c r="Q136" s="144"/>
       <c r="R136" s="148"/>
       <c r="S136" s="149" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="T136" s="149"/>
       <c r="U136" s="144">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="V136" s="144">
+      <c r="V136" s="150">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -9747,19 +9774,19 @@
       <c r="X136" s="144"/>
       <c r="Y136" s="145"/>
       <c r="Z136" s="144"/>
-      <c r="AA136" s="150"/>
+      <c r="AA136" s="151"/>
       <c r="AB136" s="145"/>
       <c r="AC136" s="144"/>
-      <c r="AD136" s="144"/>
-      <c r="AE136" s="154"/>
-      <c r="AF136" s="152"/>
+      <c r="AD136" s="152"/>
+      <c r="AE136" s="156"/>
+      <c r="AF136" s="154"/>
     </row>
     <row r="137" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A137" s="144" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B137" s="144" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C137" s="144" t="s">
         <v>194</v>
@@ -9775,9 +9802,9 @@
         <v>195</v>
       </c>
       <c r="I137" s="146" t="s">
-        <v>358</v>
-      </c>
-      <c r="J137" s="157"/>
+        <v>359</v>
+      </c>
+      <c r="J137" s="159"/>
       <c r="K137" s="145">
         <f>J137/300</f>
         <v>0</v>
@@ -9787,24 +9814,24 @@
       </c>
       <c r="M137" s="144"/>
       <c r="N137" s="144"/>
-      <c r="O137" s="152"/>
-      <c r="P137" s="152"/>
-      <c r="Q137" s="152"/>
-      <c r="R137" s="152"/>
-      <c r="S137" s="152"/>
-      <c r="T137" s="152"/>
-      <c r="U137" s="152"/>
-      <c r="V137" s="152"/>
-      <c r="W137" s="152"/>
-      <c r="X137" s="152"/>
-      <c r="Y137" s="152"/>
-      <c r="Z137" s="152"/>
-      <c r="AA137" s="152"/>
-      <c r="AB137" s="152"/>
-      <c r="AC137" s="152"/>
-      <c r="AD137" s="152"/>
-      <c r="AE137" s="152"/>
-      <c r="AF137" s="152"/>
+      <c r="O137" s="154"/>
+      <c r="P137" s="154"/>
+      <c r="Q137" s="154"/>
+      <c r="R137" s="154"/>
+      <c r="S137" s="154"/>
+      <c r="T137" s="154"/>
+      <c r="U137" s="154"/>
+      <c r="V137" s="154"/>
+      <c r="W137" s="154"/>
+      <c r="X137" s="154"/>
+      <c r="Y137" s="154"/>
+      <c r="Z137" s="154"/>
+      <c r="AA137" s="154"/>
+      <c r="AB137" s="154"/>
+      <c r="AC137" s="154"/>
+      <c r="AD137" s="154"/>
+      <c r="AE137" s="154"/>
+      <c r="AF137" s="154"/>
     </row>
     <row r="138" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A138" s="144"/>
@@ -9816,29 +9843,29 @@
       <c r="G138" s="145"/>
       <c r="H138" s="146"/>
       <c r="I138" s="146"/>
-      <c r="J138" s="157"/>
+      <c r="J138" s="159"/>
       <c r="K138" s="145"/>
       <c r="L138" s="144"/>
       <c r="M138" s="144"/>
       <c r="N138" s="144"/>
-      <c r="O138" s="152"/>
-      <c r="P138" s="152"/>
-      <c r="Q138" s="152"/>
-      <c r="R138" s="152"/>
-      <c r="S138" s="152"/>
-      <c r="T138" s="152"/>
-      <c r="U138" s="152"/>
-      <c r="V138" s="152"/>
-      <c r="W138" s="152"/>
-      <c r="X138" s="152"/>
-      <c r="Y138" s="152"/>
-      <c r="Z138" s="152"/>
-      <c r="AA138" s="152"/>
-      <c r="AB138" s="152"/>
-      <c r="AC138" s="152"/>
-      <c r="AD138" s="152"/>
-      <c r="AE138" s="152"/>
-      <c r="AF138" s="152"/>
+      <c r="O138" s="154"/>
+      <c r="P138" s="154"/>
+      <c r="Q138" s="154"/>
+      <c r="R138" s="154"/>
+      <c r="S138" s="154"/>
+      <c r="T138" s="154"/>
+      <c r="U138" s="154"/>
+      <c r="V138" s="154"/>
+      <c r="W138" s="154"/>
+      <c r="X138" s="154"/>
+      <c r="Y138" s="154"/>
+      <c r="Z138" s="154"/>
+      <c r="AA138" s="154"/>
+      <c r="AB138" s="154"/>
+      <c r="AC138" s="154"/>
+      <c r="AD138" s="154"/>
+      <c r="AE138" s="154"/>
+      <c r="AF138" s="154"/>
     </row>
     <row r="139" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A139" s="144"/>
@@ -9850,29 +9877,29 @@
       <c r="G139" s="145"/>
       <c r="H139" s="146"/>
       <c r="I139" s="146"/>
-      <c r="J139" s="157"/>
+      <c r="J139" s="159"/>
       <c r="K139" s="145"/>
       <c r="L139" s="144"/>
       <c r="M139" s="144"/>
       <c r="N139" s="144"/>
-      <c r="O139" s="152"/>
-      <c r="P139" s="152"/>
-      <c r="Q139" s="152"/>
-      <c r="R139" s="152"/>
-      <c r="S139" s="152"/>
-      <c r="T139" s="152"/>
-      <c r="U139" s="152"/>
-      <c r="V139" s="152"/>
-      <c r="W139" s="152"/>
-      <c r="X139" s="152"/>
-      <c r="Y139" s="152"/>
-      <c r="Z139" s="152"/>
-      <c r="AA139" s="152"/>
-      <c r="AB139" s="152"/>
-      <c r="AC139" s="152"/>
-      <c r="AD139" s="152"/>
-      <c r="AE139" s="152"/>
-      <c r="AF139" s="152"/>
+      <c r="O139" s="154"/>
+      <c r="P139" s="154"/>
+      <c r="Q139" s="154"/>
+      <c r="R139" s="154"/>
+      <c r="S139" s="154"/>
+      <c r="T139" s="154"/>
+      <c r="U139" s="154"/>
+      <c r="V139" s="154"/>
+      <c r="W139" s="154"/>
+      <c r="X139" s="154"/>
+      <c r="Y139" s="154"/>
+      <c r="Z139" s="154"/>
+      <c r="AA139" s="154"/>
+      <c r="AB139" s="154"/>
+      <c r="AC139" s="154"/>
+      <c r="AD139" s="154"/>
+      <c r="AE139" s="154"/>
+      <c r="AF139" s="154"/>
     </row>
     <row r="140" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A140" s="144"/>
@@ -9884,29 +9911,29 @@
       <c r="G140" s="145"/>
       <c r="H140" s="146"/>
       <c r="I140" s="146"/>
-      <c r="J140" s="157"/>
+      <c r="J140" s="159"/>
       <c r="K140" s="145"/>
       <c r="L140" s="144"/>
       <c r="M140" s="144"/>
       <c r="N140" s="144"/>
-      <c r="O140" s="152"/>
-      <c r="P140" s="152"/>
-      <c r="Q140" s="152"/>
-      <c r="R140" s="152"/>
-      <c r="S140" s="152"/>
-      <c r="T140" s="152"/>
-      <c r="U140" s="152"/>
-      <c r="V140" s="152"/>
-      <c r="W140" s="152"/>
-      <c r="X140" s="152"/>
-      <c r="Y140" s="152"/>
-      <c r="Z140" s="152"/>
-      <c r="AA140" s="152"/>
-      <c r="AB140" s="152"/>
-      <c r="AC140" s="152"/>
-      <c r="AD140" s="152"/>
-      <c r="AE140" s="152"/>
-      <c r="AF140" s="152"/>
+      <c r="O140" s="154"/>
+      <c r="P140" s="154"/>
+      <c r="Q140" s="154"/>
+      <c r="R140" s="154"/>
+      <c r="S140" s="154"/>
+      <c r="T140" s="154"/>
+      <c r="U140" s="154"/>
+      <c r="V140" s="154"/>
+      <c r="W140" s="154"/>
+      <c r="X140" s="154"/>
+      <c r="Y140" s="154"/>
+      <c r="Z140" s="154"/>
+      <c r="AA140" s="154"/>
+      <c r="AB140" s="154"/>
+      <c r="AC140" s="154"/>
+      <c r="AD140" s="154"/>
+      <c r="AE140" s="154"/>
+      <c r="AF140" s="154"/>
     </row>
     <row r="141" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A141" s="144"/>
@@ -9918,34 +9945,34 @@
       <c r="G141" s="145"/>
       <c r="H141" s="146"/>
       <c r="I141" s="146"/>
-      <c r="J141" s="157"/>
+      <c r="J141" s="159"/>
       <c r="K141" s="145"/>
       <c r="L141" s="144"/>
       <c r="M141" s="144"/>
       <c r="N141" s="144"/>
-      <c r="O141" s="152"/>
-      <c r="P141" s="152"/>
-      <c r="Q141" s="152"/>
-      <c r="R141" s="152"/>
-      <c r="S141" s="152"/>
-      <c r="T141" s="152"/>
-      <c r="U141" s="152"/>
-      <c r="V141" s="152"/>
-      <c r="W141" s="152"/>
-      <c r="X141" s="152"/>
-      <c r="Y141" s="152"/>
-      <c r="Z141" s="152"/>
-      <c r="AA141" s="152"/>
-      <c r="AB141" s="152"/>
-      <c r="AC141" s="152"/>
-      <c r="AD141" s="152"/>
-      <c r="AE141" s="152"/>
-      <c r="AF141" s="152"/>
+      <c r="O141" s="154"/>
+      <c r="P141" s="154"/>
+      <c r="Q141" s="154"/>
+      <c r="R141" s="154"/>
+      <c r="S141" s="154"/>
+      <c r="T141" s="154"/>
+      <c r="U141" s="154"/>
+      <c r="V141" s="154"/>
+      <c r="W141" s="154"/>
+      <c r="X141" s="154"/>
+      <c r="Y141" s="154"/>
+      <c r="Z141" s="154"/>
+      <c r="AA141" s="154"/>
+      <c r="AB141" s="154"/>
+      <c r="AC141" s="154"/>
+      <c r="AD141" s="154"/>
+      <c r="AE141" s="154"/>
+      <c r="AF141" s="154"/>
     </row>
     <row r="142" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A142" s="144"/>
       <c r="B142" s="144" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C142" s="144" t="s">
         <v>194</v>
@@ -9961,7 +9988,7 @@
         <v>195</v>
       </c>
       <c r="I142" s="146" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="J142" s="144"/>
       <c r="K142" s="145">
@@ -9971,24 +9998,24 @@
       <c r="L142" s="144"/>
       <c r="M142" s="144"/>
       <c r="N142" s="144"/>
-      <c r="O142" s="152"/>
-      <c r="P142" s="152"/>
-      <c r="Q142" s="152"/>
-      <c r="R142" s="152"/>
-      <c r="S142" s="152"/>
-      <c r="T142" s="152"/>
-      <c r="U142" s="152"/>
-      <c r="V142" s="152"/>
-      <c r="W142" s="152"/>
-      <c r="X142" s="152"/>
-      <c r="Y142" s="152"/>
-      <c r="Z142" s="152"/>
-      <c r="AA142" s="152"/>
-      <c r="AB142" s="152"/>
-      <c r="AC142" s="152"/>
-      <c r="AD142" s="152"/>
-      <c r="AE142" s="152"/>
-      <c r="AF142" s="152"/>
+      <c r="O142" s="154"/>
+      <c r="P142" s="154"/>
+      <c r="Q142" s="154"/>
+      <c r="R142" s="154"/>
+      <c r="S142" s="154"/>
+      <c r="T142" s="154"/>
+      <c r="U142" s="154"/>
+      <c r="V142" s="154"/>
+      <c r="W142" s="154"/>
+      <c r="X142" s="154"/>
+      <c r="Y142" s="154"/>
+      <c r="Z142" s="154"/>
+      <c r="AA142" s="154"/>
+      <c r="AB142" s="154"/>
+      <c r="AC142" s="154"/>
+      <c r="AD142" s="154"/>
+      <c r="AE142" s="154"/>
+      <c r="AF142" s="154"/>
     </row>
     <row r="143" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A143" s="144"/>
@@ -10005,24 +10032,24 @@
       <c r="L143" s="144"/>
       <c r="M143" s="144"/>
       <c r="N143" s="144"/>
-      <c r="O143" s="152"/>
-      <c r="P143" s="152"/>
-      <c r="Q143" s="152"/>
-      <c r="R143" s="152"/>
-      <c r="S143" s="152"/>
-      <c r="T143" s="152"/>
-      <c r="U143" s="152"/>
-      <c r="V143" s="152"/>
-      <c r="W143" s="152"/>
-      <c r="X143" s="152"/>
-      <c r="Y143" s="152"/>
-      <c r="Z143" s="152"/>
-      <c r="AA143" s="152"/>
-      <c r="AB143" s="152"/>
-      <c r="AC143" s="152"/>
-      <c r="AD143" s="152"/>
-      <c r="AE143" s="152"/>
-      <c r="AF143" s="152"/>
+      <c r="O143" s="154"/>
+      <c r="P143" s="154"/>
+      <c r="Q143" s="154"/>
+      <c r="R143" s="154"/>
+      <c r="S143" s="154"/>
+      <c r="T143" s="154"/>
+      <c r="U143" s="154"/>
+      <c r="V143" s="154"/>
+      <c r="W143" s="154"/>
+      <c r="X143" s="154"/>
+      <c r="Y143" s="154"/>
+      <c r="Z143" s="154"/>
+      <c r="AA143" s="154"/>
+      <c r="AB143" s="154"/>
+      <c r="AC143" s="154"/>
+      <c r="AD143" s="154"/>
+      <c r="AE143" s="154"/>
+      <c r="AF143" s="154"/>
     </row>
     <row r="144" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A144" s="144"/>
@@ -10039,24 +10066,24 @@
       <c r="L144" s="144"/>
       <c r="M144" s="144"/>
       <c r="N144" s="144"/>
-      <c r="O144" s="152"/>
-      <c r="P144" s="152"/>
-      <c r="Q144" s="152"/>
-      <c r="R144" s="152"/>
-      <c r="S144" s="152"/>
-      <c r="T144" s="152"/>
-      <c r="U144" s="152"/>
-      <c r="V144" s="152"/>
-      <c r="W144" s="152"/>
-      <c r="X144" s="152"/>
-      <c r="Y144" s="152"/>
-      <c r="Z144" s="152"/>
-      <c r="AA144" s="152"/>
-      <c r="AB144" s="152"/>
-      <c r="AC144" s="152"/>
-      <c r="AD144" s="152"/>
-      <c r="AE144" s="152"/>
-      <c r="AF144" s="152"/>
+      <c r="O144" s="154"/>
+      <c r="P144" s="154"/>
+      <c r="Q144" s="154"/>
+      <c r="R144" s="154"/>
+      <c r="S144" s="154"/>
+      <c r="T144" s="154"/>
+      <c r="U144" s="154"/>
+      <c r="V144" s="154"/>
+      <c r="W144" s="154"/>
+      <c r="X144" s="154"/>
+      <c r="Y144" s="154"/>
+      <c r="Z144" s="154"/>
+      <c r="AA144" s="154"/>
+      <c r="AB144" s="154"/>
+      <c r="AC144" s="154"/>
+      <c r="AD144" s="154"/>
+      <c r="AE144" s="154"/>
+      <c r="AF144" s="154"/>
     </row>
     <row r="145" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A145" s="144"/>
@@ -10073,24 +10100,24 @@
       <c r="L145" s="144"/>
       <c r="M145" s="144"/>
       <c r="N145" s="144"/>
-      <c r="O145" s="152"/>
-      <c r="P145" s="152"/>
-      <c r="Q145" s="152"/>
-      <c r="R145" s="152"/>
-      <c r="S145" s="152"/>
-      <c r="T145" s="152"/>
-      <c r="U145" s="152"/>
-      <c r="V145" s="152"/>
-      <c r="W145" s="152"/>
-      <c r="X145" s="152"/>
-      <c r="Y145" s="152"/>
-      <c r="Z145" s="152"/>
-      <c r="AA145" s="152"/>
-      <c r="AB145" s="152"/>
-      <c r="AC145" s="152"/>
-      <c r="AD145" s="152"/>
-      <c r="AE145" s="152"/>
-      <c r="AF145" s="152"/>
+      <c r="O145" s="154"/>
+      <c r="P145" s="154"/>
+      <c r="Q145" s="154"/>
+      <c r="R145" s="154"/>
+      <c r="S145" s="154"/>
+      <c r="T145" s="154"/>
+      <c r="U145" s="154"/>
+      <c r="V145" s="154"/>
+      <c r="W145" s="154"/>
+      <c r="X145" s="154"/>
+      <c r="Y145" s="154"/>
+      <c r="Z145" s="154"/>
+      <c r="AA145" s="154"/>
+      <c r="AB145" s="154"/>
+      <c r="AC145" s="154"/>
+      <c r="AD145" s="154"/>
+      <c r="AE145" s="154"/>
+      <c r="AF145" s="154"/>
     </row>
     <row r="146" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A146" s="144"/>
@@ -10107,31 +10134,31 @@
       <c r="L146" s="144"/>
       <c r="M146" s="144"/>
       <c r="N146" s="144"/>
-      <c r="O146" s="152"/>
-      <c r="P146" s="152"/>
-      <c r="Q146" s="152"/>
-      <c r="R146" s="152"/>
-      <c r="S146" s="152"/>
-      <c r="T146" s="152"/>
-      <c r="U146" s="152"/>
-      <c r="V146" s="152"/>
-      <c r="W146" s="152"/>
-      <c r="X146" s="152"/>
-      <c r="Y146" s="152"/>
-      <c r="Z146" s="152"/>
-      <c r="AA146" s="152"/>
-      <c r="AB146" s="152"/>
-      <c r="AC146" s="152"/>
-      <c r="AD146" s="152"/>
-      <c r="AE146" s="152"/>
-      <c r="AF146" s="152"/>
+      <c r="O146" s="154"/>
+      <c r="P146" s="154"/>
+      <c r="Q146" s="154"/>
+      <c r="R146" s="154"/>
+      <c r="S146" s="154"/>
+      <c r="T146" s="154"/>
+      <c r="U146" s="154"/>
+      <c r="V146" s="154"/>
+      <c r="W146" s="154"/>
+      <c r="X146" s="154"/>
+      <c r="Y146" s="154"/>
+      <c r="Z146" s="154"/>
+      <c r="AA146" s="154"/>
+      <c r="AB146" s="154"/>
+      <c r="AC146" s="154"/>
+      <c r="AD146" s="154"/>
+      <c r="AE146" s="154"/>
+      <c r="AF146" s="154"/>
     </row>
     <row r="147" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A147" s="144" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B147" s="144" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C147" s="144" t="s">
         <v>194</v>
@@ -10147,7 +10174,7 @@
         <v>195</v>
       </c>
       <c r="I147" s="146" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J147" s="144"/>
       <c r="K147" s="145">
@@ -10159,24 +10186,24 @@
       </c>
       <c r="M147" s="144"/>
       <c r="N147" s="144"/>
-      <c r="O147" s="152"/>
-      <c r="P147" s="152"/>
-      <c r="Q147" s="152"/>
-      <c r="R147" s="152"/>
-      <c r="S147" s="152"/>
-      <c r="T147" s="152"/>
-      <c r="U147" s="152"/>
-      <c r="V147" s="152"/>
-      <c r="W147" s="152"/>
-      <c r="X147" s="152"/>
-      <c r="Y147" s="152"/>
-      <c r="Z147" s="152"/>
-      <c r="AA147" s="152"/>
-      <c r="AB147" s="152"/>
-      <c r="AC147" s="152"/>
-      <c r="AD147" s="152"/>
-      <c r="AE147" s="152"/>
-      <c r="AF147" s="152"/>
+      <c r="O147" s="154"/>
+      <c r="P147" s="154"/>
+      <c r="Q147" s="154"/>
+      <c r="R147" s="154"/>
+      <c r="S147" s="154"/>
+      <c r="T147" s="154"/>
+      <c r="U147" s="154"/>
+      <c r="V147" s="154"/>
+      <c r="W147" s="154"/>
+      <c r="X147" s="154"/>
+      <c r="Y147" s="154"/>
+      <c r="Z147" s="154"/>
+      <c r="AA147" s="154"/>
+      <c r="AB147" s="154"/>
+      <c r="AC147" s="154"/>
+      <c r="AD147" s="154"/>
+      <c r="AE147" s="154"/>
+      <c r="AF147" s="154"/>
     </row>
     <row r="148" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A148" s="144"/>
@@ -10193,24 +10220,24 @@
       <c r="L148" s="144"/>
       <c r="M148" s="144"/>
       <c r="N148" s="144"/>
-      <c r="O148" s="152"/>
-      <c r="P148" s="152"/>
-      <c r="Q148" s="152"/>
-      <c r="R148" s="152"/>
-      <c r="S148" s="152"/>
-      <c r="T148" s="152"/>
-      <c r="U148" s="152"/>
-      <c r="V148" s="152"/>
-      <c r="W148" s="152"/>
-      <c r="X148" s="152"/>
-      <c r="Y148" s="152"/>
-      <c r="Z148" s="152"/>
-      <c r="AA148" s="152"/>
-      <c r="AB148" s="152"/>
-      <c r="AC148" s="152"/>
-      <c r="AD148" s="152"/>
-      <c r="AE148" s="152"/>
-      <c r="AF148" s="152"/>
+      <c r="O148" s="154"/>
+      <c r="P148" s="154"/>
+      <c r="Q148" s="154"/>
+      <c r="R148" s="154"/>
+      <c r="S148" s="154"/>
+      <c r="T148" s="154"/>
+      <c r="U148" s="154"/>
+      <c r="V148" s="154"/>
+      <c r="W148" s="154"/>
+      <c r="X148" s="154"/>
+      <c r="Y148" s="154"/>
+      <c r="Z148" s="154"/>
+      <c r="AA148" s="154"/>
+      <c r="AB148" s="154"/>
+      <c r="AC148" s="154"/>
+      <c r="AD148" s="154"/>
+      <c r="AE148" s="154"/>
+      <c r="AF148" s="154"/>
     </row>
     <row r="149" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A149" s="144"/>
@@ -10227,24 +10254,24 @@
       <c r="L149" s="144"/>
       <c r="M149" s="144"/>
       <c r="N149" s="144"/>
-      <c r="O149" s="152"/>
-      <c r="P149" s="152"/>
-      <c r="Q149" s="152"/>
-      <c r="R149" s="152"/>
-      <c r="S149" s="152"/>
-      <c r="T149" s="152"/>
-      <c r="U149" s="152"/>
-      <c r="V149" s="152"/>
-      <c r="W149" s="152"/>
-      <c r="X149" s="152"/>
-      <c r="Y149" s="152"/>
-      <c r="Z149" s="152"/>
-      <c r="AA149" s="152"/>
-      <c r="AB149" s="152"/>
-      <c r="AC149" s="152"/>
-      <c r="AD149" s="152"/>
-      <c r="AE149" s="152"/>
-      <c r="AF149" s="152"/>
+      <c r="O149" s="154"/>
+      <c r="P149" s="154"/>
+      <c r="Q149" s="154"/>
+      <c r="R149" s="154"/>
+      <c r="S149" s="154"/>
+      <c r="T149" s="154"/>
+      <c r="U149" s="154"/>
+      <c r="V149" s="154"/>
+      <c r="W149" s="154"/>
+      <c r="X149" s="154"/>
+      <c r="Y149" s="154"/>
+      <c r="Z149" s="154"/>
+      <c r="AA149" s="154"/>
+      <c r="AB149" s="154"/>
+      <c r="AC149" s="154"/>
+      <c r="AD149" s="154"/>
+      <c r="AE149" s="154"/>
+      <c r="AF149" s="154"/>
     </row>
     <row r="150" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A150" s="144"/>
@@ -10261,24 +10288,24 @@
       <c r="L150" s="144"/>
       <c r="M150" s="144"/>
       <c r="N150" s="144"/>
-      <c r="O150" s="152"/>
-      <c r="P150" s="152"/>
-      <c r="Q150" s="152"/>
-      <c r="R150" s="152"/>
-      <c r="S150" s="152"/>
-      <c r="T150" s="152"/>
-      <c r="U150" s="152"/>
-      <c r="V150" s="152"/>
-      <c r="W150" s="152"/>
-      <c r="X150" s="152"/>
-      <c r="Y150" s="152"/>
-      <c r="Z150" s="152"/>
-      <c r="AA150" s="152"/>
-      <c r="AB150" s="152"/>
-      <c r="AC150" s="152"/>
-      <c r="AD150" s="152"/>
-      <c r="AE150" s="152"/>
-      <c r="AF150" s="152"/>
+      <c r="O150" s="154"/>
+      <c r="P150" s="154"/>
+      <c r="Q150" s="154"/>
+      <c r="R150" s="154"/>
+      <c r="S150" s="154"/>
+      <c r="T150" s="154"/>
+      <c r="U150" s="154"/>
+      <c r="V150" s="154"/>
+      <c r="W150" s="154"/>
+      <c r="X150" s="154"/>
+      <c r="Y150" s="154"/>
+      <c r="Z150" s="154"/>
+      <c r="AA150" s="154"/>
+      <c r="AB150" s="154"/>
+      <c r="AC150" s="154"/>
+      <c r="AD150" s="154"/>
+      <c r="AE150" s="154"/>
+      <c r="AF150" s="154"/>
     </row>
     <row r="151" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A151" s="144"/>
@@ -10295,29 +10322,29 @@
       <c r="L151" s="144"/>
       <c r="M151" s="144"/>
       <c r="N151" s="144"/>
-      <c r="O151" s="152"/>
-      <c r="P151" s="152"/>
-      <c r="Q151" s="152"/>
-      <c r="R151" s="152"/>
-      <c r="S151" s="152"/>
-      <c r="T151" s="152"/>
-      <c r="U151" s="152"/>
-      <c r="V151" s="152"/>
-      <c r="W151" s="152"/>
-      <c r="X151" s="152"/>
-      <c r="Y151" s="152"/>
-      <c r="Z151" s="152"/>
-      <c r="AA151" s="152"/>
-      <c r="AB151" s="152"/>
-      <c r="AC151" s="152"/>
-      <c r="AD151" s="152"/>
-      <c r="AE151" s="152"/>
-      <c r="AF151" s="152"/>
+      <c r="O151" s="154"/>
+      <c r="P151" s="154"/>
+      <c r="Q151" s="154"/>
+      <c r="R151" s="154"/>
+      <c r="S151" s="154"/>
+      <c r="T151" s="154"/>
+      <c r="U151" s="154"/>
+      <c r="V151" s="154"/>
+      <c r="W151" s="154"/>
+      <c r="X151" s="154"/>
+      <c r="Y151" s="154"/>
+      <c r="Z151" s="154"/>
+      <c r="AA151" s="154"/>
+      <c r="AB151" s="154"/>
+      <c r="AC151" s="154"/>
+      <c r="AD151" s="154"/>
+      <c r="AE151" s="154"/>
+      <c r="AF151" s="154"/>
     </row>
     <row r="152" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A152" s="144"/>
       <c r="B152" s="144" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C152" s="144" t="s">
         <v>194</v>
@@ -10333,7 +10360,7 @@
         <v>195</v>
       </c>
       <c r="I152" s="146" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J152" s="144"/>
       <c r="K152" s="145">
@@ -10343,24 +10370,24 @@
       <c r="L152" s="144"/>
       <c r="M152" s="144"/>
       <c r="N152" s="144"/>
-      <c r="O152" s="152"/>
-      <c r="P152" s="152"/>
-      <c r="Q152" s="152"/>
-      <c r="R152" s="152"/>
-      <c r="S152" s="152"/>
-      <c r="T152" s="152"/>
-      <c r="U152" s="152"/>
-      <c r="V152" s="152"/>
-      <c r="W152" s="152"/>
-      <c r="X152" s="152"/>
-      <c r="Y152" s="152"/>
-      <c r="Z152" s="152"/>
-      <c r="AA152" s="152"/>
-      <c r="AB152" s="152"/>
-      <c r="AC152" s="152"/>
-      <c r="AD152" s="152"/>
-      <c r="AE152" s="152"/>
-      <c r="AF152" s="152"/>
+      <c r="O152" s="154"/>
+      <c r="P152" s="154"/>
+      <c r="Q152" s="154"/>
+      <c r="R152" s="154"/>
+      <c r="S152" s="154"/>
+      <c r="T152" s="154"/>
+      <c r="U152" s="154"/>
+      <c r="V152" s="154"/>
+      <c r="W152" s="154"/>
+      <c r="X152" s="154"/>
+      <c r="Y152" s="154"/>
+      <c r="Z152" s="154"/>
+      <c r="AA152" s="154"/>
+      <c r="AB152" s="154"/>
+      <c r="AC152" s="154"/>
+      <c r="AD152" s="154"/>
+      <c r="AE152" s="154"/>
+      <c r="AF152" s="154"/>
     </row>
     <row r="153" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A153" s="144"/>
@@ -10377,24 +10404,24 @@
       <c r="L153" s="144"/>
       <c r="M153" s="144"/>
       <c r="N153" s="144"/>
-      <c r="O153" s="152"/>
-      <c r="P153" s="152"/>
-      <c r="Q153" s="152"/>
-      <c r="R153" s="152"/>
-      <c r="S153" s="152"/>
-      <c r="T153" s="152"/>
-      <c r="U153" s="152"/>
-      <c r="V153" s="152"/>
-      <c r="W153" s="152"/>
-      <c r="X153" s="152"/>
-      <c r="Y153" s="152"/>
-      <c r="Z153" s="152"/>
-      <c r="AA153" s="152"/>
-      <c r="AB153" s="152"/>
-      <c r="AC153" s="152"/>
-      <c r="AD153" s="152"/>
-      <c r="AE153" s="152"/>
-      <c r="AF153" s="152"/>
+      <c r="O153" s="154"/>
+      <c r="P153" s="154"/>
+      <c r="Q153" s="154"/>
+      <c r="R153" s="154"/>
+      <c r="S153" s="154"/>
+      <c r="T153" s="154"/>
+      <c r="U153" s="154"/>
+      <c r="V153" s="154"/>
+      <c r="W153" s="154"/>
+      <c r="X153" s="154"/>
+      <c r="Y153" s="154"/>
+      <c r="Z153" s="154"/>
+      <c r="AA153" s="154"/>
+      <c r="AB153" s="154"/>
+      <c r="AC153" s="154"/>
+      <c r="AD153" s="154"/>
+      <c r="AE153" s="154"/>
+      <c r="AF153" s="154"/>
     </row>
     <row r="154" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A154" s="144"/>
@@ -10411,24 +10438,24 @@
       <c r="L154" s="144"/>
       <c r="M154" s="144"/>
       <c r="N154" s="144"/>
-      <c r="O154" s="152"/>
-      <c r="P154" s="152"/>
-      <c r="Q154" s="152"/>
-      <c r="R154" s="152"/>
-      <c r="S154" s="152"/>
-      <c r="T154" s="152"/>
-      <c r="U154" s="152"/>
-      <c r="V154" s="152"/>
-      <c r="W154" s="152"/>
-      <c r="X154" s="152"/>
-      <c r="Y154" s="152"/>
-      <c r="Z154" s="152"/>
-      <c r="AA154" s="152"/>
-      <c r="AB154" s="152"/>
-      <c r="AC154" s="152"/>
-      <c r="AD154" s="152"/>
-      <c r="AE154" s="152"/>
-      <c r="AF154" s="152"/>
+      <c r="O154" s="154"/>
+      <c r="P154" s="154"/>
+      <c r="Q154" s="154"/>
+      <c r="R154" s="154"/>
+      <c r="S154" s="154"/>
+      <c r="T154" s="154"/>
+      <c r="U154" s="154"/>
+      <c r="V154" s="154"/>
+      <c r="W154" s="154"/>
+      <c r="X154" s="154"/>
+      <c r="Y154" s="154"/>
+      <c r="Z154" s="154"/>
+      <c r="AA154" s="154"/>
+      <c r="AB154" s="154"/>
+      <c r="AC154" s="154"/>
+      <c r="AD154" s="154"/>
+      <c r="AE154" s="154"/>
+      <c r="AF154" s="154"/>
     </row>
     <row r="155" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A155" s="144"/>
@@ -10445,24 +10472,24 @@
       <c r="L155" s="144"/>
       <c r="M155" s="144"/>
       <c r="N155" s="144"/>
-      <c r="O155" s="152"/>
-      <c r="P155" s="152"/>
-      <c r="Q155" s="152"/>
-      <c r="R155" s="152"/>
-      <c r="S155" s="152"/>
-      <c r="T155" s="152"/>
-      <c r="U155" s="152"/>
-      <c r="V155" s="152"/>
-      <c r="W155" s="152"/>
-      <c r="X155" s="152"/>
-      <c r="Y155" s="152"/>
-      <c r="Z155" s="152"/>
-      <c r="AA155" s="152"/>
-      <c r="AB155" s="152"/>
-      <c r="AC155" s="152"/>
-      <c r="AD155" s="152"/>
-      <c r="AE155" s="152"/>
-      <c r="AF155" s="152"/>
+      <c r="O155" s="154"/>
+      <c r="P155" s="154"/>
+      <c r="Q155" s="154"/>
+      <c r="R155" s="154"/>
+      <c r="S155" s="154"/>
+      <c r="T155" s="154"/>
+      <c r="U155" s="154"/>
+      <c r="V155" s="154"/>
+      <c r="W155" s="154"/>
+      <c r="X155" s="154"/>
+      <c r="Y155" s="154"/>
+      <c r="Z155" s="154"/>
+      <c r="AA155" s="154"/>
+      <c r="AB155" s="154"/>
+      <c r="AC155" s="154"/>
+      <c r="AD155" s="154"/>
+      <c r="AE155" s="154"/>
+      <c r="AF155" s="154"/>
     </row>
     <row r="156" s="10" customFormat="1" ht="16.5" customHeight="1" spans="1:32">
       <c r="A156" s="144"/>
@@ -10479,24 +10506,24 @@
       <c r="L156" s="144"/>
       <c r="M156" s="144"/>
       <c r="N156" s="144"/>
-      <c r="O156" s="152"/>
-      <c r="P156" s="152"/>
-      <c r="Q156" s="152"/>
-      <c r="R156" s="152"/>
-      <c r="S156" s="152"/>
-      <c r="T156" s="152"/>
-      <c r="U156" s="152"/>
-      <c r="V156" s="152"/>
-      <c r="W156" s="152"/>
-      <c r="X156" s="152"/>
-      <c r="Y156" s="152"/>
-      <c r="Z156" s="152"/>
-      <c r="AA156" s="152"/>
-      <c r="AB156" s="152"/>
-      <c r="AC156" s="152"/>
-      <c r="AD156" s="152"/>
-      <c r="AE156" s="152"/>
-      <c r="AF156" s="152"/>
+      <c r="O156" s="154"/>
+      <c r="P156" s="154"/>
+      <c r="Q156" s="154"/>
+      <c r="R156" s="154"/>
+      <c r="S156" s="154"/>
+      <c r="T156" s="154"/>
+      <c r="U156" s="154"/>
+      <c r="V156" s="154"/>
+      <c r="W156" s="154"/>
+      <c r="X156" s="154"/>
+      <c r="Y156" s="154"/>
+      <c r="Z156" s="154"/>
+      <c r="AA156" s="154"/>
+      <c r="AB156" s="154"/>
+      <c r="AC156" s="154"/>
+      <c r="AD156" s="154"/>
+      <c r="AE156" s="154"/>
+      <c r="AF156" s="154"/>
     </row>
   </sheetData>
   <protectedRanges>
@@ -11196,7 +11223,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1da3db35-e0de-4637-8cac-3c85e7214f3c}</x14:id>
+          <x14:id>{c225ef76-32b1-4107-b13f-e45856487c0d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11208,7 +11235,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{474b9d92-1ffe-4115-82c8-ec6b40fcd5a4}</x14:id>
+          <x14:id>{46a6ce33-a119-4f0f-9e9c-0af763e560d1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11220,7 +11247,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e0ce3279-baf1-47aa-91c5-0b8563f222a0}</x14:id>
+          <x14:id>{4dee5fbe-8b0c-4148-84e4-a0e4ca015b21}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11232,7 +11259,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1e5930d1-e00e-452d-8fa3-dae07de9dcf7}</x14:id>
+          <x14:id>{f252c381-faa2-43c3-ac8c-769660b7722d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11244,7 +11271,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{eeccbae5-276b-43f8-a71f-e2eb915fb9bc}</x14:id>
+          <x14:id>{af6bfa59-2503-4199-93c8-065423321a52}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11256,7 +11283,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{556339b3-d1ef-439b-99d2-f8eb96afb18e}</x14:id>
+          <x14:id>{7c6f9303-3371-416b-b614-5e07de55d60b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11268,7 +11295,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2db46e07-ff34-4840-bd4a-135b2336675c}</x14:id>
+          <x14:id>{478cac5c-4898-48d0-8066-d2c7b9d17061}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11280,7 +11307,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6521ab67-9f01-402a-97c0-0d915b92a321}</x14:id>
+          <x14:id>{78c9caf2-fc88-4cac-aff4-f0f9dfbb20de}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11294,7 +11321,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9faa95e9-88d2-4727-86b2-0fb536804f95}</x14:id>
+          <x14:id>{d660ff2f-58af-4ad0-b6f8-09a9d94d4bd5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11306,7 +11333,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2587a784-9c20-4dcb-b833-c69f805759f0}</x14:id>
+          <x14:id>{e7f8e0c2-fc85-4c77-b601-a43fc186b5c5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11318,7 +11345,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{43d832dc-c892-4954-b2c1-6b501a9267f2}</x14:id>
+          <x14:id>{d0a6cac1-cfbe-4a3a-9a9e-f07b2c487ca0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11330,7 +11357,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{af39b56f-c4b5-4572-9790-21a3c54b81c8}</x14:id>
+          <x14:id>{b512685c-c9c1-48b1-bfa7-ab7f3b53babb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11342,7 +11369,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0bcb0cd1-0bdc-477e-8a9b-33867e2f0fba}</x14:id>
+          <x14:id>{e813553f-d111-4b2f-9da4-d1bcc630326f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11354,7 +11381,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8bdadc4f-6d93-4c45-a48d-c2869299329c}</x14:id>
+          <x14:id>{8bdb300b-fe6d-4a9b-8084-0d876a36e294}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11366,7 +11393,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{673e544d-8894-4fc3-a197-f35ea33dc948}</x14:id>
+          <x14:id>{97d7c685-6583-4710-8165-3088da514fdb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11378,7 +11405,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4d377490-d59b-4332-af3f-da73565f9d87}</x14:id>
+          <x14:id>{377bcbb3-c3a6-4daf-abb6-47bd8caba8ed}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11392,7 +11419,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9dcc16f2-2563-4136-b255-ead55e4f64df}</x14:id>
+          <x14:id>{cf1dd6e6-dcb3-4fa1-bf31-2fd5dda5783d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11404,7 +11431,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{20836c02-3095-4d39-b1e0-cbdfdf20850f}</x14:id>
+          <x14:id>{58aadbbe-a478-41bb-881d-90e7ef242127}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11416,7 +11443,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3a9c2586-9524-48e6-b4e3-e4793ca77f19}</x14:id>
+          <x14:id>{c5382078-42c8-4c88-a3d7-1262eadc26f8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11428,7 +11455,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9194b549-efb1-4449-8d2a-c19c0fa1a603}</x14:id>
+          <x14:id>{8e93b0d0-323b-4ee6-b55c-4db0b5b3bf11}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11440,7 +11467,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ec5fd816-b684-416b-b8d0-bcd438e0e1cd}</x14:id>
+          <x14:id>{a7215c72-9388-45c7-a128-8abd51e34b81}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11452,7 +11479,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ae1c7fdc-3583-43fe-a643-40fcee8d880d}</x14:id>
+          <x14:id>{1b8330c5-f320-40ef-a39e-7b4d47cfc94a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11464,7 +11491,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b7d0c8ad-79d9-485d-96f2-c0fd547b5797}</x14:id>
+          <x14:id>{33470546-db21-4587-8f2f-50a1ee0471ce}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11476,7 +11503,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dbffe5e6-9a99-4713-b84b-224185c9bea5}</x14:id>
+          <x14:id>{9b85416c-96fb-472d-a412-5c5f2e181852}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11490,7 +11517,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c9836aef-56e4-4308-aa81-4975bc28c8aa}</x14:id>
+          <x14:id>{6ec4b172-19b0-4ed4-a5f1-d31a01c712ce}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11502,7 +11529,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4f03b995-96e3-4cad-86b1-a19d196d956f}</x14:id>
+          <x14:id>{c81fee0f-9cca-4b0e-8095-0c6c44946cda}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11514,7 +11541,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e66765d7-fd81-4ca0-b791-0b4e4f821316}</x14:id>
+          <x14:id>{d6b1edf8-7445-4954-a5f3-c9963cddc74f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11526,7 +11553,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e943295f-0c7a-4057-a716-fca669db8cbd}</x14:id>
+          <x14:id>{8da5670e-87d3-49a5-898a-e4bf5b0cfce7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11538,7 +11565,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b65dda20-f4b3-4ddd-b307-2c4e8621ba90}</x14:id>
+          <x14:id>{3754de99-96e9-4fce-ae40-035b7acfccd0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11550,7 +11577,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{87673fc6-aff5-4cd5-8937-8ebfa3b25ac8}</x14:id>
+          <x14:id>{2e542bea-9208-4ab1-981d-743d946f2639}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11562,7 +11589,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7702302b-a4f7-4023-b972-1e591c44c741}</x14:id>
+          <x14:id>{e85b31fd-afeb-416d-8eaf-7a9f23f21d79}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11574,7 +11601,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{db276c26-b88a-45f5-ae0f-f8699e86348f}</x14:id>
+          <x14:id>{173cc9b7-8046-4c69-afdb-5731e46922bb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11588,7 +11615,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{332a349c-ba9c-44ae-b309-36f044f3b59c}</x14:id>
+          <x14:id>{522d9ecf-93c3-4a8d-b97c-a18e478013d7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11600,7 +11627,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0ff3786b-d8c8-466d-b37f-be6e728b64cb}</x14:id>
+          <x14:id>{aeb2684c-0698-412b-9433-2276031bcd97}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11612,7 +11639,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{85162bb4-1156-41df-a6a1-5a9b7fd44c51}</x14:id>
+          <x14:id>{1fadca5e-532e-47cd-9f78-553e49cd3a15}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11624,7 +11651,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e9dadf45-3852-4644-8175-f3d774c883b1}</x14:id>
+          <x14:id>{997ab22c-e880-4834-812e-e8c85e47d3ea}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11636,7 +11663,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f92c8313-2d16-483a-b750-c5f8bde29a51}</x14:id>
+          <x14:id>{7aec1cda-b23b-489f-bd42-9b4ba0d853c3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11648,7 +11675,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1354f2bd-ed6f-48c6-9b32-1c63461643bf}</x14:id>
+          <x14:id>{6d6aa373-2269-46d3-8464-8c932609ce2c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11660,7 +11687,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{751d7f5b-ee3b-4eac-8d8d-f5629105a874}</x14:id>
+          <x14:id>{46f6c195-718d-4e14-9728-15ef54a6bf5c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11672,7 +11699,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{efea9994-7ebf-4f3b-afdf-4be1f3d3c3bb}</x14:id>
+          <x14:id>{d5209a5e-f2a3-4e3a-8a77-1299dda3f7b9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11686,7 +11713,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9a7b94d4-0abe-4442-a079-80e6113e65aa}</x14:id>
+          <x14:id>{5c90f9be-5f18-46af-a49f-b7b41a3fe50a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11698,7 +11725,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d2723b4a-e9c7-4284-bf96-1b02f99c9f40}</x14:id>
+          <x14:id>{2d59d358-75d8-4e3d-b081-0233aee43e60}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11710,7 +11737,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d0a9292a-cf53-466d-bb98-84a6b079abac}</x14:id>
+          <x14:id>{42cad728-6bf9-4112-8d89-7bf6e89af1c8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11722,7 +11749,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{656d8af9-a1a7-4187-b1ca-6f9fc987f9e3}</x14:id>
+          <x14:id>{6a4a0517-ebf3-4b28-af23-cc2a63f8ae51}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11734,7 +11761,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d848efc1-5079-431c-b889-11c2b8128978}</x14:id>
+          <x14:id>{b073d464-325f-46f4-8aca-82c911c2c54a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11746,7 +11773,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d6c1169e-903a-4a43-b569-024053012600}</x14:id>
+          <x14:id>{ac525358-0bbb-4b2b-94d7-f5b2f8600c14}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11758,7 +11785,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{09202eaf-4698-468c-b0f4-4f7934a661c6}</x14:id>
+          <x14:id>{a680082a-f179-41e4-8956-83005cabed5a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11770,7 +11797,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cbb49d92-2bfe-4d5b-94d8-5e669449f4d4}</x14:id>
+          <x14:id>{99057d32-4a90-4216-ac02-7e171d381eba}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11784,7 +11811,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{50ddb17c-8b0b-489d-b05a-8b6ed8eadc39}</x14:id>
+          <x14:id>{76e93a2b-b739-407a-822a-a21f39353549}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11796,7 +11823,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{793ff324-a580-4faf-b775-ce2a0a32f947}</x14:id>
+          <x14:id>{e3f9f10b-6c8b-4d75-bb07-c78530f64295}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11808,7 +11835,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{795875a8-2197-4ea1-a2db-68f8b88009a5}</x14:id>
+          <x14:id>{c352ec72-1372-4ecf-914c-876293976760}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11822,7 +11849,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6b838c8f-79f2-48a1-994c-879afe768f49}</x14:id>
+          <x14:id>{b4c305d3-68e1-45e5-9afa-971f2e4f0dbc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11834,7 +11861,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e6e7d347-d4d0-4fe8-864c-ca973fface99}</x14:id>
+          <x14:id>{8952e5d4-f15f-4bbe-9bcb-c544521cacb3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11846,7 +11873,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{945f2514-266e-4714-ae41-19452013187f}</x14:id>
+          <x14:id>{10d58e92-8da8-4f3b-ab82-88e5f58cd001}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11860,7 +11887,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{49f721c3-43e3-42d6-88a4-6922da978388}</x14:id>
+          <x14:id>{7006c997-06b7-42f1-b915-e8f9e36068e6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11872,7 +11899,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{775eeb1e-986d-4170-b7e9-1b7dbd146952}</x14:id>
+          <x14:id>{b7e4c6d3-2fbe-4198-9f18-06ec345a0676}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11886,7 +11913,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f3da6d2c-0058-49f7-891b-958eb706ca40}</x14:id>
+          <x14:id>{11f93e7b-d009-4058-97ab-7ee0d80c5603}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11898,7 +11925,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e669da9d-968a-4cb7-a0f8-de24d8b7204b}</x14:id>
+          <x14:id>{16a7be33-addc-4f85-92ca-9ca9b6a83538}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11910,7 +11937,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{73d7254b-8e4f-4eaa-910a-63b1cb687810}</x14:id>
+          <x14:id>{15d49145-47bb-4181-b484-e1e5afba6595}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11924,7 +11951,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{35190ae1-ddc7-4c8d-8458-af532f2cde6f}</x14:id>
+          <x14:id>{ff95bea1-253f-41a2-aa3e-8d24806fe3e0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11936,7 +11963,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{06b69c74-1b95-4997-b297-1f7cc576c3e6}</x14:id>
+          <x14:id>{db8b16ff-a075-4566-a062-f61ffb4cd307}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11948,7 +11975,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{436a0d13-61f0-4be0-b5aa-22fc6eb8e6c1}</x14:id>
+          <x14:id>{5bb9d894-234f-483c-b4c8-76e4da462943}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11962,7 +11989,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{706a3fcb-1d85-40b2-898e-fd06f3e2bcf0}</x14:id>
+          <x14:id>{2c9fe9b6-a00e-4c10-b264-c9dee6fc60b6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11974,7 +12001,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{231ca8ec-2eb4-4352-8e09-8a12a66c054f}</x14:id>
+          <x14:id>{1ce93724-31e5-4546-a045-f58ec92721ee}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11986,7 +12013,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4e6d922e-0e9d-4bae-a172-645d781604e1}</x14:id>
+          <x14:id>{cc9886ff-fcd6-4a53-8597-54d7f2112de1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12000,7 +12027,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c1437ea7-ec3a-48d8-873a-390dba8d7244}</x14:id>
+          <x14:id>{cf58e321-69c2-4c9d-9878-23da3030c0d6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12012,7 +12039,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c62a4a68-77e7-47b2-bf65-44fdcb3a6ba9}</x14:id>
+          <x14:id>{41c26bca-2b74-4ba8-b670-f8441c67ee18}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12024,7 +12051,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{308aaaf8-de3d-491d-8809-f9390adcd150}</x14:id>
+          <x14:id>{8ac2b46b-415a-4c3c-a747-7c9df6bb0856}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12038,7 +12065,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6e9531bb-ec62-46ba-9bfa-658ad9e5b0bb}</x14:id>
+          <x14:id>{20d1b445-c590-4204-94bd-072baa64b8ea}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12050,7 +12077,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4e0640a1-c697-4278-bd18-3640b683175e}</x14:id>
+          <x14:id>{313d2e12-39fe-4e0f-9dd0-91c7f0629e7c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12062,7 +12089,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1dea3367-eacb-49a0-83c2-c9f651a841bf}</x14:id>
+          <x14:id>{8bc30156-b7bf-4f9d-999c-fd63f94ac7c1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12076,7 +12103,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b557506d-2332-4c67-912e-e6bdae802d34}</x14:id>
+          <x14:id>{9c5da7b0-fd1e-420c-a06c-70fc4175f740}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12088,7 +12115,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{50feb3ad-3624-4d68-b2ee-b8b2446f41b8}</x14:id>
+          <x14:id>{a3ebd163-8418-45f5-9a43-c932ae836997}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12100,7 +12127,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a4bf74ed-cbfa-4b68-b0d5-d7975c80e69d}</x14:id>
+          <x14:id>{4e18ea4e-eab5-4d2b-a497-db14fc0efdd0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12112,7 +12139,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e73e25a9-b3d3-4109-adcd-318d50948973}</x14:id>
+          <x14:id>{e86cbe27-076f-4dd2-85ea-76837f71adc1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12124,7 +12151,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{be8ac6ba-d692-4685-948d-8b2b4c46042b}</x14:id>
+          <x14:id>{e1c4336d-ff8b-41e7-b3eb-b727fecf193c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12136,7 +12163,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2274d0da-65c8-4d66-930f-fc62421f30ed}</x14:id>
+          <x14:id>{adefc37a-f16a-4187-89b7-2299314341a0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12148,7 +12175,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cd557e40-4a23-4200-852a-f07214b169e1}</x14:id>
+          <x14:id>{e757e693-15e0-4595-bf74-1109be2e8df7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12160,7 +12187,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cbb84d30-4e47-4591-83dd-f60f47757922}</x14:id>
+          <x14:id>{b2a70351-b30b-41ee-8f5e-8d9f5dcccaf4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12174,7 +12201,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{63a08510-99d1-455f-9ac2-933b5d813967}</x14:id>
+          <x14:id>{1b751ad6-9aae-471e-856b-6b9fcea12d3b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12186,7 +12213,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3e43d9ad-f536-4b93-be9d-40b883fd13d0}</x14:id>
+          <x14:id>{7c1051e5-84af-4990-a0d9-677820f1a72a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12200,7 +12227,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5f9bcfac-43de-4c82-983b-df2034727220}</x14:id>
+          <x14:id>{3ca49927-f367-4b32-bcfa-ad5fcecf97b0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12214,7 +12241,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8ac50690-eb3e-436a-bb90-364a1ef77013}</x14:id>
+          <x14:id>{94f1da0b-76fa-4aaa-9ae2-89cc207e971b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12228,7 +12255,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8d01d611-0c1a-4df7-99bf-9a4f7500aa65}</x14:id>
+          <x14:id>{e40576c4-ad51-4ab1-845c-5c5f9924b5bd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12242,7 +12269,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{06bc5bb0-3a29-4b18-bc3a-64698600c1fe}</x14:id>
+          <x14:id>{e71d0b06-aca6-4d08-8db7-4dd7f409e5e1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12256,7 +12283,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5902d624-66be-4b22-937f-1f9ac871a476}</x14:id>
+          <x14:id>{b3375f06-4fac-496a-afe6-954864bee6d8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12268,7 +12295,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9141eac8-21c4-45ec-88df-70bc8ffe0dba}</x14:id>
+          <x14:id>{c67fac55-97ca-4f40-9b7e-a88664bda925}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12280,7 +12307,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9e9d23a1-8322-4080-aa88-9e8d6e6e8ddf}</x14:id>
+          <x14:id>{ffc1f4f4-4385-4e5d-abe4-2607d9d10086}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12294,7 +12321,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e9fcbe0b-2a6f-4291-bb5d-999e5c13b8c6}</x14:id>
+          <x14:id>{e6424149-2dbf-4588-978c-3e06a1c904c3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12306,7 +12333,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{02498975-8e3b-4555-8b2a-27d512282a33}</x14:id>
+          <x14:id>{f80f76eb-67c8-489c-8ec1-130ed5158f5a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12318,7 +12345,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f22738fc-b7a1-4b66-ac0a-2df173d21147}</x14:id>
+          <x14:id>{dc2858ff-8f8f-4d63-9f3f-5754d621243d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12332,7 +12359,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9fc64bf2-4283-4e67-acbc-a6cd9b17cd1d}</x14:id>
+          <x14:id>{71c86f7b-727a-4c53-9192-e0f4010c8f60}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12344,7 +12371,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{91f69053-db54-4ce6-8ec5-ff34b0c6a9de}</x14:id>
+          <x14:id>{7af86aec-9371-4dec-b230-bdaf05af3f4e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12356,7 +12383,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2ccd3aa7-106f-4180-9e53-76f7f699ec68}</x14:id>
+          <x14:id>{ebb74a8b-084f-4efa-8224-17d458b412a7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12370,7 +12397,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{25470856-6f23-4593-8ec4-f86affb01ee0}</x14:id>
+          <x14:id>{d867b97b-7a06-4f0b-b6fc-883b61e7ab14}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12382,7 +12409,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0839ac72-afc6-4229-9e68-09b9356349d3}</x14:id>
+          <x14:id>{bce4b6be-cdab-48a9-a066-2c4253c80a15}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12394,7 +12421,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e37b83ed-9c68-45e0-b4eb-444c9bc888b3}</x14:id>
+          <x14:id>{cb30e02c-cc76-4ea7-98ff-dfe6013a897f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12408,7 +12435,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{00cfb6ef-13e0-4395-b33b-0513f6ae6320}</x14:id>
+          <x14:id>{eb2fbaac-ad3a-4509-acad-a72f80cd0ad5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12420,7 +12447,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{86936f7d-2a48-4bd5-9abe-940fc10c68a4}</x14:id>
+          <x14:id>{b91e7df2-5bed-47dc-832e-6ba01f1c322b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12434,7 +12461,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8378c0a3-1189-4703-9bb8-28d85b14e686}</x14:id>
+          <x14:id>{0e72f36c-5955-4e72-b67d-c9a69fb5ee7b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12446,7 +12473,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dcbe0761-6206-4cad-b35b-c7883721cdc1}</x14:id>
+          <x14:id>{075b32f0-5559-4110-9e64-c8e4b78b53f9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12458,7 +12485,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5ae50ee2-7ea8-4cd9-a668-736ace3fd960}</x14:id>
+          <x14:id>{24f2a45b-dd32-4f1f-a235-3be38e264c81}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12472,7 +12499,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8a42bb25-8a8a-4eb1-b363-b34dae49c8e9}</x14:id>
+          <x14:id>{5a73aaa2-8814-467a-8278-425d1ba1d4af}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12484,7 +12511,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c909e2ce-ba4f-4b08-8248-09e330ec0f70}</x14:id>
+          <x14:id>{8d59a0a5-ffda-4090-877e-a55bb619f89a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12496,7 +12523,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{81ecb00b-3b42-40b9-acb8-8ba0f5c396b7}</x14:id>
+          <x14:id>{f0cd1e36-12dd-4dd4-ae4b-63cf2f88022b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12510,7 +12537,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dc34360e-ce4c-4a57-8132-20b34c230b4c}</x14:id>
+          <x14:id>{35198f7e-39ba-47d9-96fb-7482b4546696}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12522,7 +12549,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{74322a95-9f58-4b91-82df-432823bc7208}</x14:id>
+          <x14:id>{f61ca27d-8472-4383-ae26-282214c5eecc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12544,7 +12571,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G6:I6 P6:R6">
       <formula1>"A班,B班,C班,D班"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A51:B51 A11:B18 A20:B48 A49:B50">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A11:B18 A20:B51">
       <formula1>"A楼,B楼,C楼,D楼,E楼"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12556,7 +12583,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1da3db35-e0de-4637-8cac-3c85e7214f3c}">
+          <x14:cfRule type="dataBar" id="{c225ef76-32b1-4107-b13f-e45856487c0d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12565,7 +12592,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{474b9d92-1ffe-4115-82c8-ec6b40fcd5a4}">
+          <x14:cfRule type="dataBar" id="{46a6ce33-a119-4f0f-9e9c-0af763e560d1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12574,7 +12601,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e0ce3279-baf1-47aa-91c5-0b8563f222a0}">
+          <x14:cfRule type="dataBar" id="{4dee5fbe-8b0c-4148-84e4-a0e4ca015b21}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12585,7 +12612,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1e5930d1-e00e-452d-8fa3-dae07de9dcf7}">
+          <x14:cfRule type="dataBar" id="{f252c381-faa2-43c3-ac8c-769660b7722d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12596,7 +12623,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{eeccbae5-276b-43f8-a71f-e2eb915fb9bc}">
+          <x14:cfRule type="dataBar" id="{af6bfa59-2503-4199-93c8-065423321a52}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12607,14 +12634,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{556339b3-d1ef-439b-99d2-f8eb96afb18e}">
+          <x14:cfRule type="dataBar" id="{7c6f9303-3371-416b-b614-5e07de55d60b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2db46e07-ff34-4840-bd4a-135b2336675c}">
+          <x14:cfRule type="dataBar" id="{478cac5c-4898-48d0-8066-d2c7b9d17061}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12625,7 +12652,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6521ab67-9f01-402a-97c0-0d915b92a321}">
+          <x14:cfRule type="dataBar" id="{78c9caf2-fc88-4cac-aff4-f0f9dfbb20de}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12639,7 +12666,7 @@
           <xm:sqref>AD58</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9faa95e9-88d2-4727-86b2-0fb536804f95}">
+          <x14:cfRule type="dataBar" id="{d660ff2f-58af-4ad0-b6f8-09a9d94d4bd5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12648,7 +12675,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2587a784-9c20-4dcb-b833-c69f805759f0}">
+          <x14:cfRule type="dataBar" id="{e7f8e0c2-fc85-4c77-b601-a43fc186b5c5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12657,7 +12684,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{43d832dc-c892-4954-b2c1-6b501a9267f2}">
+          <x14:cfRule type="dataBar" id="{d0a6cac1-cfbe-4a3a-9a9e-f07b2c487ca0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12668,7 +12695,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{af39b56f-c4b5-4572-9790-21a3c54b81c8}">
+          <x14:cfRule type="dataBar" id="{b512685c-c9c1-48b1-bfa7-ab7f3b53babb}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12679,7 +12706,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0bcb0cd1-0bdc-477e-8a9b-33867e2f0fba}">
+          <x14:cfRule type="dataBar" id="{e813553f-d111-4b2f-9da4-d1bcc630326f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12690,14 +12717,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8bdadc4f-6d93-4c45-a48d-c2869299329c}">
+          <x14:cfRule type="dataBar" id="{8bdb300b-fe6d-4a9b-8084-0d876a36e294}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{673e544d-8894-4fc3-a197-f35ea33dc948}">
+          <x14:cfRule type="dataBar" id="{97d7c685-6583-4710-8165-3088da514fdb}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12708,7 +12735,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4d377490-d59b-4332-af3f-da73565f9d87}">
+          <x14:cfRule type="dataBar" id="{377bcbb3-c3a6-4daf-abb6-47bd8caba8ed}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12722,7 +12749,7 @@
           <xm:sqref>K62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9dcc16f2-2563-4136-b255-ead55e4f64df}">
+          <x14:cfRule type="dataBar" id="{cf1dd6e6-dcb3-4fa1-bf31-2fd5dda5783d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12731,7 +12758,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{20836c02-3095-4d39-b1e0-cbdfdf20850f}">
+          <x14:cfRule type="dataBar" id="{58aadbbe-a478-41bb-881d-90e7ef242127}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12740,7 +12767,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3a9c2586-9524-48e6-b4e3-e4793ca77f19}">
+          <x14:cfRule type="dataBar" id="{c5382078-42c8-4c88-a3d7-1262eadc26f8}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12751,7 +12778,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9194b549-efb1-4449-8d2a-c19c0fa1a603}">
+          <x14:cfRule type="dataBar" id="{8e93b0d0-323b-4ee6-b55c-4db0b5b3bf11}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12762,7 +12789,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ec5fd816-b684-416b-b8d0-bcd438e0e1cd}">
+          <x14:cfRule type="dataBar" id="{a7215c72-9388-45c7-a128-8abd51e34b81}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12773,14 +12800,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ae1c7fdc-3583-43fe-a643-40fcee8d880d}">
+          <x14:cfRule type="dataBar" id="{1b8330c5-f320-40ef-a39e-7b4d47cfc94a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b7d0c8ad-79d9-485d-96f2-c0fd547b5797}">
+          <x14:cfRule type="dataBar" id="{33470546-db21-4587-8f2f-50a1ee0471ce}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12791,7 +12818,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{dbffe5e6-9a99-4713-b84b-224185c9bea5}">
+          <x14:cfRule type="dataBar" id="{9b85416c-96fb-472d-a412-5c5f2e181852}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12805,7 +12832,7 @@
           <xm:sqref>AD62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c9836aef-56e4-4308-aa81-4975bc28c8aa}">
+          <x14:cfRule type="dataBar" id="{6ec4b172-19b0-4ed4-a5f1-d31a01c712ce}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12814,7 +12841,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4f03b995-96e3-4cad-86b1-a19d196d956f}">
+          <x14:cfRule type="dataBar" id="{c81fee0f-9cca-4b0e-8095-0c6c44946cda}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12823,7 +12850,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e66765d7-fd81-4ca0-b791-0b4e4f821316}">
+          <x14:cfRule type="dataBar" id="{d6b1edf8-7445-4954-a5f3-c9963cddc74f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12834,7 +12861,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e943295f-0c7a-4057-a716-fca669db8cbd}">
+          <x14:cfRule type="dataBar" id="{8da5670e-87d3-49a5-898a-e4bf5b0cfce7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12845,7 +12872,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b65dda20-f4b3-4ddd-b307-2c4e8621ba90}">
+          <x14:cfRule type="dataBar" id="{3754de99-96e9-4fce-ae40-035b7acfccd0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12856,14 +12883,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{87673fc6-aff5-4cd5-8937-8ebfa3b25ac8}">
+          <x14:cfRule type="dataBar" id="{2e542bea-9208-4ab1-981d-743d946f2639}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7702302b-a4f7-4023-b972-1e591c44c741}">
+          <x14:cfRule type="dataBar" id="{e85b31fd-afeb-416d-8eaf-7a9f23f21d79}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12874,7 +12901,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{db276c26-b88a-45f5-ae0f-f8699e86348f}">
+          <x14:cfRule type="dataBar" id="{173cc9b7-8046-4c69-afdb-5731e46922bb}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12888,7 +12915,7 @@
           <xm:sqref>K63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{332a349c-ba9c-44ae-b309-36f044f3b59c}">
+          <x14:cfRule type="dataBar" id="{522d9ecf-93c3-4a8d-b97c-a18e478013d7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12897,7 +12924,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0ff3786b-d8c8-466d-b37f-be6e728b64cb}">
+          <x14:cfRule type="dataBar" id="{aeb2684c-0698-412b-9433-2276031bcd97}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12906,7 +12933,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{85162bb4-1156-41df-a6a1-5a9b7fd44c51}">
+          <x14:cfRule type="dataBar" id="{1fadca5e-532e-47cd-9f78-553e49cd3a15}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12917,7 +12944,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e9dadf45-3852-4644-8175-f3d774c883b1}">
+          <x14:cfRule type="dataBar" id="{997ab22c-e880-4834-812e-e8c85e47d3ea}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12928,7 +12955,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f92c8313-2d16-483a-b750-c5f8bde29a51}">
+          <x14:cfRule type="dataBar" id="{7aec1cda-b23b-489f-bd42-9b4ba0d853c3}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12939,14 +12966,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1354f2bd-ed6f-48c6-9b32-1c63461643bf}">
+          <x14:cfRule type="dataBar" id="{6d6aa373-2269-46d3-8464-8c932609ce2c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{751d7f5b-ee3b-4eac-8d8d-f5629105a874}">
+          <x14:cfRule type="dataBar" id="{46f6c195-718d-4e14-9728-15ef54a6bf5c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12957,7 +12984,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{efea9994-7ebf-4f3b-afdf-4be1f3d3c3bb}">
+          <x14:cfRule type="dataBar" id="{d5209a5e-f2a3-4e3a-8a77-1299dda3f7b9}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12971,7 +12998,7 @@
           <xm:sqref>K64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9a7b94d4-0abe-4442-a079-80e6113e65aa}">
+          <x14:cfRule type="dataBar" id="{5c90f9be-5f18-46af-a49f-b7b41a3fe50a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12980,7 +13007,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d2723b4a-e9c7-4284-bf96-1b02f99c9f40}">
+          <x14:cfRule type="dataBar" id="{2d59d358-75d8-4e3d-b081-0233aee43e60}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12989,7 +13016,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d0a9292a-cf53-466d-bb98-84a6b079abac}">
+          <x14:cfRule type="dataBar" id="{42cad728-6bf9-4112-8d89-7bf6e89af1c8}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13000,7 +13027,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{656d8af9-a1a7-4187-b1ca-6f9fc987f9e3}">
+          <x14:cfRule type="dataBar" id="{6a4a0517-ebf3-4b28-af23-cc2a63f8ae51}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -13011,7 +13038,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d848efc1-5079-431c-b889-11c2b8128978}">
+          <x14:cfRule type="dataBar" id="{b073d464-325f-46f4-8aca-82c911c2c54a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -13022,14 +13049,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d6c1169e-903a-4a43-b569-024053012600}">
+          <x14:cfRule type="dataBar" id="{ac525358-0bbb-4b2b-94d7-f5b2f8600c14}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{09202eaf-4698-468c-b0f4-4f7934a661c6}">
+          <x14:cfRule type="dataBar" id="{a680082a-f179-41e4-8956-83005cabed5a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13040,7 +13067,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{cbb49d92-2bfe-4d5b-94d8-5e669449f4d4}">
+          <x14:cfRule type="dataBar" id="{99057d32-4a90-4216-ac02-7e171d381eba}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -13054,7 +13081,7 @@
           <xm:sqref>K65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{50ddb17c-8b0b-489d-b05a-8b6ed8eadc39}">
+          <x14:cfRule type="dataBar" id="{76e93a2b-b739-407a-822a-a21f39353549}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13064,7 +13091,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{793ff324-a580-4faf-b775-ce2a0a32f947}">
+          <x14:cfRule type="dataBar" id="{e3f9f10b-6c8b-4d75-bb07-c78530f64295}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13073,7 +13100,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{795875a8-2197-4ea1-a2db-68f8b88009a5}">
+          <x14:cfRule type="dataBar" id="{c352ec72-1372-4ecf-914c-876293976760}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13085,7 +13112,7 @@
           <xm:sqref>AB69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6b838c8f-79f2-48a1-994c-879afe768f49}">
+          <x14:cfRule type="dataBar" id="{b4c305d3-68e1-45e5-9afa-971f2e4f0dbc}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13095,7 +13122,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e6e7d347-d4d0-4fe8-864c-ca973fface99}">
+          <x14:cfRule type="dataBar" id="{8952e5d4-f15f-4bbe-9bcb-c544521cacb3}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13104,7 +13131,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{945f2514-266e-4714-ae41-19452013187f}">
+          <x14:cfRule type="dataBar" id="{10d58e92-8da8-4f3b-ab82-88e5f58cd001}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13116,7 +13143,7 @@
           <xm:sqref>AB103</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{49f721c3-43e3-42d6-88a4-6922da978388}">
+          <x14:cfRule type="dataBar" id="{7006c997-06b7-42f1-b915-e8f9e36068e6}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13125,7 +13152,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{775eeb1e-986d-4170-b7e9-1b7dbd146952}">
+          <x14:cfRule type="dataBar" id="{b7e4c6d3-2fbe-4198-9f18-06ec345a0676}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13137,7 +13164,7 @@
           <xm:sqref>AB117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f3da6d2c-0058-49f7-891b-958eb706ca40}">
+          <x14:cfRule type="dataBar" id="{11f93e7b-d009-4058-97ab-7ee0d80c5603}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13147,7 +13174,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e669da9d-968a-4cb7-a0f8-de24d8b7204b}">
+          <x14:cfRule type="dataBar" id="{16a7be33-addc-4f85-92ca-9ca9b6a83538}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13156,7 +13183,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{73d7254b-8e4f-4eaa-910a-63b1cb687810}">
+          <x14:cfRule type="dataBar" id="{15d49145-47bb-4181-b484-e1e5afba6595}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13168,7 +13195,7 @@
           <xm:sqref>AB127</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{35190ae1-ddc7-4c8d-8458-af532f2cde6f}">
+          <x14:cfRule type="dataBar" id="{ff95bea1-253f-41a2-aa3e-8d24806fe3e0}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13178,7 +13205,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{06b69c74-1b95-4997-b297-1f7cc576c3e6}">
+          <x14:cfRule type="dataBar" id="{db8b16ff-a075-4566-a062-f61ffb4cd307}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13187,7 +13214,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{436a0d13-61f0-4be0-b5aa-22fc6eb8e6c1}">
+          <x14:cfRule type="dataBar" id="{5bb9d894-234f-483c-b4c8-76e4da462943}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13199,7 +13226,7 @@
           <xm:sqref>K137</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{706a3fcb-1d85-40b2-898e-fd06f3e2bcf0}">
+          <x14:cfRule type="dataBar" id="{2c9fe9b6-a00e-4c10-b264-c9dee6fc60b6}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13209,7 +13236,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{231ca8ec-2eb4-4352-8e09-8a12a66c054f}">
+          <x14:cfRule type="dataBar" id="{1ce93724-31e5-4546-a045-f58ec92721ee}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13218,7 +13245,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4e6d922e-0e9d-4bae-a172-645d781604e1}">
+          <x14:cfRule type="dataBar" id="{cc9886ff-fcd6-4a53-8597-54d7f2112de1}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13230,7 +13257,7 @@
           <xm:sqref>K142</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c1437ea7-ec3a-48d8-873a-390dba8d7244}">
+          <x14:cfRule type="dataBar" id="{cf58e321-69c2-4c9d-9878-23da3030c0d6}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13240,7 +13267,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c62a4a68-77e7-47b2-bf65-44fdcb3a6ba9}">
+          <x14:cfRule type="dataBar" id="{41c26bca-2b74-4ba8-b670-f8441c67ee18}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13249,7 +13276,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{308aaaf8-de3d-491d-8809-f9390adcd150}">
+          <x14:cfRule type="dataBar" id="{8ac2b46b-415a-4c3c-a747-7c9df6bb0856}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13261,7 +13288,7 @@
           <xm:sqref>K147</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6e9531bb-ec62-46ba-9bfa-658ad9e5b0bb}">
+          <x14:cfRule type="dataBar" id="{20d1b445-c590-4204-94bd-072baa64b8ea}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13271,7 +13298,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4e0640a1-c697-4278-bd18-3640b683175e}">
+          <x14:cfRule type="dataBar" id="{313d2e12-39fe-4e0f-9dd0-91c7f0629e7c}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13280,7 +13307,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1dea3367-eacb-49a0-83c2-c9f651a841bf}">
+          <x14:cfRule type="dataBar" id="{8bc30156-b7bf-4f9d-999c-fd63f94ac7c1}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13292,7 +13319,7 @@
           <xm:sqref>K152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b557506d-2332-4c67-912e-e6bdae802d34}">
+          <x14:cfRule type="dataBar" id="{9c5da7b0-fd1e-420c-a06c-70fc4175f740}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13301,7 +13328,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{50feb3ad-3624-4d68-b2ee-b8b2446f41b8}">
+          <x14:cfRule type="dataBar" id="{a3ebd163-8418-45f5-9a43-c932ae836997}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13310,7 +13337,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a4bf74ed-cbfa-4b68-b0d5-d7975c80e69d}">
+          <x14:cfRule type="dataBar" id="{4e18ea4e-eab5-4d2b-a497-db14fc0efdd0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13321,7 +13348,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e73e25a9-b3d3-4109-adcd-318d50948973}">
+          <x14:cfRule type="dataBar" id="{e86cbe27-076f-4dd2-85ea-76837f71adc1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -13332,7 +13359,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{be8ac6ba-d692-4685-948d-8b2b4c46042b}">
+          <x14:cfRule type="dataBar" id="{e1c4336d-ff8b-41e7-b3eb-b727fecf193c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -13343,14 +13370,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2274d0da-65c8-4d66-930f-fc62421f30ed}">
+          <x14:cfRule type="dataBar" id="{adefc37a-f16a-4187-89b7-2299314341a0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{cd557e40-4a23-4200-852a-f07214b169e1}">
+          <x14:cfRule type="dataBar" id="{e757e693-15e0-4595-bf74-1109be2e8df7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13361,7 +13388,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{cbb84d30-4e47-4591-83dd-f60f47757922}">
+          <x14:cfRule type="dataBar" id="{b2a70351-b30b-41ee-8f5e-8d9f5dcccaf4}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -13375,7 +13402,7 @@
           <xm:sqref>K59:K60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{63a08510-99d1-455f-9ac2-933b5d813967}">
+          <x14:cfRule type="dataBar" id="{1b751ad6-9aae-471e-856b-6b9fcea12d3b}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13385,7 +13412,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3e43d9ad-f536-4b93-be9d-40b883fd13d0}">
+          <x14:cfRule type="dataBar" id="{7c1051e5-84af-4990-a0d9-677820f1a72a}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13397,7 +13424,7 @@
           <xm:sqref>Y69:Y88</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5f9bcfac-43de-4c82-983b-df2034727220}">
+          <x14:cfRule type="dataBar" id="{3ca49927-f367-4b32-bcfa-ad5fcecf97b0}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13410,7 +13437,7 @@
           <xm:sqref>Y79:Y88</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8ac50690-eb3e-436a-bb90-364a1ef77013}">
+          <x14:cfRule type="dataBar" id="{94f1da0b-76fa-4aaa-9ae2-89cc207e971b}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13423,7 +13450,7 @@
           <xm:sqref>AB117:AB126</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8d01d611-0c1a-4df7-99bf-9a4f7500aa65}">
+          <x14:cfRule type="dataBar" id="{e40576c4-ad51-4ab1-845c-5c5f9924b5bd}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13435,7 +13462,7 @@
           <xm:sqref>AD58:AE59</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{06bc5bb0-3a29-4b18-bc3a-64698600c1fe}">
+          <x14:cfRule type="dataBar" id="{e71d0b06-aca6-4d08-8db7-4dd7f409e5e1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13447,7 +13474,7 @@
           <xm:sqref>AD62:AE65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5902d624-66be-4b22-937f-1f9ac871a476}">
+          <x14:cfRule type="dataBar" id="{b3375f06-4fac-496a-afe6-954864bee6d8}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13457,7 +13484,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9141eac8-21c4-45ec-88df-70bc8ffe0dba}">
+          <x14:cfRule type="dataBar" id="{c67fac55-97ca-4f40-9b7e-a88664bda925}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13466,7 +13493,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9e9d23a1-8322-4080-aa88-9e8d6e6e8ddf}">
+          <x14:cfRule type="dataBar" id="{ffc1f4f4-4385-4e5d-abe4-2607d9d10086}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13478,7 +13505,7 @@
           <xm:sqref>F69 F74 F79 F84</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e9fcbe0b-2a6f-4291-bb5d-999e5c13b8c6}">
+          <x14:cfRule type="dataBar" id="{e6424149-2dbf-4588-978c-3e06a1c904c3}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13488,7 +13515,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{02498975-8e3b-4555-8b2a-27d512282a33}">
+          <x14:cfRule type="dataBar" id="{f80f76eb-67c8-489c-8ec1-130ed5158f5a}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13497,7 +13524,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f22738fc-b7a1-4b66-ac0a-2df173d21147}">
+          <x14:cfRule type="dataBar" id="{dc2858ff-8f8f-4d63-9f3f-5754d621243d}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13509,7 +13536,7 @@
           <xm:sqref>K69 K79 K89 K103</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9fc64bf2-4283-4e67-acbc-a6cd9b17cd1d}">
+          <x14:cfRule type="dataBar" id="{71c86f7b-727a-4c53-9192-e0f4010c8f60}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13519,7 +13546,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{91f69053-db54-4ce6-8ec5-ff34b0c6a9de}">
+          <x14:cfRule type="dataBar" id="{7af86aec-9371-4dec-b230-bdaf05af3f4e}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13528,7 +13555,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2ccd3aa7-106f-4180-9e53-76f7f699ec68}">
+          <x14:cfRule type="dataBar" id="{ebb74a8b-084f-4efa-8224-17d458b412a7}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13540,7 +13567,7 @@
           <xm:sqref>AB79 AB89</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{25470856-6f23-4593-8ec4-f86affb01ee0}">
+          <x14:cfRule type="dataBar" id="{d867b97b-7a06-4f0b-b6fc-883b61e7ab14}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13550,7 +13577,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0839ac72-afc6-4229-9e68-09b9356349d3}">
+          <x14:cfRule type="dataBar" id="{bce4b6be-cdab-48a9-a066-2c4253c80a15}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13559,7 +13586,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e37b83ed-9c68-45e0-b4eb-444c9bc888b3}">
+          <x14:cfRule type="dataBar" id="{cb30e02c-cc76-4ea7-98ff-dfe6013a897f}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13571,7 +13598,7 @@
           <xm:sqref>F89 F96 F103 F110</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{00cfb6ef-13e0-4395-b33b-0513f6ae6320}">
+          <x14:cfRule type="dataBar" id="{eb2fbaac-ad3a-4509-acad-a72f80cd0ad5}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13581,7 +13608,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{86936f7d-2a48-4bd5-9abe-940fc10c68a4}">
+          <x14:cfRule type="dataBar" id="{b91e7df2-5bed-47dc-832e-6ba01f1c322b}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13593,7 +13620,7 @@
           <xm:sqref>Y89 Y103</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8378c0a3-1189-4703-9bb8-28d85b14e686}">
+          <x14:cfRule type="dataBar" id="{0e72f36c-5955-4e72-b67d-c9a69fb5ee7b}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13603,7 +13630,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{dcbe0761-6206-4cad-b35b-c7883721cdc1}">
+          <x14:cfRule type="dataBar" id="{075b32f0-5559-4110-9e64-c8e4b78b53f9}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13612,7 +13639,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5ae50ee2-7ea8-4cd9-a668-736ace3fd960}">
+          <x14:cfRule type="dataBar" id="{24f2a45b-dd32-4f1f-a235-3be38e264c81}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13624,7 +13651,7 @@
           <xm:sqref>F117 F122 F127 F132 F137 F142 F147 F152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8a42bb25-8a8a-4eb1-b363-b34dae49c8e9}">
+          <x14:cfRule type="dataBar" id="{5a73aaa2-8814-467a-8278-425d1ba1d4af}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13634,7 +13661,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c909e2ce-ba4f-4b08-8248-09e330ec0f70}">
+          <x14:cfRule type="dataBar" id="{8d59a0a5-ffda-4090-877e-a55bb619f89a}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13643,7 +13670,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{81ecb00b-3b42-40b9-acb8-8ba0f5c396b7}">
+          <x14:cfRule type="dataBar" id="{f0cd1e36-12dd-4dd4-ae4b-63cf2f88022b}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13655,7 +13682,7 @@
           <xm:sqref>K117 K127</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dc34360e-ce4c-4a57-8132-20b34c230b4c}">
+          <x14:cfRule type="dataBar" id="{35198f7e-39ba-47d9-96fb-7482b4546696}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13665,7 +13692,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{74322a95-9f58-4b91-82df-432823bc7208}">
+          <x14:cfRule type="dataBar" id="{f61ca27d-8472-4383-ae26-282214c5eecc}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13696,63 +13723,63 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B2" s="4">
         <v>36.11</v>
@@ -13806,7 +13833,7 @@
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B3" s="6">
         <v>12689.5</v>
@@ -13863,7 +13890,7 @@
     </row>
     <row r="4" ht="28" customHeight="1" spans="1:18">
       <c r="A4" s="9" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B4" s="7">
         <f t="shared" ref="B4:O4" si="0">B3*0.86/1000</f>
@@ -13934,7 +13961,7 @@
     </row>
     <row r="6" spans="1:18">
       <c r="A6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>

--- a/外网端源码/其他楼交接班容量报表空模板.xlsx
+++ b/外网端源码/其他楼交接班容量报表空模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView windowHeight="22020"/>
   </bookViews>
   <sheets>
     <sheet name="本班组" sheetId="1" r:id="rId1"/>
@@ -3210,28 +3210,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AF156"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="18.1818181818182" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.1851851851852" style="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.9363636363636" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.9351851851852" style="1" customWidth="1"/>
     <col min="7" max="8" width="9" style="1" customWidth="1"/>
-    <col min="9" max="9" width="16.4090909090909" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.4074074074074" style="1" customWidth="1"/>
     <col min="10" max="11" width="9" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.9363636363636" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.9351851851852" style="1" customWidth="1"/>
     <col min="13" max="13" width="9" style="1" customWidth="1"/>
-    <col min="14" max="14" width="8.75454545454545" style="1" customWidth="1"/>
-    <col min="15" max="15" width="38.1818181818182" style="1" customWidth="1"/>
+    <col min="14" max="14" width="8.75" style="1" customWidth="1"/>
+    <col min="15" max="15" width="38.1851851851852" style="1" customWidth="1"/>
     <col min="16" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="12.5909090909091" style="1" customWidth="1"/>
-    <col min="20" max="20" width="16.5090909090909" style="1" customWidth="1"/>
+    <col min="19" max="19" width="12.5925925925926" style="1" customWidth="1"/>
+    <col min="20" max="20" width="16.5092592592593" style="1" customWidth="1"/>
     <col min="21" max="21" width="9" style="1" customWidth="1"/>
-    <col min="22" max="22" width="14.1545454545455" style="1" customWidth="1"/>
+    <col min="22" max="22" width="14.1574074074074" style="1" customWidth="1"/>
     <col min="23" max="24" width="9" style="1" customWidth="1"/>
-    <col min="25" max="25" width="10.2545454545455" style="1" customWidth="1"/>
+    <col min="25" max="25" width="10.25" style="1" customWidth="1"/>
     <col min="26" max="27" width="9" style="1" customWidth="1"/>
-    <col min="28" max="28" width="17.4181818181818" style="1" customWidth="1"/>
+    <col min="28" max="28" width="17.4166666666667" style="1" customWidth="1"/>
     <col min="31" max="31" width="11" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3798,15 +3798,15 @@
         <v>25</v>
       </c>
       <c r="T14" s="66"/>
-      <c r="U14" s="68">
-        <f>(U13-U12)/100</f>
-        <v>0</v>
+      <c r="U14" s="68" t="e">
+        <f>(U13-U12)/U12</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="V14" s="69"/>
       <c r="W14" s="70"/>
-      <c r="X14" s="68">
-        <f>(X13-X12)/100</f>
-        <v>0</v>
+      <c r="X14" s="68" t="e">
+        <f>(X13-X12)/X12</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="Y14" s="70"/>
       <c r="Z14" s="58"/>
@@ -6359,7 +6359,7 @@
       <c r="AD66" s="64"/>
       <c r="AE66" s="64"/>
     </row>
-    <row r="67" s="10" customFormat="1" ht="17.5" spans="1:32">
+    <row r="67" s="10" customFormat="1" ht="17.4" spans="1:32">
       <c r="A67" s="137"/>
       <c r="B67" s="138"/>
       <c r="C67" s="138"/>
@@ -11223,7 +11223,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c225ef76-32b1-4107-b13f-e45856487c0d}</x14:id>
+          <x14:id>{d4877931-dfce-4551-8728-152f925220c7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11235,7 +11235,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{46a6ce33-a119-4f0f-9e9c-0af763e560d1}</x14:id>
+          <x14:id>{8bf915ef-bc4b-4e1d-9874-f07f569f96c7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11247,7 +11247,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4dee5fbe-8b0c-4148-84e4-a0e4ca015b21}</x14:id>
+          <x14:id>{7e5527ef-53fa-479e-ac3a-7e0235785738}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11259,7 +11259,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f252c381-faa2-43c3-ac8c-769660b7722d}</x14:id>
+          <x14:id>{2eccd957-0aee-441b-b443-9d9f882c3446}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11271,7 +11271,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{af6bfa59-2503-4199-93c8-065423321a52}</x14:id>
+          <x14:id>{23613c43-f60b-4b73-aa1d-5a1142f19079}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11283,7 +11283,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7c6f9303-3371-416b-b614-5e07de55d60b}</x14:id>
+          <x14:id>{37f5f3dd-5396-4628-93eb-616d602135ec}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11295,7 +11295,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{478cac5c-4898-48d0-8066-d2c7b9d17061}</x14:id>
+          <x14:id>{ded25921-a00c-466f-821d-503dc560ad34}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11307,7 +11307,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{78c9caf2-fc88-4cac-aff4-f0f9dfbb20de}</x14:id>
+          <x14:id>{fa7dba31-f165-447b-8c64-365251170942}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11321,7 +11321,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d660ff2f-58af-4ad0-b6f8-09a9d94d4bd5}</x14:id>
+          <x14:id>{39317d3e-dec9-4e47-9f89-6593f4aa16ee}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11333,7 +11333,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e7f8e0c2-fc85-4c77-b601-a43fc186b5c5}</x14:id>
+          <x14:id>{99e2477e-1f72-493d-bb17-13f8f52dd026}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11345,7 +11345,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d0a6cac1-cfbe-4a3a-9a9e-f07b2c487ca0}</x14:id>
+          <x14:id>{f47a0988-9422-4884-a6de-29c552527747}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11357,7 +11357,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b512685c-c9c1-48b1-bfa7-ab7f3b53babb}</x14:id>
+          <x14:id>{3cf721bd-e272-4c16-a098-a56991919aa2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11369,7 +11369,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e813553f-d111-4b2f-9da4-d1bcc630326f}</x14:id>
+          <x14:id>{c5593dd7-cceb-455d-8809-0c587881d535}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11381,7 +11381,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8bdb300b-fe6d-4a9b-8084-0d876a36e294}</x14:id>
+          <x14:id>{5c27ac20-1dcb-4006-b3a7-968c4d6c32e7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11393,7 +11393,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{97d7c685-6583-4710-8165-3088da514fdb}</x14:id>
+          <x14:id>{dc0aa2e1-cca6-40b4-8c55-893176e671f0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11405,7 +11405,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{377bcbb3-c3a6-4daf-abb6-47bd8caba8ed}</x14:id>
+          <x14:id>{34af5fe1-4b57-4ead-a3a8-847ba191d16a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11419,7 +11419,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cf1dd6e6-dcb3-4fa1-bf31-2fd5dda5783d}</x14:id>
+          <x14:id>{25e1d582-a05a-4f9e-ad9a-807df3cfb8bc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11431,7 +11431,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{58aadbbe-a478-41bb-881d-90e7ef242127}</x14:id>
+          <x14:id>{00a27792-e4ea-4606-988f-e7c424702b88}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11443,7 +11443,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c5382078-42c8-4c88-a3d7-1262eadc26f8}</x14:id>
+          <x14:id>{3246ba4a-250d-4018-8cff-1fd73d55f392}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11455,7 +11455,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8e93b0d0-323b-4ee6-b55c-4db0b5b3bf11}</x14:id>
+          <x14:id>{850d7515-f0d1-4ee1-8c07-64ac37188a75}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11467,7 +11467,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a7215c72-9388-45c7-a128-8abd51e34b81}</x14:id>
+          <x14:id>{1b94d11c-4715-417f-94e3-08be37bc7de1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11479,7 +11479,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1b8330c5-f320-40ef-a39e-7b4d47cfc94a}</x14:id>
+          <x14:id>{babda1b1-026f-4d00-b4af-68dd112decce}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11491,7 +11491,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{33470546-db21-4587-8f2f-50a1ee0471ce}</x14:id>
+          <x14:id>{24add29d-5ce1-4141-bf99-878e7b7a9cb4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11503,7 +11503,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9b85416c-96fb-472d-a412-5c5f2e181852}</x14:id>
+          <x14:id>{84ff42ae-3bc8-427e-a99e-4ed61f2056de}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11517,7 +11517,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6ec4b172-19b0-4ed4-a5f1-d31a01c712ce}</x14:id>
+          <x14:id>{fff4a9d0-dbb5-458a-b9a4-416284621ba3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11529,7 +11529,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c81fee0f-9cca-4b0e-8095-0c6c44946cda}</x14:id>
+          <x14:id>{a718fdd4-e714-43b9-8298-2ef7eb1922eb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11541,7 +11541,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d6b1edf8-7445-4954-a5f3-c9963cddc74f}</x14:id>
+          <x14:id>{0073319a-3e61-4e4e-9182-00119553b575}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11553,7 +11553,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8da5670e-87d3-49a5-898a-e4bf5b0cfce7}</x14:id>
+          <x14:id>{4511bcac-36b5-4698-a420-8f402682f901}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11565,7 +11565,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3754de99-96e9-4fce-ae40-035b7acfccd0}</x14:id>
+          <x14:id>{2d3ce388-9e99-4ba1-977b-334c304c197a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11577,7 +11577,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2e542bea-9208-4ab1-981d-743d946f2639}</x14:id>
+          <x14:id>{0a6197b4-2eb8-46fe-8eff-3da4ac1f6ccc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11589,7 +11589,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e85b31fd-afeb-416d-8eaf-7a9f23f21d79}</x14:id>
+          <x14:id>{143dc1c0-192f-4b62-9354-e99d14ee15ea}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11601,7 +11601,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{173cc9b7-8046-4c69-afdb-5731e46922bb}</x14:id>
+          <x14:id>{925ff35d-464a-4152-bc1e-4245330e5997}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11615,7 +11615,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{522d9ecf-93c3-4a8d-b97c-a18e478013d7}</x14:id>
+          <x14:id>{e55ecc99-61ab-4ad3-8a2a-68bcdea30102}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11627,7 +11627,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{aeb2684c-0698-412b-9433-2276031bcd97}</x14:id>
+          <x14:id>{82b6a770-9d3b-425f-be5f-d884a44c240c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11639,7 +11639,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1fadca5e-532e-47cd-9f78-553e49cd3a15}</x14:id>
+          <x14:id>{e5331c35-36e8-4a81-9494-687831b019fa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11651,7 +11651,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{997ab22c-e880-4834-812e-e8c85e47d3ea}</x14:id>
+          <x14:id>{280caff2-74f5-4b0d-a56a-0e45fb5c10d7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11663,7 +11663,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7aec1cda-b23b-489f-bd42-9b4ba0d853c3}</x14:id>
+          <x14:id>{2493c57f-4b7e-437e-b83e-14a67b08a919}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11675,7 +11675,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6d6aa373-2269-46d3-8464-8c932609ce2c}</x14:id>
+          <x14:id>{b7372b0e-0fa7-4475-a82b-730aaf412d63}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11687,7 +11687,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{46f6c195-718d-4e14-9728-15ef54a6bf5c}</x14:id>
+          <x14:id>{bb6d9611-7406-4b71-ac03-94695ed0d5f0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11699,7 +11699,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d5209a5e-f2a3-4e3a-8a77-1299dda3f7b9}</x14:id>
+          <x14:id>{daf20764-0e40-4d50-8689-2f1333de3b80}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11713,7 +11713,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5c90f9be-5f18-46af-a49f-b7b41a3fe50a}</x14:id>
+          <x14:id>{43a4f6d6-f04f-42e9-b90a-6eafa34a8656}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11725,7 +11725,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2d59d358-75d8-4e3d-b081-0233aee43e60}</x14:id>
+          <x14:id>{f5939dd2-7152-4175-a5a6-0ea51b3bcbc4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11737,7 +11737,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{42cad728-6bf9-4112-8d89-7bf6e89af1c8}</x14:id>
+          <x14:id>{1e45f251-2c8f-441f-81e1-0605c88c8312}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11749,7 +11749,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6a4a0517-ebf3-4b28-af23-cc2a63f8ae51}</x14:id>
+          <x14:id>{910c0f33-467c-4749-b8bd-cb280a8ac582}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11761,7 +11761,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b073d464-325f-46f4-8aca-82c911c2c54a}</x14:id>
+          <x14:id>{57d7a39c-e066-437e-b53d-d1ac48237712}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11773,7 +11773,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ac525358-0bbb-4b2b-94d7-f5b2f8600c14}</x14:id>
+          <x14:id>{e73bf181-0d20-487b-9eb6-22df4e5292d4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11785,7 +11785,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a680082a-f179-41e4-8956-83005cabed5a}</x14:id>
+          <x14:id>{c11e52f1-38f2-4af0-a076-d2b17600ff6a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11797,7 +11797,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{99057d32-4a90-4216-ac02-7e171d381eba}</x14:id>
+          <x14:id>{7948c94e-f69e-4e64-b7d0-0f563212f70c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11811,7 +11811,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{76e93a2b-b739-407a-822a-a21f39353549}</x14:id>
+          <x14:id>{0e94f7af-e845-4408-b884-01babb5df860}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11823,7 +11823,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e3f9f10b-6c8b-4d75-bb07-c78530f64295}</x14:id>
+          <x14:id>{94bcd1db-88bf-42b8-837c-f8c1b7fa169e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11835,7 +11835,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c352ec72-1372-4ecf-914c-876293976760}</x14:id>
+          <x14:id>{1db48018-b53c-4ccf-8df7-c29d745d9966}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11849,7 +11849,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b4c305d3-68e1-45e5-9afa-971f2e4f0dbc}</x14:id>
+          <x14:id>{b8fe6fee-caee-42c1-9a92-6ef57adf7699}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11861,7 +11861,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8952e5d4-f15f-4bbe-9bcb-c544521cacb3}</x14:id>
+          <x14:id>{2268fb69-e943-4688-8771-90b2d4300452}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11873,7 +11873,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{10d58e92-8da8-4f3b-ab82-88e5f58cd001}</x14:id>
+          <x14:id>{64afb03a-928d-43c6-8767-d87de82635e2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11887,7 +11887,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7006c997-06b7-42f1-b915-e8f9e36068e6}</x14:id>
+          <x14:id>{5f5107c4-286e-45fe-b104-cce2792a1b96}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11899,7 +11899,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b7e4c6d3-2fbe-4198-9f18-06ec345a0676}</x14:id>
+          <x14:id>{45578e32-148b-44b6-9c9d-8bee23b9e3db}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11913,7 +11913,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{11f93e7b-d009-4058-97ab-7ee0d80c5603}</x14:id>
+          <x14:id>{9ded9fd1-a30e-4067-81a0-2527a36b725d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11925,7 +11925,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{16a7be33-addc-4f85-92ca-9ca9b6a83538}</x14:id>
+          <x14:id>{a63f0f08-1667-4be7-b016-db2e54248f85}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11937,7 +11937,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{15d49145-47bb-4181-b484-e1e5afba6595}</x14:id>
+          <x14:id>{3094a5f2-195d-44c2-ab22-ed724d28fd48}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11951,7 +11951,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ff95bea1-253f-41a2-aa3e-8d24806fe3e0}</x14:id>
+          <x14:id>{50b0b2cb-6b69-43f5-97f6-487813a6a6ff}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11963,7 +11963,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{db8b16ff-a075-4566-a062-f61ffb4cd307}</x14:id>
+          <x14:id>{c3f69d74-f89b-40a3-808c-b422169ec85f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11975,7 +11975,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5bb9d894-234f-483c-b4c8-76e4da462943}</x14:id>
+          <x14:id>{048a0a12-faa7-442c-ab01-cffc7fb00953}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11989,7 +11989,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2c9fe9b6-a00e-4c10-b264-c9dee6fc60b6}</x14:id>
+          <x14:id>{bd4080ea-4f39-494e-ae92-b72eb777baa5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12001,7 +12001,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1ce93724-31e5-4546-a045-f58ec92721ee}</x14:id>
+          <x14:id>{fff168ef-270e-4ebb-ad04-c451d2a788a0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12013,7 +12013,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cc9886ff-fcd6-4a53-8597-54d7f2112de1}</x14:id>
+          <x14:id>{132548c4-a2ad-4fee-96ad-4e678db4a997}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12027,7 +12027,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cf58e321-69c2-4c9d-9878-23da3030c0d6}</x14:id>
+          <x14:id>{8a83dc2b-b030-4565-8c7c-2082312bbffa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12039,7 +12039,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{41c26bca-2b74-4ba8-b670-f8441c67ee18}</x14:id>
+          <x14:id>{618224f1-8993-4438-b9a0-b730641e9be6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12051,7 +12051,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8ac2b46b-415a-4c3c-a747-7c9df6bb0856}</x14:id>
+          <x14:id>{643645c8-0c55-4079-a596-4d26a30e0a72}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12065,7 +12065,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{20d1b445-c590-4204-94bd-072baa64b8ea}</x14:id>
+          <x14:id>{808714b1-fcbb-4f12-98b9-8c1f05198e57}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12077,7 +12077,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{313d2e12-39fe-4e0f-9dd0-91c7f0629e7c}</x14:id>
+          <x14:id>{057ff636-faf5-47bd-bbf9-fe53e5c6c4fe}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12089,7 +12089,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8bc30156-b7bf-4f9d-999c-fd63f94ac7c1}</x14:id>
+          <x14:id>{26c3cabb-1848-499c-b301-03e2f385070c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12103,7 +12103,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9c5da7b0-fd1e-420c-a06c-70fc4175f740}</x14:id>
+          <x14:id>{fee870b3-6248-4625-9360-bc028983d9fa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12115,7 +12115,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a3ebd163-8418-45f5-9a43-c932ae836997}</x14:id>
+          <x14:id>{7b61ebec-519c-40e1-b40b-771cd5f5d0ed}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12127,7 +12127,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4e18ea4e-eab5-4d2b-a497-db14fc0efdd0}</x14:id>
+          <x14:id>{6c511f62-3be6-41f9-a287-435254c360b9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12139,7 +12139,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e86cbe27-076f-4dd2-85ea-76837f71adc1}</x14:id>
+          <x14:id>{03fe8fe4-57a7-46dd-b9ee-adad359b0361}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12151,7 +12151,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e1c4336d-ff8b-41e7-b3eb-b727fecf193c}</x14:id>
+          <x14:id>{9cc2fe4a-d406-4b26-83b2-3b6b96746d31}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12163,7 +12163,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{adefc37a-f16a-4187-89b7-2299314341a0}</x14:id>
+          <x14:id>{66ba7f92-1f43-444c-a584-e716105a9b13}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12175,7 +12175,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e757e693-15e0-4595-bf74-1109be2e8df7}</x14:id>
+          <x14:id>{2446b1fa-793d-4932-8b0f-d4caac932e48}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12187,7 +12187,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b2a70351-b30b-41ee-8f5e-8d9f5dcccaf4}</x14:id>
+          <x14:id>{b7c8e005-0673-46e9-b740-25fe2a239856}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12201,7 +12201,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1b751ad6-9aae-471e-856b-6b9fcea12d3b}</x14:id>
+          <x14:id>{00fc752f-a51a-4f9f-880c-66e2b71cb475}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12213,7 +12213,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7c1051e5-84af-4990-a0d9-677820f1a72a}</x14:id>
+          <x14:id>{04d800a5-dbb6-4629-b328-024f72cd9d31}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12227,7 +12227,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3ca49927-f367-4b32-bcfa-ad5fcecf97b0}</x14:id>
+          <x14:id>{0a1d25be-456f-4916-bec3-3c3555183f04}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12241,7 +12241,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{94f1da0b-76fa-4aaa-9ae2-89cc207e971b}</x14:id>
+          <x14:id>{18c1dd8d-68df-4b40-8511-4673843676a9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12255,7 +12255,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e40576c4-ad51-4ab1-845c-5c5f9924b5bd}</x14:id>
+          <x14:id>{33efd8c8-9d94-403a-81ca-0b56685fda94}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12269,7 +12269,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e71d0b06-aca6-4d08-8db7-4dd7f409e5e1}</x14:id>
+          <x14:id>{b1ab472e-1668-41af-9582-5161d848a33a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12283,7 +12283,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b3375f06-4fac-496a-afe6-954864bee6d8}</x14:id>
+          <x14:id>{65888510-a5e8-45a9-8203-27351fb42e22}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12295,7 +12295,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c67fac55-97ca-4f40-9b7e-a88664bda925}</x14:id>
+          <x14:id>{9f7169d8-5531-45b0-ba4f-41d8c2f08590}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12307,7 +12307,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ffc1f4f4-4385-4e5d-abe4-2607d9d10086}</x14:id>
+          <x14:id>{a65b4136-0a2d-49dc-a7e1-def6830a230d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12321,7 +12321,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e6424149-2dbf-4588-978c-3e06a1c904c3}</x14:id>
+          <x14:id>{0b74384e-ab59-4c49-bd63-2efdccd9a8cf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12333,7 +12333,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f80f76eb-67c8-489c-8ec1-130ed5158f5a}</x14:id>
+          <x14:id>{47627bef-38ab-4e19-89e6-69f5334b0f86}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12345,7 +12345,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dc2858ff-8f8f-4d63-9f3f-5754d621243d}</x14:id>
+          <x14:id>{b270289d-37fd-4335-9030-29f1fd34f883}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12359,7 +12359,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{71c86f7b-727a-4c53-9192-e0f4010c8f60}</x14:id>
+          <x14:id>{56a8f6f8-fb05-457a-b81a-3dd793549c15}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12371,7 +12371,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7af86aec-9371-4dec-b230-bdaf05af3f4e}</x14:id>
+          <x14:id>{73a0a36a-a630-4115-9410-c4814f3104be}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12383,7 +12383,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ebb74a8b-084f-4efa-8224-17d458b412a7}</x14:id>
+          <x14:id>{ed331490-d0ab-4bad-b17b-f5db4ae144e5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12397,7 +12397,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d867b97b-7a06-4f0b-b6fc-883b61e7ab14}</x14:id>
+          <x14:id>{53e4be7a-4fad-45c0-af5d-86629edc2522}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12409,7 +12409,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bce4b6be-cdab-48a9-a066-2c4253c80a15}</x14:id>
+          <x14:id>{a067a6ca-07f7-4816-9ee5-1e00f45c5929}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12421,7 +12421,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cb30e02c-cc76-4ea7-98ff-dfe6013a897f}</x14:id>
+          <x14:id>{fbd5c5df-458b-46e4-8ad8-6e5c52a2f4a5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12435,7 +12435,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{eb2fbaac-ad3a-4509-acad-a72f80cd0ad5}</x14:id>
+          <x14:id>{dd8e0560-423a-4c31-8656-c6a8dd6fde50}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12447,7 +12447,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b91e7df2-5bed-47dc-832e-6ba01f1c322b}</x14:id>
+          <x14:id>{0ae66ab8-e9bb-404f-bcee-885569b0188b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12461,7 +12461,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0e72f36c-5955-4e72-b67d-c9a69fb5ee7b}</x14:id>
+          <x14:id>{ce78fbe4-ef71-4cb6-965b-28e84b9a2e60}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12473,7 +12473,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{075b32f0-5559-4110-9e64-c8e4b78b53f9}</x14:id>
+          <x14:id>{33710180-8d2f-488f-946e-38fe92e76cc4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12485,7 +12485,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{24f2a45b-dd32-4f1f-a235-3be38e264c81}</x14:id>
+          <x14:id>{8a05a893-39d2-4d03-aa9f-d12d96ee0abe}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12499,7 +12499,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5a73aaa2-8814-467a-8278-425d1ba1d4af}</x14:id>
+          <x14:id>{8ec76ca4-f9d6-4e12-9c49-d7d662d51c7f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12511,7 +12511,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8d59a0a5-ffda-4090-877e-a55bb619f89a}</x14:id>
+          <x14:id>{dcaafd60-e93b-4d3b-a10b-1da24f947bb5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12523,7 +12523,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f0cd1e36-12dd-4dd4-ae4b-63cf2f88022b}</x14:id>
+          <x14:id>{a760a73a-4818-494f-9502-468b45f1e8dc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12537,7 +12537,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{35198f7e-39ba-47d9-96fb-7482b4546696}</x14:id>
+          <x14:id>{cbc48366-b730-49f8-b9f2-6a11065ee809}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12549,7 +12549,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f61ca27d-8472-4383-ae26-282214c5eecc}</x14:id>
+          <x14:id>{5aedb19b-6e0d-4c77-9de3-ca10b9ca0370}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12583,7 +12583,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c225ef76-32b1-4107-b13f-e45856487c0d}">
+          <x14:cfRule type="dataBar" id="{d4877931-dfce-4551-8728-152f925220c7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12592,7 +12592,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{46a6ce33-a119-4f0f-9e9c-0af763e560d1}">
+          <x14:cfRule type="dataBar" id="{8bf915ef-bc4b-4e1d-9874-f07f569f96c7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12601,7 +12601,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4dee5fbe-8b0c-4148-84e4-a0e4ca015b21}">
+          <x14:cfRule type="dataBar" id="{7e5527ef-53fa-479e-ac3a-7e0235785738}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12612,7 +12612,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f252c381-faa2-43c3-ac8c-769660b7722d}">
+          <x14:cfRule type="dataBar" id="{2eccd957-0aee-441b-b443-9d9f882c3446}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12623,7 +12623,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{af6bfa59-2503-4199-93c8-065423321a52}">
+          <x14:cfRule type="dataBar" id="{23613c43-f60b-4b73-aa1d-5a1142f19079}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12634,14 +12634,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7c6f9303-3371-416b-b614-5e07de55d60b}">
+          <x14:cfRule type="dataBar" id="{37f5f3dd-5396-4628-93eb-616d602135ec}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{478cac5c-4898-48d0-8066-d2c7b9d17061}">
+          <x14:cfRule type="dataBar" id="{ded25921-a00c-466f-821d-503dc560ad34}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12652,7 +12652,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{78c9caf2-fc88-4cac-aff4-f0f9dfbb20de}">
+          <x14:cfRule type="dataBar" id="{fa7dba31-f165-447b-8c64-365251170942}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12666,7 +12666,7 @@
           <xm:sqref>AD58</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d660ff2f-58af-4ad0-b6f8-09a9d94d4bd5}">
+          <x14:cfRule type="dataBar" id="{39317d3e-dec9-4e47-9f89-6593f4aa16ee}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12675,7 +12675,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e7f8e0c2-fc85-4c77-b601-a43fc186b5c5}">
+          <x14:cfRule type="dataBar" id="{99e2477e-1f72-493d-bb17-13f8f52dd026}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12684,7 +12684,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d0a6cac1-cfbe-4a3a-9a9e-f07b2c487ca0}">
+          <x14:cfRule type="dataBar" id="{f47a0988-9422-4884-a6de-29c552527747}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12695,7 +12695,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b512685c-c9c1-48b1-bfa7-ab7f3b53babb}">
+          <x14:cfRule type="dataBar" id="{3cf721bd-e272-4c16-a098-a56991919aa2}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12706,7 +12706,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e813553f-d111-4b2f-9da4-d1bcc630326f}">
+          <x14:cfRule type="dataBar" id="{c5593dd7-cceb-455d-8809-0c587881d535}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12717,14 +12717,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8bdb300b-fe6d-4a9b-8084-0d876a36e294}">
+          <x14:cfRule type="dataBar" id="{5c27ac20-1dcb-4006-b3a7-968c4d6c32e7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{97d7c685-6583-4710-8165-3088da514fdb}">
+          <x14:cfRule type="dataBar" id="{dc0aa2e1-cca6-40b4-8c55-893176e671f0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12735,7 +12735,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{377bcbb3-c3a6-4daf-abb6-47bd8caba8ed}">
+          <x14:cfRule type="dataBar" id="{34af5fe1-4b57-4ead-a3a8-847ba191d16a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12749,7 +12749,7 @@
           <xm:sqref>K62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cf1dd6e6-dcb3-4fa1-bf31-2fd5dda5783d}">
+          <x14:cfRule type="dataBar" id="{25e1d582-a05a-4f9e-ad9a-807df3cfb8bc}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12758,7 +12758,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{58aadbbe-a478-41bb-881d-90e7ef242127}">
+          <x14:cfRule type="dataBar" id="{00a27792-e4ea-4606-988f-e7c424702b88}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12767,7 +12767,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c5382078-42c8-4c88-a3d7-1262eadc26f8}">
+          <x14:cfRule type="dataBar" id="{3246ba4a-250d-4018-8cff-1fd73d55f392}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12778,7 +12778,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8e93b0d0-323b-4ee6-b55c-4db0b5b3bf11}">
+          <x14:cfRule type="dataBar" id="{850d7515-f0d1-4ee1-8c07-64ac37188a75}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12789,7 +12789,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a7215c72-9388-45c7-a128-8abd51e34b81}">
+          <x14:cfRule type="dataBar" id="{1b94d11c-4715-417f-94e3-08be37bc7de1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12800,14 +12800,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1b8330c5-f320-40ef-a39e-7b4d47cfc94a}">
+          <x14:cfRule type="dataBar" id="{babda1b1-026f-4d00-b4af-68dd112decce}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{33470546-db21-4587-8f2f-50a1ee0471ce}">
+          <x14:cfRule type="dataBar" id="{24add29d-5ce1-4141-bf99-878e7b7a9cb4}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12818,7 +12818,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9b85416c-96fb-472d-a412-5c5f2e181852}">
+          <x14:cfRule type="dataBar" id="{84ff42ae-3bc8-427e-a99e-4ed61f2056de}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12832,7 +12832,7 @@
           <xm:sqref>AD62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6ec4b172-19b0-4ed4-a5f1-d31a01c712ce}">
+          <x14:cfRule type="dataBar" id="{fff4a9d0-dbb5-458a-b9a4-416284621ba3}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12841,7 +12841,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c81fee0f-9cca-4b0e-8095-0c6c44946cda}">
+          <x14:cfRule type="dataBar" id="{a718fdd4-e714-43b9-8298-2ef7eb1922eb}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12850,7 +12850,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d6b1edf8-7445-4954-a5f3-c9963cddc74f}">
+          <x14:cfRule type="dataBar" id="{0073319a-3e61-4e4e-9182-00119553b575}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12861,7 +12861,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8da5670e-87d3-49a5-898a-e4bf5b0cfce7}">
+          <x14:cfRule type="dataBar" id="{4511bcac-36b5-4698-a420-8f402682f901}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12872,7 +12872,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3754de99-96e9-4fce-ae40-035b7acfccd0}">
+          <x14:cfRule type="dataBar" id="{2d3ce388-9e99-4ba1-977b-334c304c197a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12883,14 +12883,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2e542bea-9208-4ab1-981d-743d946f2639}">
+          <x14:cfRule type="dataBar" id="{0a6197b4-2eb8-46fe-8eff-3da4ac1f6ccc}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e85b31fd-afeb-416d-8eaf-7a9f23f21d79}">
+          <x14:cfRule type="dataBar" id="{143dc1c0-192f-4b62-9354-e99d14ee15ea}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12901,7 +12901,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{173cc9b7-8046-4c69-afdb-5731e46922bb}">
+          <x14:cfRule type="dataBar" id="{925ff35d-464a-4152-bc1e-4245330e5997}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12915,7 +12915,7 @@
           <xm:sqref>K63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{522d9ecf-93c3-4a8d-b97c-a18e478013d7}">
+          <x14:cfRule type="dataBar" id="{e55ecc99-61ab-4ad3-8a2a-68bcdea30102}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12924,7 +12924,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{aeb2684c-0698-412b-9433-2276031bcd97}">
+          <x14:cfRule type="dataBar" id="{82b6a770-9d3b-425f-be5f-d884a44c240c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12933,7 +12933,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1fadca5e-532e-47cd-9f78-553e49cd3a15}">
+          <x14:cfRule type="dataBar" id="{e5331c35-36e8-4a81-9494-687831b019fa}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12944,7 +12944,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{997ab22c-e880-4834-812e-e8c85e47d3ea}">
+          <x14:cfRule type="dataBar" id="{280caff2-74f5-4b0d-a56a-0e45fb5c10d7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12955,7 +12955,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7aec1cda-b23b-489f-bd42-9b4ba0d853c3}">
+          <x14:cfRule type="dataBar" id="{2493c57f-4b7e-437e-b83e-14a67b08a919}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12966,14 +12966,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6d6aa373-2269-46d3-8464-8c932609ce2c}">
+          <x14:cfRule type="dataBar" id="{b7372b0e-0fa7-4475-a82b-730aaf412d63}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{46f6c195-718d-4e14-9728-15ef54a6bf5c}">
+          <x14:cfRule type="dataBar" id="{bb6d9611-7406-4b71-ac03-94695ed0d5f0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12984,7 +12984,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d5209a5e-f2a3-4e3a-8a77-1299dda3f7b9}">
+          <x14:cfRule type="dataBar" id="{daf20764-0e40-4d50-8689-2f1333de3b80}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12998,7 +12998,7 @@
           <xm:sqref>K64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5c90f9be-5f18-46af-a49f-b7b41a3fe50a}">
+          <x14:cfRule type="dataBar" id="{43a4f6d6-f04f-42e9-b90a-6eafa34a8656}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13007,7 +13007,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2d59d358-75d8-4e3d-b081-0233aee43e60}">
+          <x14:cfRule type="dataBar" id="{f5939dd2-7152-4175-a5a6-0ea51b3bcbc4}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13016,7 +13016,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{42cad728-6bf9-4112-8d89-7bf6e89af1c8}">
+          <x14:cfRule type="dataBar" id="{1e45f251-2c8f-441f-81e1-0605c88c8312}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13027,7 +13027,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6a4a0517-ebf3-4b28-af23-cc2a63f8ae51}">
+          <x14:cfRule type="dataBar" id="{910c0f33-467c-4749-b8bd-cb280a8ac582}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -13038,7 +13038,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b073d464-325f-46f4-8aca-82c911c2c54a}">
+          <x14:cfRule type="dataBar" id="{57d7a39c-e066-437e-b53d-d1ac48237712}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -13049,14 +13049,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ac525358-0bbb-4b2b-94d7-f5b2f8600c14}">
+          <x14:cfRule type="dataBar" id="{e73bf181-0d20-487b-9eb6-22df4e5292d4}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a680082a-f179-41e4-8956-83005cabed5a}">
+          <x14:cfRule type="dataBar" id="{c11e52f1-38f2-4af0-a076-d2b17600ff6a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13067,7 +13067,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{99057d32-4a90-4216-ac02-7e171d381eba}">
+          <x14:cfRule type="dataBar" id="{7948c94e-f69e-4e64-b7d0-0f563212f70c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -13081,7 +13081,7 @@
           <xm:sqref>K65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{76e93a2b-b739-407a-822a-a21f39353549}">
+          <x14:cfRule type="dataBar" id="{0e94f7af-e845-4408-b884-01babb5df860}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13091,7 +13091,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e3f9f10b-6c8b-4d75-bb07-c78530f64295}">
+          <x14:cfRule type="dataBar" id="{94bcd1db-88bf-42b8-837c-f8c1b7fa169e}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13100,7 +13100,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c352ec72-1372-4ecf-914c-876293976760}">
+          <x14:cfRule type="dataBar" id="{1db48018-b53c-4ccf-8df7-c29d745d9966}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13112,7 +13112,7 @@
           <xm:sqref>AB69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b4c305d3-68e1-45e5-9afa-971f2e4f0dbc}">
+          <x14:cfRule type="dataBar" id="{b8fe6fee-caee-42c1-9a92-6ef57adf7699}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13122,7 +13122,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8952e5d4-f15f-4bbe-9bcb-c544521cacb3}">
+          <x14:cfRule type="dataBar" id="{2268fb69-e943-4688-8771-90b2d4300452}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13131,7 +13131,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{10d58e92-8da8-4f3b-ab82-88e5f58cd001}">
+          <x14:cfRule type="dataBar" id="{64afb03a-928d-43c6-8767-d87de82635e2}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13143,7 +13143,7 @@
           <xm:sqref>AB103</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7006c997-06b7-42f1-b915-e8f9e36068e6}">
+          <x14:cfRule type="dataBar" id="{5f5107c4-286e-45fe-b104-cce2792a1b96}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13152,7 +13152,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b7e4c6d3-2fbe-4198-9f18-06ec345a0676}">
+          <x14:cfRule type="dataBar" id="{45578e32-148b-44b6-9c9d-8bee23b9e3db}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13164,7 +13164,7 @@
           <xm:sqref>AB117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{11f93e7b-d009-4058-97ab-7ee0d80c5603}">
+          <x14:cfRule type="dataBar" id="{9ded9fd1-a30e-4067-81a0-2527a36b725d}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13174,7 +13174,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{16a7be33-addc-4f85-92ca-9ca9b6a83538}">
+          <x14:cfRule type="dataBar" id="{a63f0f08-1667-4be7-b016-db2e54248f85}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13183,7 +13183,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{15d49145-47bb-4181-b484-e1e5afba6595}">
+          <x14:cfRule type="dataBar" id="{3094a5f2-195d-44c2-ab22-ed724d28fd48}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13195,7 +13195,7 @@
           <xm:sqref>AB127</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ff95bea1-253f-41a2-aa3e-8d24806fe3e0}">
+          <x14:cfRule type="dataBar" id="{50b0b2cb-6b69-43f5-97f6-487813a6a6ff}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13205,7 +13205,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{db8b16ff-a075-4566-a062-f61ffb4cd307}">
+          <x14:cfRule type="dataBar" id="{c3f69d74-f89b-40a3-808c-b422169ec85f}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13214,7 +13214,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5bb9d894-234f-483c-b4c8-76e4da462943}">
+          <x14:cfRule type="dataBar" id="{048a0a12-faa7-442c-ab01-cffc7fb00953}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13226,7 +13226,7 @@
           <xm:sqref>K137</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2c9fe9b6-a00e-4c10-b264-c9dee6fc60b6}">
+          <x14:cfRule type="dataBar" id="{bd4080ea-4f39-494e-ae92-b72eb777baa5}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13236,7 +13236,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1ce93724-31e5-4546-a045-f58ec92721ee}">
+          <x14:cfRule type="dataBar" id="{fff168ef-270e-4ebb-ad04-c451d2a788a0}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13245,7 +13245,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{cc9886ff-fcd6-4a53-8597-54d7f2112de1}">
+          <x14:cfRule type="dataBar" id="{132548c4-a2ad-4fee-96ad-4e678db4a997}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13257,7 +13257,7 @@
           <xm:sqref>K142</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cf58e321-69c2-4c9d-9878-23da3030c0d6}">
+          <x14:cfRule type="dataBar" id="{8a83dc2b-b030-4565-8c7c-2082312bbffa}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13267,7 +13267,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{41c26bca-2b74-4ba8-b670-f8441c67ee18}">
+          <x14:cfRule type="dataBar" id="{618224f1-8993-4438-b9a0-b730641e9be6}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13276,7 +13276,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8ac2b46b-415a-4c3c-a747-7c9df6bb0856}">
+          <x14:cfRule type="dataBar" id="{643645c8-0c55-4079-a596-4d26a30e0a72}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13288,7 +13288,7 @@
           <xm:sqref>K147</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{20d1b445-c590-4204-94bd-072baa64b8ea}">
+          <x14:cfRule type="dataBar" id="{808714b1-fcbb-4f12-98b9-8c1f05198e57}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13298,7 +13298,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{313d2e12-39fe-4e0f-9dd0-91c7f0629e7c}">
+          <x14:cfRule type="dataBar" id="{057ff636-faf5-47bd-bbf9-fe53e5c6c4fe}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13307,7 +13307,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8bc30156-b7bf-4f9d-999c-fd63f94ac7c1}">
+          <x14:cfRule type="dataBar" id="{26c3cabb-1848-499c-b301-03e2f385070c}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13319,7 +13319,7 @@
           <xm:sqref>K152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9c5da7b0-fd1e-420c-a06c-70fc4175f740}">
+          <x14:cfRule type="dataBar" id="{fee870b3-6248-4625-9360-bc028983d9fa}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13328,7 +13328,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a3ebd163-8418-45f5-9a43-c932ae836997}">
+          <x14:cfRule type="dataBar" id="{7b61ebec-519c-40e1-b40b-771cd5f5d0ed}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13337,7 +13337,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4e18ea4e-eab5-4d2b-a497-db14fc0efdd0}">
+          <x14:cfRule type="dataBar" id="{6c511f62-3be6-41f9-a287-435254c360b9}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13348,7 +13348,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e86cbe27-076f-4dd2-85ea-76837f71adc1}">
+          <x14:cfRule type="dataBar" id="{03fe8fe4-57a7-46dd-b9ee-adad359b0361}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -13359,7 +13359,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e1c4336d-ff8b-41e7-b3eb-b727fecf193c}">
+          <x14:cfRule type="dataBar" id="{9cc2fe4a-d406-4b26-83b2-3b6b96746d31}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -13370,14 +13370,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{adefc37a-f16a-4187-89b7-2299314341a0}">
+          <x14:cfRule type="dataBar" id="{66ba7f92-1f43-444c-a584-e716105a9b13}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e757e693-15e0-4595-bf74-1109be2e8df7}">
+          <x14:cfRule type="dataBar" id="{2446b1fa-793d-4932-8b0f-d4caac932e48}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13388,7 +13388,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b2a70351-b30b-41ee-8f5e-8d9f5dcccaf4}">
+          <x14:cfRule type="dataBar" id="{b7c8e005-0673-46e9-b740-25fe2a239856}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -13402,7 +13402,7 @@
           <xm:sqref>K59:K60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1b751ad6-9aae-471e-856b-6b9fcea12d3b}">
+          <x14:cfRule type="dataBar" id="{00fc752f-a51a-4f9f-880c-66e2b71cb475}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13412,7 +13412,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7c1051e5-84af-4990-a0d9-677820f1a72a}">
+          <x14:cfRule type="dataBar" id="{04d800a5-dbb6-4629-b328-024f72cd9d31}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13424,7 +13424,7 @@
           <xm:sqref>Y69:Y88</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3ca49927-f367-4b32-bcfa-ad5fcecf97b0}">
+          <x14:cfRule type="dataBar" id="{0a1d25be-456f-4916-bec3-3c3555183f04}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13437,7 +13437,7 @@
           <xm:sqref>Y79:Y88</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{94f1da0b-76fa-4aaa-9ae2-89cc207e971b}">
+          <x14:cfRule type="dataBar" id="{18c1dd8d-68df-4b40-8511-4673843676a9}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13450,7 +13450,7 @@
           <xm:sqref>AB117:AB126</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e40576c4-ad51-4ab1-845c-5c5f9924b5bd}">
+          <x14:cfRule type="dataBar" id="{33efd8c8-9d94-403a-81ca-0b56685fda94}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13462,7 +13462,7 @@
           <xm:sqref>AD58:AE59</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e71d0b06-aca6-4d08-8db7-4dd7f409e5e1}">
+          <x14:cfRule type="dataBar" id="{b1ab472e-1668-41af-9582-5161d848a33a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13474,7 +13474,7 @@
           <xm:sqref>AD62:AE65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b3375f06-4fac-496a-afe6-954864bee6d8}">
+          <x14:cfRule type="dataBar" id="{65888510-a5e8-45a9-8203-27351fb42e22}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13484,7 +13484,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c67fac55-97ca-4f40-9b7e-a88664bda925}">
+          <x14:cfRule type="dataBar" id="{9f7169d8-5531-45b0-ba4f-41d8c2f08590}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13493,7 +13493,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ffc1f4f4-4385-4e5d-abe4-2607d9d10086}">
+          <x14:cfRule type="dataBar" id="{a65b4136-0a2d-49dc-a7e1-def6830a230d}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13505,7 +13505,7 @@
           <xm:sqref>F69 F74 F79 F84</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e6424149-2dbf-4588-978c-3e06a1c904c3}">
+          <x14:cfRule type="dataBar" id="{0b74384e-ab59-4c49-bd63-2efdccd9a8cf}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13515,7 +13515,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f80f76eb-67c8-489c-8ec1-130ed5158f5a}">
+          <x14:cfRule type="dataBar" id="{47627bef-38ab-4e19-89e6-69f5334b0f86}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13524,7 +13524,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{dc2858ff-8f8f-4d63-9f3f-5754d621243d}">
+          <x14:cfRule type="dataBar" id="{b270289d-37fd-4335-9030-29f1fd34f883}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13536,7 +13536,7 @@
           <xm:sqref>K69 K79 K89 K103</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{71c86f7b-727a-4c53-9192-e0f4010c8f60}">
+          <x14:cfRule type="dataBar" id="{56a8f6f8-fb05-457a-b81a-3dd793549c15}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13546,7 +13546,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7af86aec-9371-4dec-b230-bdaf05af3f4e}">
+          <x14:cfRule type="dataBar" id="{73a0a36a-a630-4115-9410-c4814f3104be}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13555,7 +13555,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ebb74a8b-084f-4efa-8224-17d458b412a7}">
+          <x14:cfRule type="dataBar" id="{ed331490-d0ab-4bad-b17b-f5db4ae144e5}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13567,7 +13567,7 @@
           <xm:sqref>AB79 AB89</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d867b97b-7a06-4f0b-b6fc-883b61e7ab14}">
+          <x14:cfRule type="dataBar" id="{53e4be7a-4fad-45c0-af5d-86629edc2522}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13577,7 +13577,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{bce4b6be-cdab-48a9-a066-2c4253c80a15}">
+          <x14:cfRule type="dataBar" id="{a067a6ca-07f7-4816-9ee5-1e00f45c5929}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13586,7 +13586,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{cb30e02c-cc76-4ea7-98ff-dfe6013a897f}">
+          <x14:cfRule type="dataBar" id="{fbd5c5df-458b-46e4-8ad8-6e5c52a2f4a5}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13598,7 +13598,7 @@
           <xm:sqref>F89 F96 F103 F110</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{eb2fbaac-ad3a-4509-acad-a72f80cd0ad5}">
+          <x14:cfRule type="dataBar" id="{dd8e0560-423a-4c31-8656-c6a8dd6fde50}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13608,7 +13608,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b91e7df2-5bed-47dc-832e-6ba01f1c322b}">
+          <x14:cfRule type="dataBar" id="{0ae66ab8-e9bb-404f-bcee-885569b0188b}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13620,7 +13620,7 @@
           <xm:sqref>Y89 Y103</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0e72f36c-5955-4e72-b67d-c9a69fb5ee7b}">
+          <x14:cfRule type="dataBar" id="{ce78fbe4-ef71-4cb6-965b-28e84b9a2e60}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13630,7 +13630,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{075b32f0-5559-4110-9e64-c8e4b78b53f9}">
+          <x14:cfRule type="dataBar" id="{33710180-8d2f-488f-946e-38fe92e76cc4}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13639,7 +13639,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{24f2a45b-dd32-4f1f-a235-3be38e264c81}">
+          <x14:cfRule type="dataBar" id="{8a05a893-39d2-4d03-aa9f-d12d96ee0abe}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13651,7 +13651,7 @@
           <xm:sqref>F117 F122 F127 F132 F137 F142 F147 F152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5a73aaa2-8814-467a-8278-425d1ba1d4af}">
+          <x14:cfRule type="dataBar" id="{8ec76ca4-f9d6-4e12-9c49-d7d662d51c7f}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13661,7 +13661,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8d59a0a5-ffda-4090-877e-a55bb619f89a}">
+          <x14:cfRule type="dataBar" id="{dcaafd60-e93b-4d3b-a10b-1da24f947bb5}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13670,7 +13670,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f0cd1e36-12dd-4dd4-ae4b-63cf2f88022b}">
+          <x14:cfRule type="dataBar" id="{a760a73a-4818-494f-9502-468b45f1e8dc}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13682,7 +13682,7 @@
           <xm:sqref>K117 K127</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{35198f7e-39ba-47d9-96fb-7482b4546696}">
+          <x14:cfRule type="dataBar" id="{cbc48366-b730-49f8-b9f2-6a11065ee809}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13692,7 +13692,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f61ca27d-8472-4383-ae26-282214c5eecc}">
+          <x14:cfRule type="dataBar" id="{5aedb19b-6e0d-4c77-9de3-ca10b9ca0370}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13713,12 +13713,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="26.8818181818182" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.38181818181818" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.21818181818182" style="1" customWidth="1"/>
-    <col min="18" max="18" width="9.38181818181818" style="1" customWidth="1"/>
+    <col min="1" max="1" width="26.8796296296296" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.37962962962963" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.22222222222222" style="1" customWidth="1"/>
+    <col min="18" max="18" width="9.37962962962963" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">

--- a/外网端源码/其他楼交接班容量报表空模板.xlsx
+++ b/外网端源码/其他楼交接班容量报表空模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="22020"/>
+    <workbookView windowWidth="24750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="本班组" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="389">
   <si>
     <t>班次</t>
   </si>
@@ -3210,28 +3210,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AF156"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="18.1851851851852" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.1818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.9351851851852" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.9363636363636" style="1" customWidth="1"/>
     <col min="7" max="8" width="9" style="1" customWidth="1"/>
-    <col min="9" max="9" width="16.4074074074074" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.4090909090909" style="1" customWidth="1"/>
     <col min="10" max="11" width="9" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.9351851851852" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.9363636363636" style="1" customWidth="1"/>
     <col min="13" max="13" width="9" style="1" customWidth="1"/>
-    <col min="14" max="14" width="8.75" style="1" customWidth="1"/>
-    <col min="15" max="15" width="38.1851851851852" style="1" customWidth="1"/>
+    <col min="14" max="14" width="8.75454545454545" style="1" customWidth="1"/>
+    <col min="15" max="15" width="38.1818181818182" style="1" customWidth="1"/>
     <col min="16" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="12.5925925925926" style="1" customWidth="1"/>
-    <col min="20" max="20" width="16.5092592592593" style="1" customWidth="1"/>
+    <col min="19" max="19" width="12.5909090909091" style="1" customWidth="1"/>
+    <col min="20" max="20" width="16.5090909090909" style="1" customWidth="1"/>
     <col min="21" max="21" width="9" style="1" customWidth="1"/>
-    <col min="22" max="22" width="14.1574074074074" style="1" customWidth="1"/>
+    <col min="22" max="22" width="14.1545454545455" style="1" customWidth="1"/>
     <col min="23" max="24" width="9" style="1" customWidth="1"/>
-    <col min="25" max="25" width="10.25" style="1" customWidth="1"/>
+    <col min="25" max="25" width="10.2545454545455" style="1" customWidth="1"/>
     <col min="26" max="27" width="9" style="1" customWidth="1"/>
-    <col min="28" max="28" width="17.4166666666667" style="1" customWidth="1"/>
+    <col min="28" max="28" width="17.4181818181818" style="1" customWidth="1"/>
     <col min="31" max="31" width="11" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4236,7 +4236,10 @@
       <c r="AB24" s="89" t="s">
         <v>73</v>
       </c>
-      <c r="AC24" s="90"/>
+      <c r="AC24" s="90" t="e">
+        <f>AC29/O59*24</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AD24" s="52"/>
       <c r="AE24" s="53"/>
     </row>
@@ -4264,11 +4267,15 @@
       <c r="K25" s="84" t="s">
         <v>75</v>
       </c>
-      <c r="L25" s="88"/>
+      <c r="L25" s="88" t="s">
+        <v>15</v>
+      </c>
       <c r="M25" s="84" t="s">
         <v>76</v>
       </c>
-      <c r="N25" s="88"/>
+      <c r="N25" s="88" t="s">
+        <v>15</v>
+      </c>
       <c r="O25" s="55"/>
       <c r="P25" s="91" t="s">
         <v>74</v>
@@ -4291,11 +4298,15 @@
       <c r="X25" s="84" t="s">
         <v>75</v>
       </c>
-      <c r="Y25" s="88"/>
+      <c r="Y25" s="88" t="s">
+        <v>15</v>
+      </c>
       <c r="Z25" s="84" t="s">
         <v>76</v>
       </c>
-      <c r="AA25" s="88"/>
+      <c r="AA25" s="88" t="s">
+        <v>15</v>
+      </c>
       <c r="AB25" s="89" t="s">
         <v>77</v>
       </c>
@@ -4329,7 +4340,9 @@
       <c r="K26" s="84" t="s">
         <v>82</v>
       </c>
-      <c r="L26" s="74"/>
+      <c r="L26" s="74" t="s">
+        <v>15</v>
+      </c>
       <c r="M26" s="84" t="s">
         <v>83</v>
       </c>
@@ -4361,7 +4374,9 @@
       <c r="X26" s="84" t="s">
         <v>82</v>
       </c>
-      <c r="Y26" s="94"/>
+      <c r="Y26" s="94" t="s">
+        <v>15</v>
+      </c>
       <c r="Z26" s="84" t="s">
         <v>83</v>
       </c>
@@ -4441,13 +4456,15 @@
       <c r="K28" s="84" t="s">
         <v>88</v>
       </c>
-      <c r="L28" s="88"/>
+      <c r="L28" s="88" t="s">
+        <v>15</v>
+      </c>
       <c r="M28" s="84" t="s">
         <v>89</v>
       </c>
-      <c r="N28" s="88">
+      <c r="N28" s="88" t="e">
         <f>N25-N26</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="O28" s="55"/>
       <c r="P28" s="84" t="s">
@@ -4471,13 +4488,15 @@
       <c r="X28" s="84" t="s">
         <v>88</v>
       </c>
-      <c r="Y28" s="101"/>
+      <c r="Y28" s="101" t="s">
+        <v>15</v>
+      </c>
       <c r="Z28" s="84" t="s">
         <v>89</v>
       </c>
-      <c r="AA28" s="88">
+      <c r="AA28" s="88" t="e">
         <f>AA25-AA26</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="AB28" s="89" t="s">
         <v>90</v>
@@ -4508,11 +4527,15 @@
       <c r="K29" s="84" t="s">
         <v>94</v>
       </c>
-      <c r="L29" s="88"/>
+      <c r="L29" s="88" t="s">
+        <v>15</v>
+      </c>
       <c r="M29" s="84" t="s">
         <v>95</v>
       </c>
-      <c r="N29" s="88"/>
+      <c r="N29" s="88" t="s">
+        <v>15</v>
+      </c>
       <c r="O29" s="55"/>
       <c r="P29" s="84" t="s">
         <v>91</v>
@@ -4533,11 +4556,15 @@
       <c r="X29" s="84" t="s">
         <v>94</v>
       </c>
-      <c r="Y29" s="88"/>
+      <c r="Y29" s="88" t="s">
+        <v>15</v>
+      </c>
       <c r="Z29" s="84" t="s">
         <v>95</v>
       </c>
-      <c r="AA29" s="88"/>
+      <c r="AA29" s="88" t="s">
+        <v>15</v>
+      </c>
       <c r="AB29" s="89" t="s">
         <v>96</v>
       </c>
@@ -4570,14 +4597,16 @@
       <c r="K30" s="84" t="s">
         <v>100</v>
       </c>
-      <c r="L30" s="74">
+      <c r="L30" s="74" t="e">
         <f>L29-L25</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="M30" s="84" t="s">
         <v>101</v>
       </c>
-      <c r="N30" s="88"/>
+      <c r="N30" s="88" t="s">
+        <v>15</v>
+      </c>
       <c r="O30" s="55"/>
       <c r="P30" s="84" t="s">
         <v>97</v>
@@ -4598,14 +4627,16 @@
       <c r="X30" s="84" t="s">
         <v>100</v>
       </c>
-      <c r="Y30" s="74">
+      <c r="Y30" s="74" t="e">
         <f>Y29-Y25</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="Z30" s="84" t="s">
         <v>101</v>
       </c>
-      <c r="AA30" s="88"/>
+      <c r="AA30" s="88" t="s">
+        <v>15</v>
+      </c>
       <c r="AB30" s="102" t="s">
         <v>102</v>
       </c>
@@ -4635,9 +4666,9 @@
       <c r="M31" s="84" t="s">
         <v>105</v>
       </c>
-      <c r="N31" s="74">
+      <c r="N31" s="74" t="e">
         <f>N29-N30</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="O31" s="55"/>
       <c r="P31" s="84" t="s">
@@ -4659,9 +4690,9 @@
       <c r="Z31" s="84" t="s">
         <v>105</v>
       </c>
-      <c r="AA31" s="74">
+      <c r="AA31" s="74" t="e">
         <f>AA29-AA30</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="AE31" s="47"/>
     </row>
@@ -4828,11 +4859,15 @@
       <c r="K35" s="104" t="s">
         <v>75</v>
       </c>
-      <c r="L35" s="106"/>
+      <c r="L35" s="106" t="s">
+        <v>15</v>
+      </c>
       <c r="M35" s="104" t="s">
         <v>76</v>
       </c>
-      <c r="N35" s="107"/>
+      <c r="N35" s="107" t="s">
+        <v>15</v>
+      </c>
       <c r="O35" s="55"/>
       <c r="P35" s="105" t="s">
         <v>74</v>
@@ -4855,11 +4890,15 @@
       <c r="X35" s="104" t="s">
         <v>75</v>
       </c>
-      <c r="Y35" s="106"/>
+      <c r="Y35" s="106" t="s">
+        <v>15</v>
+      </c>
       <c r="Z35" s="104" t="s">
         <v>76</v>
       </c>
-      <c r="AA35" s="106"/>
+      <c r="AA35" s="106" t="s">
+        <v>15</v>
+      </c>
       <c r="AB35" s="89" t="s">
         <v>108</v>
       </c>
@@ -4899,7 +4938,9 @@
       <c r="K36" s="104" t="s">
         <v>82</v>
       </c>
-      <c r="L36" s="106"/>
+      <c r="L36" s="106" t="s">
+        <v>15</v>
+      </c>
       <c r="M36" s="104" t="s">
         <v>83</v>
       </c>
@@ -4935,7 +4976,9 @@
       <c r="X36" s="104" t="s">
         <v>82</v>
       </c>
-      <c r="Y36" s="106"/>
+      <c r="Y36" s="106" t="s">
+        <v>15</v>
+      </c>
       <c r="Z36" s="104" t="s">
         <v>83</v>
       </c>
@@ -5021,13 +5064,15 @@
       <c r="K38" s="104" t="s">
         <v>88</v>
       </c>
-      <c r="L38" s="106"/>
+      <c r="L38" s="106" t="s">
+        <v>15</v>
+      </c>
       <c r="M38" s="104" t="s">
         <v>89</v>
       </c>
-      <c r="N38" s="107">
+      <c r="N38" s="107" t="e">
         <f>N35-N36</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="O38" s="55"/>
       <c r="P38" s="104" t="s">
@@ -5055,13 +5100,15 @@
       <c r="X38" s="104" t="s">
         <v>88</v>
       </c>
-      <c r="Y38" s="106"/>
+      <c r="Y38" s="106" t="s">
+        <v>15</v>
+      </c>
       <c r="Z38" s="104" t="s">
         <v>89</v>
       </c>
-      <c r="AA38" s="106">
+      <c r="AA38" s="106" t="e">
         <f>AA35-AA36</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="AB38" s="89" t="s">
         <v>111</v>
@@ -5098,11 +5145,15 @@
       <c r="K39" s="104" t="s">
         <v>94</v>
       </c>
-      <c r="L39" s="106"/>
+      <c r="L39" s="106" t="s">
+        <v>15</v>
+      </c>
       <c r="M39" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="N39" s="107"/>
+      <c r="N39" s="107" t="s">
+        <v>15</v>
+      </c>
       <c r="O39" s="55"/>
       <c r="P39" s="104" t="s">
         <v>91</v>
@@ -5127,11 +5178,15 @@
       <c r="X39" s="104" t="s">
         <v>94</v>
       </c>
-      <c r="Y39" s="106"/>
+      <c r="Y39" s="106" t="s">
+        <v>15</v>
+      </c>
       <c r="Z39" s="104" t="s">
         <v>95</v>
       </c>
-      <c r="AA39" s="106"/>
+      <c r="AA39" s="106" t="s">
+        <v>15</v>
+      </c>
       <c r="AB39" s="89" t="s">
         <v>113</v>
       </c>
@@ -5167,14 +5222,16 @@
       <c r="K40" s="104" t="s">
         <v>100</v>
       </c>
-      <c r="L40" s="106">
+      <c r="L40" s="106" t="e">
         <f>L39-L35</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="M40" s="104" t="s">
         <v>101</v>
       </c>
-      <c r="N40" s="107"/>
+      <c r="N40" s="107" t="s">
+        <v>15</v>
+      </c>
       <c r="O40" s="55"/>
       <c r="P40" s="104" t="s">
         <v>97</v>
@@ -5199,14 +5256,16 @@
       <c r="X40" s="104" t="s">
         <v>100</v>
       </c>
-      <c r="Y40" s="106">
+      <c r="Y40" s="106" t="e">
         <f>Y39-Y35</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="Z40" s="104" t="s">
         <v>101</v>
       </c>
-      <c r="AA40" s="106"/>
+      <c r="AA40" s="106" t="s">
+        <v>15</v>
+      </c>
       <c r="AB40" s="89" t="s">
         <v>115</v>
       </c>
@@ -5240,9 +5299,9 @@
       <c r="M41" s="104" t="s">
         <v>105</v>
       </c>
-      <c r="N41" s="107">
+      <c r="N41" s="107" t="e">
         <f>N39-N40</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="O41" s="55"/>
       <c r="P41" s="104" t="s">
@@ -5266,9 +5325,9 @@
       <c r="Z41" s="104" t="s">
         <v>105</v>
       </c>
-      <c r="AA41" s="106">
+      <c r="AA41" s="106" t="e">
         <f>AA39-AA40</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="AB41" s="81"/>
       <c r="AC41" s="82"/>
@@ -6359,7 +6418,7 @@
       <c r="AD66" s="64"/>
       <c r="AE66" s="64"/>
     </row>
-    <row r="67" s="10" customFormat="1" ht="17.4" spans="1:32">
+    <row r="67" s="10" customFormat="1" ht="17.5" spans="1:32">
       <c r="A67" s="137"/>
       <c r="B67" s="138"/>
       <c r="C67" s="138"/>
@@ -11223,7 +11282,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d4877931-dfce-4551-8728-152f925220c7}</x14:id>
+          <x14:id>{95fc9201-06fe-4f11-9661-a8b0a3cadc22}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11235,7 +11294,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8bf915ef-bc4b-4e1d-9874-f07f569f96c7}</x14:id>
+          <x14:id>{694aa617-c5ee-4c08-854e-3b8fa928d74c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11247,7 +11306,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7e5527ef-53fa-479e-ac3a-7e0235785738}</x14:id>
+          <x14:id>{348f70ea-5a34-47b4-83aa-c924dd5dd135}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11259,7 +11318,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2eccd957-0aee-441b-b443-9d9f882c3446}</x14:id>
+          <x14:id>{228fefb1-fb1c-4e7d-8bb8-744905e05f77}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11271,7 +11330,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{23613c43-f60b-4b73-aa1d-5a1142f19079}</x14:id>
+          <x14:id>{6925e53b-fa63-4ce8-8851-49ad3d1a5949}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11283,7 +11342,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{37f5f3dd-5396-4628-93eb-616d602135ec}</x14:id>
+          <x14:id>{ecb29fc4-5b48-4c28-a973-729f594c8de5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11295,7 +11354,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ded25921-a00c-466f-821d-503dc560ad34}</x14:id>
+          <x14:id>{a4c1f7a3-b166-4740-8d08-b9f5345ec19c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11307,7 +11366,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fa7dba31-f165-447b-8c64-365251170942}</x14:id>
+          <x14:id>{d206e897-104a-4513-abff-f0acce1025c8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11321,7 +11380,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{39317d3e-dec9-4e47-9f89-6593f4aa16ee}</x14:id>
+          <x14:id>{6f31985e-3c1b-436c-af8c-01ba924c9ab0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11333,7 +11392,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{99e2477e-1f72-493d-bb17-13f8f52dd026}</x14:id>
+          <x14:id>{c367b33e-de62-4aa3-9d4d-1194922b3534}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11345,7 +11404,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f47a0988-9422-4884-a6de-29c552527747}</x14:id>
+          <x14:id>{92e8d81b-bf04-42d5-b77e-f76d6af8aa9e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11357,7 +11416,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3cf721bd-e272-4c16-a098-a56991919aa2}</x14:id>
+          <x14:id>{5eb768d9-3c90-4977-9b38-b4c3728c5239}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11369,7 +11428,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c5593dd7-cceb-455d-8809-0c587881d535}</x14:id>
+          <x14:id>{bb0ec098-3d01-42bf-ae8c-cb476fd0c935}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11381,7 +11440,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5c27ac20-1dcb-4006-b3a7-968c4d6c32e7}</x14:id>
+          <x14:id>{bfdc8412-5b81-4050-9a49-ae116f5b98eb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11393,7 +11452,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dc0aa2e1-cca6-40b4-8c55-893176e671f0}</x14:id>
+          <x14:id>{786d20d1-44d9-426f-a86c-e513aa02d002}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11405,7 +11464,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{34af5fe1-4b57-4ead-a3a8-847ba191d16a}</x14:id>
+          <x14:id>{aed3bf74-3834-4a3d-ac5b-ac85c1ec4d12}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11419,7 +11478,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{25e1d582-a05a-4f9e-ad9a-807df3cfb8bc}</x14:id>
+          <x14:id>{eff089b4-8f2e-40ce-809f-37e2eefe47bd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11431,7 +11490,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{00a27792-e4ea-4606-988f-e7c424702b88}</x14:id>
+          <x14:id>{a9639dbf-6813-4038-9a1d-ba03be45b1d1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11443,7 +11502,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3246ba4a-250d-4018-8cff-1fd73d55f392}</x14:id>
+          <x14:id>{0497d441-cd0b-4dc7-94f0-48c128bbd045}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11455,7 +11514,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{850d7515-f0d1-4ee1-8c07-64ac37188a75}</x14:id>
+          <x14:id>{0d8dc26e-4cd4-409b-b0f3-17f37978b019}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11467,7 +11526,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1b94d11c-4715-417f-94e3-08be37bc7de1}</x14:id>
+          <x14:id>{f8477233-8b62-480b-b933-c7513dc4d359}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11479,7 +11538,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{babda1b1-026f-4d00-b4af-68dd112decce}</x14:id>
+          <x14:id>{9d3b67df-0f28-4af1-aa8b-cdc3f0430085}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11491,7 +11550,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{24add29d-5ce1-4141-bf99-878e7b7a9cb4}</x14:id>
+          <x14:id>{2b1054ad-a1d5-4fba-80af-fe4cd9cf95f2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11503,7 +11562,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{84ff42ae-3bc8-427e-a99e-4ed61f2056de}</x14:id>
+          <x14:id>{9b73bd73-52cb-4696-9671-f748dd956215}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11517,7 +11576,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fff4a9d0-dbb5-458a-b9a4-416284621ba3}</x14:id>
+          <x14:id>{32cc81c0-a0a9-4ee7-8764-01969bfb7053}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11529,7 +11588,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a718fdd4-e714-43b9-8298-2ef7eb1922eb}</x14:id>
+          <x14:id>{8799a15d-c0cc-4807-b458-a5143074ddb1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11541,7 +11600,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0073319a-3e61-4e4e-9182-00119553b575}</x14:id>
+          <x14:id>{aa1c943b-39e1-4d37-a139-3ee6023987dd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11553,7 +11612,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4511bcac-36b5-4698-a420-8f402682f901}</x14:id>
+          <x14:id>{bb4794af-55ef-4769-aacd-a007dc1b9317}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11565,7 +11624,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2d3ce388-9e99-4ba1-977b-334c304c197a}</x14:id>
+          <x14:id>{ba6cc759-24bd-4c20-a20b-3193edc9d29e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11577,7 +11636,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0a6197b4-2eb8-46fe-8eff-3da4ac1f6ccc}</x14:id>
+          <x14:id>{bd02d4c0-a31e-4880-81ac-1e557686bff7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11589,7 +11648,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{143dc1c0-192f-4b62-9354-e99d14ee15ea}</x14:id>
+          <x14:id>{66ce2917-620f-43a3-a732-12ee9991e56d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11601,7 +11660,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{925ff35d-464a-4152-bc1e-4245330e5997}</x14:id>
+          <x14:id>{adb50e3c-f6ae-4b7c-a6eb-301d5cb21eb1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11615,7 +11674,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e55ecc99-61ab-4ad3-8a2a-68bcdea30102}</x14:id>
+          <x14:id>{d8f33d55-cab7-4966-9b4f-11c6cf30ce54}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11627,7 +11686,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{82b6a770-9d3b-425f-be5f-d884a44c240c}</x14:id>
+          <x14:id>{093fa95d-7ea1-499b-aa4c-8d4552a6f854}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11639,7 +11698,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e5331c35-36e8-4a81-9494-687831b019fa}</x14:id>
+          <x14:id>{ae009b05-b3cc-45c6-aecc-6806d6a3d632}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11651,7 +11710,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{280caff2-74f5-4b0d-a56a-0e45fb5c10d7}</x14:id>
+          <x14:id>{794aa47d-a3a8-46cf-a6ec-6fca7b180787}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11663,7 +11722,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2493c57f-4b7e-437e-b83e-14a67b08a919}</x14:id>
+          <x14:id>{34f3ae4b-9790-4e4a-af48-ca27ba3c5edc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11675,7 +11734,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b7372b0e-0fa7-4475-a82b-730aaf412d63}</x14:id>
+          <x14:id>{24024d23-8b0b-4e55-ba27-b664bbb1bf49}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11687,7 +11746,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bb6d9611-7406-4b71-ac03-94695ed0d5f0}</x14:id>
+          <x14:id>{25248efa-4a5e-46e7-b9f0-5480c4f3ba55}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11699,7 +11758,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{daf20764-0e40-4d50-8689-2f1333de3b80}</x14:id>
+          <x14:id>{a4ee10a4-15a0-45f2-8d78-986b10cad2b3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11713,7 +11772,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{43a4f6d6-f04f-42e9-b90a-6eafa34a8656}</x14:id>
+          <x14:id>{36b79758-d424-4c7c-8b62-b6a77c5639fe}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11725,7 +11784,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f5939dd2-7152-4175-a5a6-0ea51b3bcbc4}</x14:id>
+          <x14:id>{c3eda83d-de89-4886-afc6-26584bc41560}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11737,7 +11796,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1e45f251-2c8f-441f-81e1-0605c88c8312}</x14:id>
+          <x14:id>{df185500-f7bc-44b0-a1d3-839fdb4edbe0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11749,7 +11808,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{910c0f33-467c-4749-b8bd-cb280a8ac582}</x14:id>
+          <x14:id>{bb695873-6942-45f5-bae3-26e29662c8d4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11761,7 +11820,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{57d7a39c-e066-437e-b53d-d1ac48237712}</x14:id>
+          <x14:id>{7881e003-60eb-423f-b6c0-7247349336df}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11773,7 +11832,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e73bf181-0d20-487b-9eb6-22df4e5292d4}</x14:id>
+          <x14:id>{9c82c54a-dcb9-4291-b61e-3cec658f4612}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11785,7 +11844,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c11e52f1-38f2-4af0-a076-d2b17600ff6a}</x14:id>
+          <x14:id>{349a1dab-127c-42c2-92ea-16837ff9eb07}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11797,7 +11856,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7948c94e-f69e-4e64-b7d0-0f563212f70c}</x14:id>
+          <x14:id>{3c413e53-0d71-4e10-a9e4-b410c22b6cd9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11811,7 +11870,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0e94f7af-e845-4408-b884-01babb5df860}</x14:id>
+          <x14:id>{ef233290-8246-4ec6-8cda-1a218572b949}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11823,7 +11882,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{94bcd1db-88bf-42b8-837c-f8c1b7fa169e}</x14:id>
+          <x14:id>{8f0208a7-46a3-4db3-9ff7-e28f93388360}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11835,7 +11894,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1db48018-b53c-4ccf-8df7-c29d745d9966}</x14:id>
+          <x14:id>{300022d1-cef6-4094-9687-095ed68ab3f8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11849,7 +11908,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b8fe6fee-caee-42c1-9a92-6ef57adf7699}</x14:id>
+          <x14:id>{d1db28dd-edcd-47f0-a7c1-b4e614a46ea7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11861,7 +11920,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2268fb69-e943-4688-8771-90b2d4300452}</x14:id>
+          <x14:id>{1665de81-b3d2-4490-822b-07eea518d43f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11873,7 +11932,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{64afb03a-928d-43c6-8767-d87de82635e2}</x14:id>
+          <x14:id>{f0bcc344-c6c7-45de-82e0-60b4c5e1d231}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11887,7 +11946,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5f5107c4-286e-45fe-b104-cce2792a1b96}</x14:id>
+          <x14:id>{b0eead19-6dd5-45ee-ae32-eafe2425cbbb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11899,7 +11958,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{45578e32-148b-44b6-9c9d-8bee23b9e3db}</x14:id>
+          <x14:id>{2b3d9000-8d8c-4ec8-8675-4b6bd89162e5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11913,7 +11972,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9ded9fd1-a30e-4067-81a0-2527a36b725d}</x14:id>
+          <x14:id>{4b01864b-c52e-45b4-a8e3-2436ba997e54}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11925,7 +11984,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a63f0f08-1667-4be7-b016-db2e54248f85}</x14:id>
+          <x14:id>{9cd56678-6b38-4b3b-b05e-6c934f380c14}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11937,7 +11996,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3094a5f2-195d-44c2-ab22-ed724d28fd48}</x14:id>
+          <x14:id>{751f2d08-6eea-4ff5-96ee-82e6467dccae}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11951,7 +12010,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{50b0b2cb-6b69-43f5-97f6-487813a6a6ff}</x14:id>
+          <x14:id>{930b7479-94cb-4d87-9d40-3eb7625d5cd8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11963,7 +12022,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c3f69d74-f89b-40a3-808c-b422169ec85f}</x14:id>
+          <x14:id>{e49b4dce-6156-4a95-96b1-19ba268e5c19}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11975,7 +12034,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{048a0a12-faa7-442c-ab01-cffc7fb00953}</x14:id>
+          <x14:id>{e4a3a780-02e1-4570-b29b-ca7c3fcad664}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11989,7 +12048,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bd4080ea-4f39-494e-ae92-b72eb777baa5}</x14:id>
+          <x14:id>{3bbb6730-4790-45a9-b856-1857a27b1be7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12001,7 +12060,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fff168ef-270e-4ebb-ad04-c451d2a788a0}</x14:id>
+          <x14:id>{e8f413f3-26be-4a24-bb64-2d53b70958c7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12013,7 +12072,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{132548c4-a2ad-4fee-96ad-4e678db4a997}</x14:id>
+          <x14:id>{57a5fc59-29aa-4595-8b39-34815b5e407a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12027,7 +12086,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8a83dc2b-b030-4565-8c7c-2082312bbffa}</x14:id>
+          <x14:id>{6c00a001-b025-4281-8842-a12669763b0f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12039,7 +12098,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{618224f1-8993-4438-b9a0-b730641e9be6}</x14:id>
+          <x14:id>{793a1e8f-49d7-4d52-8cbb-7becd8fe20e9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12051,7 +12110,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{643645c8-0c55-4079-a596-4d26a30e0a72}</x14:id>
+          <x14:id>{dda2f33f-38c8-4578-9979-6de9bad79ad5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12065,7 +12124,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{808714b1-fcbb-4f12-98b9-8c1f05198e57}</x14:id>
+          <x14:id>{c18fdbd9-e05a-4ea5-996e-b2c5f72539f2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12077,7 +12136,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{057ff636-faf5-47bd-bbf9-fe53e5c6c4fe}</x14:id>
+          <x14:id>{05baf66b-4558-4742-8faf-7f7f28b73da6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12089,7 +12148,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{26c3cabb-1848-499c-b301-03e2f385070c}</x14:id>
+          <x14:id>{756909b9-2ab0-4860-a388-6c6b61fa1a02}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12103,7 +12162,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fee870b3-6248-4625-9360-bc028983d9fa}</x14:id>
+          <x14:id>{86f8293c-9317-4649-9359-4cc5fad92480}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12115,7 +12174,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7b61ebec-519c-40e1-b40b-771cd5f5d0ed}</x14:id>
+          <x14:id>{3f95dd0f-a998-44b4-8b61-7eba6f123fd1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12127,7 +12186,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6c511f62-3be6-41f9-a287-435254c360b9}</x14:id>
+          <x14:id>{88ad5191-4a14-4fd4-85e0-f24ca51de7bc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12139,7 +12198,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{03fe8fe4-57a7-46dd-b9ee-adad359b0361}</x14:id>
+          <x14:id>{83dae187-283a-48c9-9cc5-5109a406ffd9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12151,7 +12210,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9cc2fe4a-d406-4b26-83b2-3b6b96746d31}</x14:id>
+          <x14:id>{bd0b0eef-96d7-4917-a619-20b21ca0a4a3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12163,7 +12222,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{66ba7f92-1f43-444c-a584-e716105a9b13}</x14:id>
+          <x14:id>{03e41982-92da-49bb-80ce-7962d5c4ad42}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12175,7 +12234,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2446b1fa-793d-4932-8b0f-d4caac932e48}</x14:id>
+          <x14:id>{1e875aa6-f22d-48f5-978e-c49e5003f55b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12187,7 +12246,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b7c8e005-0673-46e9-b740-25fe2a239856}</x14:id>
+          <x14:id>{f6d22fea-02fc-4edb-a458-fbcb114ef29d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12201,7 +12260,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{00fc752f-a51a-4f9f-880c-66e2b71cb475}</x14:id>
+          <x14:id>{20267aae-5095-4109-a6f9-9f9274f16546}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12213,7 +12272,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{04d800a5-dbb6-4629-b328-024f72cd9d31}</x14:id>
+          <x14:id>{ad17ac9e-88d1-43fe-aaf4-7807489f809c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12227,7 +12286,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0a1d25be-456f-4916-bec3-3c3555183f04}</x14:id>
+          <x14:id>{57cd3f09-10cf-4aed-97cb-6a4f98a2438c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12241,7 +12300,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{18c1dd8d-68df-4b40-8511-4673843676a9}</x14:id>
+          <x14:id>{b8c304ab-2791-491d-aa6f-4bb2bd77c680}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12255,7 +12314,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{33efd8c8-9d94-403a-81ca-0b56685fda94}</x14:id>
+          <x14:id>{88262910-ce77-4fbd-832d-7f8b7b5fc9ae}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12269,7 +12328,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b1ab472e-1668-41af-9582-5161d848a33a}</x14:id>
+          <x14:id>{4f8ae6e5-02b8-42fe-9369-b165701c1ad9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12283,7 +12342,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{65888510-a5e8-45a9-8203-27351fb42e22}</x14:id>
+          <x14:id>{bbfea489-604d-4e79-8a83-49417788ddc9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12295,7 +12354,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9f7169d8-5531-45b0-ba4f-41d8c2f08590}</x14:id>
+          <x14:id>{ce34aa40-c046-4786-9619-f29ea12945b3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12307,7 +12366,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a65b4136-0a2d-49dc-a7e1-def6830a230d}</x14:id>
+          <x14:id>{6ad12ad1-d875-44a5-a6d0-a5e7fadbcbac}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12321,7 +12380,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0b74384e-ab59-4c49-bd63-2efdccd9a8cf}</x14:id>
+          <x14:id>{4f442e62-c4e1-4f33-b337-8c14914db47c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12333,7 +12392,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{47627bef-38ab-4e19-89e6-69f5334b0f86}</x14:id>
+          <x14:id>{b5cb1a15-ea56-4983-8090-8e4db946d512}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12345,7 +12404,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b270289d-37fd-4335-9030-29f1fd34f883}</x14:id>
+          <x14:id>{f9f52792-88b1-4c2d-b674-1b0b8dbd1a73}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12359,7 +12418,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{56a8f6f8-fb05-457a-b81a-3dd793549c15}</x14:id>
+          <x14:id>{6865e71f-1372-4678-8cce-e17ab517d11e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12371,7 +12430,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{73a0a36a-a630-4115-9410-c4814f3104be}</x14:id>
+          <x14:id>{055ce0b0-4c66-4356-b120-7d0a25b1fc87}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12383,7 +12442,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ed331490-d0ab-4bad-b17b-f5db4ae144e5}</x14:id>
+          <x14:id>{b5f46331-5e10-4cc0-841f-201cf0b486c4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12397,7 +12456,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{53e4be7a-4fad-45c0-af5d-86629edc2522}</x14:id>
+          <x14:id>{c4ea5fcf-2f6a-4ab4-ba06-585fb607d652}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12409,7 +12468,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a067a6ca-07f7-4816-9ee5-1e00f45c5929}</x14:id>
+          <x14:id>{31e9d49c-f6ce-4f49-b477-1a44936a1f6c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12421,7 +12480,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fbd5c5df-458b-46e4-8ad8-6e5c52a2f4a5}</x14:id>
+          <x14:id>{c8565e67-2050-4b0b-876d-4010e8bcc8d8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12435,7 +12494,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dd8e0560-423a-4c31-8656-c6a8dd6fde50}</x14:id>
+          <x14:id>{62321936-14a1-4e69-8f10-7ac61b7f30d4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12447,7 +12506,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0ae66ab8-e9bb-404f-bcee-885569b0188b}</x14:id>
+          <x14:id>{28f239b0-e3dc-4ef3-bbdf-b844b65ed496}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12461,7 +12520,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ce78fbe4-ef71-4cb6-965b-28e84b9a2e60}</x14:id>
+          <x14:id>{76a53066-3e04-4276-b800-a8848ec00e6d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12473,7 +12532,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{33710180-8d2f-488f-946e-38fe92e76cc4}</x14:id>
+          <x14:id>{8cbb2e52-3243-499c-93a4-ec7725742269}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12485,7 +12544,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8a05a893-39d2-4d03-aa9f-d12d96ee0abe}</x14:id>
+          <x14:id>{7bf86626-3680-4e4a-99b3-454ca1e9c002}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12499,7 +12558,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8ec76ca4-f9d6-4e12-9c49-d7d662d51c7f}</x14:id>
+          <x14:id>{4f4ccb6e-2c73-4c71-88ad-902d85e15fc9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12511,7 +12570,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dcaafd60-e93b-4d3b-a10b-1da24f947bb5}</x14:id>
+          <x14:id>{0cff5f02-ccd9-4735-a6df-24ed49eefe99}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12523,7 +12582,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a760a73a-4818-494f-9502-468b45f1e8dc}</x14:id>
+          <x14:id>{bba238ed-154d-48f0-8ad7-cecc98338924}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12537,7 +12596,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cbc48366-b730-49f8-b9f2-6a11065ee809}</x14:id>
+          <x14:id>{d3778a82-1e16-4abe-b55e-8bf651109f27}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12549,7 +12608,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5aedb19b-6e0d-4c77-9de3-ca10b9ca0370}</x14:id>
+          <x14:id>{76c486da-4f59-40d1-96d6-ff83e1c49f8c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12583,7 +12642,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d4877931-dfce-4551-8728-152f925220c7}">
+          <x14:cfRule type="dataBar" id="{95fc9201-06fe-4f11-9661-a8b0a3cadc22}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12592,7 +12651,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8bf915ef-bc4b-4e1d-9874-f07f569f96c7}">
+          <x14:cfRule type="dataBar" id="{694aa617-c5ee-4c08-854e-3b8fa928d74c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12601,7 +12660,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7e5527ef-53fa-479e-ac3a-7e0235785738}">
+          <x14:cfRule type="dataBar" id="{348f70ea-5a34-47b4-83aa-c924dd5dd135}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12612,7 +12671,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2eccd957-0aee-441b-b443-9d9f882c3446}">
+          <x14:cfRule type="dataBar" id="{228fefb1-fb1c-4e7d-8bb8-744905e05f77}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12623,7 +12682,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{23613c43-f60b-4b73-aa1d-5a1142f19079}">
+          <x14:cfRule type="dataBar" id="{6925e53b-fa63-4ce8-8851-49ad3d1a5949}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12634,14 +12693,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{37f5f3dd-5396-4628-93eb-616d602135ec}">
+          <x14:cfRule type="dataBar" id="{ecb29fc4-5b48-4c28-a973-729f594c8de5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ded25921-a00c-466f-821d-503dc560ad34}">
+          <x14:cfRule type="dataBar" id="{a4c1f7a3-b166-4740-8d08-b9f5345ec19c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12652,7 +12711,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{fa7dba31-f165-447b-8c64-365251170942}">
+          <x14:cfRule type="dataBar" id="{d206e897-104a-4513-abff-f0acce1025c8}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12666,7 +12725,7 @@
           <xm:sqref>AD58</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{39317d3e-dec9-4e47-9f89-6593f4aa16ee}">
+          <x14:cfRule type="dataBar" id="{6f31985e-3c1b-436c-af8c-01ba924c9ab0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12675,7 +12734,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{99e2477e-1f72-493d-bb17-13f8f52dd026}">
+          <x14:cfRule type="dataBar" id="{c367b33e-de62-4aa3-9d4d-1194922b3534}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12684,7 +12743,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f47a0988-9422-4884-a6de-29c552527747}">
+          <x14:cfRule type="dataBar" id="{92e8d81b-bf04-42d5-b77e-f76d6af8aa9e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12695,7 +12754,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3cf721bd-e272-4c16-a098-a56991919aa2}">
+          <x14:cfRule type="dataBar" id="{5eb768d9-3c90-4977-9b38-b4c3728c5239}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12706,7 +12765,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c5593dd7-cceb-455d-8809-0c587881d535}">
+          <x14:cfRule type="dataBar" id="{bb0ec098-3d01-42bf-ae8c-cb476fd0c935}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12717,14 +12776,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5c27ac20-1dcb-4006-b3a7-968c4d6c32e7}">
+          <x14:cfRule type="dataBar" id="{bfdc8412-5b81-4050-9a49-ae116f5b98eb}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{dc0aa2e1-cca6-40b4-8c55-893176e671f0}">
+          <x14:cfRule type="dataBar" id="{786d20d1-44d9-426f-a86c-e513aa02d002}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12735,7 +12794,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{34af5fe1-4b57-4ead-a3a8-847ba191d16a}">
+          <x14:cfRule type="dataBar" id="{aed3bf74-3834-4a3d-ac5b-ac85c1ec4d12}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12749,7 +12808,7 @@
           <xm:sqref>K62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{25e1d582-a05a-4f9e-ad9a-807df3cfb8bc}">
+          <x14:cfRule type="dataBar" id="{eff089b4-8f2e-40ce-809f-37e2eefe47bd}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12758,7 +12817,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{00a27792-e4ea-4606-988f-e7c424702b88}">
+          <x14:cfRule type="dataBar" id="{a9639dbf-6813-4038-9a1d-ba03be45b1d1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12767,7 +12826,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3246ba4a-250d-4018-8cff-1fd73d55f392}">
+          <x14:cfRule type="dataBar" id="{0497d441-cd0b-4dc7-94f0-48c128bbd045}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12778,7 +12837,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{850d7515-f0d1-4ee1-8c07-64ac37188a75}">
+          <x14:cfRule type="dataBar" id="{0d8dc26e-4cd4-409b-b0f3-17f37978b019}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12789,7 +12848,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1b94d11c-4715-417f-94e3-08be37bc7de1}">
+          <x14:cfRule type="dataBar" id="{f8477233-8b62-480b-b933-c7513dc4d359}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12800,14 +12859,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{babda1b1-026f-4d00-b4af-68dd112decce}">
+          <x14:cfRule type="dataBar" id="{9d3b67df-0f28-4af1-aa8b-cdc3f0430085}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{24add29d-5ce1-4141-bf99-878e7b7a9cb4}">
+          <x14:cfRule type="dataBar" id="{2b1054ad-a1d5-4fba-80af-fe4cd9cf95f2}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12818,7 +12877,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{84ff42ae-3bc8-427e-a99e-4ed61f2056de}">
+          <x14:cfRule type="dataBar" id="{9b73bd73-52cb-4696-9671-f748dd956215}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12832,7 +12891,7 @@
           <xm:sqref>AD62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fff4a9d0-dbb5-458a-b9a4-416284621ba3}">
+          <x14:cfRule type="dataBar" id="{32cc81c0-a0a9-4ee7-8764-01969bfb7053}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12841,7 +12900,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a718fdd4-e714-43b9-8298-2ef7eb1922eb}">
+          <x14:cfRule type="dataBar" id="{8799a15d-c0cc-4807-b458-a5143074ddb1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12850,7 +12909,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0073319a-3e61-4e4e-9182-00119553b575}">
+          <x14:cfRule type="dataBar" id="{aa1c943b-39e1-4d37-a139-3ee6023987dd}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12861,7 +12920,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4511bcac-36b5-4698-a420-8f402682f901}">
+          <x14:cfRule type="dataBar" id="{bb4794af-55ef-4769-aacd-a007dc1b9317}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12872,7 +12931,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2d3ce388-9e99-4ba1-977b-334c304c197a}">
+          <x14:cfRule type="dataBar" id="{ba6cc759-24bd-4c20-a20b-3193edc9d29e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12883,14 +12942,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0a6197b4-2eb8-46fe-8eff-3da4ac1f6ccc}">
+          <x14:cfRule type="dataBar" id="{bd02d4c0-a31e-4880-81ac-1e557686bff7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{143dc1c0-192f-4b62-9354-e99d14ee15ea}">
+          <x14:cfRule type="dataBar" id="{66ce2917-620f-43a3-a732-12ee9991e56d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12901,7 +12960,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{925ff35d-464a-4152-bc1e-4245330e5997}">
+          <x14:cfRule type="dataBar" id="{adb50e3c-f6ae-4b7c-a6eb-301d5cb21eb1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12915,7 +12974,7 @@
           <xm:sqref>K63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e55ecc99-61ab-4ad3-8a2a-68bcdea30102}">
+          <x14:cfRule type="dataBar" id="{d8f33d55-cab7-4966-9b4f-11c6cf30ce54}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12924,7 +12983,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{82b6a770-9d3b-425f-be5f-d884a44c240c}">
+          <x14:cfRule type="dataBar" id="{093fa95d-7ea1-499b-aa4c-8d4552a6f854}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12933,7 +12992,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e5331c35-36e8-4a81-9494-687831b019fa}">
+          <x14:cfRule type="dataBar" id="{ae009b05-b3cc-45c6-aecc-6806d6a3d632}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12944,7 +13003,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{280caff2-74f5-4b0d-a56a-0e45fb5c10d7}">
+          <x14:cfRule type="dataBar" id="{794aa47d-a3a8-46cf-a6ec-6fca7b180787}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12955,7 +13014,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2493c57f-4b7e-437e-b83e-14a67b08a919}">
+          <x14:cfRule type="dataBar" id="{34f3ae4b-9790-4e4a-af48-ca27ba3c5edc}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12966,14 +13025,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b7372b0e-0fa7-4475-a82b-730aaf412d63}">
+          <x14:cfRule type="dataBar" id="{24024d23-8b0b-4e55-ba27-b664bbb1bf49}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{bb6d9611-7406-4b71-ac03-94695ed0d5f0}">
+          <x14:cfRule type="dataBar" id="{25248efa-4a5e-46e7-b9f0-5480c4f3ba55}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12984,7 +13043,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{daf20764-0e40-4d50-8689-2f1333de3b80}">
+          <x14:cfRule type="dataBar" id="{a4ee10a4-15a0-45f2-8d78-986b10cad2b3}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12998,7 +13057,7 @@
           <xm:sqref>K64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{43a4f6d6-f04f-42e9-b90a-6eafa34a8656}">
+          <x14:cfRule type="dataBar" id="{36b79758-d424-4c7c-8b62-b6a77c5639fe}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13007,7 +13066,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f5939dd2-7152-4175-a5a6-0ea51b3bcbc4}">
+          <x14:cfRule type="dataBar" id="{c3eda83d-de89-4886-afc6-26584bc41560}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13016,7 +13075,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1e45f251-2c8f-441f-81e1-0605c88c8312}">
+          <x14:cfRule type="dataBar" id="{df185500-f7bc-44b0-a1d3-839fdb4edbe0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13027,7 +13086,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{910c0f33-467c-4749-b8bd-cb280a8ac582}">
+          <x14:cfRule type="dataBar" id="{bb695873-6942-45f5-bae3-26e29662c8d4}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -13038,7 +13097,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{57d7a39c-e066-437e-b53d-d1ac48237712}">
+          <x14:cfRule type="dataBar" id="{7881e003-60eb-423f-b6c0-7247349336df}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -13049,14 +13108,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e73bf181-0d20-487b-9eb6-22df4e5292d4}">
+          <x14:cfRule type="dataBar" id="{9c82c54a-dcb9-4291-b61e-3cec658f4612}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c11e52f1-38f2-4af0-a076-d2b17600ff6a}">
+          <x14:cfRule type="dataBar" id="{349a1dab-127c-42c2-92ea-16837ff9eb07}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13067,7 +13126,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7948c94e-f69e-4e64-b7d0-0f563212f70c}">
+          <x14:cfRule type="dataBar" id="{3c413e53-0d71-4e10-a9e4-b410c22b6cd9}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -13081,7 +13140,7 @@
           <xm:sqref>K65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0e94f7af-e845-4408-b884-01babb5df860}">
+          <x14:cfRule type="dataBar" id="{ef233290-8246-4ec6-8cda-1a218572b949}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13091,7 +13150,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{94bcd1db-88bf-42b8-837c-f8c1b7fa169e}">
+          <x14:cfRule type="dataBar" id="{8f0208a7-46a3-4db3-9ff7-e28f93388360}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13100,7 +13159,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1db48018-b53c-4ccf-8df7-c29d745d9966}">
+          <x14:cfRule type="dataBar" id="{300022d1-cef6-4094-9687-095ed68ab3f8}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13112,7 +13171,7 @@
           <xm:sqref>AB69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b8fe6fee-caee-42c1-9a92-6ef57adf7699}">
+          <x14:cfRule type="dataBar" id="{d1db28dd-edcd-47f0-a7c1-b4e614a46ea7}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13122,7 +13181,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2268fb69-e943-4688-8771-90b2d4300452}">
+          <x14:cfRule type="dataBar" id="{1665de81-b3d2-4490-822b-07eea518d43f}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13131,7 +13190,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{64afb03a-928d-43c6-8767-d87de82635e2}">
+          <x14:cfRule type="dataBar" id="{f0bcc344-c6c7-45de-82e0-60b4c5e1d231}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13143,7 +13202,7 @@
           <xm:sqref>AB103</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5f5107c4-286e-45fe-b104-cce2792a1b96}">
+          <x14:cfRule type="dataBar" id="{b0eead19-6dd5-45ee-ae32-eafe2425cbbb}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13152,7 +13211,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{45578e32-148b-44b6-9c9d-8bee23b9e3db}">
+          <x14:cfRule type="dataBar" id="{2b3d9000-8d8c-4ec8-8675-4b6bd89162e5}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13164,7 +13223,7 @@
           <xm:sqref>AB117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9ded9fd1-a30e-4067-81a0-2527a36b725d}">
+          <x14:cfRule type="dataBar" id="{4b01864b-c52e-45b4-a8e3-2436ba997e54}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13174,7 +13233,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a63f0f08-1667-4be7-b016-db2e54248f85}">
+          <x14:cfRule type="dataBar" id="{9cd56678-6b38-4b3b-b05e-6c934f380c14}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13183,7 +13242,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3094a5f2-195d-44c2-ab22-ed724d28fd48}">
+          <x14:cfRule type="dataBar" id="{751f2d08-6eea-4ff5-96ee-82e6467dccae}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13195,7 +13254,7 @@
           <xm:sqref>AB127</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{50b0b2cb-6b69-43f5-97f6-487813a6a6ff}">
+          <x14:cfRule type="dataBar" id="{930b7479-94cb-4d87-9d40-3eb7625d5cd8}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13205,7 +13264,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c3f69d74-f89b-40a3-808c-b422169ec85f}">
+          <x14:cfRule type="dataBar" id="{e49b4dce-6156-4a95-96b1-19ba268e5c19}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13214,7 +13273,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{048a0a12-faa7-442c-ab01-cffc7fb00953}">
+          <x14:cfRule type="dataBar" id="{e4a3a780-02e1-4570-b29b-ca7c3fcad664}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13226,7 +13285,7 @@
           <xm:sqref>K137</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bd4080ea-4f39-494e-ae92-b72eb777baa5}">
+          <x14:cfRule type="dataBar" id="{3bbb6730-4790-45a9-b856-1857a27b1be7}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13236,7 +13295,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{fff168ef-270e-4ebb-ad04-c451d2a788a0}">
+          <x14:cfRule type="dataBar" id="{e8f413f3-26be-4a24-bb64-2d53b70958c7}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13245,7 +13304,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{132548c4-a2ad-4fee-96ad-4e678db4a997}">
+          <x14:cfRule type="dataBar" id="{57a5fc59-29aa-4595-8b39-34815b5e407a}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13257,7 +13316,7 @@
           <xm:sqref>K142</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8a83dc2b-b030-4565-8c7c-2082312bbffa}">
+          <x14:cfRule type="dataBar" id="{6c00a001-b025-4281-8842-a12669763b0f}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13267,7 +13326,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{618224f1-8993-4438-b9a0-b730641e9be6}">
+          <x14:cfRule type="dataBar" id="{793a1e8f-49d7-4d52-8cbb-7becd8fe20e9}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13276,7 +13335,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{643645c8-0c55-4079-a596-4d26a30e0a72}">
+          <x14:cfRule type="dataBar" id="{dda2f33f-38c8-4578-9979-6de9bad79ad5}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13288,7 +13347,7 @@
           <xm:sqref>K147</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{808714b1-fcbb-4f12-98b9-8c1f05198e57}">
+          <x14:cfRule type="dataBar" id="{c18fdbd9-e05a-4ea5-996e-b2c5f72539f2}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13298,7 +13357,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{057ff636-faf5-47bd-bbf9-fe53e5c6c4fe}">
+          <x14:cfRule type="dataBar" id="{05baf66b-4558-4742-8faf-7f7f28b73da6}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13307,7 +13366,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{26c3cabb-1848-499c-b301-03e2f385070c}">
+          <x14:cfRule type="dataBar" id="{756909b9-2ab0-4860-a388-6c6b61fa1a02}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13319,7 +13378,7 @@
           <xm:sqref>K152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{fee870b3-6248-4625-9360-bc028983d9fa}">
+          <x14:cfRule type="dataBar" id="{86f8293c-9317-4649-9359-4cc5fad92480}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13328,7 +13387,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7b61ebec-519c-40e1-b40b-771cd5f5d0ed}">
+          <x14:cfRule type="dataBar" id="{3f95dd0f-a998-44b4-8b61-7eba6f123fd1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13337,7 +13396,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6c511f62-3be6-41f9-a287-435254c360b9}">
+          <x14:cfRule type="dataBar" id="{88ad5191-4a14-4fd4-85e0-f24ca51de7bc}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13348,7 +13407,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{03fe8fe4-57a7-46dd-b9ee-adad359b0361}">
+          <x14:cfRule type="dataBar" id="{83dae187-283a-48c9-9cc5-5109a406ffd9}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -13359,7 +13418,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9cc2fe4a-d406-4b26-83b2-3b6b96746d31}">
+          <x14:cfRule type="dataBar" id="{bd0b0eef-96d7-4917-a619-20b21ca0a4a3}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -13370,14 +13429,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{66ba7f92-1f43-444c-a584-e716105a9b13}">
+          <x14:cfRule type="dataBar" id="{03e41982-92da-49bb-80ce-7962d5c4ad42}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2446b1fa-793d-4932-8b0f-d4caac932e48}">
+          <x14:cfRule type="dataBar" id="{1e875aa6-f22d-48f5-978e-c49e5003f55b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13388,7 +13447,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b7c8e005-0673-46e9-b740-25fe2a239856}">
+          <x14:cfRule type="dataBar" id="{f6d22fea-02fc-4edb-a458-fbcb114ef29d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -13402,7 +13461,7 @@
           <xm:sqref>K59:K60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{00fc752f-a51a-4f9f-880c-66e2b71cb475}">
+          <x14:cfRule type="dataBar" id="{20267aae-5095-4109-a6f9-9f9274f16546}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13412,7 +13471,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{04d800a5-dbb6-4629-b328-024f72cd9d31}">
+          <x14:cfRule type="dataBar" id="{ad17ac9e-88d1-43fe-aaf4-7807489f809c}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13424,7 +13483,7 @@
           <xm:sqref>Y69:Y88</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0a1d25be-456f-4916-bec3-3c3555183f04}">
+          <x14:cfRule type="dataBar" id="{57cd3f09-10cf-4aed-97cb-6a4f98a2438c}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13437,7 +13496,7 @@
           <xm:sqref>Y79:Y88</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{18c1dd8d-68df-4b40-8511-4673843676a9}">
+          <x14:cfRule type="dataBar" id="{b8c304ab-2791-491d-aa6f-4bb2bd77c680}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13450,7 +13509,7 @@
           <xm:sqref>AB117:AB126</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{33efd8c8-9d94-403a-81ca-0b56685fda94}">
+          <x14:cfRule type="dataBar" id="{88262910-ce77-4fbd-832d-7f8b7b5fc9ae}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13462,7 +13521,7 @@
           <xm:sqref>AD58:AE59</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b1ab472e-1668-41af-9582-5161d848a33a}">
+          <x14:cfRule type="dataBar" id="{4f8ae6e5-02b8-42fe-9369-b165701c1ad9}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13474,7 +13533,7 @@
           <xm:sqref>AD62:AE65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{65888510-a5e8-45a9-8203-27351fb42e22}">
+          <x14:cfRule type="dataBar" id="{bbfea489-604d-4e79-8a83-49417788ddc9}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13484,7 +13543,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9f7169d8-5531-45b0-ba4f-41d8c2f08590}">
+          <x14:cfRule type="dataBar" id="{ce34aa40-c046-4786-9619-f29ea12945b3}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13493,7 +13552,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a65b4136-0a2d-49dc-a7e1-def6830a230d}">
+          <x14:cfRule type="dataBar" id="{6ad12ad1-d875-44a5-a6d0-a5e7fadbcbac}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13505,7 +13564,7 @@
           <xm:sqref>F69 F74 F79 F84</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0b74384e-ab59-4c49-bd63-2efdccd9a8cf}">
+          <x14:cfRule type="dataBar" id="{4f442e62-c4e1-4f33-b337-8c14914db47c}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13515,7 +13574,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{47627bef-38ab-4e19-89e6-69f5334b0f86}">
+          <x14:cfRule type="dataBar" id="{b5cb1a15-ea56-4983-8090-8e4db946d512}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13524,7 +13583,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b270289d-37fd-4335-9030-29f1fd34f883}">
+          <x14:cfRule type="dataBar" id="{f9f52792-88b1-4c2d-b674-1b0b8dbd1a73}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13536,7 +13595,7 @@
           <xm:sqref>K69 K79 K89 K103</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{56a8f6f8-fb05-457a-b81a-3dd793549c15}">
+          <x14:cfRule type="dataBar" id="{6865e71f-1372-4678-8cce-e17ab517d11e}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13546,7 +13605,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{73a0a36a-a630-4115-9410-c4814f3104be}">
+          <x14:cfRule type="dataBar" id="{055ce0b0-4c66-4356-b120-7d0a25b1fc87}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13555,7 +13614,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ed331490-d0ab-4bad-b17b-f5db4ae144e5}">
+          <x14:cfRule type="dataBar" id="{b5f46331-5e10-4cc0-841f-201cf0b486c4}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13567,7 +13626,7 @@
           <xm:sqref>AB79 AB89</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{53e4be7a-4fad-45c0-af5d-86629edc2522}">
+          <x14:cfRule type="dataBar" id="{c4ea5fcf-2f6a-4ab4-ba06-585fb607d652}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13577,7 +13636,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a067a6ca-07f7-4816-9ee5-1e00f45c5929}">
+          <x14:cfRule type="dataBar" id="{31e9d49c-f6ce-4f49-b477-1a44936a1f6c}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13586,7 +13645,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{fbd5c5df-458b-46e4-8ad8-6e5c52a2f4a5}">
+          <x14:cfRule type="dataBar" id="{c8565e67-2050-4b0b-876d-4010e8bcc8d8}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13598,7 +13657,7 @@
           <xm:sqref>F89 F96 F103 F110</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dd8e0560-423a-4c31-8656-c6a8dd6fde50}">
+          <x14:cfRule type="dataBar" id="{62321936-14a1-4e69-8f10-7ac61b7f30d4}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13608,7 +13667,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0ae66ab8-e9bb-404f-bcee-885569b0188b}">
+          <x14:cfRule type="dataBar" id="{28f239b0-e3dc-4ef3-bbdf-b844b65ed496}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13620,7 +13679,7 @@
           <xm:sqref>Y89 Y103</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ce78fbe4-ef71-4cb6-965b-28e84b9a2e60}">
+          <x14:cfRule type="dataBar" id="{76a53066-3e04-4276-b800-a8848ec00e6d}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13630,7 +13689,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{33710180-8d2f-488f-946e-38fe92e76cc4}">
+          <x14:cfRule type="dataBar" id="{8cbb2e52-3243-499c-93a4-ec7725742269}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13639,7 +13698,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8a05a893-39d2-4d03-aa9f-d12d96ee0abe}">
+          <x14:cfRule type="dataBar" id="{7bf86626-3680-4e4a-99b3-454ca1e9c002}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13651,7 +13710,7 @@
           <xm:sqref>F117 F122 F127 F132 F137 F142 F147 F152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8ec76ca4-f9d6-4e12-9c49-d7d662d51c7f}">
+          <x14:cfRule type="dataBar" id="{4f4ccb6e-2c73-4c71-88ad-902d85e15fc9}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13661,7 +13720,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{dcaafd60-e93b-4d3b-a10b-1da24f947bb5}">
+          <x14:cfRule type="dataBar" id="{0cff5f02-ccd9-4735-a6df-24ed49eefe99}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13670,7 +13729,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a760a73a-4818-494f-9502-468b45f1e8dc}">
+          <x14:cfRule type="dataBar" id="{bba238ed-154d-48f0-8ad7-cecc98338924}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13682,7 +13741,7 @@
           <xm:sqref>K117 K127</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cbc48366-b730-49f8-b9f2-6a11065ee809}">
+          <x14:cfRule type="dataBar" id="{d3778a82-1e16-4abe-b55e-8bf651109f27}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13692,7 +13751,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5aedb19b-6e0d-4c77-9de3-ca10b9ca0370}">
+          <x14:cfRule type="dataBar" id="{76c486da-4f59-40d1-96d6-ff83e1c49f8c}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13713,12 +13772,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="26.8796296296296" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.37962962962963" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.22222222222222" style="1" customWidth="1"/>
-    <col min="18" max="18" width="9.37962962962963" style="1" customWidth="1"/>
+    <col min="1" max="1" width="26.8818181818182" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.38181818181818" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.21818181818182" style="1" customWidth="1"/>
+    <col min="18" max="18" width="9.38181818181818" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">

--- a/外网端源码/其他楼交接班容量报表空模板.xlsx
+++ b/外网端源码/其他楼交接班容量报表空模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView windowHeight="22020"/>
   </bookViews>
   <sheets>
     <sheet name="本班组" sheetId="1" r:id="rId1"/>
@@ -3210,28 +3210,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AF156"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="18.1818181818182" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.1851851851852" style="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.9363636363636" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.9351851851852" style="1" customWidth="1"/>
     <col min="7" max="8" width="9" style="1" customWidth="1"/>
-    <col min="9" max="9" width="16.4090909090909" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.4074074074074" style="1" customWidth="1"/>
     <col min="10" max="11" width="9" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.9363636363636" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.9351851851852" style="1" customWidth="1"/>
     <col min="13" max="13" width="9" style="1" customWidth="1"/>
-    <col min="14" max="14" width="8.75454545454545" style="1" customWidth="1"/>
-    <col min="15" max="15" width="38.1818181818182" style="1" customWidth="1"/>
+    <col min="14" max="14" width="8.75" style="1" customWidth="1"/>
+    <col min="15" max="15" width="38.1851851851852" style="1" customWidth="1"/>
     <col min="16" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="12.5909090909091" style="1" customWidth="1"/>
-    <col min="20" max="20" width="16.5090909090909" style="1" customWidth="1"/>
+    <col min="19" max="19" width="12.5925925925926" style="1" customWidth="1"/>
+    <col min="20" max="20" width="16.5092592592593" style="1" customWidth="1"/>
     <col min="21" max="21" width="9" style="1" customWidth="1"/>
-    <col min="22" max="22" width="14.1545454545455" style="1" customWidth="1"/>
+    <col min="22" max="22" width="14.1574074074074" style="1" customWidth="1"/>
     <col min="23" max="24" width="9" style="1" customWidth="1"/>
-    <col min="25" max="25" width="10.2545454545455" style="1" customWidth="1"/>
+    <col min="25" max="25" width="10.25" style="1" customWidth="1"/>
     <col min="26" max="27" width="9" style="1" customWidth="1"/>
-    <col min="28" max="28" width="17.4181818181818" style="1" customWidth="1"/>
+    <col min="28" max="28" width="17.4166666666667" style="1" customWidth="1"/>
     <col min="31" max="31" width="11" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3960,7 +3960,7 @@
         <v>51</v>
       </c>
       <c r="V18" s="28">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="W18" s="15"/>
       <c r="X18" s="28" t="s">
@@ -6418,7 +6418,7 @@
       <c r="AD66" s="64"/>
       <c r="AE66" s="64"/>
     </row>
-    <row r="67" s="10" customFormat="1" ht="17.5" spans="1:32">
+    <row r="67" s="10" customFormat="1" ht="17.4" spans="1:32">
       <c r="A67" s="137"/>
       <c r="B67" s="138"/>
       <c r="C67" s="138"/>
@@ -11282,7 +11282,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{95fc9201-06fe-4f11-9661-a8b0a3cadc22}</x14:id>
+          <x14:id>{f7467478-75db-46bf-afdf-be375420c666}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11294,7 +11294,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{694aa617-c5ee-4c08-854e-3b8fa928d74c}</x14:id>
+          <x14:id>{2eb897e6-20f9-4722-856f-4dff413864ff}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11306,7 +11306,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{348f70ea-5a34-47b4-83aa-c924dd5dd135}</x14:id>
+          <x14:id>{a6e64cbb-1e66-4ffd-a734-571fd016c3a2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11318,7 +11318,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{228fefb1-fb1c-4e7d-8bb8-744905e05f77}</x14:id>
+          <x14:id>{404f47b3-97ab-443f-a6bb-1fd18a10d93d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11330,7 +11330,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6925e53b-fa63-4ce8-8851-49ad3d1a5949}</x14:id>
+          <x14:id>{4ebe11f1-ed1b-4373-b5f3-a497f0a12ff1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11342,7 +11342,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ecb29fc4-5b48-4c28-a973-729f594c8de5}</x14:id>
+          <x14:id>{39610c96-7906-418b-b6dc-73e105270551}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11354,7 +11354,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a4c1f7a3-b166-4740-8d08-b9f5345ec19c}</x14:id>
+          <x14:id>{a036462b-e794-4944-bd10-1aeec9e9f30a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11366,7 +11366,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d206e897-104a-4513-abff-f0acce1025c8}</x14:id>
+          <x14:id>{902e1d20-08c2-40f0-8eae-a206b1031f54}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11380,7 +11380,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6f31985e-3c1b-436c-af8c-01ba924c9ab0}</x14:id>
+          <x14:id>{00a1bf38-a469-4d5d-8a60-eb55dbe24561}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11392,7 +11392,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c367b33e-de62-4aa3-9d4d-1194922b3534}</x14:id>
+          <x14:id>{e00ca20e-0612-4220-8bbd-f524067cc40b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11404,7 +11404,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{92e8d81b-bf04-42d5-b77e-f76d6af8aa9e}</x14:id>
+          <x14:id>{92d75939-9f1f-4026-bd22-2f9f3d9796b5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11416,7 +11416,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5eb768d9-3c90-4977-9b38-b4c3728c5239}</x14:id>
+          <x14:id>{0bc05561-cb09-40a1-a70b-2aa8a22b4263}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11428,7 +11428,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bb0ec098-3d01-42bf-ae8c-cb476fd0c935}</x14:id>
+          <x14:id>{1b8fc686-c8e0-4cb9-bb4d-84b765af7de5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11440,7 +11440,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bfdc8412-5b81-4050-9a49-ae116f5b98eb}</x14:id>
+          <x14:id>{d4dfcdcd-f9eb-43d3-86c3-df948552b4a2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11452,7 +11452,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{786d20d1-44d9-426f-a86c-e513aa02d002}</x14:id>
+          <x14:id>{995e7234-bc1e-4ce6-be70-d1a53f7609b2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11464,7 +11464,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{aed3bf74-3834-4a3d-ac5b-ac85c1ec4d12}</x14:id>
+          <x14:id>{2f77c3f9-eea7-4fcd-8edf-71e7f1a34fc6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11478,7 +11478,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{eff089b4-8f2e-40ce-809f-37e2eefe47bd}</x14:id>
+          <x14:id>{b3419640-8a4c-46e2-b383-b1895ab4a1b9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11490,7 +11490,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a9639dbf-6813-4038-9a1d-ba03be45b1d1}</x14:id>
+          <x14:id>{bece8bee-8272-48f3-a967-dc0c0f6d7f44}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11502,7 +11502,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0497d441-cd0b-4dc7-94f0-48c128bbd045}</x14:id>
+          <x14:id>{7a42a03c-5f6a-40bf-b1fe-374e688701eb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11514,7 +11514,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0d8dc26e-4cd4-409b-b0f3-17f37978b019}</x14:id>
+          <x14:id>{ebbec158-2ace-40ca-a91d-0ff44512c666}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11526,7 +11526,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f8477233-8b62-480b-b933-c7513dc4d359}</x14:id>
+          <x14:id>{9e3f4808-aa37-4e31-8078-9acae67988fe}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11538,7 +11538,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9d3b67df-0f28-4af1-aa8b-cdc3f0430085}</x14:id>
+          <x14:id>{6cf9996c-203a-45b7-b917-eec38bd8b3b6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11550,7 +11550,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2b1054ad-a1d5-4fba-80af-fe4cd9cf95f2}</x14:id>
+          <x14:id>{2d951071-3705-4932-8929-cec1ac74dd8f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11562,7 +11562,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9b73bd73-52cb-4696-9671-f748dd956215}</x14:id>
+          <x14:id>{3c5fec94-750f-4044-8568-3284e7bd6720}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11576,7 +11576,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{32cc81c0-a0a9-4ee7-8764-01969bfb7053}</x14:id>
+          <x14:id>{b14b5c85-05e1-4732-be51-bab9a75ebfc5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11588,7 +11588,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8799a15d-c0cc-4807-b458-a5143074ddb1}</x14:id>
+          <x14:id>{803d70f5-6517-4a48-b9dd-bb0fd03bc5ba}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11600,7 +11600,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{aa1c943b-39e1-4d37-a139-3ee6023987dd}</x14:id>
+          <x14:id>{437af854-a673-4b9e-8669-1cd9af6607c4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11612,7 +11612,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bb4794af-55ef-4769-aacd-a007dc1b9317}</x14:id>
+          <x14:id>{0361bab4-e76a-4618-aada-d6c9ee872e72}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11624,7 +11624,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ba6cc759-24bd-4c20-a20b-3193edc9d29e}</x14:id>
+          <x14:id>{fcbfd4ea-5e47-455d-8ba5-9edc4f40593f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11636,7 +11636,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bd02d4c0-a31e-4880-81ac-1e557686bff7}</x14:id>
+          <x14:id>{16de1aaa-356f-4d6c-a8b9-70d3cbb3f462}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11648,7 +11648,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{66ce2917-620f-43a3-a732-12ee9991e56d}</x14:id>
+          <x14:id>{c7885fb4-1410-4cf5-9428-6e115d33029c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11660,7 +11660,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{adb50e3c-f6ae-4b7c-a6eb-301d5cb21eb1}</x14:id>
+          <x14:id>{be6fc46f-7260-43e4-95f3-48f9df34eb70}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11674,7 +11674,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d8f33d55-cab7-4966-9b4f-11c6cf30ce54}</x14:id>
+          <x14:id>{265b9ecc-b6c9-44f3-8786-b171dec3d60e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11686,7 +11686,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{093fa95d-7ea1-499b-aa4c-8d4552a6f854}</x14:id>
+          <x14:id>{e60ffd89-2d79-4bbd-8113-37735820dc42}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11698,7 +11698,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ae009b05-b3cc-45c6-aecc-6806d6a3d632}</x14:id>
+          <x14:id>{2b021631-93cd-4717-b45f-463a4e91cfd0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11710,7 +11710,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{794aa47d-a3a8-46cf-a6ec-6fca7b180787}</x14:id>
+          <x14:id>{a0e1f723-be38-43a3-8868-96f77e18a269}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11722,7 +11722,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{34f3ae4b-9790-4e4a-af48-ca27ba3c5edc}</x14:id>
+          <x14:id>{c279f90d-b0c7-47a8-a156-3b5e5e402c74}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11734,7 +11734,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{24024d23-8b0b-4e55-ba27-b664bbb1bf49}</x14:id>
+          <x14:id>{7e8bf0b9-b56b-4408-978e-70262b09018f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11746,7 +11746,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{25248efa-4a5e-46e7-b9f0-5480c4f3ba55}</x14:id>
+          <x14:id>{05c25bc6-ebbc-4c15-8a8d-80fe170e727f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11758,7 +11758,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a4ee10a4-15a0-45f2-8d78-986b10cad2b3}</x14:id>
+          <x14:id>{d69f8013-854e-4a74-9dd4-f335e38816fe}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11772,7 +11772,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{36b79758-d424-4c7c-8b62-b6a77c5639fe}</x14:id>
+          <x14:id>{a3eb7612-e084-42ee-b04e-d573ca01a7b5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11784,7 +11784,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c3eda83d-de89-4886-afc6-26584bc41560}</x14:id>
+          <x14:id>{5c77ef17-e09b-4837-8b5e-4f86d27ef522}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11796,7 +11796,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{df185500-f7bc-44b0-a1d3-839fdb4edbe0}</x14:id>
+          <x14:id>{97f7ebf3-0c8b-452f-a96d-e629a9363387}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11808,7 +11808,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bb695873-6942-45f5-bae3-26e29662c8d4}</x14:id>
+          <x14:id>{ecde5c31-37e2-47fb-84f1-92b21e83d1f8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11820,7 +11820,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7881e003-60eb-423f-b6c0-7247349336df}</x14:id>
+          <x14:id>{2bad34e7-80a6-4d57-9d5b-9a9316d3dff6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11832,7 +11832,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9c82c54a-dcb9-4291-b61e-3cec658f4612}</x14:id>
+          <x14:id>{dd46fbef-de39-4b4e-aa2c-bf6cd7992b1e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11844,7 +11844,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{349a1dab-127c-42c2-92ea-16837ff9eb07}</x14:id>
+          <x14:id>{fb3bd2cd-fa68-4390-a51d-1916842884b6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11856,7 +11856,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3c413e53-0d71-4e10-a9e4-b410c22b6cd9}</x14:id>
+          <x14:id>{38a0da66-3294-40d7-b7e5-e2d5167b6ce3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11870,7 +11870,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ef233290-8246-4ec6-8cda-1a218572b949}</x14:id>
+          <x14:id>{0a7912ea-8da3-4680-ac2e-00f4c381e6e3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11882,7 +11882,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8f0208a7-46a3-4db3-9ff7-e28f93388360}</x14:id>
+          <x14:id>{9cee8346-8284-4750-baa3-3e6474ab42fb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11894,7 +11894,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{300022d1-cef6-4094-9687-095ed68ab3f8}</x14:id>
+          <x14:id>{8b2fab17-929c-4c0d-96fc-484a771a0ebb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11908,7 +11908,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d1db28dd-edcd-47f0-a7c1-b4e614a46ea7}</x14:id>
+          <x14:id>{ae8c8b2d-a985-445d-bbab-625663859afb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11920,7 +11920,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1665de81-b3d2-4490-822b-07eea518d43f}</x14:id>
+          <x14:id>{a890313b-6127-407e-9d58-3cbc6629af67}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11932,7 +11932,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f0bcc344-c6c7-45de-82e0-60b4c5e1d231}</x14:id>
+          <x14:id>{1a86005f-b640-41f3-8edd-be624da44fae}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11946,7 +11946,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b0eead19-6dd5-45ee-ae32-eafe2425cbbb}</x14:id>
+          <x14:id>{b8785ba3-09b0-41fb-834c-41c2cc0d10d6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11958,7 +11958,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2b3d9000-8d8c-4ec8-8675-4b6bd89162e5}</x14:id>
+          <x14:id>{4480c6c9-f9d7-4cef-8868-4b2f5528be4b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11972,7 +11972,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4b01864b-c52e-45b4-a8e3-2436ba997e54}</x14:id>
+          <x14:id>{a82588ea-a9dc-444c-9170-995c95f5bb43}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11984,7 +11984,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9cd56678-6b38-4b3b-b05e-6c934f380c14}</x14:id>
+          <x14:id>{5ee6c5e1-d32a-4a52-8b13-3f8209ed6207}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11996,7 +11996,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{751f2d08-6eea-4ff5-96ee-82e6467dccae}</x14:id>
+          <x14:id>{98a04183-533e-432e-ba4f-373dad0d49cc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12010,7 +12010,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{930b7479-94cb-4d87-9d40-3eb7625d5cd8}</x14:id>
+          <x14:id>{72393acf-df5e-4987-8fd4-7e9dd881b216}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12022,7 +12022,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e49b4dce-6156-4a95-96b1-19ba268e5c19}</x14:id>
+          <x14:id>{7c6fae99-415d-45ab-84e6-76828260e16f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12034,7 +12034,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e4a3a780-02e1-4570-b29b-ca7c3fcad664}</x14:id>
+          <x14:id>{6683e022-0144-4145-b40d-59d1e95c1c45}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12048,7 +12048,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3bbb6730-4790-45a9-b856-1857a27b1be7}</x14:id>
+          <x14:id>{c5056656-db69-4f5e-975e-262245901acd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12060,7 +12060,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e8f413f3-26be-4a24-bb64-2d53b70958c7}</x14:id>
+          <x14:id>{3f6ae1ae-f6d7-4f66-90e8-5e24c97db127}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12072,7 +12072,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{57a5fc59-29aa-4595-8b39-34815b5e407a}</x14:id>
+          <x14:id>{c208452d-fdcc-436e-9b6c-53c14c76009c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12086,7 +12086,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6c00a001-b025-4281-8842-a12669763b0f}</x14:id>
+          <x14:id>{afb89e14-3874-434f-970a-bf4bb81f1240}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12098,7 +12098,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{793a1e8f-49d7-4d52-8cbb-7becd8fe20e9}</x14:id>
+          <x14:id>{ea932a56-63b4-4b38-87c9-d33fd1c63cdc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12110,7 +12110,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dda2f33f-38c8-4578-9979-6de9bad79ad5}</x14:id>
+          <x14:id>{938350f9-f7cf-44eb-af84-e2a58dd04105}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12124,7 +12124,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c18fdbd9-e05a-4ea5-996e-b2c5f72539f2}</x14:id>
+          <x14:id>{e432e9d7-8882-4563-9c41-ec0295d059be}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12136,7 +12136,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{05baf66b-4558-4742-8faf-7f7f28b73da6}</x14:id>
+          <x14:id>{91bd7701-5db2-41bd-94ce-9054d2b5ab34}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12148,7 +12148,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{756909b9-2ab0-4860-a388-6c6b61fa1a02}</x14:id>
+          <x14:id>{6f359c46-0755-4742-8561-4c97d8bdafff}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12162,7 +12162,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{86f8293c-9317-4649-9359-4cc5fad92480}</x14:id>
+          <x14:id>{cb8b3eee-7316-4225-9ac4-475dffe00db2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12174,7 +12174,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3f95dd0f-a998-44b4-8b61-7eba6f123fd1}</x14:id>
+          <x14:id>{58d9ca5b-8b67-4a9c-9692-e2fb2e6cdd9e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12186,7 +12186,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{88ad5191-4a14-4fd4-85e0-f24ca51de7bc}</x14:id>
+          <x14:id>{1dd2dd37-c212-41e0-a583-7ccdd798566f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12198,7 +12198,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{83dae187-283a-48c9-9cc5-5109a406ffd9}</x14:id>
+          <x14:id>{9ac998df-4eb4-46f2-ac46-c68b8611611e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12210,7 +12210,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bd0b0eef-96d7-4917-a619-20b21ca0a4a3}</x14:id>
+          <x14:id>{bd44ce8d-9b94-4ef5-9e32-9dbc1e5c3082}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12222,7 +12222,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{03e41982-92da-49bb-80ce-7962d5c4ad42}</x14:id>
+          <x14:id>{1f94ac4d-e045-40c4-98d7-895c72cb0ca2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12234,7 +12234,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1e875aa6-f22d-48f5-978e-c49e5003f55b}</x14:id>
+          <x14:id>{45a371ef-5e80-4024-adb4-36ff980da506}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12246,7 +12246,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f6d22fea-02fc-4edb-a458-fbcb114ef29d}</x14:id>
+          <x14:id>{aee30381-d6bb-49fb-a720-eed8c5b51d9a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12260,7 +12260,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{20267aae-5095-4109-a6f9-9f9274f16546}</x14:id>
+          <x14:id>{8a953f3a-91be-40f5-b891-fdbbbb895397}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12272,7 +12272,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ad17ac9e-88d1-43fe-aaf4-7807489f809c}</x14:id>
+          <x14:id>{cad354a9-f8df-4af6-ae80-a076ead269e0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12286,7 +12286,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{57cd3f09-10cf-4aed-97cb-6a4f98a2438c}</x14:id>
+          <x14:id>{ef3caea5-64e4-49fe-9b5d-1149c5c19f36}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12300,7 +12300,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b8c304ab-2791-491d-aa6f-4bb2bd77c680}</x14:id>
+          <x14:id>{cf0635dd-3d47-4562-b381-9f18165a80a7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12314,7 +12314,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{88262910-ce77-4fbd-832d-7f8b7b5fc9ae}</x14:id>
+          <x14:id>{b1b25a36-6144-4dee-bab9-b1fccc1c5335}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12328,7 +12328,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4f8ae6e5-02b8-42fe-9369-b165701c1ad9}</x14:id>
+          <x14:id>{e68d09d9-1eeb-4d4c-9165-dd4d4ad2a487}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12342,7 +12342,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bbfea489-604d-4e79-8a83-49417788ddc9}</x14:id>
+          <x14:id>{228b55a4-271c-414c-9484-dc396e872318}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12354,7 +12354,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ce34aa40-c046-4786-9619-f29ea12945b3}</x14:id>
+          <x14:id>{d7755af8-cece-4d94-bb2a-2b2f84bd0344}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12366,7 +12366,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6ad12ad1-d875-44a5-a6d0-a5e7fadbcbac}</x14:id>
+          <x14:id>{25d2afcb-88a5-4d5f-8776-ff444d0887cf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12380,7 +12380,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4f442e62-c4e1-4f33-b337-8c14914db47c}</x14:id>
+          <x14:id>{ea7c0a5a-b4f0-4d23-8f6c-fedae897ffe6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12392,7 +12392,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b5cb1a15-ea56-4983-8090-8e4db946d512}</x14:id>
+          <x14:id>{7cbd75c6-3612-475c-96b5-e3afd81def65}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12404,7 +12404,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f9f52792-88b1-4c2d-b674-1b0b8dbd1a73}</x14:id>
+          <x14:id>{8bbb846f-f4c4-4a47-86c8-11ffe8562191}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12418,7 +12418,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6865e71f-1372-4678-8cce-e17ab517d11e}</x14:id>
+          <x14:id>{158023cb-f866-4818-b105-acdd8a8bbbd5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12430,7 +12430,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{055ce0b0-4c66-4356-b120-7d0a25b1fc87}</x14:id>
+          <x14:id>{d58aff0d-44f7-4bff-aa4d-1932e7da3cc0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12442,7 +12442,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b5f46331-5e10-4cc0-841f-201cf0b486c4}</x14:id>
+          <x14:id>{7ec80741-a4ef-4d27-88c9-b8fc0133a177}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12456,7 +12456,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c4ea5fcf-2f6a-4ab4-ba06-585fb607d652}</x14:id>
+          <x14:id>{9ec2c6c0-3975-4698-a2cd-5b192d126d18}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12468,7 +12468,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{31e9d49c-f6ce-4f49-b477-1a44936a1f6c}</x14:id>
+          <x14:id>{b8a98878-1d9c-4f72-80ee-896b39115f45}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12480,7 +12480,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c8565e67-2050-4b0b-876d-4010e8bcc8d8}</x14:id>
+          <x14:id>{93c97e96-9d70-4a36-8e17-29c502ee7f23}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12494,7 +12494,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{62321936-14a1-4e69-8f10-7ac61b7f30d4}</x14:id>
+          <x14:id>{537e3c49-bfc4-4c08-b43b-0d9629113268}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12506,7 +12506,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{28f239b0-e3dc-4ef3-bbdf-b844b65ed496}</x14:id>
+          <x14:id>{18b40e02-a788-4c44-ae5b-bd2b33a5fada}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12520,7 +12520,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{76a53066-3e04-4276-b800-a8848ec00e6d}</x14:id>
+          <x14:id>{6d47d68d-2793-4477-b5b3-3db1c4fde99e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12532,7 +12532,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8cbb2e52-3243-499c-93a4-ec7725742269}</x14:id>
+          <x14:id>{b04baad5-38d9-4ff7-a560-24e3be9b6c3a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12544,7 +12544,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7bf86626-3680-4e4a-99b3-454ca1e9c002}</x14:id>
+          <x14:id>{40fd9384-ca68-4a80-bf0e-8b162113ab89}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12558,7 +12558,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4f4ccb6e-2c73-4c71-88ad-902d85e15fc9}</x14:id>
+          <x14:id>{b4d3e4b7-788c-45d4-9705-c2a548a1b553}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12570,7 +12570,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0cff5f02-ccd9-4735-a6df-24ed49eefe99}</x14:id>
+          <x14:id>{2cc5d0ea-f9b6-455e-990d-5f608bdced94}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12582,7 +12582,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bba238ed-154d-48f0-8ad7-cecc98338924}</x14:id>
+          <x14:id>{f28846bc-f528-4874-aba1-93536f3c9dbd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12596,7 +12596,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d3778a82-1e16-4abe-b55e-8bf651109f27}</x14:id>
+          <x14:id>{16455e2e-95bb-4f1e-9ad5-07cd2ea07d9d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12608,7 +12608,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{76c486da-4f59-40d1-96d6-ff83e1c49f8c}</x14:id>
+          <x14:id>{9ba09e57-7fac-4198-9606-513fdd01d6a2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12642,7 +12642,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{95fc9201-06fe-4f11-9661-a8b0a3cadc22}">
+          <x14:cfRule type="dataBar" id="{f7467478-75db-46bf-afdf-be375420c666}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12651,7 +12651,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{694aa617-c5ee-4c08-854e-3b8fa928d74c}">
+          <x14:cfRule type="dataBar" id="{2eb897e6-20f9-4722-856f-4dff413864ff}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12660,7 +12660,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{348f70ea-5a34-47b4-83aa-c924dd5dd135}">
+          <x14:cfRule type="dataBar" id="{a6e64cbb-1e66-4ffd-a734-571fd016c3a2}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12671,7 +12671,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{228fefb1-fb1c-4e7d-8bb8-744905e05f77}">
+          <x14:cfRule type="dataBar" id="{404f47b3-97ab-443f-a6bb-1fd18a10d93d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12682,7 +12682,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6925e53b-fa63-4ce8-8851-49ad3d1a5949}">
+          <x14:cfRule type="dataBar" id="{4ebe11f1-ed1b-4373-b5f3-a497f0a12ff1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12693,14 +12693,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ecb29fc4-5b48-4c28-a973-729f594c8de5}">
+          <x14:cfRule type="dataBar" id="{39610c96-7906-418b-b6dc-73e105270551}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a4c1f7a3-b166-4740-8d08-b9f5345ec19c}">
+          <x14:cfRule type="dataBar" id="{a036462b-e794-4944-bd10-1aeec9e9f30a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12711,7 +12711,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d206e897-104a-4513-abff-f0acce1025c8}">
+          <x14:cfRule type="dataBar" id="{902e1d20-08c2-40f0-8eae-a206b1031f54}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12725,7 +12725,7 @@
           <xm:sqref>AD58</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6f31985e-3c1b-436c-af8c-01ba924c9ab0}">
+          <x14:cfRule type="dataBar" id="{00a1bf38-a469-4d5d-8a60-eb55dbe24561}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12734,7 +12734,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c367b33e-de62-4aa3-9d4d-1194922b3534}">
+          <x14:cfRule type="dataBar" id="{e00ca20e-0612-4220-8bbd-f524067cc40b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12743,7 +12743,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{92e8d81b-bf04-42d5-b77e-f76d6af8aa9e}">
+          <x14:cfRule type="dataBar" id="{92d75939-9f1f-4026-bd22-2f9f3d9796b5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12754,7 +12754,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5eb768d9-3c90-4977-9b38-b4c3728c5239}">
+          <x14:cfRule type="dataBar" id="{0bc05561-cb09-40a1-a70b-2aa8a22b4263}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12765,7 +12765,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{bb0ec098-3d01-42bf-ae8c-cb476fd0c935}">
+          <x14:cfRule type="dataBar" id="{1b8fc686-c8e0-4cb9-bb4d-84b765af7de5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12776,14 +12776,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{bfdc8412-5b81-4050-9a49-ae116f5b98eb}">
+          <x14:cfRule type="dataBar" id="{d4dfcdcd-f9eb-43d3-86c3-df948552b4a2}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{786d20d1-44d9-426f-a86c-e513aa02d002}">
+          <x14:cfRule type="dataBar" id="{995e7234-bc1e-4ce6-be70-d1a53f7609b2}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12794,7 +12794,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{aed3bf74-3834-4a3d-ac5b-ac85c1ec4d12}">
+          <x14:cfRule type="dataBar" id="{2f77c3f9-eea7-4fcd-8edf-71e7f1a34fc6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12808,7 +12808,7 @@
           <xm:sqref>K62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{eff089b4-8f2e-40ce-809f-37e2eefe47bd}">
+          <x14:cfRule type="dataBar" id="{b3419640-8a4c-46e2-b383-b1895ab4a1b9}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12817,7 +12817,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a9639dbf-6813-4038-9a1d-ba03be45b1d1}">
+          <x14:cfRule type="dataBar" id="{bece8bee-8272-48f3-a967-dc0c0f6d7f44}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12826,7 +12826,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0497d441-cd0b-4dc7-94f0-48c128bbd045}">
+          <x14:cfRule type="dataBar" id="{7a42a03c-5f6a-40bf-b1fe-374e688701eb}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12837,7 +12837,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0d8dc26e-4cd4-409b-b0f3-17f37978b019}">
+          <x14:cfRule type="dataBar" id="{ebbec158-2ace-40ca-a91d-0ff44512c666}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12848,7 +12848,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f8477233-8b62-480b-b933-c7513dc4d359}">
+          <x14:cfRule type="dataBar" id="{9e3f4808-aa37-4e31-8078-9acae67988fe}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12859,14 +12859,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9d3b67df-0f28-4af1-aa8b-cdc3f0430085}">
+          <x14:cfRule type="dataBar" id="{6cf9996c-203a-45b7-b917-eec38bd8b3b6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2b1054ad-a1d5-4fba-80af-fe4cd9cf95f2}">
+          <x14:cfRule type="dataBar" id="{2d951071-3705-4932-8929-cec1ac74dd8f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12877,7 +12877,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9b73bd73-52cb-4696-9671-f748dd956215}">
+          <x14:cfRule type="dataBar" id="{3c5fec94-750f-4044-8568-3284e7bd6720}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12891,7 +12891,7 @@
           <xm:sqref>AD62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{32cc81c0-a0a9-4ee7-8764-01969bfb7053}">
+          <x14:cfRule type="dataBar" id="{b14b5c85-05e1-4732-be51-bab9a75ebfc5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12900,7 +12900,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8799a15d-c0cc-4807-b458-a5143074ddb1}">
+          <x14:cfRule type="dataBar" id="{803d70f5-6517-4a48-b9dd-bb0fd03bc5ba}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12909,7 +12909,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{aa1c943b-39e1-4d37-a139-3ee6023987dd}">
+          <x14:cfRule type="dataBar" id="{437af854-a673-4b9e-8669-1cd9af6607c4}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12920,7 +12920,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{bb4794af-55ef-4769-aacd-a007dc1b9317}">
+          <x14:cfRule type="dataBar" id="{0361bab4-e76a-4618-aada-d6c9ee872e72}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12931,7 +12931,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ba6cc759-24bd-4c20-a20b-3193edc9d29e}">
+          <x14:cfRule type="dataBar" id="{fcbfd4ea-5e47-455d-8ba5-9edc4f40593f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12942,14 +12942,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{bd02d4c0-a31e-4880-81ac-1e557686bff7}">
+          <x14:cfRule type="dataBar" id="{16de1aaa-356f-4d6c-a8b9-70d3cbb3f462}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{66ce2917-620f-43a3-a732-12ee9991e56d}">
+          <x14:cfRule type="dataBar" id="{c7885fb4-1410-4cf5-9428-6e115d33029c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12960,7 +12960,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{adb50e3c-f6ae-4b7c-a6eb-301d5cb21eb1}">
+          <x14:cfRule type="dataBar" id="{be6fc46f-7260-43e4-95f3-48f9df34eb70}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12974,7 +12974,7 @@
           <xm:sqref>K63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d8f33d55-cab7-4966-9b4f-11c6cf30ce54}">
+          <x14:cfRule type="dataBar" id="{265b9ecc-b6c9-44f3-8786-b171dec3d60e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12983,7 +12983,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{093fa95d-7ea1-499b-aa4c-8d4552a6f854}">
+          <x14:cfRule type="dataBar" id="{e60ffd89-2d79-4bbd-8113-37735820dc42}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12992,7 +12992,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ae009b05-b3cc-45c6-aecc-6806d6a3d632}">
+          <x14:cfRule type="dataBar" id="{2b021631-93cd-4717-b45f-463a4e91cfd0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13003,7 +13003,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{794aa47d-a3a8-46cf-a6ec-6fca7b180787}">
+          <x14:cfRule type="dataBar" id="{a0e1f723-be38-43a3-8868-96f77e18a269}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -13014,7 +13014,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{34f3ae4b-9790-4e4a-af48-ca27ba3c5edc}">
+          <x14:cfRule type="dataBar" id="{c279f90d-b0c7-47a8-a156-3b5e5e402c74}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -13025,14 +13025,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{24024d23-8b0b-4e55-ba27-b664bbb1bf49}">
+          <x14:cfRule type="dataBar" id="{7e8bf0b9-b56b-4408-978e-70262b09018f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{25248efa-4a5e-46e7-b9f0-5480c4f3ba55}">
+          <x14:cfRule type="dataBar" id="{05c25bc6-ebbc-4c15-8a8d-80fe170e727f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13043,7 +13043,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a4ee10a4-15a0-45f2-8d78-986b10cad2b3}">
+          <x14:cfRule type="dataBar" id="{d69f8013-854e-4a74-9dd4-f335e38816fe}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -13057,7 +13057,7 @@
           <xm:sqref>K64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{36b79758-d424-4c7c-8b62-b6a77c5639fe}">
+          <x14:cfRule type="dataBar" id="{a3eb7612-e084-42ee-b04e-d573ca01a7b5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13066,7 +13066,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c3eda83d-de89-4886-afc6-26584bc41560}">
+          <x14:cfRule type="dataBar" id="{5c77ef17-e09b-4837-8b5e-4f86d27ef522}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13075,7 +13075,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{df185500-f7bc-44b0-a1d3-839fdb4edbe0}">
+          <x14:cfRule type="dataBar" id="{97f7ebf3-0c8b-452f-a96d-e629a9363387}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13086,7 +13086,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{bb695873-6942-45f5-bae3-26e29662c8d4}">
+          <x14:cfRule type="dataBar" id="{ecde5c31-37e2-47fb-84f1-92b21e83d1f8}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -13097,7 +13097,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7881e003-60eb-423f-b6c0-7247349336df}">
+          <x14:cfRule type="dataBar" id="{2bad34e7-80a6-4d57-9d5b-9a9316d3dff6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -13108,14 +13108,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9c82c54a-dcb9-4291-b61e-3cec658f4612}">
+          <x14:cfRule type="dataBar" id="{dd46fbef-de39-4b4e-aa2c-bf6cd7992b1e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{349a1dab-127c-42c2-92ea-16837ff9eb07}">
+          <x14:cfRule type="dataBar" id="{fb3bd2cd-fa68-4390-a51d-1916842884b6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13126,7 +13126,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3c413e53-0d71-4e10-a9e4-b410c22b6cd9}">
+          <x14:cfRule type="dataBar" id="{38a0da66-3294-40d7-b7e5-e2d5167b6ce3}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -13140,7 +13140,7 @@
           <xm:sqref>K65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ef233290-8246-4ec6-8cda-1a218572b949}">
+          <x14:cfRule type="dataBar" id="{0a7912ea-8da3-4680-ac2e-00f4c381e6e3}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13150,7 +13150,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8f0208a7-46a3-4db3-9ff7-e28f93388360}">
+          <x14:cfRule type="dataBar" id="{9cee8346-8284-4750-baa3-3e6474ab42fb}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13159,7 +13159,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{300022d1-cef6-4094-9687-095ed68ab3f8}">
+          <x14:cfRule type="dataBar" id="{8b2fab17-929c-4c0d-96fc-484a771a0ebb}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13171,7 +13171,7 @@
           <xm:sqref>AB69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d1db28dd-edcd-47f0-a7c1-b4e614a46ea7}">
+          <x14:cfRule type="dataBar" id="{ae8c8b2d-a985-445d-bbab-625663859afb}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13181,7 +13181,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1665de81-b3d2-4490-822b-07eea518d43f}">
+          <x14:cfRule type="dataBar" id="{a890313b-6127-407e-9d58-3cbc6629af67}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13190,7 +13190,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f0bcc344-c6c7-45de-82e0-60b4c5e1d231}">
+          <x14:cfRule type="dataBar" id="{1a86005f-b640-41f3-8edd-be624da44fae}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13202,7 +13202,7 @@
           <xm:sqref>AB103</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b0eead19-6dd5-45ee-ae32-eafe2425cbbb}">
+          <x14:cfRule type="dataBar" id="{b8785ba3-09b0-41fb-834c-41c2cc0d10d6}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13211,7 +13211,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2b3d9000-8d8c-4ec8-8675-4b6bd89162e5}">
+          <x14:cfRule type="dataBar" id="{4480c6c9-f9d7-4cef-8868-4b2f5528be4b}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13223,7 +13223,7 @@
           <xm:sqref>AB117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4b01864b-c52e-45b4-a8e3-2436ba997e54}">
+          <x14:cfRule type="dataBar" id="{a82588ea-a9dc-444c-9170-995c95f5bb43}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13233,7 +13233,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9cd56678-6b38-4b3b-b05e-6c934f380c14}">
+          <x14:cfRule type="dataBar" id="{5ee6c5e1-d32a-4a52-8b13-3f8209ed6207}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13242,7 +13242,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{751f2d08-6eea-4ff5-96ee-82e6467dccae}">
+          <x14:cfRule type="dataBar" id="{98a04183-533e-432e-ba4f-373dad0d49cc}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13254,7 +13254,7 @@
           <xm:sqref>AB127</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{930b7479-94cb-4d87-9d40-3eb7625d5cd8}">
+          <x14:cfRule type="dataBar" id="{72393acf-df5e-4987-8fd4-7e9dd881b216}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13264,7 +13264,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e49b4dce-6156-4a95-96b1-19ba268e5c19}">
+          <x14:cfRule type="dataBar" id="{7c6fae99-415d-45ab-84e6-76828260e16f}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13273,7 +13273,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e4a3a780-02e1-4570-b29b-ca7c3fcad664}">
+          <x14:cfRule type="dataBar" id="{6683e022-0144-4145-b40d-59d1e95c1c45}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13285,7 +13285,7 @@
           <xm:sqref>K137</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3bbb6730-4790-45a9-b856-1857a27b1be7}">
+          <x14:cfRule type="dataBar" id="{c5056656-db69-4f5e-975e-262245901acd}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13295,7 +13295,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e8f413f3-26be-4a24-bb64-2d53b70958c7}">
+          <x14:cfRule type="dataBar" id="{3f6ae1ae-f6d7-4f66-90e8-5e24c97db127}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13304,7 +13304,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{57a5fc59-29aa-4595-8b39-34815b5e407a}">
+          <x14:cfRule type="dataBar" id="{c208452d-fdcc-436e-9b6c-53c14c76009c}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13316,7 +13316,7 @@
           <xm:sqref>K142</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6c00a001-b025-4281-8842-a12669763b0f}">
+          <x14:cfRule type="dataBar" id="{afb89e14-3874-434f-970a-bf4bb81f1240}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13326,7 +13326,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{793a1e8f-49d7-4d52-8cbb-7becd8fe20e9}">
+          <x14:cfRule type="dataBar" id="{ea932a56-63b4-4b38-87c9-d33fd1c63cdc}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13335,7 +13335,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{dda2f33f-38c8-4578-9979-6de9bad79ad5}">
+          <x14:cfRule type="dataBar" id="{938350f9-f7cf-44eb-af84-e2a58dd04105}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13347,7 +13347,7 @@
           <xm:sqref>K147</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c18fdbd9-e05a-4ea5-996e-b2c5f72539f2}">
+          <x14:cfRule type="dataBar" id="{e432e9d7-8882-4563-9c41-ec0295d059be}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13357,7 +13357,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{05baf66b-4558-4742-8faf-7f7f28b73da6}">
+          <x14:cfRule type="dataBar" id="{91bd7701-5db2-41bd-94ce-9054d2b5ab34}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13366,7 +13366,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{756909b9-2ab0-4860-a388-6c6b61fa1a02}">
+          <x14:cfRule type="dataBar" id="{6f359c46-0755-4742-8561-4c97d8bdafff}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13378,7 +13378,7 @@
           <xm:sqref>K152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{86f8293c-9317-4649-9359-4cc5fad92480}">
+          <x14:cfRule type="dataBar" id="{cb8b3eee-7316-4225-9ac4-475dffe00db2}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13387,7 +13387,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3f95dd0f-a998-44b4-8b61-7eba6f123fd1}">
+          <x14:cfRule type="dataBar" id="{58d9ca5b-8b67-4a9c-9692-e2fb2e6cdd9e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13396,7 +13396,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{88ad5191-4a14-4fd4-85e0-f24ca51de7bc}">
+          <x14:cfRule type="dataBar" id="{1dd2dd37-c212-41e0-a583-7ccdd798566f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13407,7 +13407,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{83dae187-283a-48c9-9cc5-5109a406ffd9}">
+          <x14:cfRule type="dataBar" id="{9ac998df-4eb4-46f2-ac46-c68b8611611e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -13418,7 +13418,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{bd0b0eef-96d7-4917-a619-20b21ca0a4a3}">
+          <x14:cfRule type="dataBar" id="{bd44ce8d-9b94-4ef5-9e32-9dbc1e5c3082}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -13429,14 +13429,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{03e41982-92da-49bb-80ce-7962d5c4ad42}">
+          <x14:cfRule type="dataBar" id="{1f94ac4d-e045-40c4-98d7-895c72cb0ca2}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1e875aa6-f22d-48f5-978e-c49e5003f55b}">
+          <x14:cfRule type="dataBar" id="{45a371ef-5e80-4024-adb4-36ff980da506}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13447,7 +13447,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f6d22fea-02fc-4edb-a458-fbcb114ef29d}">
+          <x14:cfRule type="dataBar" id="{aee30381-d6bb-49fb-a720-eed8c5b51d9a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -13461,7 +13461,7 @@
           <xm:sqref>K59:K60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{20267aae-5095-4109-a6f9-9f9274f16546}">
+          <x14:cfRule type="dataBar" id="{8a953f3a-91be-40f5-b891-fdbbbb895397}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13471,7 +13471,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ad17ac9e-88d1-43fe-aaf4-7807489f809c}">
+          <x14:cfRule type="dataBar" id="{cad354a9-f8df-4af6-ae80-a076ead269e0}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13483,7 +13483,7 @@
           <xm:sqref>Y69:Y88</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{57cd3f09-10cf-4aed-97cb-6a4f98a2438c}">
+          <x14:cfRule type="dataBar" id="{ef3caea5-64e4-49fe-9b5d-1149c5c19f36}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13496,7 +13496,7 @@
           <xm:sqref>Y79:Y88</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b8c304ab-2791-491d-aa6f-4bb2bd77c680}">
+          <x14:cfRule type="dataBar" id="{cf0635dd-3d47-4562-b381-9f18165a80a7}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13509,7 +13509,7 @@
           <xm:sqref>AB117:AB126</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{88262910-ce77-4fbd-832d-7f8b7b5fc9ae}">
+          <x14:cfRule type="dataBar" id="{b1b25a36-6144-4dee-bab9-b1fccc1c5335}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13521,7 +13521,7 @@
           <xm:sqref>AD58:AE59</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4f8ae6e5-02b8-42fe-9369-b165701c1ad9}">
+          <x14:cfRule type="dataBar" id="{e68d09d9-1eeb-4d4c-9165-dd4d4ad2a487}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13533,7 +13533,7 @@
           <xm:sqref>AD62:AE65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{bbfea489-604d-4e79-8a83-49417788ddc9}">
+          <x14:cfRule type="dataBar" id="{228b55a4-271c-414c-9484-dc396e872318}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13543,7 +13543,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ce34aa40-c046-4786-9619-f29ea12945b3}">
+          <x14:cfRule type="dataBar" id="{d7755af8-cece-4d94-bb2a-2b2f84bd0344}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13552,7 +13552,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6ad12ad1-d875-44a5-a6d0-a5e7fadbcbac}">
+          <x14:cfRule type="dataBar" id="{25d2afcb-88a5-4d5f-8776-ff444d0887cf}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13564,7 +13564,7 @@
           <xm:sqref>F69 F74 F79 F84</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4f442e62-c4e1-4f33-b337-8c14914db47c}">
+          <x14:cfRule type="dataBar" id="{ea7c0a5a-b4f0-4d23-8f6c-fedae897ffe6}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13574,7 +13574,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b5cb1a15-ea56-4983-8090-8e4db946d512}">
+          <x14:cfRule type="dataBar" id="{7cbd75c6-3612-475c-96b5-e3afd81def65}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13583,7 +13583,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f9f52792-88b1-4c2d-b674-1b0b8dbd1a73}">
+          <x14:cfRule type="dataBar" id="{8bbb846f-f4c4-4a47-86c8-11ffe8562191}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13595,7 +13595,7 @@
           <xm:sqref>K69 K79 K89 K103</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6865e71f-1372-4678-8cce-e17ab517d11e}">
+          <x14:cfRule type="dataBar" id="{158023cb-f866-4818-b105-acdd8a8bbbd5}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13605,7 +13605,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{055ce0b0-4c66-4356-b120-7d0a25b1fc87}">
+          <x14:cfRule type="dataBar" id="{d58aff0d-44f7-4bff-aa4d-1932e7da3cc0}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13614,7 +13614,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b5f46331-5e10-4cc0-841f-201cf0b486c4}">
+          <x14:cfRule type="dataBar" id="{7ec80741-a4ef-4d27-88c9-b8fc0133a177}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13626,7 +13626,7 @@
           <xm:sqref>AB79 AB89</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c4ea5fcf-2f6a-4ab4-ba06-585fb607d652}">
+          <x14:cfRule type="dataBar" id="{9ec2c6c0-3975-4698-a2cd-5b192d126d18}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13636,7 +13636,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{31e9d49c-f6ce-4f49-b477-1a44936a1f6c}">
+          <x14:cfRule type="dataBar" id="{b8a98878-1d9c-4f72-80ee-896b39115f45}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13645,7 +13645,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c8565e67-2050-4b0b-876d-4010e8bcc8d8}">
+          <x14:cfRule type="dataBar" id="{93c97e96-9d70-4a36-8e17-29c502ee7f23}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13657,7 +13657,7 @@
           <xm:sqref>F89 F96 F103 F110</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{62321936-14a1-4e69-8f10-7ac61b7f30d4}">
+          <x14:cfRule type="dataBar" id="{537e3c49-bfc4-4c08-b43b-0d9629113268}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13667,7 +13667,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{28f239b0-e3dc-4ef3-bbdf-b844b65ed496}">
+          <x14:cfRule type="dataBar" id="{18b40e02-a788-4c44-ae5b-bd2b33a5fada}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13679,7 +13679,7 @@
           <xm:sqref>Y89 Y103</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{76a53066-3e04-4276-b800-a8848ec00e6d}">
+          <x14:cfRule type="dataBar" id="{6d47d68d-2793-4477-b5b3-3db1c4fde99e}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13689,7 +13689,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8cbb2e52-3243-499c-93a4-ec7725742269}">
+          <x14:cfRule type="dataBar" id="{b04baad5-38d9-4ff7-a560-24e3be9b6c3a}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13698,7 +13698,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7bf86626-3680-4e4a-99b3-454ca1e9c002}">
+          <x14:cfRule type="dataBar" id="{40fd9384-ca68-4a80-bf0e-8b162113ab89}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13710,7 +13710,7 @@
           <xm:sqref>F117 F122 F127 F132 F137 F142 F147 F152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{4f4ccb6e-2c73-4c71-88ad-902d85e15fc9}">
+          <x14:cfRule type="dataBar" id="{b4d3e4b7-788c-45d4-9705-c2a548a1b553}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13720,7 +13720,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0cff5f02-ccd9-4735-a6df-24ed49eefe99}">
+          <x14:cfRule type="dataBar" id="{2cc5d0ea-f9b6-455e-990d-5f608bdced94}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13729,7 +13729,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{bba238ed-154d-48f0-8ad7-cecc98338924}">
+          <x14:cfRule type="dataBar" id="{f28846bc-f528-4874-aba1-93536f3c9dbd}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13741,7 +13741,7 @@
           <xm:sqref>K117 K127</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d3778a82-1e16-4abe-b55e-8bf651109f27}">
+          <x14:cfRule type="dataBar" id="{16455e2e-95bb-4f1e-9ad5-07cd2ea07d9d}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13751,7 +13751,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{76c486da-4f59-40d1-96d6-ff83e1c49f8c}">
+          <x14:cfRule type="dataBar" id="{9ba09e57-7fac-4198-9606-513fdd01d6a2}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13772,12 +13772,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="26.8818181818182" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.38181818181818" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.21818181818182" style="1" customWidth="1"/>
-    <col min="18" max="18" width="9.38181818181818" style="1" customWidth="1"/>
+    <col min="1" max="1" width="26.8796296296296" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.37962962962963" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.22222222222222" style="1" customWidth="1"/>
+    <col min="18" max="18" width="9.37962962962963" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">

--- a/外网端源码/其他楼交接班容量报表空模板.xlsx
+++ b/外网端源码/其他楼交接班容量报表空模板.xlsx
@@ -682,27 +682,27 @@
     <t>-202-RPP-DC-1</t>
   </si>
   <si>
+    <t>-245-HVDC-121</t>
+  </si>
+  <si>
+    <t>-202-RPP-DC-3</t>
+  </si>
+  <si>
+    <t>-245-HVDC-131</t>
+  </si>
+  <si>
+    <t>-202-RPP-DC-5</t>
+  </si>
+  <si>
+    <t>-245-HVDC-141</t>
+  </si>
+  <si>
+    <t>-202-RPP-DC-7</t>
+  </si>
+  <si>
     <t>南侧</t>
   </si>
   <si>
-    <t>-245-HVDC-121</t>
-  </si>
-  <si>
-    <t>-202-RPP-DC-3</t>
-  </si>
-  <si>
-    <t>-245-HVDC-131</t>
-  </si>
-  <si>
-    <t>-202-RPP-DC-5</t>
-  </si>
-  <si>
-    <t>-245-HVDC-141</t>
-  </si>
-  <si>
-    <t>-202-RPP-DC-7</t>
-  </si>
-  <si>
     <t xml:space="preserve"> -245-HVDC-151</t>
   </si>
   <si>
@@ -718,25 +718,25 @@
     <t>-202-RPP-DC-2</t>
   </si>
   <si>
+    <t xml:space="preserve"> -245-HVDC-221</t>
+  </si>
+  <si>
+    <t>-202-RPP-DC-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -245-HVDC-231</t>
+  </si>
+  <si>
+    <t>-202-RPP-DC-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -245-HVDC-241</t>
+  </si>
+  <si>
+    <t>-202-RPP-DC-8</t>
+  </si>
+  <si>
     <t>北侧</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -245-HVDC-221</t>
-  </si>
-  <si>
-    <t>-202-RPP-DC-4</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -245-HVDC-231</t>
-  </si>
-  <si>
-    <t>-202-RPP-DC-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -245-HVDC-241</t>
-  </si>
-  <si>
-    <t>-202-RPP-DC-8</t>
   </si>
   <si>
     <t xml:space="preserve"> -245-HVDC-251</t>
@@ -6621,9 +6621,7 @@
         <f>20-AC69</f>
         <v>20</v>
       </c>
-      <c r="AE69" s="153" t="s">
-        <v>199</v>
-      </c>
+      <c r="AE69" s="153"/>
       <c r="AF69" s="154"/>
     </row>
     <row r="70" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -6642,13 +6640,13 @@
       <c r="M70" s="144"/>
       <c r="N70" s="144"/>
       <c r="O70" s="147" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P70" s="144"/>
       <c r="Q70" s="144"/>
       <c r="R70" s="148"/>
       <c r="S70" s="149" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="T70" s="149"/>
       <c r="U70" s="144">
@@ -6686,13 +6684,13 @@
       <c r="M71" s="144"/>
       <c r="N71" s="144"/>
       <c r="O71" s="147" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P71" s="144"/>
       <c r="Q71" s="144"/>
       <c r="R71" s="148"/>
       <c r="S71" s="149" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="T71" s="149"/>
       <c r="U71" s="144">
@@ -6730,13 +6728,13 @@
       <c r="M72" s="144"/>
       <c r="N72" s="144"/>
       <c r="O72" s="147" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="P72" s="144"/>
       <c r="Q72" s="144"/>
       <c r="R72" s="148"/>
       <c r="S72" s="149" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="T72" s="149"/>
       <c r="U72" s="144">
@@ -6755,7 +6753,9 @@
       <c r="AB72" s="145"/>
       <c r="AC72" s="152"/>
       <c r="AD72" s="152"/>
-      <c r="AE72" s="153"/>
+      <c r="AE72" s="153" t="s">
+        <v>205</v>
+      </c>
       <c r="AF72" s="154"/>
     </row>
     <row r="73" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -6852,9 +6852,7 @@
       <c r="AB74" s="145"/>
       <c r="AC74" s="152"/>
       <c r="AD74" s="152"/>
-      <c r="AE74" s="153" t="s">
-        <v>211</v>
-      </c>
+      <c r="AE74" s="153"/>
       <c r="AF74" s="154"/>
     </row>
     <row r="75" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -6873,13 +6871,13 @@
       <c r="M75" s="144"/>
       <c r="N75" s="144"/>
       <c r="O75" s="147" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P75" s="144"/>
       <c r="Q75" s="144"/>
       <c r="R75" s="148"/>
       <c r="S75" s="149" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="T75" s="149"/>
       <c r="U75" s="144">
@@ -6917,13 +6915,13 @@
       <c r="M76" s="144"/>
       <c r="N76" s="144"/>
       <c r="O76" s="147" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P76" s="144"/>
       <c r="Q76" s="144"/>
       <c r="R76" s="148"/>
       <c r="S76" s="149" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="T76" s="149"/>
       <c r="U76" s="144">
@@ -6961,13 +6959,13 @@
       <c r="M77" s="144"/>
       <c r="N77" s="144"/>
       <c r="O77" s="147" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P77" s="144"/>
       <c r="Q77" s="144"/>
       <c r="R77" s="148"/>
       <c r="S77" s="149" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="T77" s="149"/>
       <c r="U77" s="144">
@@ -6986,7 +6984,9 @@
       <c r="AB77" s="145"/>
       <c r="AC77" s="152"/>
       <c r="AD77" s="152"/>
-      <c r="AE77" s="153"/>
+      <c r="AE77" s="153" t="s">
+        <v>217</v>
+      </c>
       <c r="AF77" s="154"/>
     </row>
     <row r="78" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -7112,9 +7112,7 @@
         <f>20-AC79</f>
         <v>20</v>
       </c>
-      <c r="AE79" s="153" t="s">
-        <v>199</v>
-      </c>
+      <c r="AE79" s="153"/>
       <c r="AF79" s="154"/>
     </row>
     <row r="80" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -7246,7 +7244,9 @@
       <c r="AB82" s="145"/>
       <c r="AC82" s="144"/>
       <c r="AD82" s="152"/>
-      <c r="AE82" s="153"/>
+      <c r="AE82" s="153" t="s">
+        <v>205</v>
+      </c>
       <c r="AF82" s="154"/>
     </row>
     <row r="83" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -7343,9 +7343,7 @@
       <c r="AB84" s="145"/>
       <c r="AC84" s="144"/>
       <c r="AD84" s="152"/>
-      <c r="AE84" s="153" t="s">
-        <v>211</v>
-      </c>
+      <c r="AE84" s="153"/>
       <c r="AF84" s="154"/>
     </row>
     <row r="85" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -7477,7 +7475,9 @@
       <c r="AB87" s="145"/>
       <c r="AC87" s="144"/>
       <c r="AD87" s="152"/>
-      <c r="AE87" s="153"/>
+      <c r="AE87" s="153" t="s">
+        <v>217</v>
+      </c>
       <c r="AF87" s="154"/>
     </row>
     <row r="88" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -7603,9 +7603,7 @@
         <f>20-AC89</f>
         <v>20</v>
       </c>
-      <c r="AE89" s="153" t="s">
-        <v>199</v>
-      </c>
+      <c r="AE89" s="153"/>
       <c r="AF89" s="154"/>
     </row>
     <row r="90" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -7781,7 +7779,9 @@
       <c r="AB93" s="145"/>
       <c r="AC93" s="144"/>
       <c r="AD93" s="152"/>
-      <c r="AE93" s="153"/>
+      <c r="AE93" s="153" t="s">
+        <v>205</v>
+      </c>
       <c r="AF93" s="154"/>
     </row>
     <row r="94" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -7922,9 +7922,7 @@
       <c r="AB96" s="145"/>
       <c r="AC96" s="144"/>
       <c r="AD96" s="152"/>
-      <c r="AE96" s="153" t="s">
-        <v>211</v>
-      </c>
+      <c r="AE96" s="153"/>
       <c r="AF96" s="154"/>
     </row>
     <row r="97" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -8100,7 +8098,9 @@
       <c r="AB100" s="145"/>
       <c r="AC100" s="144"/>
       <c r="AD100" s="152"/>
-      <c r="AE100" s="153"/>
+      <c r="AE100" s="153" t="s">
+        <v>217</v>
+      </c>
       <c r="AF100" s="154"/>
     </row>
     <row r="101" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -8270,9 +8270,7 @@
         <f>20-AC103</f>
         <v>20</v>
       </c>
-      <c r="AE103" s="153" t="s">
-        <v>199</v>
-      </c>
+      <c r="AE103" s="153"/>
       <c r="AF103" s="154"/>
     </row>
     <row r="104" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -8448,7 +8446,9 @@
       <c r="AB107" s="145"/>
       <c r="AC107" s="144"/>
       <c r="AD107" s="152"/>
-      <c r="AE107" s="153"/>
+      <c r="AE107" s="153" t="s">
+        <v>205</v>
+      </c>
       <c r="AF107" s="154"/>
     </row>
     <row r="108" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -8589,9 +8589,7 @@
       <c r="AB110" s="145"/>
       <c r="AC110" s="144"/>
       <c r="AD110" s="152"/>
-      <c r="AE110" s="153" t="s">
-        <v>211</v>
-      </c>
+      <c r="AE110" s="153"/>
       <c r="AF110" s="154"/>
     </row>
     <row r="111" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -8767,7 +8765,9 @@
       <c r="AB114" s="145"/>
       <c r="AC114" s="144"/>
       <c r="AD114" s="152"/>
-      <c r="AE114" s="153"/>
+      <c r="AE114" s="153" t="s">
+        <v>217</v>
+      </c>
       <c r="AF114" s="154"/>
     </row>
     <row r="115" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -8937,9 +8937,7 @@
         <f>20-AC117</f>
         <v>20</v>
       </c>
-      <c r="AE117" s="153" t="s">
-        <v>199</v>
-      </c>
+      <c r="AE117" s="153"/>
       <c r="AF117" s="154"/>
     </row>
     <row r="118" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -9071,7 +9069,9 @@
       <c r="AB120" s="145"/>
       <c r="AC120" s="144"/>
       <c r="AD120" s="152"/>
-      <c r="AE120" s="153"/>
+      <c r="AE120" s="153" t="s">
+        <v>205</v>
+      </c>
       <c r="AF120" s="154"/>
     </row>
     <row r="121" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -9168,9 +9168,7 @@
       <c r="AB122" s="145"/>
       <c r="AC122" s="144"/>
       <c r="AD122" s="152"/>
-      <c r="AE122" s="153" t="s">
-        <v>211</v>
-      </c>
+      <c r="AE122" s="153"/>
       <c r="AF122" s="154"/>
     </row>
     <row r="123" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -9302,7 +9300,9 @@
       <c r="AB125" s="145"/>
       <c r="AC125" s="144"/>
       <c r="AD125" s="152"/>
-      <c r="AE125" s="153"/>
+      <c r="AE125" s="153" t="s">
+        <v>217</v>
+      </c>
       <c r="AF125" s="154"/>
     </row>
     <row r="126" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -9428,9 +9428,7 @@
         <f>20-AC127</f>
         <v>20</v>
       </c>
-      <c r="AE127" s="153" t="s">
-        <v>199</v>
-      </c>
+      <c r="AE127" s="153"/>
       <c r="AF127" s="154"/>
     </row>
     <row r="128" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -9562,7 +9560,9 @@
       <c r="AB130" s="145"/>
       <c r="AC130" s="144"/>
       <c r="AD130" s="152"/>
-      <c r="AE130" s="153"/>
+      <c r="AE130" s="153" t="s">
+        <v>205</v>
+      </c>
       <c r="AF130" s="154"/>
     </row>
     <row r="131" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -9659,9 +9659,7 @@
       <c r="AB132" s="145"/>
       <c r="AC132" s="144"/>
       <c r="AD132" s="152"/>
-      <c r="AE132" s="153" t="s">
-        <v>211</v>
-      </c>
+      <c r="AE132" s="153"/>
       <c r="AF132" s="154"/>
     </row>
     <row r="133" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -9793,7 +9791,9 @@
       <c r="AB135" s="145"/>
       <c r="AC135" s="144"/>
       <c r="AD135" s="152"/>
-      <c r="AE135" s="153"/>
+      <c r="AE135" s="153" t="s">
+        <v>217</v>
+      </c>
       <c r="AF135" s="154"/>
     </row>
     <row r="136" s="10" customFormat="1" ht="14.15" customHeight="1" spans="1:32">
@@ -11282,7 +11282,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f7467478-75db-46bf-afdf-be375420c666}</x14:id>
+          <x14:id>{e527788e-4040-4eb9-b240-f64dca916c9a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11294,7 +11294,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2eb897e6-20f9-4722-856f-4dff413864ff}</x14:id>
+          <x14:id>{beb46d76-ffa3-424d-a154-d2f9fe58e590}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11306,7 +11306,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a6e64cbb-1e66-4ffd-a734-571fd016c3a2}</x14:id>
+          <x14:id>{5e2222b2-7c8d-446b-9c5a-0005acebdbe6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11318,7 +11318,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{404f47b3-97ab-443f-a6bb-1fd18a10d93d}</x14:id>
+          <x14:id>{843b83e2-d06f-46c8-8521-22d0a4051257}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11330,7 +11330,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4ebe11f1-ed1b-4373-b5f3-a497f0a12ff1}</x14:id>
+          <x14:id>{795d8539-b6cd-468f-86b0-6fe17d6195de}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11342,7 +11342,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{39610c96-7906-418b-b6dc-73e105270551}</x14:id>
+          <x14:id>{90020398-bdc5-46de-bafa-f85ed17ae972}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11354,7 +11354,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a036462b-e794-4944-bd10-1aeec9e9f30a}</x14:id>
+          <x14:id>{69967096-2317-45f7-8247-151340b0dfec}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11366,7 +11366,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{902e1d20-08c2-40f0-8eae-a206b1031f54}</x14:id>
+          <x14:id>{a4a32341-a597-4648-87e3-dcb1001aea70}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11380,7 +11380,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{00a1bf38-a469-4d5d-8a60-eb55dbe24561}</x14:id>
+          <x14:id>{27babd0b-79d1-4a92-bb2d-4cd4138aec80}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11392,7 +11392,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e00ca20e-0612-4220-8bbd-f524067cc40b}</x14:id>
+          <x14:id>{5923fcbf-b963-4847-a08c-fd3471f7c77b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11404,7 +11404,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{92d75939-9f1f-4026-bd22-2f9f3d9796b5}</x14:id>
+          <x14:id>{8f9dacb1-9704-44d6-8586-53f712945d35}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11416,7 +11416,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0bc05561-cb09-40a1-a70b-2aa8a22b4263}</x14:id>
+          <x14:id>{974e5550-2954-4f71-a0c8-9496f388ff47}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11428,7 +11428,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1b8fc686-c8e0-4cb9-bb4d-84b765af7de5}</x14:id>
+          <x14:id>{9f27453e-b038-488c-9239-fe35eea01dfb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11440,7 +11440,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d4dfcdcd-f9eb-43d3-86c3-df948552b4a2}</x14:id>
+          <x14:id>{541529e2-6d51-4232-b980-393f4d8a3724}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11452,7 +11452,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{995e7234-bc1e-4ce6-be70-d1a53f7609b2}</x14:id>
+          <x14:id>{594967a8-b30d-4a5b-aca4-9414a7e0aa24}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11464,7 +11464,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2f77c3f9-eea7-4fcd-8edf-71e7f1a34fc6}</x14:id>
+          <x14:id>{6903b435-54f0-4dc6-b8e6-a10860f67f4a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11478,7 +11478,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b3419640-8a4c-46e2-b383-b1895ab4a1b9}</x14:id>
+          <x14:id>{40c7af34-8452-4b7b-83cd-506ff67a80d6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11490,7 +11490,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bece8bee-8272-48f3-a967-dc0c0f6d7f44}</x14:id>
+          <x14:id>{8d07e276-1a63-4ae2-9150-1aecf0a07f3a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11502,7 +11502,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7a42a03c-5f6a-40bf-b1fe-374e688701eb}</x14:id>
+          <x14:id>{4aa53087-d18d-48da-9408-4291d57be9c2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11514,7 +11514,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ebbec158-2ace-40ca-a91d-0ff44512c666}</x14:id>
+          <x14:id>{e8d0d274-e4d8-4cc2-a473-17b516f42649}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11526,7 +11526,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9e3f4808-aa37-4e31-8078-9acae67988fe}</x14:id>
+          <x14:id>{57f53829-dcd1-494c-8ca1-2b193d3d6f35}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11538,7 +11538,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6cf9996c-203a-45b7-b917-eec38bd8b3b6}</x14:id>
+          <x14:id>{3a0b7942-7e86-41b7-b33c-7a70035147f3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11550,7 +11550,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2d951071-3705-4932-8929-cec1ac74dd8f}</x14:id>
+          <x14:id>{602930ad-9409-4489-a65e-cdecd16a61fb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11562,7 +11562,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3c5fec94-750f-4044-8568-3284e7bd6720}</x14:id>
+          <x14:id>{a944e513-65a5-44fd-89c0-8ac02931c187}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11576,7 +11576,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b14b5c85-05e1-4732-be51-bab9a75ebfc5}</x14:id>
+          <x14:id>{2984bd09-c6f4-4de8-8394-93dd1521da18}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11588,7 +11588,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{803d70f5-6517-4a48-b9dd-bb0fd03bc5ba}</x14:id>
+          <x14:id>{d5240306-e489-4d87-a552-0177c90359bc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11600,7 +11600,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{437af854-a673-4b9e-8669-1cd9af6607c4}</x14:id>
+          <x14:id>{341f6cba-74dd-4739-aa80-56d22f3e852a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11612,7 +11612,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0361bab4-e76a-4618-aada-d6c9ee872e72}</x14:id>
+          <x14:id>{916cdaa0-734d-4d5e-97cb-9e01ed78f6fc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11624,7 +11624,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fcbfd4ea-5e47-455d-8ba5-9edc4f40593f}</x14:id>
+          <x14:id>{056de079-a96d-4d7d-b010-b49eb8b9c5df}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11636,7 +11636,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{16de1aaa-356f-4d6c-a8b9-70d3cbb3f462}</x14:id>
+          <x14:id>{106b117f-8bcf-443f-9be7-248805547be1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11648,7 +11648,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c7885fb4-1410-4cf5-9428-6e115d33029c}</x14:id>
+          <x14:id>{27993b30-86e6-4273-91ab-16628e8c64d0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11660,7 +11660,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{be6fc46f-7260-43e4-95f3-48f9df34eb70}</x14:id>
+          <x14:id>{7241de54-30de-4b00-9707-6edc6bfb121b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11674,7 +11674,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{265b9ecc-b6c9-44f3-8786-b171dec3d60e}</x14:id>
+          <x14:id>{d167434e-8398-41ca-905a-9661763b52de}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11686,7 +11686,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e60ffd89-2d79-4bbd-8113-37735820dc42}</x14:id>
+          <x14:id>{ddcda096-13b1-4ce8-ad67-f1d245a2ebb7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11698,7 +11698,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2b021631-93cd-4717-b45f-463a4e91cfd0}</x14:id>
+          <x14:id>{c55bc5cc-e67c-40f6-94ad-911db305c815}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11710,7 +11710,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a0e1f723-be38-43a3-8868-96f77e18a269}</x14:id>
+          <x14:id>{b60ead94-5a05-4712-baea-12a6592738b9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11722,7 +11722,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c279f90d-b0c7-47a8-a156-3b5e5e402c74}</x14:id>
+          <x14:id>{9261e741-e472-460b-b605-6371c27bf379}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11734,7 +11734,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7e8bf0b9-b56b-4408-978e-70262b09018f}</x14:id>
+          <x14:id>{5c07fc3d-400f-4155-8b5c-c07c6b25815a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11746,7 +11746,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{05c25bc6-ebbc-4c15-8a8d-80fe170e727f}</x14:id>
+          <x14:id>{24305cf6-7e05-4da6-a576-231f612dbc18}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11758,7 +11758,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d69f8013-854e-4a74-9dd4-f335e38816fe}</x14:id>
+          <x14:id>{e1b78703-f0a3-49e3-8123-9708a33c0e97}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11772,7 +11772,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a3eb7612-e084-42ee-b04e-d573ca01a7b5}</x14:id>
+          <x14:id>{c5710624-0574-4df3-a2d3-097a1ccbff19}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11784,7 +11784,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5c77ef17-e09b-4837-8b5e-4f86d27ef522}</x14:id>
+          <x14:id>{109bdd8a-684d-4777-af20-9f7045320647}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11796,7 +11796,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{97f7ebf3-0c8b-452f-a96d-e629a9363387}</x14:id>
+          <x14:id>{38e8cda6-f7b7-40b6-b9d3-82ff57bd0686}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11808,7 +11808,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ecde5c31-37e2-47fb-84f1-92b21e83d1f8}</x14:id>
+          <x14:id>{9493c9b5-50a2-488d-a732-c5adc6201100}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11820,7 +11820,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2bad34e7-80a6-4d57-9d5b-9a9316d3dff6}</x14:id>
+          <x14:id>{1bbf1d92-1b82-49ef-ac25-7702643b408b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11832,7 +11832,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dd46fbef-de39-4b4e-aa2c-bf6cd7992b1e}</x14:id>
+          <x14:id>{c38e7502-72ab-4fd7-9e82-f983aae810d0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11844,7 +11844,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fb3bd2cd-fa68-4390-a51d-1916842884b6}</x14:id>
+          <x14:id>{72854487-6ba0-4842-a6dc-421998794cf6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11856,7 +11856,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{38a0da66-3294-40d7-b7e5-e2d5167b6ce3}</x14:id>
+          <x14:id>{29801a6e-a32b-4362-bb49-dce3bd1b56ad}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11870,7 +11870,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0a7912ea-8da3-4680-ac2e-00f4c381e6e3}</x14:id>
+          <x14:id>{cf0c93f5-04a7-44dd-b3db-4e3c014b4ab8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11882,7 +11882,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9cee8346-8284-4750-baa3-3e6474ab42fb}</x14:id>
+          <x14:id>{4fa68f15-ec46-4245-b465-c62c40cbfcf2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11894,7 +11894,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8b2fab17-929c-4c0d-96fc-484a771a0ebb}</x14:id>
+          <x14:id>{db44b9de-8939-43b3-8ff5-401170a2fa5d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11908,7 +11908,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ae8c8b2d-a985-445d-bbab-625663859afb}</x14:id>
+          <x14:id>{ebf91048-ce6e-4417-91ad-25c907c90f88}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11920,7 +11920,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a890313b-6127-407e-9d58-3cbc6629af67}</x14:id>
+          <x14:id>{ee0a650b-1747-453a-a2e1-0acebc4c0378}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11932,7 +11932,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1a86005f-b640-41f3-8edd-be624da44fae}</x14:id>
+          <x14:id>{7236781b-6e19-404a-8259-37e2f449db5b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11946,7 +11946,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b8785ba3-09b0-41fb-834c-41c2cc0d10d6}</x14:id>
+          <x14:id>{8ba684fa-b383-4a51-8528-63e7fc6bed88}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11958,7 +11958,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4480c6c9-f9d7-4cef-8868-4b2f5528be4b}</x14:id>
+          <x14:id>{7933c7c6-88b1-497a-8389-db74fcd97e6e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11972,7 +11972,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a82588ea-a9dc-444c-9170-995c95f5bb43}</x14:id>
+          <x14:id>{dd1f5dc9-99bc-4ca5-a2eb-83402e2ac75b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11984,7 +11984,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5ee6c5e1-d32a-4a52-8b13-3f8209ed6207}</x14:id>
+          <x14:id>{c6497908-49f9-4e4e-ae41-f9c33506780a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11996,7 +11996,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{98a04183-533e-432e-ba4f-373dad0d49cc}</x14:id>
+          <x14:id>{3886edd2-0b5b-4f05-babc-34841f988ed1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12010,7 +12010,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{72393acf-df5e-4987-8fd4-7e9dd881b216}</x14:id>
+          <x14:id>{317d55ee-5e4f-4b7f-b0aa-2b45ca7bb9b6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12022,7 +12022,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7c6fae99-415d-45ab-84e6-76828260e16f}</x14:id>
+          <x14:id>{5519520e-e0b9-4eeb-98b1-215ae83cbdc9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12034,7 +12034,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6683e022-0144-4145-b40d-59d1e95c1c45}</x14:id>
+          <x14:id>{22b1dd1a-a06d-4d4d-9f5b-8efd4050a449}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12048,7 +12048,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c5056656-db69-4f5e-975e-262245901acd}</x14:id>
+          <x14:id>{e2355309-e966-4c59-90fc-f37edb519a0e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12060,7 +12060,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3f6ae1ae-f6d7-4f66-90e8-5e24c97db127}</x14:id>
+          <x14:id>{ac84ed84-07b1-4901-8663-7c6734ad28f5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12072,7 +12072,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c208452d-fdcc-436e-9b6c-53c14c76009c}</x14:id>
+          <x14:id>{9caf4a6a-7144-4065-acd7-f1d3f58c89c5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12086,7 +12086,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{afb89e14-3874-434f-970a-bf4bb81f1240}</x14:id>
+          <x14:id>{ce3ee648-dba5-4a9e-9e97-a0e9d24930b7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12098,7 +12098,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ea932a56-63b4-4b38-87c9-d33fd1c63cdc}</x14:id>
+          <x14:id>{75989a7e-b7a6-4751-a6b3-fb89d2438fd1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12110,7 +12110,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{938350f9-f7cf-44eb-af84-e2a58dd04105}</x14:id>
+          <x14:id>{190b8ad7-37fd-4d64-8e30-6160563cbcb1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12124,7 +12124,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e432e9d7-8882-4563-9c41-ec0295d059be}</x14:id>
+          <x14:id>{6e86a603-2f0d-469f-902e-88e9544847b3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12136,7 +12136,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{91bd7701-5db2-41bd-94ce-9054d2b5ab34}</x14:id>
+          <x14:id>{c24fc8dc-355b-45ed-83aa-44d8a8e8990c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12148,7 +12148,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6f359c46-0755-4742-8561-4c97d8bdafff}</x14:id>
+          <x14:id>{094a42fe-35d5-454b-8d26-7506085b5bfa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12162,7 +12162,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cb8b3eee-7316-4225-9ac4-475dffe00db2}</x14:id>
+          <x14:id>{c7bb73aa-5d97-4021-ba8e-49a940d24bc6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12174,7 +12174,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{58d9ca5b-8b67-4a9c-9692-e2fb2e6cdd9e}</x14:id>
+          <x14:id>{9003f2b9-743c-4a19-ae35-706566283fe7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12186,7 +12186,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1dd2dd37-c212-41e0-a583-7ccdd798566f}</x14:id>
+          <x14:id>{13db177e-bfed-40da-aec3-79f64bd546d1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12198,7 +12198,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9ac998df-4eb4-46f2-ac46-c68b8611611e}</x14:id>
+          <x14:id>{6430fa46-2bdb-4105-98ec-f3a1feb4b999}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12210,7 +12210,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bd44ce8d-9b94-4ef5-9e32-9dbc1e5c3082}</x14:id>
+          <x14:id>{beb93417-ed26-4582-94e8-8d7eaf1a13cb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12222,7 +12222,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1f94ac4d-e045-40c4-98d7-895c72cb0ca2}</x14:id>
+          <x14:id>{b166b029-dc16-4afe-9fd2-2377903d2704}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12234,7 +12234,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{45a371ef-5e80-4024-adb4-36ff980da506}</x14:id>
+          <x14:id>{8258a538-94cc-4767-b391-e57fee97d8a5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12246,7 +12246,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{aee30381-d6bb-49fb-a720-eed8c5b51d9a}</x14:id>
+          <x14:id>{26e2c17f-7dbf-479c-805d-d33671165f38}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12260,7 +12260,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8a953f3a-91be-40f5-b891-fdbbbb895397}</x14:id>
+          <x14:id>{9c5f469e-fd8c-4ff9-b68d-abd8cb241300}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12272,7 +12272,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cad354a9-f8df-4af6-ae80-a076ead269e0}</x14:id>
+          <x14:id>{fae02a16-ac25-49b6-8cb3-5ae056423150}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12286,7 +12286,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ef3caea5-64e4-49fe-9b5d-1149c5c19f36}</x14:id>
+          <x14:id>{6eb786a4-7ab7-477d-8e61-e77466ff89a4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12300,7 +12300,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cf0635dd-3d47-4562-b381-9f18165a80a7}</x14:id>
+          <x14:id>{8e48a1c3-f861-44d7-8cc9-60016785ecf0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12314,7 +12314,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b1b25a36-6144-4dee-bab9-b1fccc1c5335}</x14:id>
+          <x14:id>{b2dfba0a-6c94-4ca5-9844-2672341b8e88}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12328,7 +12328,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e68d09d9-1eeb-4d4c-9165-dd4d4ad2a487}</x14:id>
+          <x14:id>{13d8c857-4b8b-49a1-a15f-5ed56c885eae}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12342,7 +12342,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{228b55a4-271c-414c-9484-dc396e872318}</x14:id>
+          <x14:id>{e553401f-4f17-4ba7-b754-22d92372e095}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12354,7 +12354,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d7755af8-cece-4d94-bb2a-2b2f84bd0344}</x14:id>
+          <x14:id>{32664af7-9dd0-48e3-ae8e-48f08cd4dd55}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12366,7 +12366,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{25d2afcb-88a5-4d5f-8776-ff444d0887cf}</x14:id>
+          <x14:id>{f9cba129-2192-47fe-aa0a-42cf2b4ef931}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12380,7 +12380,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ea7c0a5a-b4f0-4d23-8f6c-fedae897ffe6}</x14:id>
+          <x14:id>{81b17492-8ef5-42e6-9be5-1256952c1cf4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12392,7 +12392,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7cbd75c6-3612-475c-96b5-e3afd81def65}</x14:id>
+          <x14:id>{cf0ebaf9-0b06-45c4-b712-3150a8f8bf10}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12404,7 +12404,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8bbb846f-f4c4-4a47-86c8-11ffe8562191}</x14:id>
+          <x14:id>{037a5f3b-48db-4aae-a9f6-8133e63502c7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12418,7 +12418,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{158023cb-f866-4818-b105-acdd8a8bbbd5}</x14:id>
+          <x14:id>{8d43437a-656d-4275-aa9e-6ef78be60cba}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12430,7 +12430,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d58aff0d-44f7-4bff-aa4d-1932e7da3cc0}</x14:id>
+          <x14:id>{727dca93-2a80-426d-9663-5097d63bcdc7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12442,7 +12442,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7ec80741-a4ef-4d27-88c9-b8fc0133a177}</x14:id>
+          <x14:id>{fb2c07c2-0269-4cfc-9d64-6f0535ed445b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12456,7 +12456,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9ec2c6c0-3975-4698-a2cd-5b192d126d18}</x14:id>
+          <x14:id>{3a21bed5-c665-4d0a-af0a-5e1bdec9ae16}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12468,7 +12468,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b8a98878-1d9c-4f72-80ee-896b39115f45}</x14:id>
+          <x14:id>{29a44afb-68d9-42aa-b56d-dae68722c7be}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12480,7 +12480,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{93c97e96-9d70-4a36-8e17-29c502ee7f23}</x14:id>
+          <x14:id>{ca725459-343a-4659-b5a6-3a7e836d5942}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12494,7 +12494,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{537e3c49-bfc4-4c08-b43b-0d9629113268}</x14:id>
+          <x14:id>{cc3ea6aa-c1a6-4989-9729-881fd01860ec}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12506,7 +12506,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{18b40e02-a788-4c44-ae5b-bd2b33a5fada}</x14:id>
+          <x14:id>{f2c259c4-9ae9-4dea-9dc0-122bb34ddf0a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12520,7 +12520,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6d47d68d-2793-4477-b5b3-3db1c4fde99e}</x14:id>
+          <x14:id>{51a635ec-9505-4cfe-88ad-f8752b61094d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12532,7 +12532,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b04baad5-38d9-4ff7-a560-24e3be9b6c3a}</x14:id>
+          <x14:id>{6034b704-e8e3-44c4-b347-1fe8d38e3642}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12544,7 +12544,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{40fd9384-ca68-4a80-bf0e-8b162113ab89}</x14:id>
+          <x14:id>{bf53c710-d80c-423e-bede-30ce958e3b67}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12558,7 +12558,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b4d3e4b7-788c-45d4-9705-c2a548a1b553}</x14:id>
+          <x14:id>{271a1039-6f3a-4054-9562-6db4ef200aa1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12570,7 +12570,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2cc5d0ea-f9b6-455e-990d-5f608bdced94}</x14:id>
+          <x14:id>{c98d3cfb-eab3-41d2-a6bf-c5a920e2be64}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12582,7 +12582,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f28846bc-f528-4874-aba1-93536f3c9dbd}</x14:id>
+          <x14:id>{f74cd777-c159-4d93-a72d-41dc551dec88}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12596,7 +12596,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{16455e2e-95bb-4f1e-9ad5-07cd2ea07d9d}</x14:id>
+          <x14:id>{45408be5-592d-47f0-9e80-d41e2f23e4c5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12608,7 +12608,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9ba09e57-7fac-4198-9606-513fdd01d6a2}</x14:id>
+          <x14:id>{4e2b9c44-e595-4c77-a6f8-1900b8d8f91f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12642,7 +12642,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f7467478-75db-46bf-afdf-be375420c666}">
+          <x14:cfRule type="dataBar" id="{e527788e-4040-4eb9-b240-f64dca916c9a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12651,7 +12651,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2eb897e6-20f9-4722-856f-4dff413864ff}">
+          <x14:cfRule type="dataBar" id="{beb46d76-ffa3-424d-a154-d2f9fe58e590}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12660,7 +12660,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a6e64cbb-1e66-4ffd-a734-571fd016c3a2}">
+          <x14:cfRule type="dataBar" id="{5e2222b2-7c8d-446b-9c5a-0005acebdbe6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12671,7 +12671,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{404f47b3-97ab-443f-a6bb-1fd18a10d93d}">
+          <x14:cfRule type="dataBar" id="{843b83e2-d06f-46c8-8521-22d0a4051257}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12682,7 +12682,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4ebe11f1-ed1b-4373-b5f3-a497f0a12ff1}">
+          <x14:cfRule type="dataBar" id="{795d8539-b6cd-468f-86b0-6fe17d6195de}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12693,14 +12693,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{39610c96-7906-418b-b6dc-73e105270551}">
+          <x14:cfRule type="dataBar" id="{90020398-bdc5-46de-bafa-f85ed17ae972}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a036462b-e794-4944-bd10-1aeec9e9f30a}">
+          <x14:cfRule type="dataBar" id="{69967096-2317-45f7-8247-151340b0dfec}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12711,7 +12711,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{902e1d20-08c2-40f0-8eae-a206b1031f54}">
+          <x14:cfRule type="dataBar" id="{a4a32341-a597-4648-87e3-dcb1001aea70}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12725,7 +12725,7 @@
           <xm:sqref>AD58</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{00a1bf38-a469-4d5d-8a60-eb55dbe24561}">
+          <x14:cfRule type="dataBar" id="{27babd0b-79d1-4a92-bb2d-4cd4138aec80}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12734,7 +12734,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e00ca20e-0612-4220-8bbd-f524067cc40b}">
+          <x14:cfRule type="dataBar" id="{5923fcbf-b963-4847-a08c-fd3471f7c77b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12743,7 +12743,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{92d75939-9f1f-4026-bd22-2f9f3d9796b5}">
+          <x14:cfRule type="dataBar" id="{8f9dacb1-9704-44d6-8586-53f712945d35}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12754,7 +12754,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0bc05561-cb09-40a1-a70b-2aa8a22b4263}">
+          <x14:cfRule type="dataBar" id="{974e5550-2954-4f71-a0c8-9496f388ff47}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12765,7 +12765,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1b8fc686-c8e0-4cb9-bb4d-84b765af7de5}">
+          <x14:cfRule type="dataBar" id="{9f27453e-b038-488c-9239-fe35eea01dfb}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12776,14 +12776,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d4dfcdcd-f9eb-43d3-86c3-df948552b4a2}">
+          <x14:cfRule type="dataBar" id="{541529e2-6d51-4232-b980-393f4d8a3724}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{995e7234-bc1e-4ce6-be70-d1a53f7609b2}">
+          <x14:cfRule type="dataBar" id="{594967a8-b30d-4a5b-aca4-9414a7e0aa24}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12794,7 +12794,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2f77c3f9-eea7-4fcd-8edf-71e7f1a34fc6}">
+          <x14:cfRule type="dataBar" id="{6903b435-54f0-4dc6-b8e6-a10860f67f4a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12808,7 +12808,7 @@
           <xm:sqref>K62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b3419640-8a4c-46e2-b383-b1895ab4a1b9}">
+          <x14:cfRule type="dataBar" id="{40c7af34-8452-4b7b-83cd-506ff67a80d6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12817,7 +12817,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{bece8bee-8272-48f3-a967-dc0c0f6d7f44}">
+          <x14:cfRule type="dataBar" id="{8d07e276-1a63-4ae2-9150-1aecf0a07f3a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12826,7 +12826,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7a42a03c-5f6a-40bf-b1fe-374e688701eb}">
+          <x14:cfRule type="dataBar" id="{4aa53087-d18d-48da-9408-4291d57be9c2}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12837,7 +12837,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ebbec158-2ace-40ca-a91d-0ff44512c666}">
+          <x14:cfRule type="dataBar" id="{e8d0d274-e4d8-4cc2-a473-17b516f42649}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12848,7 +12848,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9e3f4808-aa37-4e31-8078-9acae67988fe}">
+          <x14:cfRule type="dataBar" id="{57f53829-dcd1-494c-8ca1-2b193d3d6f35}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12859,14 +12859,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6cf9996c-203a-45b7-b917-eec38bd8b3b6}">
+          <x14:cfRule type="dataBar" id="{3a0b7942-7e86-41b7-b33c-7a70035147f3}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2d951071-3705-4932-8929-cec1ac74dd8f}">
+          <x14:cfRule type="dataBar" id="{602930ad-9409-4489-a65e-cdecd16a61fb}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12877,7 +12877,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3c5fec94-750f-4044-8568-3284e7bd6720}">
+          <x14:cfRule type="dataBar" id="{a944e513-65a5-44fd-89c0-8ac02931c187}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12891,7 +12891,7 @@
           <xm:sqref>AD62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b14b5c85-05e1-4732-be51-bab9a75ebfc5}">
+          <x14:cfRule type="dataBar" id="{2984bd09-c6f4-4de8-8394-93dd1521da18}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12900,7 +12900,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{803d70f5-6517-4a48-b9dd-bb0fd03bc5ba}">
+          <x14:cfRule type="dataBar" id="{d5240306-e489-4d87-a552-0177c90359bc}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12909,7 +12909,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{437af854-a673-4b9e-8669-1cd9af6607c4}">
+          <x14:cfRule type="dataBar" id="{341f6cba-74dd-4739-aa80-56d22f3e852a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12920,7 +12920,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0361bab4-e76a-4618-aada-d6c9ee872e72}">
+          <x14:cfRule type="dataBar" id="{916cdaa0-734d-4d5e-97cb-9e01ed78f6fc}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12931,7 +12931,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{fcbfd4ea-5e47-455d-8ba5-9edc4f40593f}">
+          <x14:cfRule type="dataBar" id="{056de079-a96d-4d7d-b010-b49eb8b9c5df}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12942,14 +12942,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{16de1aaa-356f-4d6c-a8b9-70d3cbb3f462}">
+          <x14:cfRule type="dataBar" id="{106b117f-8bcf-443f-9be7-248805547be1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c7885fb4-1410-4cf5-9428-6e115d33029c}">
+          <x14:cfRule type="dataBar" id="{27993b30-86e6-4273-91ab-16628e8c64d0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12960,7 +12960,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{be6fc46f-7260-43e4-95f3-48f9df34eb70}">
+          <x14:cfRule type="dataBar" id="{7241de54-30de-4b00-9707-6edc6bfb121b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12974,7 +12974,7 @@
           <xm:sqref>K63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{265b9ecc-b6c9-44f3-8786-b171dec3d60e}">
+          <x14:cfRule type="dataBar" id="{d167434e-8398-41ca-905a-9661763b52de}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12983,7 +12983,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e60ffd89-2d79-4bbd-8113-37735820dc42}">
+          <x14:cfRule type="dataBar" id="{ddcda096-13b1-4ce8-ad67-f1d245a2ebb7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12992,7 +12992,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2b021631-93cd-4717-b45f-463a4e91cfd0}">
+          <x14:cfRule type="dataBar" id="{c55bc5cc-e67c-40f6-94ad-911db305c815}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13003,7 +13003,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a0e1f723-be38-43a3-8868-96f77e18a269}">
+          <x14:cfRule type="dataBar" id="{b60ead94-5a05-4712-baea-12a6592738b9}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -13014,7 +13014,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c279f90d-b0c7-47a8-a156-3b5e5e402c74}">
+          <x14:cfRule type="dataBar" id="{9261e741-e472-460b-b605-6371c27bf379}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -13025,14 +13025,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7e8bf0b9-b56b-4408-978e-70262b09018f}">
+          <x14:cfRule type="dataBar" id="{5c07fc3d-400f-4155-8b5c-c07c6b25815a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{05c25bc6-ebbc-4c15-8a8d-80fe170e727f}">
+          <x14:cfRule type="dataBar" id="{24305cf6-7e05-4da6-a576-231f612dbc18}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13043,7 +13043,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d69f8013-854e-4a74-9dd4-f335e38816fe}">
+          <x14:cfRule type="dataBar" id="{e1b78703-f0a3-49e3-8123-9708a33c0e97}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -13057,7 +13057,7 @@
           <xm:sqref>K64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a3eb7612-e084-42ee-b04e-d573ca01a7b5}">
+          <x14:cfRule type="dataBar" id="{c5710624-0574-4df3-a2d3-097a1ccbff19}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13066,7 +13066,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5c77ef17-e09b-4837-8b5e-4f86d27ef522}">
+          <x14:cfRule type="dataBar" id="{109bdd8a-684d-4777-af20-9f7045320647}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13075,7 +13075,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{97f7ebf3-0c8b-452f-a96d-e629a9363387}">
+          <x14:cfRule type="dataBar" id="{38e8cda6-f7b7-40b6-b9d3-82ff57bd0686}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13086,7 +13086,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ecde5c31-37e2-47fb-84f1-92b21e83d1f8}">
+          <x14:cfRule type="dataBar" id="{9493c9b5-50a2-488d-a732-c5adc6201100}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -13097,7 +13097,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2bad34e7-80a6-4d57-9d5b-9a9316d3dff6}">
+          <x14:cfRule type="dataBar" id="{1bbf1d92-1b82-49ef-ac25-7702643b408b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -13108,14 +13108,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{dd46fbef-de39-4b4e-aa2c-bf6cd7992b1e}">
+          <x14:cfRule type="dataBar" id="{c38e7502-72ab-4fd7-9e82-f983aae810d0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{fb3bd2cd-fa68-4390-a51d-1916842884b6}">
+          <x14:cfRule type="dataBar" id="{72854487-6ba0-4842-a6dc-421998794cf6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13126,7 +13126,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{38a0da66-3294-40d7-b7e5-e2d5167b6ce3}">
+          <x14:cfRule type="dataBar" id="{29801a6e-a32b-4362-bb49-dce3bd1b56ad}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -13140,7 +13140,7 @@
           <xm:sqref>K65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0a7912ea-8da3-4680-ac2e-00f4c381e6e3}">
+          <x14:cfRule type="dataBar" id="{cf0c93f5-04a7-44dd-b3db-4e3c014b4ab8}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13150,7 +13150,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9cee8346-8284-4750-baa3-3e6474ab42fb}">
+          <x14:cfRule type="dataBar" id="{4fa68f15-ec46-4245-b465-c62c40cbfcf2}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13159,7 +13159,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8b2fab17-929c-4c0d-96fc-484a771a0ebb}">
+          <x14:cfRule type="dataBar" id="{db44b9de-8939-43b3-8ff5-401170a2fa5d}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13171,7 +13171,7 @@
           <xm:sqref>AB69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ae8c8b2d-a985-445d-bbab-625663859afb}">
+          <x14:cfRule type="dataBar" id="{ebf91048-ce6e-4417-91ad-25c907c90f88}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13181,7 +13181,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a890313b-6127-407e-9d58-3cbc6629af67}">
+          <x14:cfRule type="dataBar" id="{ee0a650b-1747-453a-a2e1-0acebc4c0378}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13190,7 +13190,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1a86005f-b640-41f3-8edd-be624da44fae}">
+          <x14:cfRule type="dataBar" id="{7236781b-6e19-404a-8259-37e2f449db5b}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13202,7 +13202,7 @@
           <xm:sqref>AB103</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b8785ba3-09b0-41fb-834c-41c2cc0d10d6}">
+          <x14:cfRule type="dataBar" id="{8ba684fa-b383-4a51-8528-63e7fc6bed88}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13211,7 +13211,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4480c6c9-f9d7-4cef-8868-4b2f5528be4b}">
+          <x14:cfRule type="dataBar" id="{7933c7c6-88b1-497a-8389-db74fcd97e6e}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13223,7 +13223,7 @@
           <xm:sqref>AB117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{a82588ea-a9dc-444c-9170-995c95f5bb43}">
+          <x14:cfRule type="dataBar" id="{dd1f5dc9-99bc-4ca5-a2eb-83402e2ac75b}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13233,7 +13233,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5ee6c5e1-d32a-4a52-8b13-3f8209ed6207}">
+          <x14:cfRule type="dataBar" id="{c6497908-49f9-4e4e-ae41-f9c33506780a}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13242,7 +13242,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{98a04183-533e-432e-ba4f-373dad0d49cc}">
+          <x14:cfRule type="dataBar" id="{3886edd2-0b5b-4f05-babc-34841f988ed1}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13254,7 +13254,7 @@
           <xm:sqref>AB127</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{72393acf-df5e-4987-8fd4-7e9dd881b216}">
+          <x14:cfRule type="dataBar" id="{317d55ee-5e4f-4b7f-b0aa-2b45ca7bb9b6}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13264,7 +13264,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7c6fae99-415d-45ab-84e6-76828260e16f}">
+          <x14:cfRule type="dataBar" id="{5519520e-e0b9-4eeb-98b1-215ae83cbdc9}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13273,7 +13273,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6683e022-0144-4145-b40d-59d1e95c1c45}">
+          <x14:cfRule type="dataBar" id="{22b1dd1a-a06d-4d4d-9f5b-8efd4050a449}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13285,7 +13285,7 @@
           <xm:sqref>K137</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c5056656-db69-4f5e-975e-262245901acd}">
+          <x14:cfRule type="dataBar" id="{e2355309-e966-4c59-90fc-f37edb519a0e}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13295,7 +13295,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3f6ae1ae-f6d7-4f66-90e8-5e24c97db127}">
+          <x14:cfRule type="dataBar" id="{ac84ed84-07b1-4901-8663-7c6734ad28f5}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13304,7 +13304,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c208452d-fdcc-436e-9b6c-53c14c76009c}">
+          <x14:cfRule type="dataBar" id="{9caf4a6a-7144-4065-acd7-f1d3f58c89c5}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13316,7 +13316,7 @@
           <xm:sqref>K142</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{afb89e14-3874-434f-970a-bf4bb81f1240}">
+          <x14:cfRule type="dataBar" id="{ce3ee648-dba5-4a9e-9e97-a0e9d24930b7}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13326,7 +13326,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ea932a56-63b4-4b38-87c9-d33fd1c63cdc}">
+          <x14:cfRule type="dataBar" id="{75989a7e-b7a6-4751-a6b3-fb89d2438fd1}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13335,7 +13335,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{938350f9-f7cf-44eb-af84-e2a58dd04105}">
+          <x14:cfRule type="dataBar" id="{190b8ad7-37fd-4d64-8e30-6160563cbcb1}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13347,7 +13347,7 @@
           <xm:sqref>K147</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e432e9d7-8882-4563-9c41-ec0295d059be}">
+          <x14:cfRule type="dataBar" id="{6e86a603-2f0d-469f-902e-88e9544847b3}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13357,7 +13357,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{91bd7701-5db2-41bd-94ce-9054d2b5ab34}">
+          <x14:cfRule type="dataBar" id="{c24fc8dc-355b-45ed-83aa-44d8a8e8990c}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13366,7 +13366,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6f359c46-0755-4742-8561-4c97d8bdafff}">
+          <x14:cfRule type="dataBar" id="{094a42fe-35d5-454b-8d26-7506085b5bfa}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13378,7 +13378,7 @@
           <xm:sqref>K152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cb8b3eee-7316-4225-9ac4-475dffe00db2}">
+          <x14:cfRule type="dataBar" id="{c7bb73aa-5d97-4021-ba8e-49a940d24bc6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13387,7 +13387,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{58d9ca5b-8b67-4a9c-9692-e2fb2e6cdd9e}">
+          <x14:cfRule type="dataBar" id="{9003f2b9-743c-4a19-ae35-706566283fe7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13396,7 +13396,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1dd2dd37-c212-41e0-a583-7ccdd798566f}">
+          <x14:cfRule type="dataBar" id="{13db177e-bfed-40da-aec3-79f64bd546d1}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13407,7 +13407,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9ac998df-4eb4-46f2-ac46-c68b8611611e}">
+          <x14:cfRule type="dataBar" id="{6430fa46-2bdb-4105-98ec-f3a1feb4b999}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -13418,7 +13418,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{bd44ce8d-9b94-4ef5-9e32-9dbc1e5c3082}">
+          <x14:cfRule type="dataBar" id="{beb93417-ed26-4582-94e8-8d7eaf1a13cb}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -13429,14 +13429,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1f94ac4d-e045-40c4-98d7-895c72cb0ca2}">
+          <x14:cfRule type="dataBar" id="{b166b029-dc16-4afe-9fd2-2377903d2704}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{45a371ef-5e80-4024-adb4-36ff980da506}">
+          <x14:cfRule type="dataBar" id="{8258a538-94cc-4767-b391-e57fee97d8a5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13447,7 +13447,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{aee30381-d6bb-49fb-a720-eed8c5b51d9a}">
+          <x14:cfRule type="dataBar" id="{26e2c17f-7dbf-479c-805d-d33671165f38}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -13461,7 +13461,7 @@
           <xm:sqref>K59:K60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8a953f3a-91be-40f5-b891-fdbbbb895397}">
+          <x14:cfRule type="dataBar" id="{9c5f469e-fd8c-4ff9-b68d-abd8cb241300}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13471,7 +13471,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{cad354a9-f8df-4af6-ae80-a076ead269e0}">
+          <x14:cfRule type="dataBar" id="{fae02a16-ac25-49b6-8cb3-5ae056423150}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13483,7 +13483,7 @@
           <xm:sqref>Y69:Y88</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ef3caea5-64e4-49fe-9b5d-1149c5c19f36}">
+          <x14:cfRule type="dataBar" id="{6eb786a4-7ab7-477d-8e61-e77466ff89a4}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13496,7 +13496,7 @@
           <xm:sqref>Y79:Y88</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cf0635dd-3d47-4562-b381-9f18165a80a7}">
+          <x14:cfRule type="dataBar" id="{8e48a1c3-f861-44d7-8cc9-60016785ecf0}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13509,7 +13509,7 @@
           <xm:sqref>AB117:AB126</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b1b25a36-6144-4dee-bab9-b1fccc1c5335}">
+          <x14:cfRule type="dataBar" id="{b2dfba0a-6c94-4ca5-9844-2672341b8e88}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13521,7 +13521,7 @@
           <xm:sqref>AD58:AE59</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e68d09d9-1eeb-4d4c-9165-dd4d4ad2a487}">
+          <x14:cfRule type="dataBar" id="{13d8c857-4b8b-49a1-a15f-5ed56c885eae}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13533,7 +13533,7 @@
           <xm:sqref>AD62:AE65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{228b55a4-271c-414c-9484-dc396e872318}">
+          <x14:cfRule type="dataBar" id="{e553401f-4f17-4ba7-b754-22d92372e095}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13543,7 +13543,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d7755af8-cece-4d94-bb2a-2b2f84bd0344}">
+          <x14:cfRule type="dataBar" id="{32664af7-9dd0-48e3-ae8e-48f08cd4dd55}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13552,7 +13552,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{25d2afcb-88a5-4d5f-8776-ff444d0887cf}">
+          <x14:cfRule type="dataBar" id="{f9cba129-2192-47fe-aa0a-42cf2b4ef931}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13564,7 +13564,7 @@
           <xm:sqref>F69 F74 F79 F84</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ea7c0a5a-b4f0-4d23-8f6c-fedae897ffe6}">
+          <x14:cfRule type="dataBar" id="{81b17492-8ef5-42e6-9be5-1256952c1cf4}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13574,7 +13574,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7cbd75c6-3612-475c-96b5-e3afd81def65}">
+          <x14:cfRule type="dataBar" id="{cf0ebaf9-0b06-45c4-b712-3150a8f8bf10}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13583,7 +13583,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8bbb846f-f4c4-4a47-86c8-11ffe8562191}">
+          <x14:cfRule type="dataBar" id="{037a5f3b-48db-4aae-a9f6-8133e63502c7}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13595,7 +13595,7 @@
           <xm:sqref>K69 K79 K89 K103</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{158023cb-f866-4818-b105-acdd8a8bbbd5}">
+          <x14:cfRule type="dataBar" id="{8d43437a-656d-4275-aa9e-6ef78be60cba}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13605,7 +13605,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d58aff0d-44f7-4bff-aa4d-1932e7da3cc0}">
+          <x14:cfRule type="dataBar" id="{727dca93-2a80-426d-9663-5097d63bcdc7}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13614,7 +13614,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7ec80741-a4ef-4d27-88c9-b8fc0133a177}">
+          <x14:cfRule type="dataBar" id="{fb2c07c2-0269-4cfc-9d64-6f0535ed445b}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13626,7 +13626,7 @@
           <xm:sqref>AB79 AB89</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9ec2c6c0-3975-4698-a2cd-5b192d126d18}">
+          <x14:cfRule type="dataBar" id="{3a21bed5-c665-4d0a-af0a-5e1bdec9ae16}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13636,7 +13636,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b8a98878-1d9c-4f72-80ee-896b39115f45}">
+          <x14:cfRule type="dataBar" id="{29a44afb-68d9-42aa-b56d-dae68722c7be}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13645,7 +13645,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{93c97e96-9d70-4a36-8e17-29c502ee7f23}">
+          <x14:cfRule type="dataBar" id="{ca725459-343a-4659-b5a6-3a7e836d5942}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13657,7 +13657,7 @@
           <xm:sqref>F89 F96 F103 F110</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{537e3c49-bfc4-4c08-b43b-0d9629113268}">
+          <x14:cfRule type="dataBar" id="{cc3ea6aa-c1a6-4989-9729-881fd01860ec}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13667,7 +13667,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{18b40e02-a788-4c44-ae5b-bd2b33a5fada}">
+          <x14:cfRule type="dataBar" id="{f2c259c4-9ae9-4dea-9dc0-122bb34ddf0a}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13679,7 +13679,7 @@
           <xm:sqref>Y89 Y103</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6d47d68d-2793-4477-b5b3-3db1c4fde99e}">
+          <x14:cfRule type="dataBar" id="{51a635ec-9505-4cfe-88ad-f8752b61094d}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13689,7 +13689,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b04baad5-38d9-4ff7-a560-24e3be9b6c3a}">
+          <x14:cfRule type="dataBar" id="{6034b704-e8e3-44c4-b347-1fe8d38e3642}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13698,7 +13698,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{40fd9384-ca68-4a80-bf0e-8b162113ab89}">
+          <x14:cfRule type="dataBar" id="{bf53c710-d80c-423e-bede-30ce958e3b67}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13710,7 +13710,7 @@
           <xm:sqref>F117 F122 F127 F132 F137 F142 F147 F152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b4d3e4b7-788c-45d4-9705-c2a548a1b553}">
+          <x14:cfRule type="dataBar" id="{271a1039-6f3a-4054-9562-6db4ef200aa1}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13720,7 +13720,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2cc5d0ea-f9b6-455e-990d-5f608bdced94}">
+          <x14:cfRule type="dataBar" id="{c98d3cfb-eab3-41d2-a6bf-c5a920e2be64}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13729,7 +13729,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f28846bc-f528-4874-aba1-93536f3c9dbd}">
+          <x14:cfRule type="dataBar" id="{f74cd777-c159-4d93-a72d-41dc551dec88}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13741,7 +13741,7 @@
           <xm:sqref>K117 K127</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{16455e2e-95bb-4f1e-9ad5-07cd2ea07d9d}">
+          <x14:cfRule type="dataBar" id="{45408be5-592d-47f0-9e80-d41e2f23e4c5}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13751,7 +13751,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9ba09e57-7fac-4198-9606-513fdd01d6a2}">
+          <x14:cfRule type="dataBar" id="{4e2b9c44-e595-4c77-a6f8-1900b8d8f91f}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">

--- a/外网端源码/其他楼交接班容量报表空模板.xlsx
+++ b/外网端源码/其他楼交接班容量报表空模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="22020"/>
+    <workbookView windowWidth="24750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="本班组" sheetId="1" r:id="rId1"/>
@@ -3210,28 +3210,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AF156"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="18.1851851851852" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.1818181818182" style="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.9351851851852" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.9363636363636" style="1" customWidth="1"/>
     <col min="7" max="8" width="9" style="1" customWidth="1"/>
-    <col min="9" max="9" width="16.4074074074074" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.4090909090909" style="1" customWidth="1"/>
     <col min="10" max="11" width="9" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.9351851851852" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.9363636363636" style="1" customWidth="1"/>
     <col min="13" max="13" width="9" style="1" customWidth="1"/>
-    <col min="14" max="14" width="8.75" style="1" customWidth="1"/>
-    <col min="15" max="15" width="38.1851851851852" style="1" customWidth="1"/>
+    <col min="14" max="14" width="8.75454545454545" style="1" customWidth="1"/>
+    <col min="15" max="15" width="38.1818181818182" style="1" customWidth="1"/>
     <col min="16" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="12.5925925925926" style="1" customWidth="1"/>
-    <col min="20" max="20" width="16.5092592592593" style="1" customWidth="1"/>
+    <col min="19" max="19" width="12.5909090909091" style="1" customWidth="1"/>
+    <col min="20" max="20" width="16.5090909090909" style="1" customWidth="1"/>
     <col min="21" max="21" width="9" style="1" customWidth="1"/>
-    <col min="22" max="22" width="14.1574074074074" style="1" customWidth="1"/>
+    <col min="22" max="22" width="14.1545454545455" style="1" customWidth="1"/>
     <col min="23" max="24" width="9" style="1" customWidth="1"/>
-    <col min="25" max="25" width="10.25" style="1" customWidth="1"/>
+    <col min="25" max="25" width="10.2545454545455" style="1" customWidth="1"/>
     <col min="26" max="27" width="9" style="1" customWidth="1"/>
-    <col min="28" max="28" width="17.4166666666667" style="1" customWidth="1"/>
+    <col min="28" max="28" width="17.4181818181818" style="1" customWidth="1"/>
     <col min="31" max="31" width="11" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4568,10 +4568,7 @@
       <c r="AB29" s="89" t="s">
         <v>96</v>
       </c>
-      <c r="AC29" s="87">
-        <f>(AC26+AC28)*2.25*2.25*3.14</f>
-        <v>0</v>
-      </c>
+      <c r="AC29" s="87"/>
       <c r="AD29" s="52"/>
       <c r="AE29" s="53"/>
     </row>
@@ -6418,7 +6415,7 @@
       <c r="AD66" s="64"/>
       <c r="AE66" s="64"/>
     </row>
-    <row r="67" s="10" customFormat="1" ht="17.4" spans="1:32">
+    <row r="67" s="10" customFormat="1" ht="17.5" spans="1:32">
       <c r="A67" s="137"/>
       <c r="B67" s="138"/>
       <c r="C67" s="138"/>
@@ -11282,7 +11279,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e527788e-4040-4eb9-b240-f64dca916c9a}</x14:id>
+          <x14:id>{8d0aded1-4143-40f1-9ac0-5c38c8372908}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11294,7 +11291,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{beb46d76-ffa3-424d-a154-d2f9fe58e590}</x14:id>
+          <x14:id>{83662cda-0437-427d-94dc-a322b0186e08}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11306,7 +11303,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5e2222b2-7c8d-446b-9c5a-0005acebdbe6}</x14:id>
+          <x14:id>{5288765b-381f-4792-9b78-d8b97f08ccbc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11318,7 +11315,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{843b83e2-d06f-46c8-8521-22d0a4051257}</x14:id>
+          <x14:id>{89cf19f1-adaa-4dba-b2f1-1e71f495ba90}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11330,7 +11327,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{795d8539-b6cd-468f-86b0-6fe17d6195de}</x14:id>
+          <x14:id>{dcd6313e-7496-4d6f-ada3-b28708696945}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11342,7 +11339,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{90020398-bdc5-46de-bafa-f85ed17ae972}</x14:id>
+          <x14:id>{ee46d742-4306-4044-95ca-b7c8c10c3504}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11354,7 +11351,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{69967096-2317-45f7-8247-151340b0dfec}</x14:id>
+          <x14:id>{1b3b0fa0-6687-4d67-a48b-99ee3f67b9ce}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11366,7 +11363,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a4a32341-a597-4648-87e3-dcb1001aea70}</x14:id>
+          <x14:id>{885c77b9-4f22-4c7c-824c-54592ccce73c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11380,7 +11377,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{27babd0b-79d1-4a92-bb2d-4cd4138aec80}</x14:id>
+          <x14:id>{39f193f4-360e-44ce-bc14-cf1569334ffa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11392,7 +11389,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5923fcbf-b963-4847-a08c-fd3471f7c77b}</x14:id>
+          <x14:id>{c483943f-04e1-4bac-b5fe-339a4e0295d2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11404,7 +11401,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8f9dacb1-9704-44d6-8586-53f712945d35}</x14:id>
+          <x14:id>{9775cfd3-279e-4f73-a20e-7021c3028507}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11416,7 +11413,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{974e5550-2954-4f71-a0c8-9496f388ff47}</x14:id>
+          <x14:id>{3137a65b-ba1a-45d3-92a7-1afa408f69e6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11428,7 +11425,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9f27453e-b038-488c-9239-fe35eea01dfb}</x14:id>
+          <x14:id>{a432d611-02ec-4e9f-98b8-9258b963c298}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11440,7 +11437,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{541529e2-6d51-4232-b980-393f4d8a3724}</x14:id>
+          <x14:id>{2933fba9-a965-4f74-9cff-a41e72ace753}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11452,7 +11449,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{594967a8-b30d-4a5b-aca4-9414a7e0aa24}</x14:id>
+          <x14:id>{cbab823d-1fe4-491c-b17f-6af014278bc9}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11464,7 +11461,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6903b435-54f0-4dc6-b8e6-a10860f67f4a}</x14:id>
+          <x14:id>{e2f5da0f-7716-49f2-b4af-3870cdf0edd2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11478,7 +11475,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{40c7af34-8452-4b7b-83cd-506ff67a80d6}</x14:id>
+          <x14:id>{648716b2-f99f-4ca8-90b3-5a3ff78be3a3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11490,7 +11487,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8d07e276-1a63-4ae2-9150-1aecf0a07f3a}</x14:id>
+          <x14:id>{a3bfbf76-1d83-457b-a087-24195c5bd539}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11502,7 +11499,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4aa53087-d18d-48da-9408-4291d57be9c2}</x14:id>
+          <x14:id>{0c10358d-f3a0-491b-bd4c-f5e6a80e0077}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11514,7 +11511,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e8d0d274-e4d8-4cc2-a473-17b516f42649}</x14:id>
+          <x14:id>{ce73792d-35a9-4b6a-84b1-13e971da357d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11526,7 +11523,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{57f53829-dcd1-494c-8ca1-2b193d3d6f35}</x14:id>
+          <x14:id>{61e388e1-99c7-429a-a438-1241459e5913}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11538,7 +11535,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3a0b7942-7e86-41b7-b33c-7a70035147f3}</x14:id>
+          <x14:id>{60125260-b435-4317-a57a-cccb46648748}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11550,7 +11547,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{602930ad-9409-4489-a65e-cdecd16a61fb}</x14:id>
+          <x14:id>{3e96df0c-f2bb-46ab-ad29-3346f60506e6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11562,7 +11559,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a944e513-65a5-44fd-89c0-8ac02931c187}</x14:id>
+          <x14:id>{b478b4f9-8986-433d-b3c8-28fb7666bd97}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11576,7 +11573,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2984bd09-c6f4-4de8-8394-93dd1521da18}</x14:id>
+          <x14:id>{ed25741f-43f9-467e-bfbb-d1af30557257}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11588,7 +11585,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d5240306-e489-4d87-a552-0177c90359bc}</x14:id>
+          <x14:id>{255b0ca1-f509-4178-8961-00782ffe475d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11600,7 +11597,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{341f6cba-74dd-4739-aa80-56d22f3e852a}</x14:id>
+          <x14:id>{97ec7b1b-4a50-4506-9c92-d45ff9945b94}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11612,7 +11609,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{916cdaa0-734d-4d5e-97cb-9e01ed78f6fc}</x14:id>
+          <x14:id>{ef7e9dd1-7d75-4b6c-a694-41efd28a287b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11624,7 +11621,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{056de079-a96d-4d7d-b010-b49eb8b9c5df}</x14:id>
+          <x14:id>{aa71b0f2-f7e2-4124-8f6b-8c9bc2364341}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11636,7 +11633,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{106b117f-8bcf-443f-9be7-248805547be1}</x14:id>
+          <x14:id>{b49bc04f-4fad-4403-894e-4d49b990c5e4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11648,7 +11645,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{27993b30-86e6-4273-91ab-16628e8c64d0}</x14:id>
+          <x14:id>{f8cd7a0b-a42f-484b-ab3b-a747ad377445}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11660,7 +11657,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7241de54-30de-4b00-9707-6edc6bfb121b}</x14:id>
+          <x14:id>{c2c620b6-103f-4fbe-884d-d7ba26efa313}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11674,7 +11671,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d167434e-8398-41ca-905a-9661763b52de}</x14:id>
+          <x14:id>{74106557-f1d6-4fa7-a3ad-33d638239944}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11686,7 +11683,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ddcda096-13b1-4ce8-ad67-f1d245a2ebb7}</x14:id>
+          <x14:id>{f70af14b-465b-41d6-8a56-5e5e925bc2d7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11698,7 +11695,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c55bc5cc-e67c-40f6-94ad-911db305c815}</x14:id>
+          <x14:id>{9d2b5d6d-e308-4e22-b764-14de0e953154}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11710,7 +11707,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b60ead94-5a05-4712-baea-12a6592738b9}</x14:id>
+          <x14:id>{24f9f3d5-ed75-4e62-8cc6-4b299c5642d0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11722,7 +11719,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9261e741-e472-460b-b605-6371c27bf379}</x14:id>
+          <x14:id>{67fbae23-352c-4d31-9a2f-0a7f3d652e10}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11734,7 +11731,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5c07fc3d-400f-4155-8b5c-c07c6b25815a}</x14:id>
+          <x14:id>{ca67e61f-4df2-45e0-bb01-90618c985762}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11746,7 +11743,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{24305cf6-7e05-4da6-a576-231f612dbc18}</x14:id>
+          <x14:id>{59064ea0-31b8-4ff7-89da-54aabc24a7d6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11758,7 +11755,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e1b78703-f0a3-49e3-8123-9708a33c0e97}</x14:id>
+          <x14:id>{e9d0d1da-3b3c-43a3-850a-aab851325ad5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11772,7 +11769,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c5710624-0574-4df3-a2d3-097a1ccbff19}</x14:id>
+          <x14:id>{f9a87c6b-1728-4cd9-81de-47524608b26e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11784,7 +11781,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{109bdd8a-684d-4777-af20-9f7045320647}</x14:id>
+          <x14:id>{5e992cfd-7f1f-4f7e-86d1-33fb5deb5e56}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11796,7 +11793,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{38e8cda6-f7b7-40b6-b9d3-82ff57bd0686}</x14:id>
+          <x14:id>{65c77e2a-e537-4763-be31-80c98e8eebef}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11808,7 +11805,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9493c9b5-50a2-488d-a732-c5adc6201100}</x14:id>
+          <x14:id>{8e4c1331-0eba-45a3-91e8-f428297fa27b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11820,7 +11817,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1bbf1d92-1b82-49ef-ac25-7702643b408b}</x14:id>
+          <x14:id>{a2960452-8125-4c3d-9f81-ff8b7e9ef4e3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11832,7 +11829,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c38e7502-72ab-4fd7-9e82-f983aae810d0}</x14:id>
+          <x14:id>{d99cfe6c-a537-4444-93d1-2e014c6e4b5d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11844,7 +11841,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{72854487-6ba0-4842-a6dc-421998794cf6}</x14:id>
+          <x14:id>{6ae1e5a7-8809-4a97-b781-6085af36b69e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11856,7 +11853,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{29801a6e-a32b-4362-bb49-dce3bd1b56ad}</x14:id>
+          <x14:id>{d9e08674-fb17-4803-aef1-16b8de7fd683}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11870,7 +11867,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cf0c93f5-04a7-44dd-b3db-4e3c014b4ab8}</x14:id>
+          <x14:id>{6df1fac9-f4e6-4e1f-bfd2-e5fdb062afa7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11882,7 +11879,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4fa68f15-ec46-4245-b465-c62c40cbfcf2}</x14:id>
+          <x14:id>{ae129520-1b46-4391-95cd-2cd1016a5d97}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11894,7 +11891,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{db44b9de-8939-43b3-8ff5-401170a2fa5d}</x14:id>
+          <x14:id>{9347ac97-e345-45b6-984e-012eca7b3690}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11908,7 +11905,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ebf91048-ce6e-4417-91ad-25c907c90f88}</x14:id>
+          <x14:id>{0c6a9090-9a77-437a-b36c-076667f14979}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11920,7 +11917,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ee0a650b-1747-453a-a2e1-0acebc4c0378}</x14:id>
+          <x14:id>{a3c209ef-e149-4997-9284-e1712e04c511}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11932,7 +11929,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7236781b-6e19-404a-8259-37e2f449db5b}</x14:id>
+          <x14:id>{99fab01f-8766-402b-840e-11c4ecd19a30}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11946,7 +11943,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8ba684fa-b383-4a51-8528-63e7fc6bed88}</x14:id>
+          <x14:id>{39902288-69af-4e9b-b677-e266e8dbf020}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11958,7 +11955,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7933c7c6-88b1-497a-8389-db74fcd97e6e}</x14:id>
+          <x14:id>{e7e26f93-1d9a-492d-abae-4a0cc0a9570f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11972,7 +11969,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dd1f5dc9-99bc-4ca5-a2eb-83402e2ac75b}</x14:id>
+          <x14:id>{60330284-ca3e-4db5-8167-31322af2fbd7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11984,7 +11981,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c6497908-49f9-4e4e-ae41-f9c33506780a}</x14:id>
+          <x14:id>{25fc206f-700f-4957-ae70-930d9b1a0d53}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11996,7 +11993,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3886edd2-0b5b-4f05-babc-34841f988ed1}</x14:id>
+          <x14:id>{dd8e3bca-3075-4346-8b30-b198a6ef45ec}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12010,7 +12007,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{317d55ee-5e4f-4b7f-b0aa-2b45ca7bb9b6}</x14:id>
+          <x14:id>{61e2dc8b-b332-432c-bf46-af2f903cd0e8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12022,7 +12019,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5519520e-e0b9-4eeb-98b1-215ae83cbdc9}</x14:id>
+          <x14:id>{39f2229e-d525-468b-bb7b-fd6901200396}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12034,7 +12031,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{22b1dd1a-a06d-4d4d-9f5b-8efd4050a449}</x14:id>
+          <x14:id>{73be0989-7a90-4b8b-b2ad-46e67260a956}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12048,7 +12045,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e2355309-e966-4c59-90fc-f37edb519a0e}</x14:id>
+          <x14:id>{e420d26c-7450-489b-a295-d7ef02fd8d55}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12060,7 +12057,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ac84ed84-07b1-4901-8663-7c6734ad28f5}</x14:id>
+          <x14:id>{e178d636-18f2-409d-add0-575545e202b2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12072,7 +12069,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9caf4a6a-7144-4065-acd7-f1d3f58c89c5}</x14:id>
+          <x14:id>{1bf3d859-9e37-4a27-9a68-e06202d20170}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12086,7 +12083,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ce3ee648-dba5-4a9e-9e97-a0e9d24930b7}</x14:id>
+          <x14:id>{66daf283-2bf2-4750-83d9-663b81b8005c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12098,7 +12095,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{75989a7e-b7a6-4751-a6b3-fb89d2438fd1}</x14:id>
+          <x14:id>{79b2658f-e5e2-437a-9806-821109e248a6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12110,7 +12107,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{190b8ad7-37fd-4d64-8e30-6160563cbcb1}</x14:id>
+          <x14:id>{4a3ba873-d863-490b-9489-cfdf5b235be0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12124,7 +12121,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6e86a603-2f0d-469f-902e-88e9544847b3}</x14:id>
+          <x14:id>{6a2306b9-bdfb-4588-bac8-a126ae932caa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12136,7 +12133,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c24fc8dc-355b-45ed-83aa-44d8a8e8990c}</x14:id>
+          <x14:id>{9a5fa538-4003-4ca7-8598-74b76865fa85}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12148,7 +12145,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{094a42fe-35d5-454b-8d26-7506085b5bfa}</x14:id>
+          <x14:id>{d4139a92-0c82-4f24-9db2-2e161d3634fa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12162,7 +12159,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c7bb73aa-5d97-4021-ba8e-49a940d24bc6}</x14:id>
+          <x14:id>{38acd70b-d4ff-4ccf-ae21-7e86366e77fc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12174,7 +12171,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9003f2b9-743c-4a19-ae35-706566283fe7}</x14:id>
+          <x14:id>{624d3da9-81f0-420b-ba55-351e633b6c05}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12186,7 +12183,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{13db177e-bfed-40da-aec3-79f64bd546d1}</x14:id>
+          <x14:id>{56995fcb-30e6-4f37-bd68-64936d8f1f6a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12198,7 +12195,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6430fa46-2bdb-4105-98ec-f3a1feb4b999}</x14:id>
+          <x14:id>{66d95c7c-5929-4b1f-98f9-8e3872dcb10b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12210,7 +12207,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{beb93417-ed26-4582-94e8-8d7eaf1a13cb}</x14:id>
+          <x14:id>{e02b969d-dfcd-4dc4-be76-75444ee20285}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12222,7 +12219,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b166b029-dc16-4afe-9fd2-2377903d2704}</x14:id>
+          <x14:id>{2e20262f-6769-4b25-bd93-7a71b7793350}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12234,7 +12231,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8258a538-94cc-4767-b391-e57fee97d8a5}</x14:id>
+          <x14:id>{72470def-0ab8-417f-a9e9-8286fe31cef4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12246,7 +12243,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{26e2c17f-7dbf-479c-805d-d33671165f38}</x14:id>
+          <x14:id>{17d57a83-718e-41bb-8b00-43ce4543e505}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12260,7 +12257,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9c5f469e-fd8c-4ff9-b68d-abd8cb241300}</x14:id>
+          <x14:id>{e90c9e35-a0bf-4040-8309-3d76e1d887ec}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12272,7 +12269,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fae02a16-ac25-49b6-8cb3-5ae056423150}</x14:id>
+          <x14:id>{9d5a571b-df9d-498a-918a-99e632300ed8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12286,7 +12283,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6eb786a4-7ab7-477d-8e61-e77466ff89a4}</x14:id>
+          <x14:id>{614f3d13-ea59-4e5b-9110-00cd04cb2661}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12300,7 +12297,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8e48a1c3-f861-44d7-8cc9-60016785ecf0}</x14:id>
+          <x14:id>{1409329f-dae1-4f18-b8a3-bd7ac8271eab}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12314,7 +12311,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b2dfba0a-6c94-4ca5-9844-2672341b8e88}</x14:id>
+          <x14:id>{9419a1b5-91a5-4199-aa72-9defc34c1275}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12328,7 +12325,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{13d8c857-4b8b-49a1-a15f-5ed56c885eae}</x14:id>
+          <x14:id>{dcc515c2-0d09-4a30-a54a-19c7dbd78334}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12342,7 +12339,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e553401f-4f17-4ba7-b754-22d92372e095}</x14:id>
+          <x14:id>{2807c010-cb44-4700-9e8e-7f6eb358d7c6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12354,7 +12351,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{32664af7-9dd0-48e3-ae8e-48f08cd4dd55}</x14:id>
+          <x14:id>{6e51a2ad-aa5f-4121-bda6-80ed2c4df6d2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12366,7 +12363,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f9cba129-2192-47fe-aa0a-42cf2b4ef931}</x14:id>
+          <x14:id>{a30a34dd-d3ea-4433-946a-a5c4656fc47c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12380,7 +12377,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{81b17492-8ef5-42e6-9be5-1256952c1cf4}</x14:id>
+          <x14:id>{74943210-1894-4cca-a91c-9bb7d9f2fd75}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12392,7 +12389,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cf0ebaf9-0b06-45c4-b712-3150a8f8bf10}</x14:id>
+          <x14:id>{db925445-2b0e-41e0-8b1e-3b217ef1abf6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12404,7 +12401,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{037a5f3b-48db-4aae-a9f6-8133e63502c7}</x14:id>
+          <x14:id>{37e6c090-f06d-4de9-82df-adbd7a20fce2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12418,7 +12415,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8d43437a-656d-4275-aa9e-6ef78be60cba}</x14:id>
+          <x14:id>{7c2ffc11-9213-4471-b56e-032e5deac7bd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12430,7 +12427,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{727dca93-2a80-426d-9663-5097d63bcdc7}</x14:id>
+          <x14:id>{5980e0f8-64e2-4145-8186-a9be4c931a6f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12442,7 +12439,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{fb2c07c2-0269-4cfc-9d64-6f0535ed445b}</x14:id>
+          <x14:id>{6ed04b1b-00c9-4fae-ac3b-3aa64c514c17}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12456,7 +12453,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3a21bed5-c665-4d0a-af0a-5e1bdec9ae16}</x14:id>
+          <x14:id>{478e5895-4295-4e9f-b814-6299289721e5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12468,7 +12465,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{29a44afb-68d9-42aa-b56d-dae68722c7be}</x14:id>
+          <x14:id>{239a24bb-dea8-48d3-943f-fec256f4db45}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12480,7 +12477,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ca725459-343a-4659-b5a6-3a7e836d5942}</x14:id>
+          <x14:id>{d973b141-ce96-4cee-a3c5-663b59d9dd7c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12494,7 +12491,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cc3ea6aa-c1a6-4989-9729-881fd01860ec}</x14:id>
+          <x14:id>{2dbbc97d-1fe6-436f-a01e-76a5005a245d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12506,7 +12503,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f2c259c4-9ae9-4dea-9dc0-122bb34ddf0a}</x14:id>
+          <x14:id>{41b050dd-66ff-4e91-a5f5-abc6841d88a6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12520,7 +12517,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{51a635ec-9505-4cfe-88ad-f8752b61094d}</x14:id>
+          <x14:id>{ac6dafd8-28fe-4f06-924a-9917f8ec1a2a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12532,7 +12529,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6034b704-e8e3-44c4-b347-1fe8d38e3642}</x14:id>
+          <x14:id>{0996a186-1fdf-4c39-b60f-59d930ba3cab}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12544,7 +12541,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{bf53c710-d80c-423e-bede-30ce958e3b67}</x14:id>
+          <x14:id>{e51cd375-1cfc-4ac3-80e3-c641f53c3738}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12558,7 +12555,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{271a1039-6f3a-4054-9562-6db4ef200aa1}</x14:id>
+          <x14:id>{6cb343c7-d842-4f02-ae99-1da199a65b26}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12570,7 +12567,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c98d3cfb-eab3-41d2-a6bf-c5a920e2be64}</x14:id>
+          <x14:id>{83957e30-1c44-4fbf-a367-de62d57322d6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12582,7 +12579,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f74cd777-c159-4d93-a72d-41dc551dec88}</x14:id>
+          <x14:id>{34004ebd-2745-4e67-91dd-b5979c7ef204}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12596,7 +12593,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{45408be5-592d-47f0-9e80-d41e2f23e4c5}</x14:id>
+          <x14:id>{5cf0402c-56eb-432d-82c1-f2eac8075ae4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12608,7 +12605,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4e2b9c44-e595-4c77-a6f8-1900b8d8f91f}</x14:id>
+          <x14:id>{41f04223-b2f7-4fea-a1ac-45b5b5cdeb26}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12642,7 +12639,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e527788e-4040-4eb9-b240-f64dca916c9a}">
+          <x14:cfRule type="dataBar" id="{8d0aded1-4143-40f1-9ac0-5c38c8372908}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12651,7 +12648,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{beb46d76-ffa3-424d-a154-d2f9fe58e590}">
+          <x14:cfRule type="dataBar" id="{83662cda-0437-427d-94dc-a322b0186e08}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12660,7 +12657,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5e2222b2-7c8d-446b-9c5a-0005acebdbe6}">
+          <x14:cfRule type="dataBar" id="{5288765b-381f-4792-9b78-d8b97f08ccbc}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12671,7 +12668,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{843b83e2-d06f-46c8-8521-22d0a4051257}">
+          <x14:cfRule type="dataBar" id="{89cf19f1-adaa-4dba-b2f1-1e71f495ba90}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12682,7 +12679,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{795d8539-b6cd-468f-86b0-6fe17d6195de}">
+          <x14:cfRule type="dataBar" id="{dcd6313e-7496-4d6f-ada3-b28708696945}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12693,14 +12690,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{90020398-bdc5-46de-bafa-f85ed17ae972}">
+          <x14:cfRule type="dataBar" id="{ee46d742-4306-4044-95ca-b7c8c10c3504}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{69967096-2317-45f7-8247-151340b0dfec}">
+          <x14:cfRule type="dataBar" id="{1b3b0fa0-6687-4d67-a48b-99ee3f67b9ce}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12711,7 +12708,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a4a32341-a597-4648-87e3-dcb1001aea70}">
+          <x14:cfRule type="dataBar" id="{885c77b9-4f22-4c7c-824c-54592ccce73c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12725,7 +12722,7 @@
           <xm:sqref>AD58</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{27babd0b-79d1-4a92-bb2d-4cd4138aec80}">
+          <x14:cfRule type="dataBar" id="{39f193f4-360e-44ce-bc14-cf1569334ffa}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12734,7 +12731,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5923fcbf-b963-4847-a08c-fd3471f7c77b}">
+          <x14:cfRule type="dataBar" id="{c483943f-04e1-4bac-b5fe-339a4e0295d2}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12743,7 +12740,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8f9dacb1-9704-44d6-8586-53f712945d35}">
+          <x14:cfRule type="dataBar" id="{9775cfd3-279e-4f73-a20e-7021c3028507}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12754,7 +12751,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{974e5550-2954-4f71-a0c8-9496f388ff47}">
+          <x14:cfRule type="dataBar" id="{3137a65b-ba1a-45d3-92a7-1afa408f69e6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12765,7 +12762,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9f27453e-b038-488c-9239-fe35eea01dfb}">
+          <x14:cfRule type="dataBar" id="{a432d611-02ec-4e9f-98b8-9258b963c298}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12776,14 +12773,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{541529e2-6d51-4232-b980-393f4d8a3724}">
+          <x14:cfRule type="dataBar" id="{2933fba9-a965-4f74-9cff-a41e72ace753}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{594967a8-b30d-4a5b-aca4-9414a7e0aa24}">
+          <x14:cfRule type="dataBar" id="{cbab823d-1fe4-491c-b17f-6af014278bc9}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12794,7 +12791,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6903b435-54f0-4dc6-b8e6-a10860f67f4a}">
+          <x14:cfRule type="dataBar" id="{e2f5da0f-7716-49f2-b4af-3870cdf0edd2}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12808,7 +12805,7 @@
           <xm:sqref>K62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{40c7af34-8452-4b7b-83cd-506ff67a80d6}">
+          <x14:cfRule type="dataBar" id="{648716b2-f99f-4ca8-90b3-5a3ff78be3a3}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12817,7 +12814,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8d07e276-1a63-4ae2-9150-1aecf0a07f3a}">
+          <x14:cfRule type="dataBar" id="{a3bfbf76-1d83-457b-a087-24195c5bd539}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12826,7 +12823,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4aa53087-d18d-48da-9408-4291d57be9c2}">
+          <x14:cfRule type="dataBar" id="{0c10358d-f3a0-491b-bd4c-f5e6a80e0077}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12837,7 +12834,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e8d0d274-e4d8-4cc2-a473-17b516f42649}">
+          <x14:cfRule type="dataBar" id="{ce73792d-35a9-4b6a-84b1-13e971da357d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12848,7 +12845,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{57f53829-dcd1-494c-8ca1-2b193d3d6f35}">
+          <x14:cfRule type="dataBar" id="{61e388e1-99c7-429a-a438-1241459e5913}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12859,14 +12856,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3a0b7942-7e86-41b7-b33c-7a70035147f3}">
+          <x14:cfRule type="dataBar" id="{60125260-b435-4317-a57a-cccb46648748}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{602930ad-9409-4489-a65e-cdecd16a61fb}">
+          <x14:cfRule type="dataBar" id="{3e96df0c-f2bb-46ab-ad29-3346f60506e6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12877,7 +12874,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a944e513-65a5-44fd-89c0-8ac02931c187}">
+          <x14:cfRule type="dataBar" id="{b478b4f9-8986-433d-b3c8-28fb7666bd97}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12891,7 +12888,7 @@
           <xm:sqref>AD62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2984bd09-c6f4-4de8-8394-93dd1521da18}">
+          <x14:cfRule type="dataBar" id="{ed25741f-43f9-467e-bfbb-d1af30557257}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12900,7 +12897,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d5240306-e489-4d87-a552-0177c90359bc}">
+          <x14:cfRule type="dataBar" id="{255b0ca1-f509-4178-8961-00782ffe475d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12909,7 +12906,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{341f6cba-74dd-4739-aa80-56d22f3e852a}">
+          <x14:cfRule type="dataBar" id="{97ec7b1b-4a50-4506-9c92-d45ff9945b94}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12920,7 +12917,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{916cdaa0-734d-4d5e-97cb-9e01ed78f6fc}">
+          <x14:cfRule type="dataBar" id="{ef7e9dd1-7d75-4b6c-a694-41efd28a287b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12931,7 +12928,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{056de079-a96d-4d7d-b010-b49eb8b9c5df}">
+          <x14:cfRule type="dataBar" id="{aa71b0f2-f7e2-4124-8f6b-8c9bc2364341}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12942,14 +12939,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{106b117f-8bcf-443f-9be7-248805547be1}">
+          <x14:cfRule type="dataBar" id="{b49bc04f-4fad-4403-894e-4d49b990c5e4}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{27993b30-86e6-4273-91ab-16628e8c64d0}">
+          <x14:cfRule type="dataBar" id="{f8cd7a0b-a42f-484b-ab3b-a747ad377445}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12960,7 +12957,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7241de54-30de-4b00-9707-6edc6bfb121b}">
+          <x14:cfRule type="dataBar" id="{c2c620b6-103f-4fbe-884d-d7ba26efa313}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12974,7 +12971,7 @@
           <xm:sqref>K63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{d167434e-8398-41ca-905a-9661763b52de}">
+          <x14:cfRule type="dataBar" id="{74106557-f1d6-4fa7-a3ad-33d638239944}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12983,7 +12980,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ddcda096-13b1-4ce8-ad67-f1d245a2ebb7}">
+          <x14:cfRule type="dataBar" id="{f70af14b-465b-41d6-8a56-5e5e925bc2d7}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12992,7 +12989,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c55bc5cc-e67c-40f6-94ad-911db305c815}">
+          <x14:cfRule type="dataBar" id="{9d2b5d6d-e308-4e22-b764-14de0e953154}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13003,7 +13000,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b60ead94-5a05-4712-baea-12a6592738b9}">
+          <x14:cfRule type="dataBar" id="{24f9f3d5-ed75-4e62-8cc6-4b299c5642d0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -13014,7 +13011,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9261e741-e472-460b-b605-6371c27bf379}">
+          <x14:cfRule type="dataBar" id="{67fbae23-352c-4d31-9a2f-0a7f3d652e10}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -13025,14 +13022,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5c07fc3d-400f-4155-8b5c-c07c6b25815a}">
+          <x14:cfRule type="dataBar" id="{ca67e61f-4df2-45e0-bb01-90618c985762}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{24305cf6-7e05-4da6-a576-231f612dbc18}">
+          <x14:cfRule type="dataBar" id="{59064ea0-31b8-4ff7-89da-54aabc24a7d6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13043,7 +13040,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e1b78703-f0a3-49e3-8123-9708a33c0e97}">
+          <x14:cfRule type="dataBar" id="{e9d0d1da-3b3c-43a3-850a-aab851325ad5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -13057,7 +13054,7 @@
           <xm:sqref>K64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c5710624-0574-4df3-a2d3-097a1ccbff19}">
+          <x14:cfRule type="dataBar" id="{f9a87c6b-1728-4cd9-81de-47524608b26e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13066,7 +13063,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{109bdd8a-684d-4777-af20-9f7045320647}">
+          <x14:cfRule type="dataBar" id="{5e992cfd-7f1f-4f7e-86d1-33fb5deb5e56}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13075,7 +13072,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{38e8cda6-f7b7-40b6-b9d3-82ff57bd0686}">
+          <x14:cfRule type="dataBar" id="{65c77e2a-e537-4763-be31-80c98e8eebef}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13086,7 +13083,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9493c9b5-50a2-488d-a732-c5adc6201100}">
+          <x14:cfRule type="dataBar" id="{8e4c1331-0eba-45a3-91e8-f428297fa27b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -13097,7 +13094,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1bbf1d92-1b82-49ef-ac25-7702643b408b}">
+          <x14:cfRule type="dataBar" id="{a2960452-8125-4c3d-9f81-ff8b7e9ef4e3}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -13108,14 +13105,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c38e7502-72ab-4fd7-9e82-f983aae810d0}">
+          <x14:cfRule type="dataBar" id="{d99cfe6c-a537-4444-93d1-2e014c6e4b5d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{72854487-6ba0-4842-a6dc-421998794cf6}">
+          <x14:cfRule type="dataBar" id="{6ae1e5a7-8809-4a97-b781-6085af36b69e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13126,7 +13123,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{29801a6e-a32b-4362-bb49-dce3bd1b56ad}">
+          <x14:cfRule type="dataBar" id="{d9e08674-fb17-4803-aef1-16b8de7fd683}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -13140,7 +13137,7 @@
           <xm:sqref>K65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cf0c93f5-04a7-44dd-b3db-4e3c014b4ab8}">
+          <x14:cfRule type="dataBar" id="{6df1fac9-f4e6-4e1f-bfd2-e5fdb062afa7}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13150,7 +13147,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4fa68f15-ec46-4245-b465-c62c40cbfcf2}">
+          <x14:cfRule type="dataBar" id="{ae129520-1b46-4391-95cd-2cd1016a5d97}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13159,7 +13156,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{db44b9de-8939-43b3-8ff5-401170a2fa5d}">
+          <x14:cfRule type="dataBar" id="{9347ac97-e345-45b6-984e-012eca7b3690}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13171,7 +13168,7 @@
           <xm:sqref>AB69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ebf91048-ce6e-4417-91ad-25c907c90f88}">
+          <x14:cfRule type="dataBar" id="{0c6a9090-9a77-437a-b36c-076667f14979}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13181,7 +13178,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ee0a650b-1747-453a-a2e1-0acebc4c0378}">
+          <x14:cfRule type="dataBar" id="{a3c209ef-e149-4997-9284-e1712e04c511}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13190,7 +13187,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7236781b-6e19-404a-8259-37e2f449db5b}">
+          <x14:cfRule type="dataBar" id="{99fab01f-8766-402b-840e-11c4ecd19a30}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13202,7 +13199,7 @@
           <xm:sqref>AB103</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8ba684fa-b383-4a51-8528-63e7fc6bed88}">
+          <x14:cfRule type="dataBar" id="{39902288-69af-4e9b-b677-e266e8dbf020}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13211,7 +13208,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{7933c7c6-88b1-497a-8389-db74fcd97e6e}">
+          <x14:cfRule type="dataBar" id="{e7e26f93-1d9a-492d-abae-4a0cc0a9570f}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13223,7 +13220,7 @@
           <xm:sqref>AB117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dd1f5dc9-99bc-4ca5-a2eb-83402e2ac75b}">
+          <x14:cfRule type="dataBar" id="{60330284-ca3e-4db5-8167-31322af2fbd7}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13233,7 +13230,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c6497908-49f9-4e4e-ae41-f9c33506780a}">
+          <x14:cfRule type="dataBar" id="{25fc206f-700f-4957-ae70-930d9b1a0d53}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13242,7 +13239,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3886edd2-0b5b-4f05-babc-34841f988ed1}">
+          <x14:cfRule type="dataBar" id="{dd8e3bca-3075-4346-8b30-b198a6ef45ec}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13254,7 +13251,7 @@
           <xm:sqref>AB127</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{317d55ee-5e4f-4b7f-b0aa-2b45ca7bb9b6}">
+          <x14:cfRule type="dataBar" id="{61e2dc8b-b332-432c-bf46-af2f903cd0e8}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13264,7 +13261,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5519520e-e0b9-4eeb-98b1-215ae83cbdc9}">
+          <x14:cfRule type="dataBar" id="{39f2229e-d525-468b-bb7b-fd6901200396}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13273,7 +13270,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{22b1dd1a-a06d-4d4d-9f5b-8efd4050a449}">
+          <x14:cfRule type="dataBar" id="{73be0989-7a90-4b8b-b2ad-46e67260a956}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13285,7 +13282,7 @@
           <xm:sqref>K137</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e2355309-e966-4c59-90fc-f37edb519a0e}">
+          <x14:cfRule type="dataBar" id="{e420d26c-7450-489b-a295-d7ef02fd8d55}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13295,7 +13292,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ac84ed84-07b1-4901-8663-7c6734ad28f5}">
+          <x14:cfRule type="dataBar" id="{e178d636-18f2-409d-add0-575545e202b2}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13304,7 +13301,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9caf4a6a-7144-4065-acd7-f1d3f58c89c5}">
+          <x14:cfRule type="dataBar" id="{1bf3d859-9e37-4a27-9a68-e06202d20170}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13316,7 +13313,7 @@
           <xm:sqref>K142</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ce3ee648-dba5-4a9e-9e97-a0e9d24930b7}">
+          <x14:cfRule type="dataBar" id="{66daf283-2bf2-4750-83d9-663b81b8005c}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13326,7 +13323,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{75989a7e-b7a6-4751-a6b3-fb89d2438fd1}">
+          <x14:cfRule type="dataBar" id="{79b2658f-e5e2-437a-9806-821109e248a6}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13335,7 +13332,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{190b8ad7-37fd-4d64-8e30-6160563cbcb1}">
+          <x14:cfRule type="dataBar" id="{4a3ba873-d863-490b-9489-cfdf5b235be0}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13347,7 +13344,7 @@
           <xm:sqref>K147</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6e86a603-2f0d-469f-902e-88e9544847b3}">
+          <x14:cfRule type="dataBar" id="{6a2306b9-bdfb-4588-bac8-a126ae932caa}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13357,7 +13354,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c24fc8dc-355b-45ed-83aa-44d8a8e8990c}">
+          <x14:cfRule type="dataBar" id="{9a5fa538-4003-4ca7-8598-74b76865fa85}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13366,7 +13363,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{094a42fe-35d5-454b-8d26-7506085b5bfa}">
+          <x14:cfRule type="dataBar" id="{d4139a92-0c82-4f24-9db2-2e161d3634fa}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13378,7 +13375,7 @@
           <xm:sqref>K152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{c7bb73aa-5d97-4021-ba8e-49a940d24bc6}">
+          <x14:cfRule type="dataBar" id="{38acd70b-d4ff-4ccf-ae21-7e86366e77fc}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13387,7 +13384,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9003f2b9-743c-4a19-ae35-706566283fe7}">
+          <x14:cfRule type="dataBar" id="{624d3da9-81f0-420b-ba55-351e633b6c05}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13396,7 +13393,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{13db177e-bfed-40da-aec3-79f64bd546d1}">
+          <x14:cfRule type="dataBar" id="{56995fcb-30e6-4f37-bd68-64936d8f1f6a}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13407,7 +13404,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6430fa46-2bdb-4105-98ec-f3a1feb4b999}">
+          <x14:cfRule type="dataBar" id="{66d95c7c-5929-4b1f-98f9-8e3872dcb10b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -13418,7 +13415,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{beb93417-ed26-4582-94e8-8d7eaf1a13cb}">
+          <x14:cfRule type="dataBar" id="{e02b969d-dfcd-4dc4-be76-75444ee20285}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -13429,14 +13426,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b166b029-dc16-4afe-9fd2-2377903d2704}">
+          <x14:cfRule type="dataBar" id="{2e20262f-6769-4b25-bd93-7a71b7793350}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8258a538-94cc-4767-b391-e57fee97d8a5}">
+          <x14:cfRule type="dataBar" id="{72470def-0ab8-417f-a9e9-8286fe31cef4}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13447,7 +13444,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{26e2c17f-7dbf-479c-805d-d33671165f38}">
+          <x14:cfRule type="dataBar" id="{17d57a83-718e-41bb-8b00-43ce4543e505}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -13461,7 +13458,7 @@
           <xm:sqref>K59:K60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9c5f469e-fd8c-4ff9-b68d-abd8cb241300}">
+          <x14:cfRule type="dataBar" id="{e90c9e35-a0bf-4040-8309-3d76e1d887ec}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13471,7 +13468,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{fae02a16-ac25-49b6-8cb3-5ae056423150}">
+          <x14:cfRule type="dataBar" id="{9d5a571b-df9d-498a-918a-99e632300ed8}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13483,7 +13480,7 @@
           <xm:sqref>Y69:Y88</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6eb786a4-7ab7-477d-8e61-e77466ff89a4}">
+          <x14:cfRule type="dataBar" id="{614f3d13-ea59-4e5b-9110-00cd04cb2661}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13496,7 +13493,7 @@
           <xm:sqref>Y79:Y88</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8e48a1c3-f861-44d7-8cc9-60016785ecf0}">
+          <x14:cfRule type="dataBar" id="{1409329f-dae1-4f18-b8a3-bd7ac8271eab}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13509,7 +13506,7 @@
           <xm:sqref>AB117:AB126</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{b2dfba0a-6c94-4ca5-9844-2672341b8e88}">
+          <x14:cfRule type="dataBar" id="{9419a1b5-91a5-4199-aa72-9defc34c1275}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13521,7 +13518,7 @@
           <xm:sqref>AD58:AE59</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{13d8c857-4b8b-49a1-a15f-5ed56c885eae}">
+          <x14:cfRule type="dataBar" id="{dcc515c2-0d09-4a30-a54a-19c7dbd78334}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13533,7 +13530,7 @@
           <xm:sqref>AD62:AE65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e553401f-4f17-4ba7-b754-22d92372e095}">
+          <x14:cfRule type="dataBar" id="{2807c010-cb44-4700-9e8e-7f6eb358d7c6}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13543,7 +13540,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{32664af7-9dd0-48e3-ae8e-48f08cd4dd55}">
+          <x14:cfRule type="dataBar" id="{6e51a2ad-aa5f-4121-bda6-80ed2c4df6d2}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13552,7 +13549,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f9cba129-2192-47fe-aa0a-42cf2b4ef931}">
+          <x14:cfRule type="dataBar" id="{a30a34dd-d3ea-4433-946a-a5c4656fc47c}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13564,7 +13561,7 @@
           <xm:sqref>F69 F74 F79 F84</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{81b17492-8ef5-42e6-9be5-1256952c1cf4}">
+          <x14:cfRule type="dataBar" id="{74943210-1894-4cca-a91c-9bb7d9f2fd75}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13574,7 +13571,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{cf0ebaf9-0b06-45c4-b712-3150a8f8bf10}">
+          <x14:cfRule type="dataBar" id="{db925445-2b0e-41e0-8b1e-3b217ef1abf6}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13583,7 +13580,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{037a5f3b-48db-4aae-a9f6-8133e63502c7}">
+          <x14:cfRule type="dataBar" id="{37e6c090-f06d-4de9-82df-adbd7a20fce2}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13595,7 +13592,7 @@
           <xm:sqref>K69 K79 K89 K103</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8d43437a-656d-4275-aa9e-6ef78be60cba}">
+          <x14:cfRule type="dataBar" id="{7c2ffc11-9213-4471-b56e-032e5deac7bd}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13605,7 +13602,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{727dca93-2a80-426d-9663-5097d63bcdc7}">
+          <x14:cfRule type="dataBar" id="{5980e0f8-64e2-4145-8186-a9be4c931a6f}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13614,7 +13611,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{fb2c07c2-0269-4cfc-9d64-6f0535ed445b}">
+          <x14:cfRule type="dataBar" id="{6ed04b1b-00c9-4fae-ac3b-3aa64c514c17}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13626,7 +13623,7 @@
           <xm:sqref>AB79 AB89</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3a21bed5-c665-4d0a-af0a-5e1bdec9ae16}">
+          <x14:cfRule type="dataBar" id="{478e5895-4295-4e9f-b814-6299289721e5}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13636,7 +13633,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{29a44afb-68d9-42aa-b56d-dae68722c7be}">
+          <x14:cfRule type="dataBar" id="{239a24bb-dea8-48d3-943f-fec256f4db45}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13645,7 +13642,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ca725459-343a-4659-b5a6-3a7e836d5942}">
+          <x14:cfRule type="dataBar" id="{d973b141-ce96-4cee-a3c5-663b59d9dd7c}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13657,7 +13654,7 @@
           <xm:sqref>F89 F96 F103 F110</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{cc3ea6aa-c1a6-4989-9729-881fd01860ec}">
+          <x14:cfRule type="dataBar" id="{2dbbc97d-1fe6-436f-a01e-76a5005a245d}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13667,7 +13664,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f2c259c4-9ae9-4dea-9dc0-122bb34ddf0a}">
+          <x14:cfRule type="dataBar" id="{41b050dd-66ff-4e91-a5f5-abc6841d88a6}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13679,7 +13676,7 @@
           <xm:sqref>Y89 Y103</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{51a635ec-9505-4cfe-88ad-f8752b61094d}">
+          <x14:cfRule type="dataBar" id="{ac6dafd8-28fe-4f06-924a-9917f8ec1a2a}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13689,7 +13686,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6034b704-e8e3-44c4-b347-1fe8d38e3642}">
+          <x14:cfRule type="dataBar" id="{0996a186-1fdf-4c39-b60f-59d930ba3cab}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13698,7 +13695,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{bf53c710-d80c-423e-bede-30ce958e3b67}">
+          <x14:cfRule type="dataBar" id="{e51cd375-1cfc-4ac3-80e3-c641f53c3738}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13710,7 +13707,7 @@
           <xm:sqref>F117 F122 F127 F132 F137 F142 F147 F152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{271a1039-6f3a-4054-9562-6db4ef200aa1}">
+          <x14:cfRule type="dataBar" id="{6cb343c7-d842-4f02-ae99-1da199a65b26}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13720,7 +13717,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c98d3cfb-eab3-41d2-a6bf-c5a920e2be64}">
+          <x14:cfRule type="dataBar" id="{83957e30-1c44-4fbf-a367-de62d57322d6}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13729,7 +13726,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f74cd777-c159-4d93-a72d-41dc551dec88}">
+          <x14:cfRule type="dataBar" id="{34004ebd-2745-4e67-91dd-b5979c7ef204}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13741,7 +13738,7 @@
           <xm:sqref>K117 K127</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{45408be5-592d-47f0-9e80-d41e2f23e4c5}">
+          <x14:cfRule type="dataBar" id="{5cf0402c-56eb-432d-82c1-f2eac8075ae4}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13751,7 +13748,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4e2b9c44-e595-4c77-a6f8-1900b8d8f91f}">
+          <x14:cfRule type="dataBar" id="{41f04223-b2f7-4fea-a1ac-45b5b5cdeb26}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13772,12 +13769,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="26.8796296296296" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.37962962962963" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.22222222222222" style="1" customWidth="1"/>
-    <col min="18" max="18" width="9.37962962962963" style="1" customWidth="1"/>
+    <col min="1" max="1" width="26.8818181818182" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.38181818181818" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.21818181818182" style="1" customWidth="1"/>
+    <col min="18" max="18" width="9.38181818181818" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">

--- a/外网端源码/其他楼交接班容量报表空模板.xlsx
+++ b/外网端源码/其他楼交接班容量报表空模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView windowHeight="22020"/>
   </bookViews>
   <sheets>
     <sheet name="本班组" sheetId="1" r:id="rId1"/>
@@ -3210,28 +3210,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AF156"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="18.1818181818182" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.1851851851852" style="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1" customWidth="1"/>
     <col min="5" max="5" width="9" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.9363636363636" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.9351851851852" style="1" customWidth="1"/>
     <col min="7" max="8" width="9" style="1" customWidth="1"/>
-    <col min="9" max="9" width="16.4090909090909" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.4074074074074" style="1" customWidth="1"/>
     <col min="10" max="11" width="9" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.9363636363636" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.9351851851852" style="1" customWidth="1"/>
     <col min="13" max="13" width="9" style="1" customWidth="1"/>
-    <col min="14" max="14" width="8.75454545454545" style="1" customWidth="1"/>
-    <col min="15" max="15" width="38.1818181818182" style="1" customWidth="1"/>
+    <col min="14" max="14" width="8.75" style="1" customWidth="1"/>
+    <col min="15" max="15" width="38.1851851851852" style="1" customWidth="1"/>
     <col min="16" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="12.5909090909091" style="1" customWidth="1"/>
-    <col min="20" max="20" width="16.5090909090909" style="1" customWidth="1"/>
+    <col min="19" max="19" width="12.5925925925926" style="1" customWidth="1"/>
+    <col min="20" max="20" width="16.5092592592593" style="1" customWidth="1"/>
     <col min="21" max="21" width="9" style="1" customWidth="1"/>
-    <col min="22" max="22" width="14.1545454545455" style="1" customWidth="1"/>
+    <col min="22" max="22" width="14.1574074074074" style="1" customWidth="1"/>
     <col min="23" max="24" width="9" style="1" customWidth="1"/>
-    <col min="25" max="25" width="10.2545454545455" style="1" customWidth="1"/>
+    <col min="25" max="25" width="10.25" style="1" customWidth="1"/>
     <col min="26" max="27" width="9" style="1" customWidth="1"/>
-    <col min="28" max="28" width="17.4181818181818" style="1" customWidth="1"/>
+    <col min="28" max="28" width="17.4166666666667" style="1" customWidth="1"/>
     <col min="31" max="31" width="11" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6415,7 +6415,7 @@
       <c r="AD66" s="64"/>
       <c r="AE66" s="64"/>
     </row>
-    <row r="67" s="10" customFormat="1" ht="17.5" spans="1:32">
+    <row r="67" s="10" customFormat="1" ht="17.4" spans="1:32">
       <c r="A67" s="137"/>
       <c r="B67" s="138"/>
       <c r="C67" s="138"/>
@@ -6608,8 +6608,8 @@
         <v>168</v>
       </c>
       <c r="AB69" s="145">
-        <f>67/Z69</f>
-        <v>0.394117647058824</v>
+        <f>AA69/Z69</f>
+        <v>0.988235294117647</v>
       </c>
       <c r="AC69" s="152">
         <v>0</v>
@@ -7099,8 +7099,8 @@
         <v>170</v>
       </c>
       <c r="AB79" s="145">
-        <f>77/Z79</f>
-        <v>0.452941176470588</v>
+        <f>AA79/Z79</f>
+        <v>1</v>
       </c>
       <c r="AC79" s="144" t="s">
         <v>225</v>
@@ -7590,8 +7590,8 @@
         <v>140</v>
       </c>
       <c r="AB89" s="145">
-        <f>87/Z89</f>
-        <v>0.564935064935065</v>
+        <f>AA89/Z89</f>
+        <v>0.909090909090909</v>
       </c>
       <c r="AC89" s="144" t="s">
         <v>225</v>
@@ -8257,8 +8257,8 @@
         <v>152</v>
       </c>
       <c r="AB103" s="145">
-        <f>101/Z103</f>
-        <v>0.655844155844156</v>
+        <f>AA103/Z103</f>
+        <v>0.987012987012987</v>
       </c>
       <c r="AC103" s="144" t="s">
         <v>225</v>
@@ -8924,8 +8924,8 @@
         <v>170</v>
       </c>
       <c r="AB117" s="145">
-        <f>115/Z117</f>
-        <v>0.676470588235294</v>
+        <f>AA117/Z117</f>
+        <v>1</v>
       </c>
       <c r="AC117" s="144" t="s">
         <v>225</v>
@@ -9415,8 +9415,8 @@
         <v>170</v>
       </c>
       <c r="AB127" s="145">
-        <f>125/Z127</f>
-        <v>0.735294117647059</v>
+        <f>AA127/Z127</f>
+        <v>1</v>
       </c>
       <c r="AC127" s="144" t="s">
         <v>225</v>
@@ -11279,7 +11279,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8d0aded1-4143-40f1-9ac0-5c38c8372908}</x14:id>
+          <x14:id>{73c02118-5cb8-477b-bb66-0749c0556986}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11291,7 +11291,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{83662cda-0437-427d-94dc-a322b0186e08}</x14:id>
+          <x14:id>{1fdac81f-152a-401f-a406-2dbda8b03307}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11303,7 +11303,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5288765b-381f-4792-9b78-d8b97f08ccbc}</x14:id>
+          <x14:id>{155ff1b4-4f41-49e7-91d1-b7a03378bfbd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11315,7 +11315,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{89cf19f1-adaa-4dba-b2f1-1e71f495ba90}</x14:id>
+          <x14:id>{ded03ecf-b230-46af-a038-fd017a7be69e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11327,7 +11327,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dcd6313e-7496-4d6f-ada3-b28708696945}</x14:id>
+          <x14:id>{4d58eff6-d055-4be3-9ec7-ddc824368508}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11339,7 +11339,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ee46d742-4306-4044-95ca-b7c8c10c3504}</x14:id>
+          <x14:id>{a7ddd285-2f63-4e2f-97b8-2eb771098c46}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11351,7 +11351,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1b3b0fa0-6687-4d67-a48b-99ee3f67b9ce}</x14:id>
+          <x14:id>{a80ec421-286f-416c-ae1b-3da0667ba041}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11363,7 +11363,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{885c77b9-4f22-4c7c-824c-54592ccce73c}</x14:id>
+          <x14:id>{336093d7-f6f9-4eaa-abfe-27bdb61fd5cd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11377,7 +11377,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{39f193f4-360e-44ce-bc14-cf1569334ffa}</x14:id>
+          <x14:id>{7700b340-72b2-492f-a26a-160bde7f0b0e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11389,7 +11389,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c483943f-04e1-4bac-b5fe-339a4e0295d2}</x14:id>
+          <x14:id>{8d270c6a-24e8-4c99-9daa-804ac00f51c5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11401,7 +11401,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9775cfd3-279e-4f73-a20e-7021c3028507}</x14:id>
+          <x14:id>{15e3ecc6-8480-466c-9228-0e7c006ebf75}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11413,7 +11413,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3137a65b-ba1a-45d3-92a7-1afa408f69e6}</x14:id>
+          <x14:id>{43ba113c-1cff-433a-9fb0-5f11f7b6f974}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11425,7 +11425,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a432d611-02ec-4e9f-98b8-9258b963c298}</x14:id>
+          <x14:id>{25711304-e4d7-4d00-8539-9fca79c63cc6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11437,7 +11437,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2933fba9-a965-4f74-9cff-a41e72ace753}</x14:id>
+          <x14:id>{c394a1f1-3955-4f33-9a69-40c63db80e34}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11449,7 +11449,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{cbab823d-1fe4-491c-b17f-6af014278bc9}</x14:id>
+          <x14:id>{690b3837-2a99-4d57-ab99-1dc5181f5804}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11461,7 +11461,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e2f5da0f-7716-49f2-b4af-3870cdf0edd2}</x14:id>
+          <x14:id>{d1d22f59-c737-4c52-ae59-0a82cb30cfc6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11475,7 +11475,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{648716b2-f99f-4ca8-90b3-5a3ff78be3a3}</x14:id>
+          <x14:id>{0a57afe2-c83d-4551-842d-2e3608f61ab5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11487,7 +11487,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a3bfbf76-1d83-457b-a087-24195c5bd539}</x14:id>
+          <x14:id>{f20f7ca4-dba7-43ba-a8be-d134dea37f09}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11499,7 +11499,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0c10358d-f3a0-491b-bd4c-f5e6a80e0077}</x14:id>
+          <x14:id>{d5391ce5-2ed6-461b-8c5c-684fd066950e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11511,7 +11511,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ce73792d-35a9-4b6a-84b1-13e971da357d}</x14:id>
+          <x14:id>{31bfa20a-01ad-47ef-97e3-d8d184f1c002}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11523,7 +11523,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{61e388e1-99c7-429a-a438-1241459e5913}</x14:id>
+          <x14:id>{07e32b69-c5a1-484f-8514-309b5db065fc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11535,7 +11535,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{60125260-b435-4317-a57a-cccb46648748}</x14:id>
+          <x14:id>{a84c283d-c844-4601-b27c-a765e3691046}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11547,7 +11547,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3e96df0c-f2bb-46ab-ad29-3346f60506e6}</x14:id>
+          <x14:id>{8454aba1-a285-4af0-afa1-dc93bdf48d92}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11559,7 +11559,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b478b4f9-8986-433d-b3c8-28fb7666bd97}</x14:id>
+          <x14:id>{e2979b20-b50e-4810-a777-3eb0f67da7d4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11573,7 +11573,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ed25741f-43f9-467e-bfbb-d1af30557257}</x14:id>
+          <x14:id>{a941c2e6-cd4b-48c3-9514-ff73354e0b17}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11585,7 +11585,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{255b0ca1-f509-4178-8961-00782ffe475d}</x14:id>
+          <x14:id>{15dc8f63-0528-4394-bfac-2d81a584af6b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11597,7 +11597,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{97ec7b1b-4a50-4506-9c92-d45ff9945b94}</x14:id>
+          <x14:id>{7e949394-3dbe-400c-ad2f-526c4447ce81}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11609,7 +11609,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ef7e9dd1-7d75-4b6c-a694-41efd28a287b}</x14:id>
+          <x14:id>{ff4ba2d2-b4b4-4d76-b4b8-20eab89f17af}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11621,7 +11621,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{aa71b0f2-f7e2-4124-8f6b-8c9bc2364341}</x14:id>
+          <x14:id>{82e1bac3-b6fd-4251-8e5e-e06d21dda340}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11633,7 +11633,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{b49bc04f-4fad-4403-894e-4d49b990c5e4}</x14:id>
+          <x14:id>{228f1afe-b83a-4e56-97a1-79c84a9ba74d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11645,7 +11645,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f8cd7a0b-a42f-484b-ab3b-a747ad377445}</x14:id>
+          <x14:id>{ff09f55e-a5b0-424d-9055-947942d7b714}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11657,7 +11657,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{c2c620b6-103f-4fbe-884d-d7ba26efa313}</x14:id>
+          <x14:id>{790328fa-2cb8-4c06-b3ff-c6df26c0f760}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11671,7 +11671,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{74106557-f1d6-4fa7-a3ad-33d638239944}</x14:id>
+          <x14:id>{bbebd8f5-bc32-4b2a-89e8-d27c8469b341}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11683,7 +11683,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f70af14b-465b-41d6-8a56-5e5e925bc2d7}</x14:id>
+          <x14:id>{4f9580a7-5dd2-47e7-89c7-2d1e14426fb2}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11695,7 +11695,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9d2b5d6d-e308-4e22-b764-14de0e953154}</x14:id>
+          <x14:id>{fbc45b9a-faa4-45dd-84ee-eeb3d56d87ff}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11707,7 +11707,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{24f9f3d5-ed75-4e62-8cc6-4b299c5642d0}</x14:id>
+          <x14:id>{5c249b40-7c24-4888-9589-22d3bc1313dd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11719,7 +11719,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{67fbae23-352c-4d31-9a2f-0a7f3d652e10}</x14:id>
+          <x14:id>{dab13ebb-7f1a-477b-bbf2-dd8bedc24eb8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11731,7 +11731,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ca67e61f-4df2-45e0-bb01-90618c985762}</x14:id>
+          <x14:id>{1023eaa0-fcd6-4473-8872-40c5d4f7ec95}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11743,7 +11743,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{59064ea0-31b8-4ff7-89da-54aabc24a7d6}</x14:id>
+          <x14:id>{e7923aef-64de-4013-8fd5-84af8adaa48f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11755,7 +11755,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e9d0d1da-3b3c-43a3-850a-aab851325ad5}</x14:id>
+          <x14:id>{bcf0e6ba-465e-430c-88c2-c58371109ca8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11769,7 +11769,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{f9a87c6b-1728-4cd9-81de-47524608b26e}</x14:id>
+          <x14:id>{6faf4040-6964-4bc8-a9c9-3ef201e4eccc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11781,7 +11781,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5e992cfd-7f1f-4f7e-86d1-33fb5deb5e56}</x14:id>
+          <x14:id>{c13e8aa0-2804-446a-9394-119396f0c772}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11793,7 +11793,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{65c77e2a-e537-4763-be31-80c98e8eebef}</x14:id>
+          <x14:id>{9093dd3b-fd64-4b44-87fd-7e1090655b3c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11805,7 +11805,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8e4c1331-0eba-45a3-91e8-f428297fa27b}</x14:id>
+          <x14:id>{0af248ea-cdda-4b7c-8e41-f74d17590f12}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11817,7 +11817,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a2960452-8125-4c3d-9f81-ff8b7e9ef4e3}</x14:id>
+          <x14:id>{930ea78d-7128-4baf-a65c-6c98c8801f56}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11829,7 +11829,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d99cfe6c-a537-4444-93d1-2e014c6e4b5d}</x14:id>
+          <x14:id>{13d1c43b-5426-45b7-bb2f-56e2a05ded24}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11841,7 +11841,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6ae1e5a7-8809-4a97-b781-6085af36b69e}</x14:id>
+          <x14:id>{4b17d84d-355c-42c4-83ad-ec0685c4b2fc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11853,7 +11853,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d9e08674-fb17-4803-aef1-16b8de7fd683}</x14:id>
+          <x14:id>{69d2ebf6-9f93-4a4f-872b-af12bcf15c53}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11867,7 +11867,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6df1fac9-f4e6-4e1f-bfd2-e5fdb062afa7}</x14:id>
+          <x14:id>{6e3d7163-81a6-469a-acb0-8768107d1d41}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11879,7 +11879,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ae129520-1b46-4391-95cd-2cd1016a5d97}</x14:id>
+          <x14:id>{e60c68d0-3d36-4bdf-b650-1893a7bcd87e}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11891,7 +11891,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9347ac97-e345-45b6-984e-012eca7b3690}</x14:id>
+          <x14:id>{82c30bd8-9112-4ee6-9a60-e088abe0e57c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11905,7 +11905,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0c6a9090-9a77-437a-b36c-076667f14979}</x14:id>
+          <x14:id>{66b85cd3-002a-415b-a3a7-186feaf1ad68}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11917,7 +11917,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a3c209ef-e149-4997-9284-e1712e04c511}</x14:id>
+          <x14:id>{469ea6e9-4e29-41da-b72b-3dda878b4d7a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11929,7 +11929,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{99fab01f-8766-402b-840e-11c4ecd19a30}</x14:id>
+          <x14:id>{74be8e9d-c07c-4f0e-83c1-427a07225c54}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11943,7 +11943,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{39902288-69af-4e9b-b677-e266e8dbf020}</x14:id>
+          <x14:id>{ab93e35c-e38f-4273-89bc-88808cce893c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11955,7 +11955,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e7e26f93-1d9a-492d-abae-4a0cc0a9570f}</x14:id>
+          <x14:id>{ef7b15c5-6c96-4f44-84af-12a2476fe3a3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11969,7 +11969,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{60330284-ca3e-4db5-8167-31322af2fbd7}</x14:id>
+          <x14:id>{e51813bf-10f6-4bbe-a762-955926720f6a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11981,7 +11981,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{25fc206f-700f-4957-ae70-930d9b1a0d53}</x14:id>
+          <x14:id>{35a899bc-541d-4ea0-9e6c-84fead288b2b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11993,7 +11993,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dd8e3bca-3075-4346-8b30-b198a6ef45ec}</x14:id>
+          <x14:id>{5aacddd5-1e96-488d-bdcf-dde997447ffb}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12007,7 +12007,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{61e2dc8b-b332-432c-bf46-af2f903cd0e8}</x14:id>
+          <x14:id>{37a156c7-0251-4a7f-9777-c2eb7a829d54}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12019,7 +12019,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{39f2229e-d525-468b-bb7b-fd6901200396}</x14:id>
+          <x14:id>{98b3af3a-76d8-47fe-b609-7397e1de2d2b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12031,7 +12031,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{73be0989-7a90-4b8b-b2ad-46e67260a956}</x14:id>
+          <x14:id>{5e5f48e5-7d4d-40f8-b6c1-439eacab6977}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12045,7 +12045,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e420d26c-7450-489b-a295-d7ef02fd8d55}</x14:id>
+          <x14:id>{aedacfb4-2457-484e-9a7f-7d809d29a70b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12057,7 +12057,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e178d636-18f2-409d-add0-575545e202b2}</x14:id>
+          <x14:id>{a2ec5912-7b55-452e-acc0-e607a2315e44}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12069,7 +12069,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1bf3d859-9e37-4a27-9a68-e06202d20170}</x14:id>
+          <x14:id>{afcbfb7c-3ee6-44e4-8891-b8f7ea26df55}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12083,7 +12083,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{66daf283-2bf2-4750-83d9-663b81b8005c}</x14:id>
+          <x14:id>{f11993e2-90a1-4c4a-a792-f25cc1e88b49}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12095,7 +12095,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{79b2658f-e5e2-437a-9806-821109e248a6}</x14:id>
+          <x14:id>{20bf9ea3-2339-49e2-b9f2-2aac44f0828c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12107,7 +12107,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{4a3ba873-d863-490b-9489-cfdf5b235be0}</x14:id>
+          <x14:id>{71826df5-7d66-4b3d-b2fe-e4e22da0d47b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12121,7 +12121,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6a2306b9-bdfb-4588-bac8-a126ae932caa}</x14:id>
+          <x14:id>{48eefdbc-3383-4f15-9fdd-ec260f7e5b8f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12133,7 +12133,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9a5fa538-4003-4ca7-8598-74b76865fa85}</x14:id>
+          <x14:id>{6105d0f7-68cf-4a86-9927-e593458cf0bf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12145,7 +12145,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d4139a92-0c82-4f24-9db2-2e161d3634fa}</x14:id>
+          <x14:id>{f5b2456a-e0aa-4365-a8de-eb57ffea24ab}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12159,7 +12159,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{38acd70b-d4ff-4ccf-ae21-7e86366e77fc}</x14:id>
+          <x14:id>{1bc1fc5a-f4ca-4698-8df6-716db979012c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12171,7 +12171,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{624d3da9-81f0-420b-ba55-351e633b6c05}</x14:id>
+          <x14:id>{7d260e8e-58f8-4d91-841b-37c7406fd366}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12183,7 +12183,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{56995fcb-30e6-4f37-bd68-64936d8f1f6a}</x14:id>
+          <x14:id>{8d1ed4ec-3b90-4d7e-b50e-03b23b65d20f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12195,7 +12195,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{66d95c7c-5929-4b1f-98f9-8e3872dcb10b}</x14:id>
+          <x14:id>{86714f56-950c-42e4-b0cc-5c04e408e17f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12207,7 +12207,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e02b969d-dfcd-4dc4-be76-75444ee20285}</x14:id>
+          <x14:id>{284f9389-d273-47db-b93d-e146a5624cfa}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12219,7 +12219,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2e20262f-6769-4b25-bd93-7a71b7793350}</x14:id>
+          <x14:id>{c9849ecc-bbca-4f7d-9aed-d4228c6bd9b0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12231,7 +12231,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{72470def-0ab8-417f-a9e9-8286fe31cef4}</x14:id>
+          <x14:id>{11d77e64-3a5f-4151-8f36-fd357c6e3aec}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12243,7 +12243,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{17d57a83-718e-41bb-8b00-43ce4543e505}</x14:id>
+          <x14:id>{db5aad04-8c76-4233-aece-7b0abe9abc95}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12257,7 +12257,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e90c9e35-a0bf-4040-8309-3d76e1d887ec}</x14:id>
+          <x14:id>{024113f5-3286-4a94-83a9-88f327b6b5ab}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12269,7 +12269,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9d5a571b-df9d-498a-918a-99e632300ed8}</x14:id>
+          <x14:id>{3223f7be-d797-45a5-a955-ab8e9d1d7f77}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12283,7 +12283,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{614f3d13-ea59-4e5b-9110-00cd04cb2661}</x14:id>
+          <x14:id>{4571feab-aa4a-4bd4-90c0-d896a380606f}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12297,7 +12297,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1409329f-dae1-4f18-b8a3-bd7ac8271eab}</x14:id>
+          <x14:id>{497d6fb0-f689-4b97-8f1e-3b61a8b81bfe}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12311,7 +12311,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9419a1b5-91a5-4199-aa72-9defc34c1275}</x14:id>
+          <x14:id>{4de2becd-715b-47b6-97d9-78c51cc640ce}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12325,7 +12325,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dcc515c2-0d09-4a30-a54a-19c7dbd78334}</x14:id>
+          <x14:id>{4471bd21-baf3-46fc-842a-bbc22847eb0d}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12339,7 +12339,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2807c010-cb44-4700-9e8e-7f6eb358d7c6}</x14:id>
+          <x14:id>{2ef53344-397d-4fc3-abe1-c86596bef512}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12351,7 +12351,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6e51a2ad-aa5f-4121-bda6-80ed2c4df6d2}</x14:id>
+          <x14:id>{741f17ac-33c5-4b7d-bc2c-7fe58896402c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12363,7 +12363,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{a30a34dd-d3ea-4433-946a-a5c4656fc47c}</x14:id>
+          <x14:id>{20c99214-525e-4179-a8de-11835006f617}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12377,7 +12377,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{74943210-1894-4cca-a91c-9bb7d9f2fd75}</x14:id>
+          <x14:id>{834f3c37-b68f-4ef7-b8ac-f6f156269954}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12389,7 +12389,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{db925445-2b0e-41e0-8b1e-3b217ef1abf6}</x14:id>
+          <x14:id>{8035aea1-948e-4711-8fa6-1a8efd747baf}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12401,7 +12401,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{37e6c090-f06d-4de9-82df-adbd7a20fce2}</x14:id>
+          <x14:id>{0187092f-e124-4879-8dce-051f82127eff}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12415,7 +12415,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7c2ffc11-9213-4471-b56e-032e5deac7bd}</x14:id>
+          <x14:id>{e2b76e9a-8291-41ed-a845-bbb79a1a7a1a}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12427,7 +12427,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5980e0f8-64e2-4145-8186-a9be4c931a6f}</x14:id>
+          <x14:id>{c31e442e-7f62-4d59-88b9-d9ff4a15a735}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12439,7 +12439,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6ed04b1b-00c9-4fae-ac3b-3aa64c514c17}</x14:id>
+          <x14:id>{1ad57c6d-905c-40a6-8db2-756dee10e9dd}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12453,7 +12453,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{478e5895-4295-4e9f-b814-6299289721e5}</x14:id>
+          <x14:id>{19f4624a-2578-43b7-b16e-cb50df3f6e6c}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12465,7 +12465,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{239a24bb-dea8-48d3-943f-fec256f4db45}</x14:id>
+          <x14:id>{3ce6b947-e4a4-4ca3-aa18-34d6136f3e5b}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12477,7 +12477,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{d973b141-ce96-4cee-a3c5-663b59d9dd7c}</x14:id>
+          <x14:id>{c2698b09-8fcc-4d52-99ad-7509cac2e8a0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12491,7 +12491,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2dbbc97d-1fe6-436f-a01e-76a5005a245d}</x14:id>
+          <x14:id>{1a837990-9ce8-4b12-956a-2018c5890e74}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12503,7 +12503,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{41b050dd-66ff-4e91-a5f5-abc6841d88a6}</x14:id>
+          <x14:id>{fad696cb-39f6-4f11-b300-2f1d21ae73d7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12517,7 +12517,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{ac6dafd8-28fe-4f06-924a-9917f8ec1a2a}</x14:id>
+          <x14:id>{f593ee51-1ef8-42b2-813b-90944cf04565}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12529,7 +12529,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0996a186-1fdf-4c39-b60f-59d930ba3cab}</x14:id>
+          <x14:id>{b7ed5740-f248-4c9e-8e83-3364f996a2ce}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12541,7 +12541,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{e51cd375-1cfc-4ac3-80e3-c641f53c3738}</x14:id>
+          <x14:id>{440a2f9b-5480-4162-a177-953454b634d5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12555,7 +12555,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6cb343c7-d842-4f02-ae99-1da199a65b26}</x14:id>
+          <x14:id>{0d478caa-bfb2-4f70-983e-4c17bb7ccd95}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12567,7 +12567,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{83957e30-1c44-4fbf-a367-de62d57322d6}</x14:id>
+          <x14:id>{e4fd59ea-9e28-4fe1-9345-a0b49d9a8c03}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12579,7 +12579,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{34004ebd-2745-4e67-91dd-b5979c7ef204}</x14:id>
+          <x14:id>{2b4f730f-6f2d-4325-b0d2-6cadc495e241}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12593,7 +12593,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5cf0402c-56eb-432d-82c1-f2eac8075ae4}</x14:id>
+          <x14:id>{fa0c15f7-6054-4e40-bf17-c7e01f1eb900}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12605,7 +12605,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{41f04223-b2f7-4fea-a1ac-45b5b5cdeb26}</x14:id>
+          <x14:id>{8fc6879c-a66f-45cc-89ff-f7d844fa3177}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -12639,7 +12639,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8d0aded1-4143-40f1-9ac0-5c38c8372908}">
+          <x14:cfRule type="dataBar" id="{73c02118-5cb8-477b-bb66-0749c0556986}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12648,7 +12648,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{83662cda-0437-427d-94dc-a322b0186e08}">
+          <x14:cfRule type="dataBar" id="{1fdac81f-152a-401f-a406-2dbda8b03307}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12657,7 +12657,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5288765b-381f-4792-9b78-d8b97f08ccbc}">
+          <x14:cfRule type="dataBar" id="{155ff1b4-4f41-49e7-91d1-b7a03378bfbd}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12668,7 +12668,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{89cf19f1-adaa-4dba-b2f1-1e71f495ba90}">
+          <x14:cfRule type="dataBar" id="{ded03ecf-b230-46af-a038-fd017a7be69e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12679,7 +12679,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{dcd6313e-7496-4d6f-ada3-b28708696945}">
+          <x14:cfRule type="dataBar" id="{4d58eff6-d055-4be3-9ec7-ddc824368508}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12690,14 +12690,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ee46d742-4306-4044-95ca-b7c8c10c3504}">
+          <x14:cfRule type="dataBar" id="{a7ddd285-2f63-4e2f-97b8-2eb771098c46}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1b3b0fa0-6687-4d67-a48b-99ee3f67b9ce}">
+          <x14:cfRule type="dataBar" id="{a80ec421-286f-416c-ae1b-3da0667ba041}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12708,7 +12708,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{885c77b9-4f22-4c7c-824c-54592ccce73c}">
+          <x14:cfRule type="dataBar" id="{336093d7-f6f9-4eaa-abfe-27bdb61fd5cd}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12722,7 +12722,7 @@
           <xm:sqref>AD58</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{39f193f4-360e-44ce-bc14-cf1569334ffa}">
+          <x14:cfRule type="dataBar" id="{7700b340-72b2-492f-a26a-160bde7f0b0e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12731,7 +12731,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c483943f-04e1-4bac-b5fe-339a4e0295d2}">
+          <x14:cfRule type="dataBar" id="{8d270c6a-24e8-4c99-9daa-804ac00f51c5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12740,7 +12740,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9775cfd3-279e-4f73-a20e-7021c3028507}">
+          <x14:cfRule type="dataBar" id="{15e3ecc6-8480-466c-9228-0e7c006ebf75}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12751,7 +12751,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3137a65b-ba1a-45d3-92a7-1afa408f69e6}">
+          <x14:cfRule type="dataBar" id="{43ba113c-1cff-433a-9fb0-5f11f7b6f974}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12762,7 +12762,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a432d611-02ec-4e9f-98b8-9258b963c298}">
+          <x14:cfRule type="dataBar" id="{25711304-e4d7-4d00-8539-9fca79c63cc6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12773,14 +12773,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2933fba9-a965-4f74-9cff-a41e72ace753}">
+          <x14:cfRule type="dataBar" id="{c394a1f1-3955-4f33-9a69-40c63db80e34}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{cbab823d-1fe4-491c-b17f-6af014278bc9}">
+          <x14:cfRule type="dataBar" id="{690b3837-2a99-4d57-ab99-1dc5181f5804}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12791,7 +12791,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e2f5da0f-7716-49f2-b4af-3870cdf0edd2}">
+          <x14:cfRule type="dataBar" id="{d1d22f59-c737-4c52-ae59-0a82cb30cfc6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12805,7 +12805,7 @@
           <xm:sqref>K62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{648716b2-f99f-4ca8-90b3-5a3ff78be3a3}">
+          <x14:cfRule type="dataBar" id="{0a57afe2-c83d-4551-842d-2e3608f61ab5}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12814,7 +12814,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a3bfbf76-1d83-457b-a087-24195c5bd539}">
+          <x14:cfRule type="dataBar" id="{f20f7ca4-dba7-43ba-a8be-d134dea37f09}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12823,7 +12823,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0c10358d-f3a0-491b-bd4c-f5e6a80e0077}">
+          <x14:cfRule type="dataBar" id="{d5391ce5-2ed6-461b-8c5c-684fd066950e}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12834,7 +12834,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ce73792d-35a9-4b6a-84b1-13e971da357d}">
+          <x14:cfRule type="dataBar" id="{31bfa20a-01ad-47ef-97e3-d8d184f1c002}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12845,7 +12845,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{61e388e1-99c7-429a-a438-1241459e5913}">
+          <x14:cfRule type="dataBar" id="{07e32b69-c5a1-484f-8514-309b5db065fc}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12856,14 +12856,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{60125260-b435-4317-a57a-cccb46648748}">
+          <x14:cfRule type="dataBar" id="{a84c283d-c844-4601-b27c-a765e3691046}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{3e96df0c-f2bb-46ab-ad29-3346f60506e6}">
+          <x14:cfRule type="dataBar" id="{8454aba1-a285-4af0-afa1-dc93bdf48d92}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12874,7 +12874,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b478b4f9-8986-433d-b3c8-28fb7666bd97}">
+          <x14:cfRule type="dataBar" id="{e2979b20-b50e-4810-a777-3eb0f67da7d4}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12888,7 +12888,7 @@
           <xm:sqref>AD62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ed25741f-43f9-467e-bfbb-d1af30557257}">
+          <x14:cfRule type="dataBar" id="{a941c2e6-cd4b-48c3-9514-ff73354e0b17}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12897,7 +12897,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{255b0ca1-f509-4178-8961-00782ffe475d}">
+          <x14:cfRule type="dataBar" id="{15dc8f63-0528-4394-bfac-2d81a584af6b}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12906,7 +12906,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{97ec7b1b-4a50-4506-9c92-d45ff9945b94}">
+          <x14:cfRule type="dataBar" id="{7e949394-3dbe-400c-ad2f-526c4447ce81}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12917,7 +12917,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ef7e9dd1-7d75-4b6c-a694-41efd28a287b}">
+          <x14:cfRule type="dataBar" id="{ff4ba2d2-b4b4-4d76-b4b8-20eab89f17af}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -12928,7 +12928,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{aa71b0f2-f7e2-4124-8f6b-8c9bc2364341}">
+          <x14:cfRule type="dataBar" id="{82e1bac3-b6fd-4251-8e5e-e06d21dda340}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -12939,14 +12939,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{b49bc04f-4fad-4403-894e-4d49b990c5e4}">
+          <x14:cfRule type="dataBar" id="{228f1afe-b83a-4e56-97a1-79c84a9ba74d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f8cd7a0b-a42f-484b-ab3b-a747ad377445}">
+          <x14:cfRule type="dataBar" id="{ff09f55e-a5b0-424d-9055-947942d7b714}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -12957,7 +12957,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{c2c620b6-103f-4fbe-884d-d7ba26efa313}">
+          <x14:cfRule type="dataBar" id="{790328fa-2cb8-4c06-b3ff-c6df26c0f760}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -12971,7 +12971,7 @@
           <xm:sqref>K63</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{74106557-f1d6-4fa7-a3ad-33d638239944}">
+          <x14:cfRule type="dataBar" id="{bbebd8f5-bc32-4b2a-89e8-d27c8469b341}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12980,7 +12980,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{f70af14b-465b-41d6-8a56-5e5e925bc2d7}">
+          <x14:cfRule type="dataBar" id="{4f9580a7-5dd2-47e7-89c7-2d1e14426fb2}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -12989,7 +12989,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9d2b5d6d-e308-4e22-b764-14de0e953154}">
+          <x14:cfRule type="dataBar" id="{fbc45b9a-faa4-45dd-84ee-eeb3d56d87ff}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13000,7 +13000,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{24f9f3d5-ed75-4e62-8cc6-4b299c5642d0}">
+          <x14:cfRule type="dataBar" id="{5c249b40-7c24-4888-9589-22d3bc1313dd}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -13011,7 +13011,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{67fbae23-352c-4d31-9a2f-0a7f3d652e10}">
+          <x14:cfRule type="dataBar" id="{dab13ebb-7f1a-477b-bbf2-dd8bedc24eb8}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -13022,14 +13022,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ca67e61f-4df2-45e0-bb01-90618c985762}">
+          <x14:cfRule type="dataBar" id="{1023eaa0-fcd6-4473-8872-40c5d4f7ec95}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{59064ea0-31b8-4ff7-89da-54aabc24a7d6}">
+          <x14:cfRule type="dataBar" id="{e7923aef-64de-4013-8fd5-84af8adaa48f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13040,7 +13040,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e9d0d1da-3b3c-43a3-850a-aab851325ad5}">
+          <x14:cfRule type="dataBar" id="{bcf0e6ba-465e-430c-88c2-c58371109ca8}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -13054,7 +13054,7 @@
           <xm:sqref>K64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{f9a87c6b-1728-4cd9-81de-47524608b26e}">
+          <x14:cfRule type="dataBar" id="{6faf4040-6964-4bc8-a9c9-3ef201e4eccc}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13063,7 +13063,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5e992cfd-7f1f-4f7e-86d1-33fb5deb5e56}">
+          <x14:cfRule type="dataBar" id="{c13e8aa0-2804-446a-9394-119396f0c772}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13072,7 +13072,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{65c77e2a-e537-4763-be31-80c98e8eebef}">
+          <x14:cfRule type="dataBar" id="{9093dd3b-fd64-4b44-87fd-7e1090655b3c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13083,7 +13083,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{8e4c1331-0eba-45a3-91e8-f428297fa27b}">
+          <x14:cfRule type="dataBar" id="{0af248ea-cdda-4b7c-8e41-f74d17590f12}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -13094,7 +13094,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a2960452-8125-4c3d-9f81-ff8b7e9ef4e3}">
+          <x14:cfRule type="dataBar" id="{930ea78d-7128-4baf-a65c-6c98c8801f56}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -13105,14 +13105,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d99cfe6c-a537-4444-93d1-2e014c6e4b5d}">
+          <x14:cfRule type="dataBar" id="{13d1c43b-5426-45b7-bb2f-56e2a05ded24}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6ae1e5a7-8809-4a97-b781-6085af36b69e}">
+          <x14:cfRule type="dataBar" id="{4b17d84d-355c-42c4-83ad-ec0685c4b2fc}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13123,7 +13123,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d9e08674-fb17-4803-aef1-16b8de7fd683}">
+          <x14:cfRule type="dataBar" id="{69d2ebf6-9f93-4a4f-872b-af12bcf15c53}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -13137,7 +13137,7 @@
           <xm:sqref>K65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6df1fac9-f4e6-4e1f-bfd2-e5fdb062afa7}">
+          <x14:cfRule type="dataBar" id="{6e3d7163-81a6-469a-acb0-8768107d1d41}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13147,7 +13147,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{ae129520-1b46-4391-95cd-2cd1016a5d97}">
+          <x14:cfRule type="dataBar" id="{e60c68d0-3d36-4bdf-b650-1893a7bcd87e}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13156,7 +13156,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9347ac97-e345-45b6-984e-012eca7b3690}">
+          <x14:cfRule type="dataBar" id="{82c30bd8-9112-4ee6-9a60-e088abe0e57c}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13168,7 +13168,7 @@
           <xm:sqref>AB69</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0c6a9090-9a77-437a-b36c-076667f14979}">
+          <x14:cfRule type="dataBar" id="{66b85cd3-002a-415b-a3a7-186feaf1ad68}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13178,7 +13178,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a3c209ef-e149-4997-9284-e1712e04c511}">
+          <x14:cfRule type="dataBar" id="{469ea6e9-4e29-41da-b72b-3dda878b4d7a}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13187,7 +13187,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{99fab01f-8766-402b-840e-11c4ecd19a30}">
+          <x14:cfRule type="dataBar" id="{74be8e9d-c07c-4f0e-83c1-427a07225c54}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13199,7 +13199,7 @@
           <xm:sqref>AB103</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{39902288-69af-4e9b-b677-e266e8dbf020}">
+          <x14:cfRule type="dataBar" id="{ab93e35c-e38f-4273-89bc-88808cce893c}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13208,7 +13208,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e7e26f93-1d9a-492d-abae-4a0cc0a9570f}">
+          <x14:cfRule type="dataBar" id="{ef7b15c5-6c96-4f44-84af-12a2476fe3a3}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13220,7 +13220,7 @@
           <xm:sqref>AB117</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{60330284-ca3e-4db5-8167-31322af2fbd7}">
+          <x14:cfRule type="dataBar" id="{e51813bf-10f6-4bbe-a762-955926720f6a}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13230,7 +13230,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{25fc206f-700f-4957-ae70-930d9b1a0d53}">
+          <x14:cfRule type="dataBar" id="{35a899bc-541d-4ea0-9e6c-84fead288b2b}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13239,7 +13239,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{dd8e3bca-3075-4346-8b30-b198a6ef45ec}">
+          <x14:cfRule type="dataBar" id="{5aacddd5-1e96-488d-bdcf-dde997447ffb}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13251,7 +13251,7 @@
           <xm:sqref>AB127</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{61e2dc8b-b332-432c-bf46-af2f903cd0e8}">
+          <x14:cfRule type="dataBar" id="{37a156c7-0251-4a7f-9777-c2eb7a829d54}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13261,7 +13261,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{39f2229e-d525-468b-bb7b-fd6901200396}">
+          <x14:cfRule type="dataBar" id="{98b3af3a-76d8-47fe-b609-7397e1de2d2b}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13270,7 +13270,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{73be0989-7a90-4b8b-b2ad-46e67260a956}">
+          <x14:cfRule type="dataBar" id="{5e5f48e5-7d4d-40f8-b6c1-439eacab6977}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13282,7 +13282,7 @@
           <xm:sqref>K137</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e420d26c-7450-489b-a295-d7ef02fd8d55}">
+          <x14:cfRule type="dataBar" id="{aedacfb4-2457-484e-9a7f-7d809d29a70b}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13292,7 +13292,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e178d636-18f2-409d-add0-575545e202b2}">
+          <x14:cfRule type="dataBar" id="{a2ec5912-7b55-452e-acc0-e607a2315e44}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13301,7 +13301,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{1bf3d859-9e37-4a27-9a68-e06202d20170}">
+          <x14:cfRule type="dataBar" id="{afcbfb7c-3ee6-44e4-8891-b8f7ea26df55}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13313,7 +13313,7 @@
           <xm:sqref>K142</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{66daf283-2bf2-4750-83d9-663b81b8005c}">
+          <x14:cfRule type="dataBar" id="{f11993e2-90a1-4c4a-a792-f25cc1e88b49}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13323,7 +13323,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{79b2658f-e5e2-437a-9806-821109e248a6}">
+          <x14:cfRule type="dataBar" id="{20bf9ea3-2339-49e2-b9f2-2aac44f0828c}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13332,7 +13332,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{4a3ba873-d863-490b-9489-cfdf5b235be0}">
+          <x14:cfRule type="dataBar" id="{71826df5-7d66-4b3d-b2fe-e4e22da0d47b}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13344,7 +13344,7 @@
           <xm:sqref>K147</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6a2306b9-bdfb-4588-bac8-a126ae932caa}">
+          <x14:cfRule type="dataBar" id="{48eefdbc-3383-4f15-9fdd-ec260f7e5b8f}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13354,7 +13354,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9a5fa538-4003-4ca7-8598-74b76865fa85}">
+          <x14:cfRule type="dataBar" id="{6105d0f7-68cf-4a86-9927-e593458cf0bf}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13363,7 +13363,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d4139a92-0c82-4f24-9db2-2e161d3634fa}">
+          <x14:cfRule type="dataBar" id="{f5b2456a-e0aa-4365-a8de-eb57ffea24ab}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13375,7 +13375,7 @@
           <xm:sqref>K152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{38acd70b-d4ff-4ccf-ae21-7e86366e77fc}">
+          <x14:cfRule type="dataBar" id="{1bc1fc5a-f4ca-4698-8df6-716db979012c}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13384,7 +13384,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{624d3da9-81f0-420b-ba55-351e633b6c05}">
+          <x14:cfRule type="dataBar" id="{7d260e8e-58f8-4d91-841b-37c7406fd366}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13393,7 +13393,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{56995fcb-30e6-4f37-bd68-64936d8f1f6a}">
+          <x14:cfRule type="dataBar" id="{8d1ed4ec-3b90-4d7e-b50e-03b23b65d20f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13404,7 +13404,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{66d95c7c-5929-4b1f-98f9-8e3872dcb10b}">
+          <x14:cfRule type="dataBar" id="{86714f56-950c-42e4-b0cc-5c04e408e17f}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>0</xm:f>
@@ -13415,7 +13415,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e02b969d-dfcd-4dc4-be76-75444ee20285}">
+          <x14:cfRule type="dataBar" id="{284f9389-d273-47db-b93d-e146a5624cfa}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -13426,14 +13426,14 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{2e20262f-6769-4b25-bd93-7a71b7793350}">
+          <x14:cfRule type="dataBar" id="{c9849ecc-bbca-4f7d-9aed-d4228c6bd9b0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{72470def-0ab8-417f-a9e9-8286fe31cef4}">
+          <x14:cfRule type="dataBar" id="{11d77e64-3a5f-4151-8f36-fd357c6e3aec}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -13444,7 +13444,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{17d57a83-718e-41bb-8b00-43ce4543e505}">
+          <x14:cfRule type="dataBar" id="{db5aad04-8c76-4233-aece-7b0abe9abc95}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="percentile">
                 <xm:f>1</xm:f>
@@ -13458,7 +13458,7 @@
           <xm:sqref>K59:K60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{e90c9e35-a0bf-4040-8309-3d76e1d887ec}">
+          <x14:cfRule type="dataBar" id="{024113f5-3286-4a94-83a9-88f327b6b5ab}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13468,7 +13468,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{9d5a571b-df9d-498a-918a-99e632300ed8}">
+          <x14:cfRule type="dataBar" id="{3223f7be-d797-45a5-a955-ab8e9d1d7f77}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13480,7 +13480,7 @@
           <xm:sqref>Y69:Y88</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{614f3d13-ea59-4e5b-9110-00cd04cb2661}">
+          <x14:cfRule type="dataBar" id="{4571feab-aa4a-4bd4-90c0-d896a380606f}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13493,7 +13493,7 @@
           <xm:sqref>Y79:Y88</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1409329f-dae1-4f18-b8a3-bd7ac8271eab}">
+          <x14:cfRule type="dataBar" id="{497d6fb0-f689-4b97-8f1e-3b61a8b81bfe}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13506,7 +13506,7 @@
           <xm:sqref>AB117:AB126</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9419a1b5-91a5-4199-aa72-9defc34c1275}">
+          <x14:cfRule type="dataBar" id="{4de2becd-715b-47b6-97d9-78c51cc640ce}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13518,7 +13518,7 @@
           <xm:sqref>AD58:AE59</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dcc515c2-0d09-4a30-a54a-19c7dbd78334}">
+          <x14:cfRule type="dataBar" id="{4471bd21-baf3-46fc-842a-bbc22847eb0d}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13530,7 +13530,7 @@
           <xm:sqref>AD62:AE65</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2807c010-cb44-4700-9e8e-7f6eb358d7c6}">
+          <x14:cfRule type="dataBar" id="{2ef53344-397d-4fc3-abe1-c86596bef512}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13540,7 +13540,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6e51a2ad-aa5f-4121-bda6-80ed2c4df6d2}">
+          <x14:cfRule type="dataBar" id="{741f17ac-33c5-4b7d-bc2c-7fe58896402c}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13549,7 +13549,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{a30a34dd-d3ea-4433-946a-a5c4656fc47c}">
+          <x14:cfRule type="dataBar" id="{20c99214-525e-4179-a8de-11835006f617}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13561,7 +13561,7 @@
           <xm:sqref>F69 F74 F79 F84</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{74943210-1894-4cca-a91c-9bb7d9f2fd75}">
+          <x14:cfRule type="dataBar" id="{834f3c37-b68f-4ef7-b8ac-f6f156269954}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13571,7 +13571,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{db925445-2b0e-41e0-8b1e-3b217ef1abf6}">
+          <x14:cfRule type="dataBar" id="{8035aea1-948e-4711-8fa6-1a8efd747baf}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13580,7 +13580,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{37e6c090-f06d-4de9-82df-adbd7a20fce2}">
+          <x14:cfRule type="dataBar" id="{0187092f-e124-4879-8dce-051f82127eff}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13592,7 +13592,7 @@
           <xm:sqref>K69 K79 K89 K103</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7c2ffc11-9213-4471-b56e-032e5deac7bd}">
+          <x14:cfRule type="dataBar" id="{e2b76e9a-8291-41ed-a845-bbb79a1a7a1a}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13602,7 +13602,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{5980e0f8-64e2-4145-8186-a9be4c931a6f}">
+          <x14:cfRule type="dataBar" id="{c31e442e-7f62-4d59-88b9-d9ff4a15a735}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13611,7 +13611,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{6ed04b1b-00c9-4fae-ac3b-3aa64c514c17}">
+          <x14:cfRule type="dataBar" id="{1ad57c6d-905c-40a6-8db2-756dee10e9dd}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13623,7 +13623,7 @@
           <xm:sqref>AB79 AB89</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{478e5895-4295-4e9f-b814-6299289721e5}">
+          <x14:cfRule type="dataBar" id="{19f4624a-2578-43b7-b16e-cb50df3f6e6c}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13633,7 +13633,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{239a24bb-dea8-48d3-943f-fec256f4db45}">
+          <x14:cfRule type="dataBar" id="{3ce6b947-e4a4-4ca3-aa18-34d6136f3e5b}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13642,7 +13642,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{d973b141-ce96-4cee-a3c5-663b59d9dd7c}">
+          <x14:cfRule type="dataBar" id="{c2698b09-8fcc-4d52-99ad-7509cac2e8a0}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13654,7 +13654,7 @@
           <xm:sqref>F89 F96 F103 F110</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2dbbc97d-1fe6-436f-a01e-76a5005a245d}">
+          <x14:cfRule type="dataBar" id="{1a837990-9ce8-4b12-956a-2018c5890e74}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13664,7 +13664,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{41b050dd-66ff-4e91-a5f5-abc6841d88a6}">
+          <x14:cfRule type="dataBar" id="{fad696cb-39f6-4f11-b300-2f1d21ae73d7}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13676,7 +13676,7 @@
           <xm:sqref>Y89 Y103</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{ac6dafd8-28fe-4f06-924a-9917f8ec1a2a}">
+          <x14:cfRule type="dataBar" id="{f593ee51-1ef8-42b2-813b-90944cf04565}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13686,7 +13686,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{0996a186-1fdf-4c39-b60f-59d930ba3cab}">
+          <x14:cfRule type="dataBar" id="{b7ed5740-f248-4c9e-8e83-3364f996a2ce}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13695,7 +13695,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{e51cd375-1cfc-4ac3-80e3-c641f53c3738}">
+          <x14:cfRule type="dataBar" id="{440a2f9b-5480-4162-a177-953454b634d5}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13707,7 +13707,7 @@
           <xm:sqref>F117 F122 F127 F132 F137 F142 F147 F152</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6cb343c7-d842-4f02-ae99-1da199a65b26}">
+          <x14:cfRule type="dataBar" id="{0d478caa-bfb2-4f70-983e-4c17bb7ccd95}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13717,7 +13717,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{83957e30-1c44-4fbf-a367-de62d57322d6}">
+          <x14:cfRule type="dataBar" id="{e4fd59ea-9e28-4fe1-9345-a0b49d9a8c03}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13726,7 +13726,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{34004ebd-2745-4e67-91dd-b5979c7ef204}">
+          <x14:cfRule type="dataBar" id="{2b4f730f-6f2d-4325-b0d2-6cadc495e241}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13738,7 +13738,7 @@
           <xm:sqref>K117 K127</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5cf0402c-56eb-432d-82c1-f2eac8075ae4}">
+          <x14:cfRule type="dataBar" id="{fa0c15f7-6054-4e40-bf17-c7e01f1eb900}">
             <x14:dataBar minLength="0" maxLength="100">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="num">
@@ -13748,7 +13748,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <x14:cfRule type="dataBar" id="{41f04223-b2f7-4fea-a1ac-45b5b5cdeb26}">
+          <x14:cfRule type="dataBar" id="{8fc6879c-a66f-45cc-89ff-f7d844fa3177}">
             <x14:dataBar minLength="0" maxLength="100" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="min"/>
               <x14:cfvo type="num">
@@ -13769,12 +13769,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="26.8818181818182" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.38181818181818" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.21818181818182" style="1" customWidth="1"/>
-    <col min="18" max="18" width="9.38181818181818" style="1" customWidth="1"/>
+    <col min="1" max="1" width="26.8796296296296" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.37962962962963" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.22222222222222" style="1" customWidth="1"/>
+    <col min="18" max="18" width="9.37962962962963" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
